--- a/Document/專題/db_diagram.xlsx
+++ b/Document/專題/db_diagram.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ispan\Desktop\小組專題\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\RentalManagementPlatform\Document\專題\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C14D65-EC05-473C-980D-652DE017A7C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4AF059B-3EEB-4B2E-BB6C-25BC596C76D6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="606">
   <si>
     <t>表格名稱</t>
   </si>
@@ -1503,15 +1503,6 @@
     <t>default: 0</t>
   </si>
   <si>
-    <t>is_promoted</t>
-  </si>
-  <si>
-    <t>是否推廣</t>
-  </si>
-  <si>
-    <t>default: false</t>
-  </si>
-  <si>
     <t>post_status</t>
   </si>
   <si>
@@ -1525,80 +1516,6 @@
   </si>
   <si>
     <t>公告主表（刊登/審核/公開/下架的核心）</t>
-  </si>
-  <si>
-    <t>中文：公告狀態變更歷程_x000D_
-英文：POST_STATUS_HISTORY</t>
-  </si>
-  <si>
-    <t>post_status_history_id</t>
-  </si>
-  <si>
-    <t>post_id → POSTS.posts_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> acted_by → USER.user_id</t>
-  </si>
-  <si>
-    <t>歷程 ID</t>
-  </si>
-  <si>
-    <t>post_id</t>
-  </si>
-  <si>
-    <t>(FK) 對應 POSTS.posts_id</t>
-  </si>
-  <si>
-    <t>acted_by</t>
-  </si>
-  <si>
-    <t>操作人 ID</t>
-  </si>
-  <si>
-    <t>(FK) 對應 USER.user_id（管理/審核）</t>
-  </si>
-  <si>
-    <t>公告狀態變更留痕</t>
-  </si>
-  <si>
-    <t>索引</t>
-  </si>
-  <si>
-    <t>(post_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> created_at)</t>
-  </si>
-  <si>
-    <t>中文：審核規則_x000D_
-英文：MODERATION_RULES</t>
-  </si>
-  <si>
-    <t>moderation_rules_id</t>
-  </si>
-  <si>
-    <t>規則類型</t>
-  </si>
-  <si>
-    <t>rule_type</t>
-  </si>
-  <si>
-    <t>NOT NULL（enum：keyword / phone_blacklist / email_blacklist）</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>規則值</t>
-  </si>
-  <si>
-    <t>敏感詞/聯絡黑名單等規則</t>
-  </si>
-  <si>
-    <t>(type</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> is_active)</t>
   </si>
   <si>
     <t>中文：使用者常用報表_x000D_
@@ -1725,52 +1642,6 @@
   </si>
   <si>
     <t>檢測產生時間</t>
-  </si>
-  <si>
-    <t>中文：預約_x000D_
-英文：RESERVATION</t>
-  </si>
-  <si>
-    <t>reservation_id</t>
-  </si>
-  <si>
-    <t>listing_id → ROOM_LIST.room_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> user_id → USER.user_id</t>
-  </si>
-  <si>
-    <t>預約 ID</t>
-  </si>
-  <si>
-    <t>listing_id</t>
-  </si>
-  <si>
-    <t>end_date</t>
-  </si>
-  <si>
-    <t>結束日期</t>
-  </si>
-  <si>
-    <t>NOT NULL，ENUM: pending | confirmed | cancelled</t>
-  </si>
-  <si>
-    <t>NOT NULL，default: SYSUTCDATETIME()</t>
-  </si>
-  <si>
-    <t>CHECK 條件：StartDate &lt; EndDate</t>
-  </si>
-  <si>
-    <t>(listing_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> start_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> end_date</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> status) 名稱: IX_Reservation_List_Date</t>
   </si>
   <si>
     <t>中文：MongoDB 對應_x000D_
@@ -1981,19 +1852,7 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>status</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>狀態</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>user_role_id</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>moderation_rules_id</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
@@ -2258,7 +2117,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2436,18 +2295,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2710,7 +2557,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2739,30 +2586,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3120,7 +2943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J474"/>
+  <dimension ref="B2:J438"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
@@ -3667,17 +3490,17 @@
         <v>2</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>583</v>
+        <v>541</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>584</v>
+        <v>542</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>585</v>
+        <v>543</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1" t="s">
-        <v>586</v>
+        <v>544</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
@@ -3757,13 +3580,13 @@
         <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>587</v>
+        <v>545</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>588</v>
+        <v>546</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>589</v>
+        <v>547</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -3773,17 +3596,17 @@
         <v>8</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>590</v>
+        <v>548</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>591</v>
+        <v>549</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>592</v>
+        <v>550</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1" t="s">
-        <v>586</v>
+        <v>544</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
@@ -3809,13 +3632,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>593</v>
+        <v>551</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>595</v>
+        <v>553</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>585</v>
+        <v>543</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -3825,13 +3648,13 @@
         <v>11</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>594</v>
+        <v>552</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>596</v>
+        <v>554</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>585</v>
+        <v>543</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -3859,17 +3682,17 @@
         <v>13</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>597</v>
+        <v>555</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>598</v>
+        <v>556</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>599</v>
+        <v>557</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1" t="s">
-        <v>600</v>
+        <v>558</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
@@ -4117,7 +3940,7 @@
         <v>0</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>642</v>
+        <v>597</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="2" t="s">
@@ -4230,76 +4053,76 @@
         <v>121</v>
       </c>
     </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B70" s="14">
+    <row r="70" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="4">
         <v>5</v>
       </c>
-      <c r="C70" s="14" t="s">
-        <v>647</v>
-      </c>
-      <c r="D70" s="14" t="s">
-        <v>631</v>
-      </c>
-      <c r="E70" s="14" t="s">
-        <v>633</v>
-      </c>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B71" s="14">
+      <c r="C70" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="4">
         <v>6</v>
       </c>
-      <c r="C71" s="14" t="s">
-        <v>648</v>
-      </c>
-      <c r="D71" s="14" t="s">
-        <v>632</v>
-      </c>
-      <c r="E71" s="14" t="s">
-        <v>633</v>
-      </c>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B72" s="14">
+      <c r="C71" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="4">
         <v>7</v>
       </c>
-      <c r="C72" s="14" t="s">
-        <v>649</v>
-      </c>
-      <c r="D72" s="14" t="s">
-        <v>635</v>
-      </c>
-      <c r="E72" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B73" s="14">
+      <c r="C72" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="4">
         <v>8</v>
       </c>
-      <c r="C73" s="14" t="s">
-        <v>650</v>
-      </c>
-      <c r="D73" s="14" t="s">
-        <v>634</v>
-      </c>
-      <c r="E73" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14" t="s">
-        <v>646</v>
+      <c r="C73" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.25">
@@ -4388,110 +4211,110 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
     </row>
-    <row r="80" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="15" t="s">
+    <row r="80" spans="2:7" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C80" s="16" t="s">
-        <v>643</v>
-      </c>
-      <c r="D80" s="16"/>
-      <c r="E80" s="15" t="s">
+      <c r="C80" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="D80" s="8"/>
+      <c r="E80" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F80" s="17"/>
-      <c r="G80" s="17"/>
-    </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B81" s="15" t="s">
+      <c r="F80" s="9"/>
+      <c r="G80" s="9"/>
+    </row>
+    <row r="81" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C81" s="17" t="s">
-        <v>637</v>
-      </c>
-      <c r="D81" s="17"/>
-      <c r="E81" s="15" t="s">
+      <c r="C81" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="D81" s="9"/>
+      <c r="E81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F81" s="16" t="s">
-        <v>641</v>
-      </c>
-      <c r="G81" s="17" t="s">
+      <c r="F81" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B82" s="15" t="s">
+    <row r="82" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C82" s="15" t="s">
+      <c r="C82" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D82" s="15" t="s">
+      <c r="D82" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E82" s="15" t="s">
+      <c r="E82" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F82" s="15" t="s">
+      <c r="F82" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G82" s="15" t="s">
+      <c r="G82" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B83" s="14">
+    <row r="83" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="4">
         <v>1</v>
       </c>
-      <c r="C83" s="14" t="s">
-        <v>637</v>
-      </c>
-      <c r="D83" s="14" t="s">
+      <c r="C83" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="E83" s="14" t="s">
+      <c r="E83" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14" t="s">
+      <c r="F83" s="4"/>
+      <c r="G83" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B84" s="14">
+    <row r="84" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="4">
         <v>2</v>
       </c>
-      <c r="C84" s="14" t="s">
+      <c r="C84" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D84" s="14" t="s">
+      <c r="D84" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E84" s="14" t="s">
+      <c r="E84" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14" t="s">
+      <c r="F84" s="4"/>
+      <c r="G84" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B85" s="14">
+    <row r="85" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="4">
         <v>3</v>
       </c>
-      <c r="C85" s="14" t="s">
-        <v>638</v>
-      </c>
-      <c r="D85" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="E85" s="14" t="s">
+      <c r="C85" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="E85" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14" t="s">
-        <v>640</v>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="87" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4817,17 +4640,17 @@
         <v>2</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>603</v>
+        <v>561</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>604</v>
+        <v>562</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="4" t="s">
-        <v>608</v>
+        <v>566</v>
       </c>
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.25">
@@ -4838,7 +4661,7 @@
         <v>40</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>605</v>
+        <v>563</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>14</v>
@@ -4863,7 +4686,7 @@
       </c>
       <c r="F109" s="4"/>
       <c r="G109" s="4" t="s">
-        <v>610</v>
+        <v>568</v>
       </c>
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.25">
@@ -4881,7 +4704,7 @@
       </c>
       <c r="F110" s="4"/>
       <c r="G110" s="4" t="s">
-        <v>609</v>
+        <v>567</v>
       </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.25">
@@ -4899,7 +4722,7 @@
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="4" t="s">
-        <v>610</v>
+        <v>568</v>
       </c>
     </row>
     <row r="112" spans="2:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4907,17 +4730,17 @@
         <v>7</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>606</v>
+        <v>564</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>607</v>
+        <v>565</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="4" t="s">
-        <v>611</v>
+        <v>569</v>
       </c>
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.25">
@@ -6276,7 +6099,7 @@
         <v>3</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>601</v>
+        <v>559</v>
       </c>
       <c r="D198" s="7"/>
       <c r="E198" s="2" t="s">
@@ -6404,7 +6227,7 @@
         <v>0</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>602</v>
+        <v>560</v>
       </c>
       <c r="D206" s="6"/>
       <c r="E206" s="2" t="s">
@@ -6418,7 +6241,7 @@
         <v>3</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>628</v>
+        <v>584</v>
       </c>
       <c r="D207" s="7"/>
       <c r="E207" s="2" t="s">
@@ -8965,7 +8788,7 @@
         <v>0</v>
       </c>
       <c r="C371" s="8" t="s">
-        <v>612</v>
+        <v>570</v>
       </c>
       <c r="D371" s="8"/>
       <c r="E371" s="3" t="s">
@@ -9013,17 +8836,17 @@
         <v>1</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>614</v>
+        <v>572</v>
       </c>
       <c r="D374" s="4" t="s">
-        <v>616</v>
+        <v>574</v>
       </c>
       <c r="E374" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F374" s="4"/>
       <c r="G374" s="4" t="s">
-        <v>619</v>
+        <v>577</v>
       </c>
       <c r="H374" s="5" t="s">
         <v>459</v>
@@ -9034,17 +8857,17 @@
         <v>2</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>615</v>
+        <v>573</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>617</v>
+        <v>575</v>
       </c>
       <c r="E375" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F375" s="4"/>
       <c r="G375" s="4" t="s">
-        <v>620</v>
+        <v>578</v>
       </c>
     </row>
     <row r="376" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -9052,17 +8875,17 @@
         <v>3</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>613</v>
+        <v>571</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>618</v>
+        <v>576</v>
       </c>
       <c r="E376" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F376" s="4"/>
       <c r="G376" s="4" t="s">
-        <v>620</v>
+        <v>578</v>
       </c>
     </row>
     <row r="377" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -9070,7 +8893,7 @@
         <v>12</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>621</v>
+        <v>579</v>
       </c>
       <c r="D377" s="4"/>
       <c r="E377" s="4"/>
@@ -9143,7 +8966,7 @@
         <v>467</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>622</v>
+        <v>580</v>
       </c>
       <c r="F382" s="1"/>
       <c r="G382" s="1" t="s">
@@ -9369,21 +9192,21 @@
       </c>
     </row>
     <row r="395" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B395" s="13">
+      <c r="B395" s="1">
         <v>14</v>
       </c>
-      <c r="C395" s="13" t="s">
+      <c r="C395" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D395" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E395" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="D395" s="13" t="s">
+      <c r="F395" s="1"/>
+      <c r="G395" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="E395" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="F395" s="13"/>
-      <c r="G395" s="13" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="396" spans="2:7" x14ac:dyDescent="0.25">
@@ -9391,17 +9214,17 @@
         <v>15</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>630</v>
+        <v>31</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>487</v>
+        <v>32</v>
       </c>
       <c r="F396" s="1"/>
       <c r="G396" s="1" t="s">
-        <v>488</v>
+        <v>253</v>
       </c>
     </row>
     <row r="397" spans="2:7" x14ac:dyDescent="0.25">
@@ -9409,10 +9232,10 @@
         <v>16</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>32</v>
@@ -9427,1358 +9250,680 @@
         <v>17</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>34</v>
+        <v>486</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>35</v>
+        <v>487</v>
       </c>
       <c r="E398" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F398" s="1"/>
-      <c r="G398" s="1" t="s">
-        <v>253</v>
-      </c>
+      <c r="G398" s="1"/>
     </row>
     <row r="399" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B399" s="1">
         <v>18</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>489</v>
+        <v>581</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>490</v>
+        <v>582</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>32</v>
+        <v>583</v>
       </c>
       <c r="F399" s="1"/>
       <c r="G399" s="1"/>
     </row>
     <row r="400" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B400" s="1">
-        <v>19</v>
+      <c r="B400" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="D400" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="E400" s="1" t="s">
-        <v>625</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="D400" s="1"/>
+      <c r="E400" s="1"/>
       <c r="F400" s="1"/>
       <c r="G400" s="1"/>
     </row>
-    <row r="401" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B401" s="1" t="s">
+    <row r="402" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B402" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C402" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="D402" s="6"/>
+      <c r="E402" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F402" s="7"/>
+      <c r="G402" s="7"/>
+    </row>
+    <row r="403" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B403" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C403" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="D403" s="7"/>
+      <c r="E403" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F403" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G403" s="7"/>
+    </row>
+    <row r="404" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B404" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C404" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D404" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E404" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F404" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G404" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C401" s="1" t="s">
+    </row>
+    <row r="405" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B405" s="1">
+        <v>1</v>
+      </c>
+      <c r="C405" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D405" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="D401" s="1"/>
-      <c r="E401" s="1"/>
-      <c r="F401" s="1"/>
-      <c r="G401" s="1"/>
-    </row>
-    <row r="403" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B403" s="10" t="s">
+      <c r="E405" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F405" s="1"/>
+      <c r="G405" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="406" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B406" s="1">
+        <v>2</v>
+      </c>
+      <c r="C406" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D406" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E406" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F406" s="1"/>
+      <c r="G406" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="407" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B407" s="1">
+        <v>3</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D407" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="E407" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F407" s="1">
+        <v>50</v>
+      </c>
+      <c r="G407" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="H407" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="408" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B408" s="1">
+        <v>4</v>
+      </c>
+      <c r="C408" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D408" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E408" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="F408" s="1"/>
+      <c r="G408" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="409" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B409" s="1">
+        <v>5</v>
+      </c>
+      <c r="C409" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D409" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E409" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F409" s="1"/>
+      <c r="G409" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="411" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B411" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C403" s="11" t="s">
-        <v>492</v>
-      </c>
-      <c r="D403" s="11"/>
-      <c r="E403" s="10" t="s">
+      <c r="C411" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="D411" s="6"/>
+      <c r="E411" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F403" s="12"/>
-      <c r="G403" s="12"/>
-    </row>
-    <row r="404" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B404" s="10" t="s">
+      <c r="F411" s="7"/>
+      <c r="G411" s="7"/>
+    </row>
+    <row r="412" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B412" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C404" s="12" t="s">
-        <v>493</v>
-      </c>
-      <c r="D404" s="12"/>
-      <c r="E404" s="10" t="s">
+      <c r="C412" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="D412" s="7"/>
+      <c r="E412" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F404" s="12" t="s">
-        <v>494</v>
-      </c>
-      <c r="G404" s="12" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="405" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B405" s="10" t="s">
+      <c r="F412" s="7"/>
+      <c r="G412" s="7"/>
+    </row>
+    <row r="413" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B413" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C405" s="10" t="s">
+      <c r="C413" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D405" s="10" t="s">
+      <c r="D413" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E405" s="10" t="s">
+      <c r="E413" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F405" s="10" t="s">
+      <c r="F413" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G405" s="10" t="s">
+      <c r="G413" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="406" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B406" s="13">
+    <row r="414" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B414" s="1">
         <v>1</v>
       </c>
-      <c r="C406" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="D406" s="13" t="s">
-        <v>496</v>
-      </c>
-      <c r="E406" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="F406" s="13"/>
-      <c r="G406" s="13" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="407" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B407" s="13">
+      <c r="C414" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D414" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E414" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F414" s="1"/>
+      <c r="G414" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="415" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B415" s="1">
         <v>2</v>
       </c>
-      <c r="C407" s="13" t="s">
-        <v>497</v>
-      </c>
-      <c r="D407" s="13" t="s">
-        <v>467</v>
-      </c>
-      <c r="E407" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="F407" s="13"/>
-      <c r="G407" s="13" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="408" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B408" s="13">
+      <c r="C415" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="D415" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="E415" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F415" s="1">
+        <v>100</v>
+      </c>
+      <c r="G415" s="1" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="416" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B416" s="1">
         <v>3</v>
       </c>
-      <c r="C408" s="13" t="s">
-        <v>499</v>
-      </c>
-      <c r="D408" s="13" t="s">
-        <v>500</v>
-      </c>
-      <c r="E408" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="F408" s="13"/>
-      <c r="G408" s="13" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="409" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B409" s="13">
+      <c r="C416" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="D416" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E416" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F416" s="1">
+        <v>50</v>
+      </c>
+      <c r="G416" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="417" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B417" s="1">
         <v>4</v>
       </c>
-      <c r="C409" s="13" t="s">
-        <v>626</v>
-      </c>
-      <c r="D409" s="13" t="s">
-        <v>627</v>
-      </c>
-      <c r="E409" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="F409" s="13">
-        <v>20</v>
-      </c>
-      <c r="G409" s="13"/>
-    </row>
-    <row r="410" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B410" s="13">
+      <c r="C417" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D417" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="E417" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="F417" s="1"/>
+      <c r="G417" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="418" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B418" s="1">
         <v>5</v>
       </c>
-      <c r="C410" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="D410" s="13" t="s">
-        <v>431</v>
-      </c>
-      <c r="E410" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="F410" s="13">
-        <v>500</v>
-      </c>
-      <c r="G410" s="13"/>
-    </row>
-    <row r="411" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B411" s="13">
+      <c r="C418" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="E418" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F418" s="1">
+        <v>10</v>
+      </c>
+      <c r="G418" s="1">
+        <v>2</v>
+      </c>
+      <c r="H418" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="419" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B419" s="1">
         <v>6</v>
       </c>
-      <c r="C411" s="13" t="s">
+      <c r="C419" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D419" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E419" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F419" s="1"/>
+      <c r="G419" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="H419" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="420" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B420" s="1">
+        <v>7</v>
+      </c>
+      <c r="C420" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D411" s="13" t="s">
+      <c r="D420" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E411" s="13" t="s">
+      <c r="E420" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F411" s="13"/>
-      <c r="G411" s="13" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="412" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B412" s="13" t="s">
+      <c r="F420" s="1"/>
+      <c r="G420" s="1"/>
+    </row>
+    <row r="422" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B422" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C422" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="D422" s="6"/>
+      <c r="E422" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F422" s="7"/>
+      <c r="G422" s="7"/>
+    </row>
+    <row r="423" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B423" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C423" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="D423" s="7"/>
+      <c r="E423" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F423" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="G423" s="7"/>
+    </row>
+    <row r="424" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B424" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C424" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D424" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E424" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F424" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G424" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C412" s="13" t="s">
-        <v>502</v>
-      </c>
-      <c r="D412" s="13"/>
-      <c r="E412" s="13"/>
-      <c r="F412" s="13"/>
-      <c r="G412" s="13"/>
-    </row>
-    <row r="413" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B413" s="13" t="s">
-        <v>503</v>
-      </c>
-      <c r="C413" s="13" t="s">
-        <v>504</v>
-      </c>
-      <c r="D413" s="13" t="s">
-        <v>505</v>
-      </c>
-      <c r="E413" s="13"/>
-      <c r="F413" s="13"/>
-      <c r="G413" s="13"/>
-    </row>
-    <row r="415" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B415" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C415" s="11" t="s">
-        <v>506</v>
-      </c>
-      <c r="D415" s="11"/>
-      <c r="E415" s="10" t="s">
+    </row>
+    <row r="425" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B425" s="1">
+        <v>1</v>
+      </c>
+      <c r="C425" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="D425" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="E425" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F425" s="1"/>
+      <c r="G425" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="426" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B426" s="1">
         <v>2</v>
       </c>
-      <c r="F415" s="12"/>
-      <c r="G415" s="12"/>
-    </row>
-    <row r="416" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B416" s="10" t="s">
+      <c r="C426" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D426" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="E426" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F426" s="1"/>
+      <c r="G426" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="427" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B427" s="1">
         <v>3</v>
       </c>
-      <c r="C416" s="12" t="s">
-        <v>629</v>
-      </c>
-      <c r="D416" s="12"/>
-      <c r="E416" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F416" s="12"/>
-      <c r="G416" s="12"/>
-    </row>
-    <row r="417" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B417" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C417" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D417" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E417" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F417" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G417" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="418" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B418" s="13">
-        <v>1</v>
-      </c>
-      <c r="C418" s="13" t="s">
-        <v>507</v>
-      </c>
-      <c r="D418" s="13" t="s">
-        <v>352</v>
-      </c>
-      <c r="E418" s="13" t="s">
+      <c r="C427" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D427" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="E427" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F418" s="13"/>
-      <c r="G418" s="13" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="419" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B419" s="13">
-        <v>2</v>
-      </c>
-      <c r="C419" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="D419" s="13" t="s">
-        <v>508</v>
-      </c>
-      <c r="E419" s="13" t="s">
-        <v>509</v>
-      </c>
-      <c r="F419" s="13"/>
-      <c r="G419" s="13" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="420" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B420" s="13">
-        <v>3</v>
-      </c>
-      <c r="C420" s="13" t="s">
-        <v>511</v>
-      </c>
-      <c r="D420" s="13" t="s">
-        <v>512</v>
-      </c>
-      <c r="E420" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="F420" s="13">
-        <v>255</v>
-      </c>
-      <c r="G420" s="13" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="421" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B421" s="13">
-        <v>4</v>
-      </c>
-      <c r="C421" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="D421" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="E421" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="F421" s="13"/>
-      <c r="G421" s="13" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="422" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B422" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C422" s="13" t="s">
-        <v>513</v>
-      </c>
-      <c r="D422" s="13"/>
-      <c r="E422" s="13"/>
-      <c r="F422" s="13"/>
-      <c r="G422" s="13"/>
-    </row>
-    <row r="423" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B423" s="13" t="s">
-        <v>503</v>
-      </c>
-      <c r="C423" s="13" t="s">
-        <v>514</v>
-      </c>
-      <c r="D423" s="13" t="s">
-        <v>515</v>
-      </c>
-      <c r="E423" s="13"/>
-      <c r="F423" s="13"/>
-      <c r="G423" s="13"/>
-    </row>
-    <row r="425" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B425" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C425" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="D425" s="6"/>
-      <c r="E425" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F425" s="7"/>
-      <c r="G425" s="7"/>
-    </row>
-    <row r="426" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B426" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C426" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="D426" s="7"/>
-      <c r="E426" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F426" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="G426" s="7"/>
-    </row>
-    <row r="427" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B427" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C427" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D427" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E427" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F427" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G427" s="2" t="s">
-        <v>12</v>
+      <c r="F427" s="1"/>
+      <c r="G427" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="428" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B428" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F428" s="1"/>
-      <c r="G428" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
+      </c>
+      <c r="F428" s="1">
+        <v>18</v>
+      </c>
+      <c r="G428" s="1">
+        <v>2</v>
+      </c>
+      <c r="H428" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="429" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B429" s="1">
+        <v>5</v>
+      </c>
+      <c r="C429" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D429" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="E429" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F429" s="1">
+        <v>18</v>
+      </c>
+      <c r="G429" s="1">
         <v>2</v>
       </c>
-      <c r="C429" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D429" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E429" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F429" s="1"/>
-      <c r="G429" s="1" t="s">
-        <v>38</v>
+      <c r="H429" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="430" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B430" s="1">
+        <v>6</v>
+      </c>
+      <c r="C430" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D430" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="E430" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F430" s="1"/>
+      <c r="G430" s="1"/>
+    </row>
+    <row r="432" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B432" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C432" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="D432" s="6"/>
+      <c r="E432" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F432" s="7"/>
+      <c r="G432" s="7"/>
+    </row>
+    <row r="433" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B433" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C430" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="D430" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="E430" s="1" t="s">
+      <c r="C433" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="D433" s="7"/>
+      <c r="E433" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F433" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="G433" s="7"/>
+    </row>
+    <row r="434" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B434" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C434" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D434" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E434" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F434" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G434" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="435" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B435" s="1">
+        <v>1</v>
+      </c>
+      <c r="C435" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D435" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="E435" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F430" s="1">
-        <v>50</v>
-      </c>
-      <c r="G430" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="H430" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="431" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B431" s="1">
+      <c r="F435" s="1">
+        <v>24</v>
+      </c>
+      <c r="G435" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="436" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B436" s="1">
+        <v>2</v>
+      </c>
+      <c r="C436" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D436" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="E436" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F436" s="1"/>
+      <c r="G436" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="437" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B437" s="1">
+        <v>3</v>
+      </c>
+      <c r="C437" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D437" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="E437" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F437" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="G437" s="1"/>
+    </row>
+    <row r="438" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B438" s="1">
         <v>4</v>
       </c>
-      <c r="C431" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="D431" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="E431" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="F431" s="1"/>
-      <c r="G431" s="1" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="432" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B432" s="1">
-        <v>5</v>
-      </c>
-      <c r="C432" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D432" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E432" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F432" s="1"/>
-      <c r="G432" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="434" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B434" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C434" s="6" t="s">
-        <v>526</v>
-      </c>
-      <c r="D434" s="6"/>
-      <c r="E434" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F434" s="7"/>
-      <c r="G434" s="7"/>
-    </row>
-    <row r="435" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B435" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C435" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="D435" s="7"/>
-      <c r="E435" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F435" s="7"/>
-      <c r="G435" s="7"/>
-    </row>
-    <row r="436" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B436" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C436" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D436" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E436" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F436" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G436" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="437" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B437" s="1">
-        <v>1</v>
-      </c>
-      <c r="C437" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="D437" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="E437" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F437" s="1"/>
-      <c r="G437" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="438" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B438" s="1">
-        <v>2</v>
-      </c>
       <c r="C438" s="1" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="F438" s="1">
-        <v>100</v>
-      </c>
-      <c r="G438" s="1" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="439" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B439" s="1">
-        <v>3</v>
-      </c>
-      <c r="C439" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="D439" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="E439" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F439" s="1">
-        <v>50</v>
-      </c>
-      <c r="G439" s="1" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="440" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B440" s="1">
-        <v>4</v>
-      </c>
-      <c r="C440" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="D440" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="E440" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="F440" s="1"/>
-      <c r="G440" s="1" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="441" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B441" s="1">
-        <v>5</v>
-      </c>
-      <c r="C441" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="D441" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="E441" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F441" s="1">
-        <v>10</v>
-      </c>
-      <c r="G441" s="1">
-        <v>2</v>
-      </c>
-      <c r="H441" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="442" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B442" s="1">
-        <v>6</v>
-      </c>
-      <c r="C442" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="D442" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="E442" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F442" s="1"/>
-      <c r="G442" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="H442" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="443" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B443" s="1">
-        <v>7</v>
-      </c>
-      <c r="C443" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D443" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E443" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F443" s="1"/>
-      <c r="G443" s="1"/>
-    </row>
-    <row r="445" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B445" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C445" s="6" t="s">
-        <v>541</v>
-      </c>
-      <c r="D445" s="6"/>
-      <c r="E445" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F445" s="7"/>
-      <c r="G445" s="7"/>
-    </row>
-    <row r="446" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B446" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C446" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="D446" s="7"/>
-      <c r="E446" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F446" s="7" t="s">
-        <v>543</v>
-      </c>
-      <c r="G446" s="7"/>
-    </row>
-    <row r="447" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B447" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C447" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D447" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E447" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F447" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G447" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="448" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B448" s="1">
-        <v>1</v>
-      </c>
-      <c r="C448" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="D448" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="E448" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F448" s="1"/>
-      <c r="G448" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="449" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B449" s="1">
-        <v>2</v>
-      </c>
-      <c r="C449" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="D449" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="E449" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F449" s="1"/>
-      <c r="G449" s="1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="450" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B450" s="1">
-        <v>3</v>
-      </c>
-      <c r="C450" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="D450" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="E450" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F450" s="1"/>
-      <c r="G450" s="1" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="451" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B451" s="1">
-        <v>4</v>
-      </c>
-      <c r="C451" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="D451" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="E451" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F451" s="1">
-        <v>18</v>
-      </c>
-      <c r="G451" s="1">
-        <v>2</v>
-      </c>
-      <c r="H451" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="452" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B452" s="1">
-        <v>5</v>
-      </c>
-      <c r="C452" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="D452" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="E452" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F452" s="1">
-        <v>18</v>
-      </c>
-      <c r="G452" s="1">
-        <v>2</v>
-      </c>
-      <c r="H452" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="453" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B453" s="1">
-        <v>6</v>
-      </c>
-      <c r="C453" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D453" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="E453" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F453" s="1"/>
-      <c r="G453" s="1"/>
-    </row>
-    <row r="455" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B455" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C455" s="11" t="s">
-        <v>557</v>
-      </c>
-      <c r="D455" s="11"/>
-      <c r="E455" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="F455" s="12"/>
-      <c r="G455" s="12"/>
-    </row>
-    <row r="456" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B456" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C456" s="12" t="s">
-        <v>558</v>
-      </c>
-      <c r="D456" s="12"/>
-      <c r="E456" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F456" s="12" t="s">
-        <v>559</v>
-      </c>
-      <c r="G456" s="12" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="457" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B457" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C457" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D457" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E457" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F457" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G457" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="458" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B458" s="13">
-        <v>1</v>
-      </c>
-      <c r="C458" s="13" t="s">
-        <v>558</v>
-      </c>
-      <c r="D458" s="13" t="s">
-        <v>561</v>
-      </c>
-      <c r="E458" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F458" s="13"/>
-      <c r="G458" s="13" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="459" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B459" s="13">
-        <v>2</v>
-      </c>
-      <c r="C459" s="13" t="s">
-        <v>562</v>
-      </c>
-      <c r="D459" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E459" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F459" s="13"/>
-      <c r="G459" s="13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="460" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B460" s="13">
-        <v>3</v>
-      </c>
-      <c r="C460" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D460" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E460" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F460" s="13"/>
-      <c r="G460" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="461" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B461" s="13">
-        <v>4</v>
-      </c>
-      <c r="C461" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="D461" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="E461" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="F461" s="13"/>
-      <c r="G461" s="13" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="462" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B462" s="13">
-        <v>5</v>
-      </c>
-      <c r="C462" s="13" t="s">
-        <v>563</v>
-      </c>
-      <c r="D462" s="13" t="s">
-        <v>564</v>
-      </c>
-      <c r="E462" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="F462" s="13"/>
-      <c r="G462" s="13" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="463" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B463" s="13">
-        <v>6</v>
-      </c>
-      <c r="C463" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D463" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="E463" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="F463" s="13">
-        <v>20</v>
-      </c>
-      <c r="G463" s="13" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="464" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B464" s="13">
-        <v>7</v>
-      </c>
-      <c r="C464" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D464" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E464" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="F464" s="13"/>
-      <c r="G464" s="13" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="465" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B465" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C465" s="13" t="s">
-        <v>567</v>
-      </c>
-      <c r="D465" s="13"/>
-      <c r="E465" s="13"/>
-      <c r="F465" s="13"/>
-      <c r="G465" s="13"/>
-    </row>
-    <row r="466" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B466" s="13" t="s">
-        <v>503</v>
-      </c>
-      <c r="C466" s="13" t="s">
-        <v>568</v>
-      </c>
-      <c r="D466" s="13" t="s">
-        <v>569</v>
-      </c>
-      <c r="E466" s="13" t="s">
-        <v>570</v>
-      </c>
-      <c r="F466" s="13" t="s">
-        <v>571</v>
-      </c>
-      <c r="G466" s="13"/>
-    </row>
-    <row r="468" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B468" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C468" s="6" t="s">
-        <v>572</v>
-      </c>
-      <c r="D468" s="6"/>
-      <c r="E468" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F468" s="7"/>
-      <c r="G468" s="7"/>
-    </row>
-    <row r="469" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B469" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C469" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="D469" s="7"/>
-      <c r="E469" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F469" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="G469" s="7"/>
-    </row>
-    <row r="470" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B470" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C470" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D470" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E470" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F470" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G470" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="471" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B471" s="1">
-        <v>1</v>
-      </c>
-      <c r="C471" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="D471" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="E471" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F471" s="1">
-        <v>24</v>
-      </c>
-      <c r="G471" s="1" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="472" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B472" s="1">
-        <v>2</v>
-      </c>
-      <c r="C472" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="D472" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="E472" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F472" s="1"/>
-      <c r="G472" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="473" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B473" s="1">
-        <v>3</v>
-      </c>
-      <c r="C473" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D473" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="E473" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="F473" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="G473" s="1"/>
-    </row>
-    <row r="474" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B474" s="1">
-        <v>4</v>
-      </c>
-      <c r="C474" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="D474" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="E474" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="F474" s="1">
         <v>500</v>
       </c>
-      <c r="G474" s="1"/>
+      <c r="G438" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="160">
-    <mergeCell ref="C425:D425"/>
-    <mergeCell ref="F425:G425"/>
-    <mergeCell ref="C426:D426"/>
-    <mergeCell ref="F426:G426"/>
-    <mergeCell ref="C434:D434"/>
-    <mergeCell ref="F434:G434"/>
-    <mergeCell ref="C469:D469"/>
-    <mergeCell ref="F469:G469"/>
-    <mergeCell ref="C455:D455"/>
-    <mergeCell ref="F455:G455"/>
-    <mergeCell ref="C456:D456"/>
-    <mergeCell ref="F456:G456"/>
-    <mergeCell ref="C468:D468"/>
-    <mergeCell ref="F468:G468"/>
-    <mergeCell ref="C435:D435"/>
-    <mergeCell ref="F435:G435"/>
-    <mergeCell ref="C445:D445"/>
-    <mergeCell ref="F445:G445"/>
-    <mergeCell ref="C446:D446"/>
-    <mergeCell ref="F446:G446"/>
-    <mergeCell ref="C415:D415"/>
-    <mergeCell ref="F415:G415"/>
-    <mergeCell ref="C416:D416"/>
-    <mergeCell ref="F416:G416"/>
-    <mergeCell ref="C380:D380"/>
-    <mergeCell ref="F380:G380"/>
-    <mergeCell ref="C403:D403"/>
-    <mergeCell ref="F403:G403"/>
-    <mergeCell ref="C404:D404"/>
-    <mergeCell ref="F404:G404"/>
-    <mergeCell ref="C364:D364"/>
-    <mergeCell ref="F364:G364"/>
-    <mergeCell ref="C379:D379"/>
-    <mergeCell ref="F379:G379"/>
-    <mergeCell ref="C348:D348"/>
-    <mergeCell ref="F348:G348"/>
-    <mergeCell ref="C371:D371"/>
-    <mergeCell ref="F371:G371"/>
-    <mergeCell ref="C372:D372"/>
-    <mergeCell ref="F372:G372"/>
-    <mergeCell ref="C347:D347"/>
-    <mergeCell ref="F347:G347"/>
-    <mergeCell ref="C317:D317"/>
-    <mergeCell ref="F317:G317"/>
-    <mergeCell ref="C335:D335"/>
-    <mergeCell ref="F335:G335"/>
-    <mergeCell ref="C336:D336"/>
-    <mergeCell ref="F336:G336"/>
-    <mergeCell ref="C363:D363"/>
-    <mergeCell ref="F363:G363"/>
-    <mergeCell ref="C303:D303"/>
-    <mergeCell ref="F303:G303"/>
-    <mergeCell ref="C304:D304"/>
-    <mergeCell ref="F304:G304"/>
-    <mergeCell ref="C316:D316"/>
-    <mergeCell ref="F316:G316"/>
-    <mergeCell ref="C278:D278"/>
-    <mergeCell ref="F278:G278"/>
-    <mergeCell ref="C290:D290"/>
-    <mergeCell ref="F290:G290"/>
-    <mergeCell ref="C291:D291"/>
-    <mergeCell ref="F291:G291"/>
-    <mergeCell ref="C264:D264"/>
-    <mergeCell ref="F264:G264"/>
-    <mergeCell ref="C265:D265"/>
-    <mergeCell ref="F265:G265"/>
-    <mergeCell ref="C277:D277"/>
-    <mergeCell ref="F277:G277"/>
-    <mergeCell ref="C241:D241"/>
-    <mergeCell ref="F241:G241"/>
-    <mergeCell ref="C252:D252"/>
-    <mergeCell ref="F252:G252"/>
-    <mergeCell ref="C253:D253"/>
-    <mergeCell ref="F253:G253"/>
-    <mergeCell ref="C228:D228"/>
-    <mergeCell ref="F228:G228"/>
-    <mergeCell ref="C229:D229"/>
-    <mergeCell ref="F229:G229"/>
-    <mergeCell ref="C240:D240"/>
-    <mergeCell ref="F240:G240"/>
-    <mergeCell ref="C207:D207"/>
-    <mergeCell ref="F207:G207"/>
-    <mergeCell ref="C214:D214"/>
-    <mergeCell ref="F214:G214"/>
-    <mergeCell ref="C215:D215"/>
-    <mergeCell ref="F215:G215"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="F197:G197"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="F198:G198"/>
-    <mergeCell ref="C206:D206"/>
-    <mergeCell ref="F206:G206"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="F176:G176"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="F185:G185"/>
-    <mergeCell ref="C186:D186"/>
-    <mergeCell ref="F186:G186"/>
-    <mergeCell ref="C168:D168"/>
-    <mergeCell ref="F168:G168"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="F175:G175"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="F142:G142"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="F153:G153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="F154:G154"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="F141:G141"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="F130:G130"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="F167:G167"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="F103:G103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="F104:G104"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="F116:G116"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="F97:G97"/>
+  <mergeCells count="148">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:G14"/>
     <mergeCell ref="C63:D63"/>
     <mergeCell ref="F63:G63"/>
     <mergeCell ref="C64:D64"/>
@@ -10795,20 +9940,124 @@
     <mergeCell ref="F80:G80"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="F81:G81"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="F116:G116"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="F141:G141"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="F167:G167"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="F168:G168"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="F175:G175"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="F142:G142"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="F153:G153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="F154:G154"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="F197:G197"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="F198:G198"/>
+    <mergeCell ref="C206:D206"/>
+    <mergeCell ref="F206:G206"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="F176:G176"/>
+    <mergeCell ref="C185:D185"/>
+    <mergeCell ref="F185:G185"/>
+    <mergeCell ref="C186:D186"/>
+    <mergeCell ref="F186:G186"/>
+    <mergeCell ref="C228:D228"/>
+    <mergeCell ref="F228:G228"/>
+    <mergeCell ref="C229:D229"/>
+    <mergeCell ref="F229:G229"/>
+    <mergeCell ref="C240:D240"/>
+    <mergeCell ref="F240:G240"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="F207:G207"/>
+    <mergeCell ref="C214:D214"/>
+    <mergeCell ref="F214:G214"/>
+    <mergeCell ref="C215:D215"/>
+    <mergeCell ref="F215:G215"/>
+    <mergeCell ref="C264:D264"/>
+    <mergeCell ref="F264:G264"/>
+    <mergeCell ref="C265:D265"/>
+    <mergeCell ref="F265:G265"/>
+    <mergeCell ref="C277:D277"/>
+    <mergeCell ref="F277:G277"/>
+    <mergeCell ref="C241:D241"/>
+    <mergeCell ref="F241:G241"/>
+    <mergeCell ref="C252:D252"/>
+    <mergeCell ref="F252:G252"/>
+    <mergeCell ref="C253:D253"/>
+    <mergeCell ref="F253:G253"/>
+    <mergeCell ref="C303:D303"/>
+    <mergeCell ref="F303:G303"/>
+    <mergeCell ref="C304:D304"/>
+    <mergeCell ref="F304:G304"/>
+    <mergeCell ref="C316:D316"/>
+    <mergeCell ref="F316:G316"/>
+    <mergeCell ref="C278:D278"/>
+    <mergeCell ref="F278:G278"/>
+    <mergeCell ref="C290:D290"/>
+    <mergeCell ref="F290:G290"/>
+    <mergeCell ref="C291:D291"/>
+    <mergeCell ref="F291:G291"/>
+    <mergeCell ref="C347:D347"/>
+    <mergeCell ref="F347:G347"/>
+    <mergeCell ref="C317:D317"/>
+    <mergeCell ref="F317:G317"/>
+    <mergeCell ref="C335:D335"/>
+    <mergeCell ref="F335:G335"/>
+    <mergeCell ref="C336:D336"/>
+    <mergeCell ref="F336:G336"/>
+    <mergeCell ref="C363:D363"/>
+    <mergeCell ref="F363:G363"/>
+    <mergeCell ref="C364:D364"/>
+    <mergeCell ref="F364:G364"/>
+    <mergeCell ref="C379:D379"/>
+    <mergeCell ref="F379:G379"/>
+    <mergeCell ref="C348:D348"/>
+    <mergeCell ref="F348:G348"/>
+    <mergeCell ref="C371:D371"/>
+    <mergeCell ref="F371:G371"/>
+    <mergeCell ref="C372:D372"/>
+    <mergeCell ref="F372:G372"/>
+    <mergeCell ref="C380:D380"/>
+    <mergeCell ref="F380:G380"/>
+    <mergeCell ref="C402:D402"/>
+    <mergeCell ref="F402:G402"/>
+    <mergeCell ref="C403:D403"/>
+    <mergeCell ref="F403:G403"/>
+    <mergeCell ref="C411:D411"/>
+    <mergeCell ref="F411:G411"/>
+    <mergeCell ref="C433:D433"/>
+    <mergeCell ref="F433:G433"/>
+    <mergeCell ref="C432:D432"/>
+    <mergeCell ref="F432:G432"/>
+    <mergeCell ref="C412:D412"/>
+    <mergeCell ref="F412:G412"/>
+    <mergeCell ref="C422:D422"/>
+    <mergeCell ref="F422:G422"/>
+    <mergeCell ref="C423:D423"/>
+    <mergeCell ref="F423:G423"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Document/專題/db_diagram.xlsx
+++ b/Document/專題/db_diagram.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\RentalManagementPlatform\Document\專題\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4AF059B-3EEB-4B2E-BB6C-25BC596C76D6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A48D6FA-EA9C-4624-B35D-8FC88D5CEA69}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="db" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">db!$I$2:$I$438</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="593">
   <si>
     <t>表格名稱</t>
   </si>
@@ -107,9 +110,6 @@
     <t>路名與門牌</t>
   </si>
   <si>
-    <t>STRING</t>
-  </si>
-  <si>
     <t>例：復興南路一段 390 號 10 樓</t>
   </si>
   <si>
@@ -119,9 +119,6 @@
     <t>建立時間</t>
   </si>
   <si>
-    <t>DATETIME</t>
-  </si>
-  <si>
     <t>建立紀錄時間</t>
   </si>
   <si>
@@ -132,9 +129,6 @@
   </si>
   <si>
     <t>最後更新時間</t>
-  </si>
-  <si>
-    <t>board_id → PROPERTY_MANAGEMENT_BOARD.board_id</t>
   </si>
   <si>
     <t>(FK) 對應 USER.user_id</t>
@@ -153,9 +147,6 @@
     <t xml:space="preserve"> guest_id → USER.user_id</t>
   </si>
   <si>
-    <t xml:space="preserve"> room_id → ROOM_LIST.room_id</t>
-  </si>
-  <si>
     <t>訂單 ID</t>
   </si>
   <si>
@@ -280,9 +271,6 @@
     <t>自動訂閱</t>
   </si>
   <si>
-    <t>BOOL</t>
-  </si>
-  <si>
     <t>true/false</t>
   </si>
   <si>
@@ -480,12 +468,6 @@
     <t xml:space="preserve"> booking_id → BOOKING.booking_id</t>
   </si>
   <si>
-    <t xml:space="preserve"> receiver_id → USER.user_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> sender_id → USER.user_id</t>
-  </si>
-  <si>
     <t>訊息 ID</t>
   </si>
   <si>
@@ -645,9 +627,6 @@
     <t xml:space="preserve"> host_id → USER.user_id</t>
   </si>
   <si>
-    <t xml:space="preserve"> reviewer_id → USER.user_id</t>
-  </si>
-  <si>
     <t>評論 ID</t>
   </si>
   <si>
@@ -768,12 +747,6 @@
     <t>角色 ID</t>
   </si>
   <si>
-    <t>IDENTITY(1</t>
-  </si>
-  <si>
-    <t>1)</t>
-  </si>
-  <si>
     <t>role_code</t>
   </si>
   <si>
@@ -909,9 +882,6 @@
     <t>結算週期開始</t>
   </si>
   <si>
-    <t>DATE</t>
-  </si>
-  <si>
     <t>cycle_end</t>
   </si>
   <si>
@@ -998,9 +968,6 @@
     <t>加速審核/優先曝光</t>
   </si>
   <si>
-    <t>BOOLEAN</t>
-  </si>
-  <si>
     <t>perk_analytics</t>
   </si>
   <si>
@@ -1271,9 +1238,6 @@
     <t>內容</t>
   </si>
   <si>
-    <t>TEXT</t>
-  </si>
-  <si>
     <t>is_pinned</t>
   </si>
   <si>
@@ -1424,12 +1388,6 @@
     <t>分類 ID</t>
   </si>
   <si>
-    <t>NOT NULL (PK</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 自動遞增)</t>
-  </si>
-  <si>
     <t>NOT NULL，唯一</t>
   </si>
   <si>
@@ -1449,9 +1407,6 @@
     <t xml:space="preserve"> category_id → CATEGORIES.categories_id</t>
   </si>
   <si>
-    <t xml:space="preserve"> region_id → DISTRICT.district_id</t>
-  </si>
-  <si>
     <t>公告 ID</t>
   </si>
   <si>
@@ -1501,9 +1456,6 @@
   </si>
   <si>
     <t>default: 0</t>
-  </si>
-  <si>
-    <t>post_status</t>
   </si>
   <si>
     <t>NOT NULL，default: draft</t>
@@ -1534,12 +1486,6 @@
     <t>報表類型</t>
   </si>
   <si>
-    <t>例：OrderRevenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> RoomStats</t>
-  </si>
-  <si>
     <t>report_params</t>
   </si>
   <si>
@@ -1586,15 +1532,6 @@
     <t>閾值</t>
   </si>
   <si>
-    <t>例：0.5 表示 50%</t>
-  </si>
-  <si>
-    <t>1=啟用</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0=停用</t>
-  </si>
-  <si>
     <t>中文：異常檢測紀錄_x000D_
 英文：ANOMALY_DETECTION_LOG</t>
   </si>
@@ -1702,19 +1639,11 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>CHAR</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>birth_date</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>生日</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>DATE</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
@@ -1824,10 +1753,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>NOT NULL (PK</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>NOT NULL</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -1877,10 +1802,6 @@
   </si>
   <si>
     <t>租期區間開始</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>DATETIME</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
@@ -1940,6 +1861,62 @@
   </si>
   <si>
     <t>end_rental_period</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>18,2</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,2</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>1=啟用, 0=停用</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>例：0.5 表示 50%</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>例：OrderRevenue, RoomStats</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_id → USER.user_id
+ region_id → DISTRICT.district_id</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT NULL (PK 自動遞增)</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT NULL (PK 自動遞增)</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>IDENTITY(1,1)</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>booking_id → BOOKING.booking_id
+ reviewer_id → USER.user_id</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>board_id → PROPERTY_MANAGEMENT_BOARD.board_id
+ receiver_id → USER.user_id</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>coupon_id → COUPON.coupon_id
+ room_id → ROOM_LIST.room_id</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>9,6</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -2943,7 +2920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J438"/>
+  <dimension ref="B2:I438"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
@@ -2954,7 +2931,7 @@
     <col min="7" max="7" width="62.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2968,7 +2945,7 @@
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
@@ -2984,7 +2961,7 @@
       </c>
       <c r="G3" s="7"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -3004,7 +2981,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -3022,7 +2999,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -3040,7 +3017,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -3053,17 +3030,14 @@
       <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="1">
-        <v>9</v>
-      </c>
-      <c r="G7" s="1">
-        <v>6</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="F7" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -3076,17 +3050,14 @@
       <c r="E8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="1">
-        <v>9</v>
-      </c>
-      <c r="G8" s="1">
-        <v>6</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="F8" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -3097,55 +3068,55 @@
         <v>27</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="2" t="s">
@@ -3154,28 +3125,25 @@
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>41</v>
+      <c r="F14" s="6" t="s">
+        <v>591</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>7</v>
       </c>
@@ -3195,15 +3163,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>14</v>
@@ -3218,17 +3186,17 @@
         <v>2</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -3236,17 +3204,17 @@
         <v>3</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -3254,17 +3222,17 @@
         <v>4</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -3272,13 +3240,13 @@
         <v>5</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -3288,17 +3256,17 @@
         <v>6</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -3306,17 +3274,17 @@
         <v>7</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -3324,17 +3292,17 @@
         <v>8</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -3342,10 +3310,10 @@
         <v>9</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>21</v>
@@ -3358,10 +3326,10 @@
         <v>10</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>14</v>
@@ -3374,10 +3342,10 @@
         <v>11</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>14</v>
@@ -3390,17 +3358,17 @@
         <v>12</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -3408,13 +3376,13 @@
         <v>13</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E28" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -3424,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="2" t="s">
@@ -3438,7 +3406,7 @@
         <v>3</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="2" t="s">
@@ -3472,10 +3440,10 @@
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>14</v>
@@ -3490,17 +3458,17 @@
         <v>2</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>541</v>
+        <v>519</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>542</v>
+        <v>520</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>543</v>
+        <v>521</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1" t="s">
-        <v>544</v>
+        <v>522</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
@@ -3508,17 +3476,17 @@
         <v>3</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
@@ -3526,17 +3494,17 @@
         <v>4</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
@@ -3544,17 +3512,17 @@
         <v>5</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>85</v>
+        <v>269</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
@@ -3562,17 +3530,17 @@
         <v>6</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
@@ -3580,13 +3548,13 @@
         <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>545</v>
+        <v>523</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>547</v>
+        <v>524</v>
+      </c>
+      <c r="E39" t="s">
+        <v>238</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -3596,17 +3564,17 @@
         <v>8</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>548</v>
+        <v>525</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>549</v>
+        <v>526</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>550</v>
+        <v>245</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1" t="s">
-        <v>544</v>
+        <v>522</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
@@ -3614,17 +3582,17 @@
         <v>9</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
@@ -3632,13 +3600,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>551</v>
+        <v>527</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>553</v>
+        <v>529</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>543</v>
+        <v>521</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -3648,13 +3616,13 @@
         <v>11</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>552</v>
+        <v>528</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>554</v>
+        <v>530</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>543</v>
+        <v>521</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -3664,17 +3632,17 @@
         <v>12</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
@@ -3682,17 +3650,17 @@
         <v>13</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>555</v>
+        <v>531</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>556</v>
+        <v>532</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>557</v>
+        <v>533</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1" t="s">
-        <v>558</v>
+        <v>534</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
@@ -3700,17 +3668,17 @@
         <v>14</v>
       </c>
       <c r="C46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E46" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
@@ -3718,13 +3686,13 @@
         <v>15</v>
       </c>
       <c r="C47" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="E47" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -3734,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="2" t="s">
@@ -3748,14 +3716,14 @@
         <v>3</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D50" s="7"/>
       <c r="E50" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G50" s="7"/>
     </row>
@@ -3784,10 +3752,10 @@
         <v>1</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>14</v>
@@ -3802,17 +3770,17 @@
         <v>2</v>
       </c>
       <c r="C53" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
@@ -3820,17 +3788,17 @@
         <v>3</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
@@ -3838,17 +3806,17 @@
         <v>4</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3856,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="2" t="s">
@@ -3870,7 +3838,7 @@
         <v>3</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D58" s="7"/>
       <c r="E58" s="2" t="s">
@@ -3904,10 +3872,10 @@
         <v>1</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>14</v>
@@ -3922,17 +3890,17 @@
         <v>2</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3940,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>597</v>
+        <v>571</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="2" t="s">
@@ -3954,7 +3922,7 @@
         <v>3</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D64" s="7"/>
       <c r="E64" s="2" t="s">
@@ -3963,7 +3931,7 @@
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B65" s="2" t="s">
         <v>7</v>
       </c>
@@ -3983,15 +3951,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B66" s="1">
         <v>1</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>14</v>
@@ -4001,222 +3969,226 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B67" s="1">
         <v>2</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B68" s="1">
         <v>3</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B69" s="1">
         <v>4</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="70" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="4">
         <v>5</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>602</v>
+        <v>576</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>586</v>
+        <v>561</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>588</v>
+        <v>563</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="71" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>573</v>
+      </c>
+      <c r="I70"/>
+    </row>
+    <row r="71" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B71" s="4">
         <v>6</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>603</v>
+        <v>577</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>587</v>
+        <v>562</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>588</v>
+        <v>563</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="72" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+      <c r="I71"/>
+    </row>
+    <row r="72" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B72" s="4">
         <v>7</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>604</v>
+        <v>578</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>590</v>
+        <v>565</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>591</v>
+        <v>245</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="4" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="73" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>575</v>
+      </c>
+      <c r="I72"/>
+    </row>
+    <row r="73" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B73" s="4">
         <v>8</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>605</v>
+        <v>579</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>589</v>
+        <v>564</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>591</v>
+        <v>245</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="4" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
+        <v>575</v>
+      </c>
+      <c r="I73"/>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B74" s="1">
         <v>9</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B75" s="1">
         <v>10</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B76" s="1">
         <v>11</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B77" s="1">
         <v>12</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B78" s="1">
         <v>13</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
     </row>
-    <row r="80" spans="2:7" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>598</v>
+        <v>572</v>
       </c>
       <c r="D80" s="8"/>
       <c r="E80" s="3" t="s">
@@ -4224,26 +4196,28 @@
       </c>
       <c r="F80" s="9"/>
       <c r="G80" s="9"/>
-    </row>
-    <row r="81" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I80"/>
+    </row>
+    <row r="81" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>592</v>
+        <v>566</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="82" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="I81"/>
+    </row>
+    <row r="82" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B82" s="3" t="s">
         <v>7</v>
       </c>
@@ -4262,16 +4236,17 @@
       <c r="G82" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="83" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I82"/>
+    </row>
+    <row r="83" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B83" s="4">
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>592</v>
+        <v>566</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>14</v>
@@ -4280,49 +4255,52 @@
       <c r="G83" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="84" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I83"/>
+    </row>
+    <row r="84" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="4">
         <v>2</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="85" spans="2:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="I84"/>
+    </row>
+    <row r="85" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B85" s="4">
         <v>3</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>593</v>
+        <v>567</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>594</v>
+        <v>568</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="87" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>569</v>
+      </c>
+      <c r="I85"/>
+    </row>
+    <row r="87" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D87" s="6"/>
       <c r="E87" s="2" t="s">
@@ -4331,25 +4309,25 @@
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
     </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B88" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D88" s="7"/>
       <c r="E88" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B89" s="2" t="s">
         <v>7</v>
       </c>
@@ -4369,15 +4347,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B90" s="1">
         <v>1</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>14</v>
@@ -4387,80 +4365,80 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B91" s="1">
         <v>2</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B92" s="1">
         <v>3</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F92" s="1"/>
       <c r="G92" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B93" s="1">
         <v>4</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
     </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B94" s="1">
         <v>5</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
     </row>
-    <row r="96" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D96" s="6"/>
       <c r="E96" s="2" t="s">
@@ -4469,7 +4447,7 @@
       <c r="F96" s="7"/>
       <c r="G96" s="7"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B97" s="2" t="s">
         <v>3</v>
       </c>
@@ -4481,11 +4459,11 @@
         <v>5</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G97" s="7"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B98" s="2" t="s">
         <v>7</v>
       </c>
@@ -4505,7 +4483,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B99" s="1">
         <v>1</v>
       </c>
@@ -4523,48 +4501,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B100" s="1">
         <v>2</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F100" s="1"/>
       <c r="G100" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B101" s="1">
         <v>3</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F101" s="1"/>
       <c r="G101" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="103" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="103" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D103" s="8"/>
       <c r="E103" s="3" t="s">
@@ -4573,31 +4551,25 @@
       <c r="F103" s="9"/>
       <c r="G103" s="9"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B104" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D104" s="9"/>
       <c r="E104" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F104" s="9" t="s">
-        <v>37</v>
+      <c r="F104" s="8" t="s">
+        <v>590</v>
       </c>
       <c r="G104" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="H104" t="s">
-        <v>150</v>
-      </c>
-      <c r="J104" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B105" s="3" t="s">
         <v>7</v>
       </c>
@@ -4617,15 +4589,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B106" s="4">
         <v>1</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>14</v>
@@ -4635,130 +4607,132 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="2:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B107" s="4">
         <v>2</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>561</v>
+        <v>537</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>562</v>
+        <v>538</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="4" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
+        <v>542</v>
+      </c>
+      <c r="I107"/>
+    </row>
+    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B108" s="4">
         <v>3</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>563</v>
+        <v>539</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F108" s="4"/>
       <c r="G108" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B109" s="4">
         <v>4</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F109" s="4"/>
       <c r="G109" s="4" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B110" s="4">
         <v>5</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F110" s="4"/>
       <c r="G110" s="4" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B111" s="4">
         <v>6</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="4" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="112" spans="2:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="112" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B112" s="4">
         <v>7</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>564</v>
+        <v>540</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>565</v>
+        <v>541</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="4" t="s">
-        <v>569</v>
-      </c>
+        <v>545</v>
+      </c>
+      <c r="I112"/>
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B113" s="4">
         <v>8</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F113" s="4"/>
       <c r="G113" s="4" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="114" spans="2:7" x14ac:dyDescent="0.25">
@@ -4766,13 +4740,13 @@
         <v>9</v>
       </c>
       <c r="C114" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D114" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D114" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="E114" s="4" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
@@ -4782,7 +4756,7 @@
         <v>0</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D116" s="6"/>
       <c r="E116" s="2" t="s">
@@ -4796,14 +4770,14 @@
         <v>3</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D117" s="7"/>
       <c r="E117" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G117" s="7"/>
     </row>
@@ -4832,10 +4806,10 @@
         <v>1</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>14</v>
@@ -4850,17 +4824,17 @@
         <v>2</v>
       </c>
       <c r="C120" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F120" s="1"/>
       <c r="G120" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="121" spans="2:7" x14ac:dyDescent="0.25">
@@ -4868,17 +4842,17 @@
         <v>3</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F121" s="1"/>
       <c r="G121" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="122" spans="2:7" x14ac:dyDescent="0.25">
@@ -4886,17 +4860,17 @@
         <v>4</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F122" s="1"/>
       <c r="G122" s="1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="123" spans="2:7" x14ac:dyDescent="0.25">
@@ -4904,13 +4878,13 @@
         <v>5</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
@@ -4920,13 +4894,13 @@
         <v>6</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
@@ -4936,13 +4910,13 @@
         <v>7</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
@@ -4952,17 +4926,17 @@
         <v>8</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F126" s="1"/>
       <c r="G126" s="1" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="127" spans="2:7" x14ac:dyDescent="0.25">
@@ -4970,23 +4944,23 @@
         <v>9</v>
       </c>
       <c r="C127" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D127" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>
     </row>
-    <row r="129" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B129" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="D129" s="6"/>
       <c r="E129" s="2" t="s">
@@ -4995,23 +4969,23 @@
       <c r="F129" s="7"/>
       <c r="G129" s="7"/>
     </row>
-    <row r="130" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B130" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D130" s="7"/>
       <c r="E130" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="G130" s="7"/>
     </row>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B131" s="2" t="s">
         <v>7</v>
       </c>
@@ -5031,15 +5005,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B132" s="1">
         <v>1</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>14</v>
@@ -5049,130 +5023,130 @@
         <v>15</v>
       </c>
     </row>
-    <row r="133" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B133" s="1">
         <v>2</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F133" s="1"/>
       <c r="G133" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="134" spans="2:8" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="134" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B134" s="1">
         <v>3</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
     </row>
-    <row r="135" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B135" s="1">
         <v>4</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F135" s="1"/>
       <c r="G135" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="136" spans="2:8" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="136" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B136" s="1">
         <v>5</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F136" s="1"/>
       <c r="G136" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="137" spans="2:8" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="137" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B137" s="1">
         <v>6</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
     </row>
-    <row r="138" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B138" s="1">
         <v>7</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F138" s="1"/>
       <c r="G138" s="1"/>
     </row>
-    <row r="139" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B139" s="1">
         <v>8</v>
       </c>
       <c r="C139" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D139" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
     </row>
-    <row r="141" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B141" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D141" s="6"/>
       <c r="E141" s="2" t="s">
@@ -5181,28 +5155,25 @@
       <c r="F141" s="7"/>
       <c r="G141" s="7"/>
     </row>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B142" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D142" s="7"/>
       <c r="E142" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F142" s="7" t="s">
-        <v>99</v>
+      <c r="F142" s="6" t="s">
+        <v>589</v>
       </c>
       <c r="G142" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="H142" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="143" spans="2:8" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="143" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B143" s="2" t="s">
         <v>7</v>
       </c>
@@ -5222,15 +5193,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B144" s="1">
         <v>1</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>14</v>
@@ -5245,17 +5216,17 @@
         <v>2</v>
       </c>
       <c r="C145" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F145" s="1"/>
       <c r="G145" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="146" spans="2:7" x14ac:dyDescent="0.25">
@@ -5263,17 +5234,17 @@
         <v>3</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F146" s="1"/>
       <c r="G146" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="147" spans="2:7" x14ac:dyDescent="0.25">
@@ -5281,17 +5252,17 @@
         <v>4</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F147" s="1"/>
       <c r="G147" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="148" spans="2:7" x14ac:dyDescent="0.25">
@@ -5299,17 +5270,17 @@
         <v>5</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F148" s="1"/>
       <c r="G148" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="149" spans="2:7" x14ac:dyDescent="0.25">
@@ -5317,17 +5288,17 @@
         <v>6</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F149" s="1"/>
       <c r="G149" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="150" spans="2:7" x14ac:dyDescent="0.25">
@@ -5335,17 +5306,17 @@
         <v>7</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F150" s="1"/>
       <c r="G150" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="151" spans="2:7" x14ac:dyDescent="0.25">
@@ -5353,13 +5324,13 @@
         <v>8</v>
       </c>
       <c r="C151" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D151" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E151" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F151" s="1"/>
       <c r="G151" s="1"/>
@@ -5369,7 +5340,7 @@
         <v>0</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D153" s="6"/>
       <c r="E153" s="2" t="s">
@@ -5383,17 +5354,17 @@
         <v>3</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D154" s="7"/>
       <c r="E154" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="155" spans="2:7" x14ac:dyDescent="0.25">
@@ -5421,10 +5392,10 @@
         <v>1</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>14</v>
@@ -5449,7 +5420,7 @@
       </c>
       <c r="F157" s="1"/>
       <c r="G157" s="1" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="158" spans="2:7" x14ac:dyDescent="0.25">
@@ -5457,17 +5428,17 @@
         <v>3</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F158" s="1"/>
       <c r="G158" s="1" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="159" spans="2:7" x14ac:dyDescent="0.25">
@@ -5475,17 +5446,17 @@
         <v>4</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="1" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="160" spans="2:7" x14ac:dyDescent="0.25">
@@ -5493,17 +5464,17 @@
         <v>5</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F160" s="1"/>
       <c r="G160" s="1" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="161" spans="2:7" x14ac:dyDescent="0.25">
@@ -5511,17 +5482,17 @@
         <v>6</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F161" s="1"/>
       <c r="G161" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
     </row>
     <row r="162" spans="2:7" x14ac:dyDescent="0.25">
@@ -5529,17 +5500,17 @@
         <v>7</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F162" s="1"/>
       <c r="G162" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
     <row r="163" spans="2:7" x14ac:dyDescent="0.25">
@@ -5547,17 +5518,17 @@
         <v>8</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F163" s="1"/>
       <c r="G163" s="1" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="164" spans="2:7" x14ac:dyDescent="0.25">
@@ -5565,13 +5536,13 @@
         <v>9</v>
       </c>
       <c r="C164" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D164" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E164" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F164" s="1"/>
       <c r="G164" s="1"/>
@@ -5581,13 +5552,13 @@
         <v>10</v>
       </c>
       <c r="C165" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D165" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F165" s="1"/>
       <c r="G165" s="1"/>
@@ -5597,7 +5568,7 @@
         <v>0</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="D167" s="6"/>
       <c r="E167" s="2" t="s">
@@ -5611,14 +5582,14 @@
         <v>3</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D168" s="7"/>
       <c r="E168" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="G168" s="7"/>
     </row>
@@ -5647,10 +5618,10 @@
         <v>1</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>14</v>
@@ -5665,17 +5636,17 @@
         <v>2</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F171" s="1"/>
       <c r="G171" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="172" spans="2:7" x14ac:dyDescent="0.25">
@@ -5683,17 +5654,17 @@
         <v>3</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F172" s="1"/>
       <c r="G172" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
     </row>
     <row r="173" spans="2:7" x14ac:dyDescent="0.25">
@@ -5701,17 +5672,17 @@
         <v>4</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F173" s="1"/>
       <c r="G173" s="1" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
     </row>
     <row r="175" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5719,7 +5690,7 @@
         <v>0</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D175" s="6"/>
       <c r="E175" s="2" t="s">
@@ -5733,7 +5704,7 @@
         <v>3</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D176" s="7"/>
       <c r="E176" s="2" t="s">
@@ -5742,7 +5713,7 @@
       <c r="F176" s="7"/>
       <c r="G176" s="7"/>
     </row>
-    <row r="177" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B177" s="2" t="s">
         <v>7</v>
       </c>
@@ -5762,127 +5733,124 @@
         <v>12</v>
       </c>
     </row>
-    <row r="178" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B178" s="1">
         <v>1</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F178" s="1"/>
       <c r="G178" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="H178" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="179" spans="2:8" x14ac:dyDescent="0.25">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="179" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B179" s="1">
         <v>2</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F179" s="1">
         <v>50</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="180" spans="2:8" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="180" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B180" s="1">
         <v>3</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F180" s="1">
         <v>100</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="181" spans="2:8" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="181" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B181" s="1">
         <v>4</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F181" s="1">
         <v>500</v>
       </c>
       <c r="G181" s="1"/>
     </row>
-    <row r="182" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B182" s="1">
         <v>5</v>
       </c>
       <c r="C182" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D182" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E182" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="F182" s="1"/>
       <c r="G182" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="183" spans="2:8" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="183" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B183" s="1">
         <v>6</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="F183" s="1"/>
       <c r="G183" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="185" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="185" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B185" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="D185" s="6"/>
       <c r="E185" s="2" t="s">
@@ -5891,12 +5859,12 @@
       <c r="F185" s="7"/>
       <c r="G185" s="7"/>
     </row>
-    <row r="186" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B186" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D186" s="7"/>
       <c r="E186" s="2" t="s">
@@ -5905,7 +5873,7 @@
       <c r="F186" s="7"/>
       <c r="G186" s="7"/>
     </row>
-    <row r="187" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B187" s="2" t="s">
         <v>7</v>
       </c>
@@ -5925,105 +5893,102 @@
         <v>12</v>
       </c>
     </row>
-    <row r="188" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B188" s="1">
         <v>1</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F188" s="1"/>
       <c r="G188" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="H188" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="189" spans="2:8" x14ac:dyDescent="0.25">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="189" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B189" s="1">
         <v>2</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F189" s="1">
         <v>100</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="190" spans="2:8" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="190" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B190" s="1">
         <v>3</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F190" s="1">
         <v>200</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="191" spans="2:8" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="191" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B191" s="1">
         <v>4</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F191" s="1">
         <v>50</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="192" spans="2:8" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="192" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B192" s="1">
         <v>5</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F192" s="1">
         <v>50</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="193" spans="2:7" x14ac:dyDescent="0.25">
@@ -6031,13 +5996,13 @@
         <v>6</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F193" s="1">
         <v>500</v>
@@ -6049,17 +6014,17 @@
         <v>7</v>
       </c>
       <c r="C194" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D194" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E194" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="F194" s="1"/>
       <c r="G194" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
     </row>
     <row r="195" spans="2:7" x14ac:dyDescent="0.25">
@@ -6067,17 +6032,17 @@
         <v>8</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="F195" s="1"/>
       <c r="G195" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
     </row>
     <row r="197" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6085,7 +6050,7 @@
         <v>0</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D197" s="6"/>
       <c r="E197" s="2" t="s">
@@ -6099,17 +6064,17 @@
         <v>3</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>559</v>
+        <v>535</v>
       </c>
       <c r="D198" s="7"/>
       <c r="E198" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="G198" s="7" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
     </row>
     <row r="199" spans="2:7" x14ac:dyDescent="0.25">
@@ -6137,17 +6102,17 @@
         <v>1</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F200" s="1"/>
       <c r="G200" s="1" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
     </row>
     <row r="201" spans="2:7" x14ac:dyDescent="0.25">
@@ -6155,17 +6120,17 @@
         <v>2</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F201" s="1"/>
       <c r="G201" s="1" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
     </row>
     <row r="202" spans="2:7" x14ac:dyDescent="0.25">
@@ -6173,17 +6138,17 @@
         <v>3</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F202" s="1"/>
       <c r="G202" s="1" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
     </row>
     <row r="203" spans="2:7" x14ac:dyDescent="0.25">
@@ -6191,17 +6156,17 @@
         <v>4</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="F203" s="1"/>
       <c r="G203" s="1" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
     <row r="204" spans="2:7" x14ac:dyDescent="0.25">
@@ -6209,17 +6174,17 @@
         <v>5</v>
       </c>
       <c r="C204" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D204" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E204" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="F204" s="1"/>
       <c r="G204" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
     </row>
     <row r="206" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6227,7 +6192,7 @@
         <v>0</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>560</v>
+        <v>536</v>
       </c>
       <c r="D206" s="6"/>
       <c r="E206" s="2" t="s">
@@ -6241,17 +6206,17 @@
         <v>3</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>584</v>
+        <v>559</v>
       </c>
       <c r="D207" s="7"/>
       <c r="E207" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="G207" s="7" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
     </row>
     <row r="208" spans="2:7" x14ac:dyDescent="0.25">
@@ -6279,10 +6244,10 @@
         <v>1</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>14</v>
@@ -6297,17 +6262,17 @@
         <v>2</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F210" s="1"/>
       <c r="G210" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="211" spans="2:7" x14ac:dyDescent="0.25">
@@ -6315,17 +6280,17 @@
         <v>3</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F211" s="1"/>
       <c r="G211" s="1" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
     </row>
     <row r="212" spans="2:7" x14ac:dyDescent="0.25">
@@ -6333,17 +6298,17 @@
         <v>4</v>
       </c>
       <c r="C212" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D212" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E212" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="F212" s="1"/>
       <c r="G212" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
     </row>
     <row r="214" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6351,7 +6316,7 @@
         <v>0</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="D214" s="6"/>
       <c r="E214" s="2" t="s">
@@ -6365,14 +6330,14 @@
         <v>3</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="D215" s="7"/>
       <c r="E215" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G215" s="7"/>
     </row>
@@ -6401,10 +6366,10 @@
         <v>1</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>14</v>
@@ -6419,17 +6384,17 @@
         <v>2</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F218" s="1"/>
       <c r="G218" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="219" spans="2:7" x14ac:dyDescent="0.25">
@@ -6437,13 +6402,13 @@
         <v>3</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>290</v>
+        <v>245</v>
       </c>
       <c r="F219" s="1"/>
       <c r="G219" s="1"/>
@@ -6453,13 +6418,13 @@
         <v>4</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>290</v>
+        <v>245</v>
       </c>
       <c r="F220" s="1"/>
       <c r="G220" s="1"/>
@@ -6469,10 +6434,10 @@
         <v>5</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>21</v>
@@ -6485,10 +6450,10 @@
         <v>6</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>21</v>
@@ -6501,10 +6466,10 @@
         <v>7</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>21</v>
@@ -6517,13 +6482,13 @@
         <v>8</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F224" s="1"/>
       <c r="G224" s="1"/>
@@ -6533,13 +6498,13 @@
         <v>9</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F225" s="1"/>
       <c r="G225" s="1"/>
@@ -6549,13 +6514,13 @@
         <v>10</v>
       </c>
       <c r="C226" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D226" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D226" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E226" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F226" s="1"/>
       <c r="G226" s="1"/>
@@ -6565,7 +6530,7 @@
         <v>0</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="D228" s="6"/>
       <c r="E228" s="2" t="s">
@@ -6579,17 +6544,17 @@
         <v>3</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D229" s="7"/>
       <c r="E229" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F229" s="7" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="G229" s="7" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="230" spans="2:7" x14ac:dyDescent="0.25">
@@ -6617,10 +6582,10 @@
         <v>1</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>14</v>
@@ -6635,17 +6600,17 @@
         <v>2</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F232" s="1"/>
       <c r="G232" s="1" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
     </row>
     <row r="233" spans="2:7" x14ac:dyDescent="0.25">
@@ -6653,17 +6618,17 @@
         <v>3</v>
       </c>
       <c r="C233" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D233" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="D233" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F233" s="1"/>
       <c r="G233" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="234" spans="2:7" x14ac:dyDescent="0.25">
@@ -6671,13 +6636,13 @@
         <v>4</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F234" s="1"/>
       <c r="G234" s="1"/>
@@ -6687,10 +6652,10 @@
         <v>5</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>21</v>
@@ -6703,10 +6668,10 @@
         <v>6</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>21</v>
@@ -6719,10 +6684,10 @@
         <v>7</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>21</v>
@@ -6735,10 +6700,10 @@
         <v>8</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>21</v>
@@ -6751,7 +6716,7 @@
         <v>0</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="D240" s="6"/>
       <c r="E240" s="2" t="s">
@@ -6765,7 +6730,7 @@
         <v>3</v>
       </c>
       <c r="C241" s="7" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="D241" s="7"/>
       <c r="E241" s="2" t="s">
@@ -6799,10 +6764,10 @@
         <v>1</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>14</v>
@@ -6817,17 +6782,17 @@
         <v>2</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F244" s="1"/>
       <c r="G244" s="1" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
     </row>
     <row r="245" spans="2:7" x14ac:dyDescent="0.25">
@@ -6835,17 +6800,17 @@
         <v>3</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F245" s="1"/>
       <c r="G245" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="246" spans="2:7" x14ac:dyDescent="0.25">
@@ -6853,10 +6818,10 @@
         <v>4</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>21</v>
@@ -6869,13 +6834,13 @@
         <v>5</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="F247" s="1"/>
       <c r="G247" s="1"/>
@@ -6885,13 +6850,13 @@
         <v>6</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="F248" s="1"/>
       <c r="G248" s="1"/>
@@ -6901,13 +6866,13 @@
         <v>7</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="F249" s="1"/>
       <c r="G249" s="1"/>
@@ -6917,13 +6882,13 @@
         <v>8</v>
       </c>
       <c r="C250" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D250" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D250" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E250" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F250" s="1"/>
       <c r="G250" s="1"/>
@@ -6933,7 +6898,7 @@
         <v>0</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="D252" s="6"/>
       <c r="E252" s="2" t="s">
@@ -6947,17 +6912,17 @@
         <v>3</v>
       </c>
       <c r="C253" s="7" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="D253" s="7"/>
       <c r="E253" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F253" s="7" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G253" s="7" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
     </row>
     <row r="254" spans="2:7" x14ac:dyDescent="0.25">
@@ -6985,10 +6950,10 @@
         <v>1</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>14</v>
@@ -7003,17 +6968,17 @@
         <v>2</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F256" s="1"/>
       <c r="G256" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="257" spans="2:7" x14ac:dyDescent="0.25">
@@ -7021,17 +6986,17 @@
         <v>3</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F257" s="1"/>
       <c r="G257" s="1" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
     </row>
     <row r="258" spans="2:7" x14ac:dyDescent="0.25">
@@ -7039,13 +7004,13 @@
         <v>4</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>290</v>
+        <v>245</v>
       </c>
       <c r="F258" s="1"/>
       <c r="G258" s="1"/>
@@ -7055,13 +7020,13 @@
         <v>5</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>290</v>
+        <v>245</v>
       </c>
       <c r="F259" s="1"/>
       <c r="G259" s="1"/>
@@ -7071,17 +7036,17 @@
         <v>6</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="F260" s="1"/>
       <c r="G260" s="1" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="261" spans="2:7" x14ac:dyDescent="0.25">
@@ -7089,17 +7054,17 @@
         <v>7</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F261" s="1"/>
       <c r="G261" s="1" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
     </row>
     <row r="262" spans="2:7" x14ac:dyDescent="0.25">
@@ -7107,13 +7072,13 @@
         <v>8</v>
       </c>
       <c r="C262" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D262" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D262" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E262" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F262" s="1"/>
       <c r="G262" s="1"/>
@@ -7123,7 +7088,7 @@
         <v>0</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="D264" s="6"/>
       <c r="E264" s="2" t="s">
@@ -7137,14 +7102,14 @@
         <v>3</v>
       </c>
       <c r="C265" s="7" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="D265" s="7"/>
       <c r="E265" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F265" s="7" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="G265" s="7"/>
     </row>
@@ -7173,10 +7138,10 @@
         <v>1</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>14</v>
@@ -7191,17 +7156,17 @@
         <v>2</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F268" s="1"/>
       <c r="G268" s="1" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
     </row>
     <row r="269" spans="2:7" x14ac:dyDescent="0.25">
@@ -7209,13 +7174,13 @@
         <v>3</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>290</v>
+        <v>245</v>
       </c>
       <c r="F269" s="1"/>
       <c r="G269" s="1"/>
@@ -7225,13 +7190,13 @@
         <v>4</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>290</v>
+        <v>245</v>
       </c>
       <c r="F270" s="1"/>
       <c r="G270" s="1"/>
@@ -7241,10 +7206,10 @@
         <v>5</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>21</v>
@@ -7257,17 +7222,17 @@
         <v>6</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F272" s="1"/>
       <c r="G272" s="1" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
     </row>
     <row r="273" spans="2:7" x14ac:dyDescent="0.25">
@@ -7275,13 +7240,13 @@
         <v>7</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F273" s="1"/>
       <c r="G273" s="1"/>
@@ -7291,13 +7256,13 @@
         <v>8</v>
       </c>
       <c r="C274" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D274" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D274" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E274" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F274" s="1"/>
       <c r="G274" s="1"/>
@@ -7307,13 +7272,13 @@
         <v>9</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F275" s="1"/>
       <c r="G275" s="1"/>
@@ -7323,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="D277" s="6"/>
       <c r="E277" s="2" t="s">
@@ -7337,7 +7302,7 @@
         <v>3</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="D278" s="7"/>
       <c r="E278" s="2" t="s">
@@ -7371,10 +7336,10 @@
         <v>1</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>14</v>
@@ -7389,17 +7354,17 @@
         <v>2</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F281" s="1"/>
       <c r="G281" s="1" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
     </row>
     <row r="282" spans="2:7" x14ac:dyDescent="0.25">
@@ -7407,10 +7372,10 @@
         <v>3</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>14</v>
@@ -7423,17 +7388,17 @@
         <v>4</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F283" s="1"/>
       <c r="G283" s="1" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
     </row>
     <row r="284" spans="2:7" x14ac:dyDescent="0.25">
@@ -7441,17 +7406,17 @@
         <v>5</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F284" s="1"/>
       <c r="G284" s="1" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
     </row>
     <row r="285" spans="2:7" x14ac:dyDescent="0.25">
@@ -7459,13 +7424,13 @@
         <v>6</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>290</v>
+        <v>245</v>
       </c>
       <c r="F285" s="1"/>
       <c r="G285" s="1"/>
@@ -7475,13 +7440,13 @@
         <v>7</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>290</v>
+        <v>245</v>
       </c>
       <c r="F286" s="1"/>
       <c r="G286" s="1"/>
@@ -7491,13 +7456,13 @@
         <v>8</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="F287" s="1"/>
       <c r="G287" s="1"/>
@@ -7507,13 +7472,13 @@
         <v>9</v>
       </c>
       <c r="C288" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D288" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D288" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E288" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F288" s="1"/>
       <c r="G288" s="1"/>
@@ -7523,7 +7488,7 @@
         <v>0</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="D290" s="6"/>
       <c r="E290" s="2" t="s">
@@ -7537,17 +7502,17 @@
         <v>3</v>
       </c>
       <c r="C291" s="7" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="D291" s="7"/>
       <c r="E291" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F291" s="7" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="G291" s="7" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="292" spans="2:7" x14ac:dyDescent="0.25">
@@ -7575,10 +7540,10 @@
         <v>1</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>14</v>
@@ -7593,17 +7558,17 @@
         <v>2</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F294" s="1"/>
       <c r="G294" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="295" spans="2:7" x14ac:dyDescent="0.25">
@@ -7611,17 +7576,17 @@
         <v>3</v>
       </c>
       <c r="C295" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D295" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="D295" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F295" s="1"/>
       <c r="G295" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="296" spans="2:7" x14ac:dyDescent="0.25">
@@ -7629,13 +7594,13 @@
         <v>4</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F296" s="1"/>
       <c r="G296" s="1"/>
@@ -7645,17 +7610,17 @@
         <v>5</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F297" s="1"/>
       <c r="G297" s="1" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
     </row>
     <row r="298" spans="2:7" x14ac:dyDescent="0.25">
@@ -7663,10 +7628,10 @@
         <v>6</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>14</v>
@@ -7679,13 +7644,13 @@
         <v>7</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F299" s="1"/>
       <c r="G299" s="1"/>
@@ -7695,13 +7660,13 @@
         <v>8</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F300" s="1"/>
       <c r="G300" s="1"/>
@@ -7711,13 +7676,13 @@
         <v>9</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>28</v>
+        <v>242</v>
       </c>
       <c r="F301" s="1"/>
       <c r="G301" s="1"/>
@@ -7727,7 +7692,7 @@
         <v>0</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="D303" s="6"/>
       <c r="E303" s="2" t="s">
@@ -7741,14 +7706,14 @@
         <v>3</v>
       </c>
       <c r="C304" s="7" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="D304" s="7"/>
       <c r="E304" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F304" s="7" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="G304" s="7"/>
     </row>
@@ -7777,13 +7742,13 @@
         <v>1</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="F306" s="1"/>
       <c r="G306" s="1" t="s">
@@ -7795,17 +7760,17 @@
         <v>2</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F307" s="1"/>
       <c r="G307" s="1" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
     </row>
     <row r="308" spans="2:7" x14ac:dyDescent="0.25">
@@ -7813,17 +7778,17 @@
         <v>3</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="F308" s="1"/>
       <c r="G308" s="1" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
     </row>
     <row r="309" spans="2:7" x14ac:dyDescent="0.25">
@@ -7831,13 +7796,13 @@
         <v>4</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F309" s="1"/>
       <c r="G309" s="1"/>
@@ -7847,13 +7812,13 @@
         <v>5</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F310" s="1"/>
       <c r="G310" s="1"/>
@@ -7863,10 +7828,10 @@
         <v>6</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>14</v>
@@ -7879,13 +7844,13 @@
         <v>7</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="F312" s="1"/>
       <c r="G312" s="1"/>
@@ -7895,13 +7860,13 @@
         <v>8</v>
       </c>
       <c r="C313" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D313" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D313" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E313" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F313" s="1"/>
       <c r="G313" s="1"/>
@@ -7911,13 +7876,13 @@
         <v>9</v>
       </c>
       <c r="C314" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D314" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D314" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="E314" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F314" s="1"/>
       <c r="G314" s="1"/>
@@ -7927,7 +7892,7 @@
         <v>0</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="D316" s="6"/>
       <c r="E316" s="2" t="s">
@@ -7941,17 +7906,17 @@
         <v>3</v>
       </c>
       <c r="C317" s="7" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="D317" s="7"/>
       <c r="E317" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F317" s="7" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="G317" s="7" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
     </row>
     <row r="318" spans="2:7" x14ac:dyDescent="0.25">
@@ -7979,13 +7944,13 @@
         <v>1</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="F319" s="1"/>
       <c r="G319" s="1" t="s">
@@ -7997,17 +7962,17 @@
         <v>2</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F320" s="1"/>
       <c r="G320" s="1" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
     </row>
     <row r="321" spans="2:7" x14ac:dyDescent="0.25">
@@ -8015,17 +7980,17 @@
         <v>3</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="F321" s="1"/>
       <c r="G321" s="1" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
     </row>
     <row r="322" spans="2:7" x14ac:dyDescent="0.25">
@@ -8033,17 +7998,17 @@
         <v>4</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="F322" s="1"/>
       <c r="G322" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="323" spans="2:7" x14ac:dyDescent="0.25">
@@ -8051,13 +8016,13 @@
         <v>5</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F323" s="1"/>
       <c r="G323" s="1"/>
@@ -8067,13 +8032,13 @@
         <v>6</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F324" s="1"/>
       <c r="G324" s="1"/>
@@ -8083,13 +8048,13 @@
         <v>7</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>408</v>
+        <v>242</v>
       </c>
       <c r="F325" s="1"/>
       <c r="G325" s="1"/>
@@ -8099,13 +8064,13 @@
         <v>8</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="F326" s="1"/>
       <c r="G326" s="1"/>
@@ -8115,13 +8080,13 @@
         <v>9</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F327" s="1"/>
       <c r="G327" s="1"/>
@@ -8131,10 +8096,10 @@
         <v>10</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>14</v>
@@ -8147,10 +8112,10 @@
         <v>11</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>14</v>
@@ -8163,10 +8128,10 @@
         <v>12</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>14</v>
@@ -8179,17 +8144,17 @@
         <v>13</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F331" s="1"/>
       <c r="G331" s="1" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
     </row>
     <row r="332" spans="2:7" x14ac:dyDescent="0.25">
@@ -8197,13 +8162,13 @@
         <v>14</v>
       </c>
       <c r="C332" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D332" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D332" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E332" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F332" s="1"/>
       <c r="G332" s="1"/>
@@ -8213,13 +8178,13 @@
         <v>15</v>
       </c>
       <c r="C333" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D333" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D333" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="E333" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F333" s="1"/>
       <c r="G333" s="1"/>
@@ -8229,7 +8194,7 @@
         <v>0</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="D335" s="6"/>
       <c r="E335" s="2" t="s">
@@ -8243,14 +8208,14 @@
         <v>3</v>
       </c>
       <c r="C336" s="7" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="D336" s="7"/>
       <c r="E336" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F336" s="7" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="G336" s="7"/>
     </row>
@@ -8279,13 +8244,13 @@
         <v>1</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="F338" s="1"/>
       <c r="G338" s="1" t="s">
@@ -8297,17 +8262,17 @@
         <v>2</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="F339" s="1"/>
       <c r="G339" s="1" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
     </row>
     <row r="340" spans="2:7" x14ac:dyDescent="0.25">
@@ -8315,13 +8280,13 @@
         <v>3</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="F340" s="1"/>
       <c r="G340" s="1"/>
@@ -8331,17 +8296,17 @@
         <v>4</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F341" s="1"/>
       <c r="G341" s="1" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
     </row>
     <row r="342" spans="2:7" x14ac:dyDescent="0.25">
@@ -8349,13 +8314,13 @@
         <v>5</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F342" s="1"/>
       <c r="G342" s="1"/>
@@ -8365,13 +8330,13 @@
         <v>6</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F343" s="1"/>
       <c r="G343" s="1"/>
@@ -8381,13 +8346,13 @@
         <v>7</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="F344" s="1"/>
       <c r="G344" s="1"/>
@@ -8397,13 +8362,13 @@
         <v>8</v>
       </c>
       <c r="C345" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D345" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D345" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E345" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F345" s="1"/>
       <c r="G345" s="1"/>
@@ -8413,7 +8378,7 @@
         <v>0</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="D347" s="6"/>
       <c r="E347" s="2" t="s">
@@ -8427,17 +8392,17 @@
         <v>3</v>
       </c>
       <c r="C348" s="7" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="D348" s="7"/>
       <c r="E348" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F348" s="7" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="G348" s="7" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
     </row>
     <row r="349" spans="2:7" x14ac:dyDescent="0.25">
@@ -8465,13 +8430,13 @@
         <v>1</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="F350" s="1"/>
       <c r="G350" s="1" t="s">
@@ -8483,17 +8448,17 @@
         <v>2</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="F351" s="1"/>
       <c r="G351" s="1" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
     </row>
     <row r="352" spans="2:7" x14ac:dyDescent="0.25">
@@ -8501,175 +8466,175 @@
         <v>3</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="F352" s="1"/>
       <c r="G352" s="1"/>
     </row>
-    <row r="353" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B353" s="1">
         <v>4</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="F353" s="1"/>
       <c r="G353" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="354" spans="2:8" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="354" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B354" s="1">
         <v>5</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F354" s="1"/>
       <c r="G354" s="1"/>
     </row>
-    <row r="355" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B355" s="1">
         <v>6</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>408</v>
+        <v>242</v>
       </c>
       <c r="F355" s="1"/>
       <c r="G355" s="1"/>
     </row>
-    <row r="356" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B356" s="1">
         <v>7</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F356" s="1"/>
       <c r="G356" s="1"/>
     </row>
-    <row r="357" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B357" s="1">
         <v>8</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F357" s="1"/>
       <c r="G357" s="1" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="358" spans="2:8" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="358" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B358" s="1">
         <v>9</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F358" s="1"/>
       <c r="G358" s="1" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="359" spans="2:8" x14ac:dyDescent="0.25">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="359" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B359" s="1">
         <v>10</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F359" s="1"/>
       <c r="G359" s="1" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="360" spans="2:8" x14ac:dyDescent="0.25">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="360" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B360" s="1">
         <v>11</v>
       </c>
       <c r="C360" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D360" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D360" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E360" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F360" s="1"/>
       <c r="G360" s="1"/>
     </row>
-    <row r="361" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B361" s="1">
         <v>12</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F361" s="1"/>
       <c r="G361" s="1"/>
     </row>
-    <row r="363" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B363" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C363" s="6" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="D363" s="6"/>
       <c r="E363" s="2" t="s">
@@ -8678,12 +8643,12 @@
       <c r="F363" s="7"/>
       <c r="G363" s="7"/>
     </row>
-    <row r="364" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B364" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C364" s="7" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="D364" s="7"/>
       <c r="E364" s="2" t="s">
@@ -8692,7 +8657,7 @@
       <c r="F364" s="7"/>
       <c r="G364" s="7"/>
     </row>
-    <row r="365" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B365" s="2" t="s">
         <v>7</v>
       </c>
@@ -8712,83 +8677,80 @@
         <v>12</v>
       </c>
     </row>
-    <row r="366" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B366" s="1">
         <v>1</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F366" s="1"/>
       <c r="G366" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="H366" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="367" spans="2:8" x14ac:dyDescent="0.25">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="367" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B367" s="1">
         <v>2</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F367" s="1">
         <v>50</v>
       </c>
       <c r="G367" s="1" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="368" spans="2:8" x14ac:dyDescent="0.25">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="368" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B368" s="1">
         <v>3</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="F368" s="1"/>
       <c r="G368" s="1" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="369" spans="2:8" x14ac:dyDescent="0.25">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="369" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B369" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="D369" s="1"/>
       <c r="E369" s="1"/>
       <c r="F369" s="1"/>
       <c r="G369" s="1"/>
     </row>
-    <row r="371" spans="2:8" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:9" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B371" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C371" s="8" t="s">
-        <v>570</v>
+        <v>546</v>
       </c>
       <c r="D371" s="8"/>
       <c r="E371" s="3" t="s">
@@ -8796,13 +8758,14 @@
       </c>
       <c r="F371" s="9"/>
       <c r="G371" s="9"/>
-    </row>
-    <row r="372" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I371"/>
+    </row>
+    <row r="372" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B372" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C372" s="9" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="D372" s="9"/>
       <c r="E372" s="3" t="s">
@@ -8810,8 +8773,9 @@
       </c>
       <c r="F372" s="9"/>
       <c r="G372" s="9"/>
-    </row>
-    <row r="373" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I372"/>
+    </row>
+    <row r="373" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B373" s="3" t="s">
         <v>7</v>
       </c>
@@ -8830,82 +8794,84 @@
       <c r="G373" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="374" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I373"/>
+    </row>
+    <row r="374" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B374" s="4">
         <v>1</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>572</v>
+        <v>548</v>
       </c>
       <c r="D374" s="4" t="s">
-        <v>574</v>
+        <v>550</v>
       </c>
       <c r="E374" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F374" s="4"/>
       <c r="G374" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="H374" s="5" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="375" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>586</v>
+      </c>
+      <c r="I374"/>
+    </row>
+    <row r="375" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B375" s="4">
         <v>2</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>573</v>
+        <v>549</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>575</v>
+        <v>551</v>
       </c>
       <c r="E375" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F375" s="4"/>
       <c r="G375" s="4" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="376" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>553</v>
+      </c>
+      <c r="I375"/>
+    </row>
+    <row r="376" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B376" s="4">
         <v>3</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>571</v>
+        <v>547</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>576</v>
+        <v>552</v>
       </c>
       <c r="E376" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F376" s="4"/>
       <c r="G376" s="4" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="377" spans="2:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>553</v>
+      </c>
+      <c r="I376"/>
+    </row>
+    <row r="377" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B377" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>579</v>
+        <v>554</v>
       </c>
       <c r="D377" s="4"/>
       <c r="E377" s="4"/>
       <c r="F377" s="4"/>
       <c r="G377" s="4"/>
-    </row>
-    <row r="379" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I377"/>
+    </row>
+    <row r="379" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B379" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C379" s="6" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="D379" s="6"/>
       <c r="E379" s="2" t="s">
@@ -8914,28 +8880,25 @@
       <c r="F379" s="7"/>
       <c r="G379" s="7"/>
     </row>
-    <row r="380" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B380" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C380" s="7" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="D380" s="7"/>
       <c r="E380" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F380" s="7" t="s">
-        <v>282</v>
+      <c r="F380" s="6" t="s">
+        <v>585</v>
       </c>
       <c r="G380" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="H380" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="381" spans="2:8" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="381" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B381" s="2" t="s">
         <v>7</v>
       </c>
@@ -8955,48 +8918,48 @@
         <v>12</v>
       </c>
     </row>
-    <row r="382" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B382" s="1">
         <v>1</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>580</v>
+        <v>555</v>
       </c>
       <c r="F382" s="1"/>
       <c r="G382" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="383" spans="2:8" x14ac:dyDescent="0.25">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="383" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B383" s="1">
         <v>2</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="F383" s="1"/>
       <c r="G383" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="384" spans="2:8" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="384" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B384" s="1">
         <v>3</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="D384" s="1" t="s">
         <v>17</v>
@@ -9014,19 +8977,19 @@
         <v>4</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F385" s="1">
         <v>120</v>
       </c>
       <c r="G385" s="1" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="386" spans="2:7" x14ac:dyDescent="0.25">
@@ -9034,19 +8997,19 @@
         <v>5</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F386" s="1">
         <v>100</v>
       </c>
       <c r="G386" s="1" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="387" spans="2:7" x14ac:dyDescent="0.25">
@@ -9054,17 +9017,17 @@
         <v>6</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>408</v>
+        <v>242</v>
       </c>
       <c r="F387" s="1"/>
       <c r="G387" s="1" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="388" spans="2:7" x14ac:dyDescent="0.25">
@@ -9072,19 +9035,19 @@
         <v>7</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F388" s="1">
         <v>255</v>
       </c>
       <c r="G388" s="1" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
     </row>
     <row r="389" spans="2:7" x14ac:dyDescent="0.25">
@@ -9092,13 +9055,13 @@
         <v>8</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F389" s="1">
         <v>30</v>
@@ -9110,13 +9073,13 @@
         <v>9</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F390" s="1">
         <v>255</v>
@@ -9128,13 +9091,13 @@
         <v>10</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F391" s="1">
         <v>255</v>
@@ -9146,13 +9109,13 @@
         <v>11</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F392" s="1"/>
       <c r="G392" s="1"/>
@@ -9162,13 +9125,13 @@
         <v>12</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F393" s="1"/>
       <c r="G393" s="1"/>
@@ -9178,17 +9141,17 @@
         <v>13</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="D394" s="1" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F394" s="1"/>
       <c r="G394" s="1" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
     </row>
     <row r="395" spans="2:7" x14ac:dyDescent="0.25">
@@ -9196,17 +9159,17 @@
         <v>14</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>585</v>
+        <v>560</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>484</v>
+        <v>238</v>
       </c>
       <c r="F395" s="1"/>
       <c r="G395" s="1" t="s">
-        <v>485</v>
+        <v>468</v>
       </c>
     </row>
     <row r="396" spans="2:7" x14ac:dyDescent="0.25">
@@ -9214,17 +9177,17 @@
         <v>15</v>
       </c>
       <c r="C396" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D396" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D396" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E396" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F396" s="1"/>
       <c r="G396" s="1" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="397" spans="2:7" x14ac:dyDescent="0.25">
@@ -9232,17 +9195,17 @@
         <v>16</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F397" s="1"/>
       <c r="G397" s="1" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="398" spans="2:7" x14ac:dyDescent="0.25">
@@ -9250,13 +9213,13 @@
         <v>17</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>486</v>
+        <v>469</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>487</v>
+        <v>470</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F398" s="1"/>
       <c r="G398" s="1"/>
@@ -9266,13 +9229,13 @@
         <v>18</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>581</v>
+        <v>556</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>583</v>
+        <v>558</v>
       </c>
       <c r="F399" s="1"/>
       <c r="G399" s="1"/>
@@ -9282,19 +9245,19 @@
         <v>12</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="D400" s="1"/>
       <c r="E400" s="1"/>
       <c r="F400" s="1"/>
       <c r="G400" s="1"/>
     </row>
-    <row r="402" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B402" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C402" s="6" t="s">
-        <v>489</v>
+        <v>472</v>
       </c>
       <c r="D402" s="6"/>
       <c r="E402" s="2" t="s">
@@ -9303,23 +9266,23 @@
       <c r="F402" s="7"/>
       <c r="G402" s="7"/>
     </row>
-    <row r="403" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B403" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C403" s="7" t="s">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="D403" s="7"/>
       <c r="E403" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F403" s="7" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="G403" s="7"/>
     </row>
-    <row r="404" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B404" s="2" t="s">
         <v>7</v>
       </c>
@@ -9339,15 +9302,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="405" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B405" s="1">
         <v>1</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>491</v>
+        <v>474</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>14</v>
@@ -9357,89 +9320,86 @@
         <v>15</v>
       </c>
     </row>
-    <row r="406" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B406" s="1">
         <v>2</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F406" s="1"/>
       <c r="G406" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="407" spans="2:8" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="407" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B407" s="1">
         <v>3</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>492</v>
+        <v>475</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>493</v>
+        <v>476</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F407" s="1">
         <v>50</v>
       </c>
       <c r="G407" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="H407" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="408" spans="2:8" x14ac:dyDescent="0.25">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="408" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B408" s="1">
         <v>4</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>496</v>
+        <v>477</v>
       </c>
       <c r="D408" s="1" t="s">
-        <v>497</v>
+        <v>478</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>408</v>
+        <v>242</v>
       </c>
       <c r="F408" s="1"/>
       <c r="G408" s="1" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="409" spans="2:8" x14ac:dyDescent="0.25">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="409" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B409" s="1">
         <v>5</v>
       </c>
       <c r="C409" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D409" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D409" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E409" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F409" s="1"/>
       <c r="G409" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="411" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="411" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B411" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C411" s="6" t="s">
-        <v>499</v>
+        <v>480</v>
       </c>
       <c r="D411" s="6"/>
       <c r="E411" s="2" t="s">
@@ -9448,12 +9408,12 @@
       <c r="F411" s="7"/>
       <c r="G411" s="7"/>
     </row>
-    <row r="412" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B412" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C412" s="7" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="D412" s="7"/>
       <c r="E412" s="2" t="s">
@@ -9462,7 +9422,7 @@
       <c r="F412" s="7"/>
       <c r="G412" s="7"/>
     </row>
-    <row r="413" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B413" s="2" t="s">
         <v>7</v>
       </c>
@@ -9482,15 +9442,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="414" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B414" s="1">
         <v>1</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>14</v>
@@ -9500,130 +9460,124 @@
         <v>15</v>
       </c>
     </row>
-    <row r="415" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B415" s="1">
         <v>2</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>500</v>
+        <v>481</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>501</v>
+        <v>482</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F415" s="1">
         <v>100</v>
       </c>
       <c r="G415" s="1" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="416" spans="2:8" x14ac:dyDescent="0.25">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="416" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B416" s="1">
         <v>3</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>503</v>
+        <v>484</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>504</v>
+        <v>485</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F416" s="1">
         <v>50</v>
       </c>
       <c r="G416" s="1" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="417" spans="2:8" x14ac:dyDescent="0.25">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="417" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B417" s="1">
         <v>4</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>507</v>
+        <v>488</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>408</v>
+        <v>242</v>
       </c>
       <c r="F417" s="1"/>
       <c r="G417" s="1" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="418" spans="2:8" x14ac:dyDescent="0.25">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="418" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B418" s="1">
         <v>5</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>510</v>
+        <v>491</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F418" s="1">
-        <v>10</v>
-      </c>
-      <c r="G418" s="1">
-        <v>2</v>
-      </c>
-      <c r="H418" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="419" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F418" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="G418" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="419" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B419" s="1">
         <v>6</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>85</v>
+        <v>269</v>
       </c>
       <c r="F419" s="1"/>
       <c r="G419" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="H419" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="420" spans="2:8" x14ac:dyDescent="0.25">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="420" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B420" s="1">
         <v>7</v>
       </c>
       <c r="C420" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D420" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D420" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E420" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F420" s="1"/>
       <c r="G420" s="1"/>
     </row>
-    <row r="422" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B422" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C422" s="6" t="s">
-        <v>514</v>
+        <v>492</v>
       </c>
       <c r="D422" s="6"/>
       <c r="E422" s="2" t="s">
@@ -9632,23 +9586,23 @@
       <c r="F422" s="7"/>
       <c r="G422" s="7"/>
     </row>
-    <row r="423" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B423" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C423" s="7" t="s">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="D423" s="7"/>
       <c r="E423" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F423" s="7" t="s">
-        <v>516</v>
+        <v>494</v>
       </c>
       <c r="G423" s="7"/>
     </row>
-    <row r="424" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B424" s="2" t="s">
         <v>7</v>
       </c>
@@ -9668,15 +9622,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="425" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B425" s="1">
         <v>1</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>517</v>
+        <v>495</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>14</v>
@@ -9686,110 +9640,104 @@
         <v>15</v>
       </c>
     </row>
-    <row r="426" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B426" s="1">
         <v>2</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>518</v>
+        <v>496</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F426" s="1"/>
       <c r="G426" s="1" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="427" spans="2:8" x14ac:dyDescent="0.25">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="427" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B427" s="1">
         <v>3</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>520</v>
+        <v>498</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>521</v>
+        <v>499</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F427" s="1"/>
       <c r="G427" s="1" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="428" spans="2:8" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="428" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B428" s="1">
         <v>4</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>524</v>
+        <v>502</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F428" s="1">
-        <v>18</v>
-      </c>
-      <c r="G428" s="1">
-        <v>2</v>
-      </c>
-      <c r="H428" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="429" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F428" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="G428" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="429" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B429" s="1">
         <v>5</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>526</v>
+        <v>504</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>527</v>
+        <v>505</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F429" s="1">
-        <v>18</v>
-      </c>
-      <c r="G429" s="1">
-        <v>2</v>
-      </c>
-      <c r="H429" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="430" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F429" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="G429" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="430" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B430" s="1">
         <v>6</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>529</v>
+        <v>507</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="F430" s="1"/>
       <c r="G430" s="1"/>
     </row>
-    <row r="432" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B432" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C432" s="6" t="s">
-        <v>530</v>
+        <v>508</v>
       </c>
       <c r="D432" s="6"/>
       <c r="E432" s="2" t="s">
@@ -9803,14 +9751,14 @@
         <v>3</v>
       </c>
       <c r="C433" s="7" t="s">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="D433" s="7"/>
       <c r="E433" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F433" s="7" t="s">
-        <v>532</v>
+        <v>510</v>
       </c>
       <c r="G433" s="7"/>
     </row>
@@ -9839,19 +9787,19 @@
         <v>1</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>533</v>
+        <v>511</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="F435" s="1">
         <v>24</v>
       </c>
       <c r="G435" s="1" t="s">
-        <v>534</v>
+        <v>512</v>
       </c>
     </row>
     <row r="436" spans="2:7" x14ac:dyDescent="0.25">
@@ -9859,17 +9807,17 @@
         <v>2</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>535</v>
+        <v>513</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>536</v>
+        <v>514</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F436" s="1"/>
       <c r="G436" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="437" spans="2:7" x14ac:dyDescent="0.25">
@@ -9877,16 +9825,16 @@
         <v>3</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>537</v>
+        <v>515</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>538</v>
+        <v>516</v>
       </c>
       <c r="G437" s="1"/>
     </row>
@@ -9895,13 +9843,13 @@
         <v>4</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>539</v>
+        <v>517</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>540</v>
+        <v>518</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F438" s="1">
         <v>500</v>
@@ -9910,136 +9858,6 @@
     </row>
   </sheetData>
   <mergeCells count="148">
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="F103:G103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="F104:G104"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="F116:G116"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="F141:G141"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="F130:G130"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="F167:G167"/>
-    <mergeCell ref="C168:D168"/>
-    <mergeCell ref="F168:G168"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="F175:G175"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="F142:G142"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="F153:G153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="F154:G154"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="F197:G197"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="F198:G198"/>
-    <mergeCell ref="C206:D206"/>
-    <mergeCell ref="F206:G206"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="F176:G176"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="F185:G185"/>
-    <mergeCell ref="C186:D186"/>
-    <mergeCell ref="F186:G186"/>
-    <mergeCell ref="C228:D228"/>
-    <mergeCell ref="F228:G228"/>
-    <mergeCell ref="C229:D229"/>
-    <mergeCell ref="F229:G229"/>
-    <mergeCell ref="C240:D240"/>
-    <mergeCell ref="F240:G240"/>
-    <mergeCell ref="C207:D207"/>
-    <mergeCell ref="F207:G207"/>
-    <mergeCell ref="C214:D214"/>
-    <mergeCell ref="F214:G214"/>
-    <mergeCell ref="C215:D215"/>
-    <mergeCell ref="F215:G215"/>
-    <mergeCell ref="C264:D264"/>
-    <mergeCell ref="F264:G264"/>
-    <mergeCell ref="C265:D265"/>
-    <mergeCell ref="F265:G265"/>
-    <mergeCell ref="C277:D277"/>
-    <mergeCell ref="F277:G277"/>
-    <mergeCell ref="C241:D241"/>
-    <mergeCell ref="F241:G241"/>
-    <mergeCell ref="C252:D252"/>
-    <mergeCell ref="F252:G252"/>
-    <mergeCell ref="C253:D253"/>
-    <mergeCell ref="F253:G253"/>
-    <mergeCell ref="C303:D303"/>
-    <mergeCell ref="F303:G303"/>
-    <mergeCell ref="C304:D304"/>
-    <mergeCell ref="F304:G304"/>
-    <mergeCell ref="C316:D316"/>
-    <mergeCell ref="F316:G316"/>
-    <mergeCell ref="C278:D278"/>
-    <mergeCell ref="F278:G278"/>
-    <mergeCell ref="C290:D290"/>
-    <mergeCell ref="F290:G290"/>
-    <mergeCell ref="C291:D291"/>
-    <mergeCell ref="F291:G291"/>
-    <mergeCell ref="C347:D347"/>
-    <mergeCell ref="F347:G347"/>
-    <mergeCell ref="C317:D317"/>
-    <mergeCell ref="F317:G317"/>
-    <mergeCell ref="C335:D335"/>
-    <mergeCell ref="F335:G335"/>
-    <mergeCell ref="C336:D336"/>
-    <mergeCell ref="F336:G336"/>
-    <mergeCell ref="C363:D363"/>
-    <mergeCell ref="F363:G363"/>
-    <mergeCell ref="C364:D364"/>
-    <mergeCell ref="F364:G364"/>
-    <mergeCell ref="C379:D379"/>
-    <mergeCell ref="F379:G379"/>
-    <mergeCell ref="C348:D348"/>
-    <mergeCell ref="F348:G348"/>
-    <mergeCell ref="C371:D371"/>
-    <mergeCell ref="F371:G371"/>
-    <mergeCell ref="C372:D372"/>
-    <mergeCell ref="F372:G372"/>
     <mergeCell ref="C380:D380"/>
     <mergeCell ref="F380:G380"/>
     <mergeCell ref="C402:D402"/>
@@ -10058,6 +9876,136 @@
     <mergeCell ref="F422:G422"/>
     <mergeCell ref="C423:D423"/>
     <mergeCell ref="F423:G423"/>
+    <mergeCell ref="C364:D364"/>
+    <mergeCell ref="F364:G364"/>
+    <mergeCell ref="C379:D379"/>
+    <mergeCell ref="F379:G379"/>
+    <mergeCell ref="C348:D348"/>
+    <mergeCell ref="F348:G348"/>
+    <mergeCell ref="C371:D371"/>
+    <mergeCell ref="F371:G371"/>
+    <mergeCell ref="C372:D372"/>
+    <mergeCell ref="F372:G372"/>
+    <mergeCell ref="C347:D347"/>
+    <mergeCell ref="F347:G347"/>
+    <mergeCell ref="C317:D317"/>
+    <mergeCell ref="F317:G317"/>
+    <mergeCell ref="C335:D335"/>
+    <mergeCell ref="F335:G335"/>
+    <mergeCell ref="C336:D336"/>
+    <mergeCell ref="F336:G336"/>
+    <mergeCell ref="C363:D363"/>
+    <mergeCell ref="F363:G363"/>
+    <mergeCell ref="C303:D303"/>
+    <mergeCell ref="F303:G303"/>
+    <mergeCell ref="C304:D304"/>
+    <mergeCell ref="F304:G304"/>
+    <mergeCell ref="C316:D316"/>
+    <mergeCell ref="F316:G316"/>
+    <mergeCell ref="C278:D278"/>
+    <mergeCell ref="F278:G278"/>
+    <mergeCell ref="C290:D290"/>
+    <mergeCell ref="F290:G290"/>
+    <mergeCell ref="C291:D291"/>
+    <mergeCell ref="F291:G291"/>
+    <mergeCell ref="C264:D264"/>
+    <mergeCell ref="F264:G264"/>
+    <mergeCell ref="C265:D265"/>
+    <mergeCell ref="F265:G265"/>
+    <mergeCell ref="C277:D277"/>
+    <mergeCell ref="F277:G277"/>
+    <mergeCell ref="C241:D241"/>
+    <mergeCell ref="F241:G241"/>
+    <mergeCell ref="C252:D252"/>
+    <mergeCell ref="F252:G252"/>
+    <mergeCell ref="C253:D253"/>
+    <mergeCell ref="F253:G253"/>
+    <mergeCell ref="C228:D228"/>
+    <mergeCell ref="F228:G228"/>
+    <mergeCell ref="C229:D229"/>
+    <mergeCell ref="F229:G229"/>
+    <mergeCell ref="C240:D240"/>
+    <mergeCell ref="F240:G240"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="F207:G207"/>
+    <mergeCell ref="C214:D214"/>
+    <mergeCell ref="F214:G214"/>
+    <mergeCell ref="C215:D215"/>
+    <mergeCell ref="F215:G215"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="F197:G197"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="F198:G198"/>
+    <mergeCell ref="C206:D206"/>
+    <mergeCell ref="F206:G206"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="F176:G176"/>
+    <mergeCell ref="C185:D185"/>
+    <mergeCell ref="F185:G185"/>
+    <mergeCell ref="C186:D186"/>
+    <mergeCell ref="F186:G186"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="F168:G168"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="F175:G175"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="F142:G142"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="F153:G153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="F154:G154"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="F141:G141"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="F167:G167"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="F116:G116"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:G14"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Document/專題/db_diagram.xlsx
+++ b/Document/專題/db_diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\RentalManagementPlatform\Document\專題\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A48D6FA-EA9C-4624-B35D-8FC88D5CEA69}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851A35FB-FA46-43E8-898F-7961CA8FB4D8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="592">
   <si>
     <t>表格名稱</t>
   </si>
@@ -751,9 +751,6 @@
   </si>
   <si>
     <t>角色代碼</t>
-  </si>
-  <si>
-    <t>VARCHAR</t>
   </si>
   <si>
     <t>唯一且 NOT NULL</t>
@@ -2554,10 +2551,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2935,31 +2932,31 @@
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="6"/>
+      <c r="D2" s="7"/>
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="7"/>
+      <c r="D3" s="6"/>
       <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="7"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
@@ -3031,7 +3028,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>22</v>
@@ -3051,7 +3048,7 @@
         <v>21</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>25</v>
@@ -3068,7 +3065,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
@@ -3086,7 +3083,7 @@
         <v>30</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
@@ -3104,7 +3101,7 @@
         <v>33</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
@@ -3115,31 +3112,31 @@
       <c r="B13" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="6"/>
+      <c r="D13" s="7"/>
       <c r="E13" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="7"/>
+      <c r="D14" s="6"/>
       <c r="E14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>591</v>
-      </c>
-      <c r="G14" s="7" t="s">
+      <c r="F14" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3246,7 +3243,7 @@
         <v>51</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -3262,7 +3259,7 @@
         <v>53</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
@@ -3280,7 +3277,7 @@
         <v>56</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
@@ -3364,7 +3361,7 @@
         <v>68</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1" t="s">
@@ -3382,7 +3379,7 @@
         <v>30</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -3391,29 +3388,29 @@
       <c r="B30" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D30" s="6"/>
+      <c r="D30" s="7"/>
       <c r="E30" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D31" s="7"/>
+      <c r="D31" s="6"/>
       <c r="E31" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
@@ -3458,17 +3455,17 @@
         <v>2</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>521</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
@@ -3482,7 +3479,7 @@
         <v>74</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
@@ -3500,7 +3497,7 @@
         <v>77</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1" t="s">
@@ -3518,7 +3515,7 @@
         <v>80</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1" t="s">
@@ -3536,7 +3533,7 @@
         <v>83</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1" t="s">
@@ -3548,13 +3545,13 @@
         <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>524</v>
-      </c>
       <c r="E39" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -3564,17 +3561,17 @@
         <v>8</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>526</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
@@ -3588,7 +3585,7 @@
         <v>86</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1" t="s">
@@ -3600,13 +3597,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -3616,13 +3613,13 @@
         <v>11</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -3650,17 +3647,17 @@
         <v>13</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>532</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>533</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
@@ -3674,7 +3671,7 @@
         <v>30</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1" t="s">
@@ -3692,7 +3689,7 @@
         <v>34</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -3701,31 +3698,31 @@
       <c r="B49" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D49" s="6"/>
+      <c r="D49" s="7"/>
       <c r="E49" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D50" s="7"/>
+      <c r="D50" s="6"/>
       <c r="E50" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="F50" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="G50" s="7"/>
+      <c r="G50" s="6"/>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B51" s="2" t="s">
@@ -3794,7 +3791,7 @@
         <v>98</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1" t="s">
@@ -3812,7 +3809,7 @@
         <v>101</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1" t="s">
@@ -3823,29 +3820,29 @@
       <c r="B57" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D57" s="6"/>
+      <c r="D57" s="7"/>
       <c r="E57" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D58" s="7"/>
+      <c r="D58" s="6"/>
       <c r="E58" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B59" s="2" t="s">
@@ -3896,7 +3893,7 @@
         <v>107</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1" t="s">
@@ -3907,29 +3904,29 @@
       <c r="B63" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C63" s="6" t="s">
-        <v>571</v>
-      </c>
-      <c r="D63" s="6"/>
+      <c r="C63" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="D63" s="7"/>
       <c r="E63" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F63" s="7"/>
-      <c r="G63" s="7"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D64" s="7"/>
+      <c r="D64" s="6"/>
       <c r="E64" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F64" s="7"/>
-      <c r="G64" s="7"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B65" s="2" t="s">
@@ -3980,7 +3977,7 @@
         <v>110</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1" t="s">
@@ -3998,7 +3995,7 @@
         <v>113</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
@@ -4014,7 +4011,7 @@
         <v>115</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1" t="s">
@@ -4026,17 +4023,17 @@
         <v>5</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I70"/>
     </row>
@@ -4045,17 +4042,17 @@
         <v>6</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D71" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="E71" s="4" t="s">
         <v>562</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>563</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I71"/>
     </row>
@@ -4064,17 +4061,17 @@
         <v>7</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="I72"/>
     </row>
@@ -4083,17 +4080,17 @@
         <v>8</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="I73"/>
     </row>
@@ -4108,7 +4105,7 @@
         <v>118</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1" t="s">
@@ -4144,7 +4141,7 @@
         <v>124</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
@@ -4178,7 +4175,7 @@
         <v>129</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
@@ -4188,7 +4185,7 @@
         <v>0</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D80" s="8"/>
       <c r="E80" s="3" t="s">
@@ -4203,14 +4200,14 @@
         <v>3</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G81" s="9" t="s">
         <v>39</v>
@@ -4243,7 +4240,7 @@
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>132</v>
@@ -4281,17 +4278,17 @@
         <v>3</v>
       </c>
       <c r="C85" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>567</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>568</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="I85"/>
     </row>
@@ -4299,31 +4296,31 @@
       <c r="B87" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C87" s="6" t="s">
+      <c r="C87" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D87" s="6"/>
+      <c r="D87" s="7"/>
       <c r="E87" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F87" s="7"/>
-      <c r="G87" s="7"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="6"/>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B88" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C88" s="7" t="s">
+      <c r="C88" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D88" s="7"/>
+      <c r="D88" s="6"/>
       <c r="E88" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F88" s="7" t="s">
+      <c r="F88" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G88" s="7" t="s">
+      <c r="G88" s="6" t="s">
         <v>39</v>
       </c>
     </row>
@@ -4412,7 +4409,7 @@
         <v>30</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
@@ -4428,7 +4425,7 @@
         <v>135</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
@@ -4437,31 +4434,31 @@
       <c r="B96" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C96" s="6" t="s">
+      <c r="C96" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="D96" s="6"/>
+      <c r="D96" s="7"/>
       <c r="E96" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F96" s="7"/>
-      <c r="G96" s="7"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="6"/>
     </row>
     <row r="97" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B97" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C97" s="7" t="s">
+      <c r="C97" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D97" s="7"/>
+      <c r="D97" s="6"/>
       <c r="E97" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F97" s="7" t="s">
+      <c r="F97" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="G97" s="7"/>
+      <c r="G97" s="6"/>
     </row>
     <row r="98" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B98" s="2" t="s">
@@ -4530,7 +4527,7 @@
         <v>140</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F101" s="1"/>
       <c r="G101" s="1" t="s">
@@ -4563,7 +4560,7 @@
         <v>5</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G104" s="9" t="s">
         <v>144</v>
@@ -4612,17 +4609,17 @@
         <v>2</v>
       </c>
       <c r="C107" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="D107" s="4" t="s">
         <v>537</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>538</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I107"/>
     </row>
@@ -4634,7 +4631,7 @@
         <v>37</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>14</v>
@@ -4659,7 +4656,7 @@
       </c>
       <c r="F109" s="4"/>
       <c r="G109" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="110" spans="2:9" x14ac:dyDescent="0.25">
@@ -4677,7 +4674,7 @@
       </c>
       <c r="F110" s="4"/>
       <c r="G110" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="111" spans="2:9" x14ac:dyDescent="0.25">
@@ -4695,7 +4692,7 @@
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="112" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4703,17 +4700,17 @@
         <v>7</v>
       </c>
       <c r="C112" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="D112" s="4" t="s">
         <v>540</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>541</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I112"/>
     </row>
@@ -4728,7 +4725,7 @@
         <v>152</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F113" s="4"/>
       <c r="G113" s="4" t="s">
@@ -4746,7 +4743,7 @@
         <v>30</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
@@ -4755,31 +4752,31 @@
       <c r="B116" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C116" s="6" t="s">
+      <c r="C116" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="D116" s="6"/>
+      <c r="D116" s="7"/>
       <c r="E116" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F116" s="7"/>
-      <c r="G116" s="7"/>
+      <c r="F116" s="6"/>
+      <c r="G116" s="6"/>
     </row>
     <row r="117" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B117" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C117" s="7" t="s">
+      <c r="C117" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="D117" s="7"/>
+      <c r="D117" s="6"/>
       <c r="E117" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F117" s="7" t="s">
+      <c r="F117" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="G117" s="7"/>
+      <c r="G117" s="6"/>
     </row>
     <row r="118" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B118" s="2" t="s">
@@ -4866,7 +4863,7 @@
         <v>161</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F122" s="1"/>
       <c r="G122" s="1" t="s">
@@ -4884,7 +4881,7 @@
         <v>164</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
@@ -4900,7 +4897,7 @@
         <v>166</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
@@ -4916,7 +4913,7 @@
         <v>168</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
@@ -4932,7 +4929,7 @@
         <v>169</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F126" s="1"/>
       <c r="G126" s="1" t="s">
@@ -4950,7 +4947,7 @@
         <v>30</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>
@@ -4959,31 +4956,31 @@
       <c r="B129" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C129" s="6" t="s">
+      <c r="C129" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="D129" s="6"/>
+      <c r="D129" s="7"/>
       <c r="E129" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F129" s="7"/>
-      <c r="G129" s="7"/>
+      <c r="F129" s="6"/>
+      <c r="G129" s="6"/>
     </row>
     <row r="130" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B130" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C130" s="7" t="s">
+      <c r="C130" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D130" s="7"/>
+      <c r="D130" s="6"/>
       <c r="E130" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F130" s="7" t="s">
+      <c r="F130" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="G130" s="7"/>
+      <c r="G130" s="6"/>
     </row>
     <row r="131" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B131" s="2" t="s">
@@ -5052,7 +5049,7 @@
         <v>177</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
@@ -5068,7 +5065,7 @@
         <v>179</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F135" s="1"/>
       <c r="G135" s="1" t="s">
@@ -5086,7 +5083,7 @@
         <v>182</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F136" s="1"/>
       <c r="G136" s="1" t="s">
@@ -5104,7 +5101,7 @@
         <v>185</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
@@ -5120,7 +5117,7 @@
         <v>187</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F138" s="1"/>
       <c r="G138" s="1"/>
@@ -5136,7 +5133,7 @@
         <v>30</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
@@ -5145,31 +5142,31 @@
       <c r="B141" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C141" s="6" t="s">
+      <c r="C141" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D141" s="6"/>
+      <c r="D141" s="7"/>
       <c r="E141" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F141" s="7"/>
-      <c r="G141" s="7"/>
+      <c r="F141" s="6"/>
+      <c r="G141" s="6"/>
     </row>
     <row r="142" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B142" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C142" s="7" t="s">
+      <c r="C142" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="D142" s="7"/>
+      <c r="D142" s="6"/>
       <c r="E142" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F142" s="6" t="s">
-        <v>589</v>
-      </c>
-      <c r="G142" s="7" t="s">
+      <c r="F142" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="G142" s="6" t="s">
         <v>196</v>
       </c>
     </row>
@@ -5294,7 +5291,7 @@
         <v>203</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F149" s="1"/>
       <c r="G149" s="1" t="s">
@@ -5330,7 +5327,7 @@
         <v>30</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F151" s="1"/>
       <c r="G151" s="1"/>
@@ -5339,31 +5336,31 @@
       <c r="B153" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C153" s="6" t="s">
+      <c r="C153" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="D153" s="6"/>
+      <c r="D153" s="7"/>
       <c r="E153" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F153" s="7"/>
-      <c r="G153" s="7"/>
+      <c r="F153" s="6"/>
+      <c r="G153" s="6"/>
     </row>
     <row r="154" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B154" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C154" s="7" t="s">
+      <c r="C154" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D154" s="7"/>
+      <c r="D154" s="6"/>
       <c r="E154" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F154" s="7" t="s">
+      <c r="F154" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="G154" s="7" t="s">
+      <c r="G154" s="6" t="s">
         <v>196</v>
       </c>
     </row>
@@ -5452,7 +5449,7 @@
         <v>211</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="1" t="s">
@@ -5470,7 +5467,7 @@
         <v>213</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F160" s="1"/>
       <c r="G160" s="1" t="s">
@@ -5524,7 +5521,7 @@
         <v>221</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F163" s="1"/>
       <c r="G163" s="1" t="s">
@@ -5542,7 +5539,7 @@
         <v>30</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F164" s="1"/>
       <c r="G164" s="1"/>
@@ -5558,7 +5555,7 @@
         <v>34</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F165" s="1"/>
       <c r="G165" s="1"/>
@@ -5567,31 +5564,31 @@
       <c r="B167" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C167" s="6" t="s">
+      <c r="C167" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D167" s="6"/>
+      <c r="D167" s="7"/>
       <c r="E167" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F167" s="7"/>
-      <c r="G167" s="7"/>
+      <c r="F167" s="6"/>
+      <c r="G167" s="6"/>
     </row>
     <row r="168" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B168" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C168" s="7" t="s">
+      <c r="C168" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="D168" s="7"/>
+      <c r="D168" s="6"/>
       <c r="E168" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F168" s="7" t="s">
+      <c r="F168" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="G168" s="7"/>
+      <c r="G168" s="6"/>
     </row>
     <row r="169" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B169" s="2" t="s">
@@ -5660,7 +5657,7 @@
         <v>228</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F172" s="1"/>
       <c r="G172" s="1" t="s">
@@ -5689,29 +5686,29 @@
       <c r="B175" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C175" s="6" t="s">
+      <c r="C175" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="D175" s="6"/>
+      <c r="D175" s="7"/>
       <c r="E175" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F175" s="7"/>
-      <c r="G175" s="7"/>
+      <c r="F175" s="6"/>
+      <c r="G175" s="6"/>
     </row>
     <row r="176" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B176" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C176" s="7" t="s">
+      <c r="C176" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="D176" s="7"/>
+      <c r="D176" s="6"/>
       <c r="E176" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F176" s="7"/>
-      <c r="G176" s="7"/>
+      <c r="F176" s="6"/>
+      <c r="G176" s="6"/>
     </row>
     <row r="177" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B177" s="2" t="s">
@@ -5748,7 +5745,7 @@
       </c>
       <c r="F178" s="1"/>
       <c r="G178" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="179" spans="2:7" x14ac:dyDescent="0.25">
@@ -5762,13 +5759,13 @@
         <v>237</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F179" s="1">
         <v>50</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="180" spans="2:7" x14ac:dyDescent="0.25">
@@ -5776,19 +5773,19 @@
         <v>3</v>
       </c>
       <c r="C180" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D180" s="1" t="s">
+      <c r="E180" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="E180" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="F180" s="1">
         <v>100</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="181" spans="2:7" x14ac:dyDescent="0.25">
@@ -5799,10 +5796,10 @@
         <v>114</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F181" s="1">
         <v>500</v>
@@ -5820,11 +5817,11 @@
         <v>30</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F182" s="1"/>
       <c r="G182" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="183" spans="2:7" x14ac:dyDescent="0.25">
@@ -5838,40 +5835,40 @@
         <v>33</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F183" s="1"/>
       <c r="G183" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="185" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B185" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C185" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="D185" s="6"/>
+      <c r="C185" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D185" s="7"/>
       <c r="E185" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F185" s="7"/>
-      <c r="G185" s="7"/>
+      <c r="F185" s="6"/>
+      <c r="G185" s="6"/>
     </row>
     <row r="186" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B186" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C186" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D186" s="7"/>
+      <c r="C186" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="D186" s="6"/>
       <c r="E186" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F186" s="7"/>
-      <c r="G186" s="7"/>
+      <c r="F186" s="6"/>
+      <c r="G186" s="6"/>
     </row>
     <row r="187" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B187" s="2" t="s">
@@ -5898,17 +5895,17 @@
         <v>1</v>
       </c>
       <c r="C188" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F188" s="1"/>
       <c r="G188" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="189" spans="2:7" x14ac:dyDescent="0.25">
@@ -5916,19 +5913,19 @@
         <v>2</v>
       </c>
       <c r="C189" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="D189" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="E189" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F189" s="1">
         <v>100</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="190" spans="2:7" x14ac:dyDescent="0.25">
@@ -5936,19 +5933,19 @@
         <v>3</v>
       </c>
       <c r="C190" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="D190" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="E190" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F190" s="1">
         <v>200</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="191" spans="2:7" x14ac:dyDescent="0.25">
@@ -5956,19 +5953,19 @@
         <v>4</v>
       </c>
       <c r="C191" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="D191" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="E191" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F191" s="1">
         <v>50</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="192" spans="2:7" x14ac:dyDescent="0.25">
@@ -5976,19 +5973,19 @@
         <v>5</v>
       </c>
       <c r="C192" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D192" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="E192" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F192" s="1">
         <v>50</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="193" spans="2:7" x14ac:dyDescent="0.25">
@@ -5999,10 +5996,10 @@
         <v>114</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F193" s="1">
         <v>500</v>
@@ -6020,11 +6017,11 @@
         <v>30</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F194" s="1"/>
       <c r="G194" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="195" spans="2:7" x14ac:dyDescent="0.25">
@@ -6038,43 +6035,43 @@
         <v>33</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F195" s="1"/>
       <c r="G195" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="197" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B197" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C197" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="D197" s="6"/>
+      <c r="C197" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D197" s="7"/>
       <c r="E197" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F197" s="7"/>
-      <c r="G197" s="7"/>
+      <c r="F197" s="6"/>
+      <c r="G197" s="6"/>
     </row>
     <row r="198" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B198" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C198" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="D198" s="7"/>
+      <c r="C198" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="D198" s="6"/>
       <c r="E198" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F198" s="7" t="s">
+      <c r="F198" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="G198" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="G198" s="7" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="199" spans="2:7" x14ac:dyDescent="0.25">
@@ -6102,17 +6099,17 @@
         <v>1</v>
       </c>
       <c r="C200" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F200" s="1"/>
       <c r="G200" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="201" spans="2:7" x14ac:dyDescent="0.25">
@@ -6130,7 +6127,7 @@
       </c>
       <c r="F201" s="1"/>
       <c r="G201" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="202" spans="2:7" x14ac:dyDescent="0.25">
@@ -6138,17 +6135,17 @@
         <v>3</v>
       </c>
       <c r="C202" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F202" s="1"/>
       <c r="G202" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="203" spans="2:7" x14ac:dyDescent="0.25">
@@ -6156,17 +6153,17 @@
         <v>4</v>
       </c>
       <c r="C203" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D203" s="1" t="s">
+      <c r="E203" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="F203" s="1"/>
       <c r="G203" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="204" spans="2:7" x14ac:dyDescent="0.25">
@@ -6180,43 +6177,43 @@
         <v>30</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F204" s="1"/>
       <c r="G204" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="206" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C206" s="6" t="s">
-        <v>536</v>
-      </c>
-      <c r="D206" s="6"/>
+      <c r="C206" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="D206" s="7"/>
       <c r="E206" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F206" s="7"/>
-      <c r="G206" s="7"/>
+      <c r="F206" s="6"/>
+      <c r="G206" s="6"/>
     </row>
     <row r="207" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B207" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C207" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="D207" s="7"/>
+      <c r="C207" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="D207" s="6"/>
       <c r="E207" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F207" s="7" t="s">
+      <c r="F207" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="G207" s="6" t="s">
         <v>272</v>
-      </c>
-      <c r="G207" s="7" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="208" spans="2:7" x14ac:dyDescent="0.25">
@@ -6244,10 +6241,10 @@
         <v>1</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>14</v>
@@ -6290,7 +6287,7 @@
       </c>
       <c r="F211" s="1"/>
       <c r="G211" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="212" spans="2:7" x14ac:dyDescent="0.25">
@@ -6304,42 +6301,42 @@
         <v>30</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F212" s="1"/>
       <c r="G212" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="214" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B214" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C214" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="D214" s="6"/>
+      <c r="C214" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D214" s="7"/>
       <c r="E214" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F214" s="7"/>
-      <c r="G214" s="7"/>
+      <c r="F214" s="6"/>
+      <c r="G214" s="6"/>
     </row>
     <row r="215" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B215" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C215" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="D215" s="7"/>
+      <c r="C215" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="D215" s="6"/>
       <c r="E215" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F215" s="7" t="s">
+      <c r="F215" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="G215" s="7"/>
+      <c r="G215" s="6"/>
     </row>
     <row r="216" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B216" s="2" t="s">
@@ -6366,10 +6363,10 @@
         <v>1</v>
       </c>
       <c r="C217" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D217" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="D217" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>14</v>
@@ -6402,13 +6399,13 @@
         <v>3</v>
       </c>
       <c r="C219" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D219" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D219" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="E219" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F219" s="1"/>
       <c r="G219" s="1"/>
@@ -6418,13 +6415,13 @@
         <v>4</v>
       </c>
       <c r="C220" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D220" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="E220" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F220" s="1"/>
       <c r="G220" s="1"/>
@@ -6434,10 +6431,10 @@
         <v>5</v>
       </c>
       <c r="C221" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D221" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>21</v>
@@ -6450,10 +6447,10 @@
         <v>6</v>
       </c>
       <c r="C222" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>21</v>
@@ -6466,10 +6463,10 @@
         <v>7</v>
       </c>
       <c r="C223" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D223" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>21</v>
@@ -6485,10 +6482,10 @@
         <v>163</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F224" s="1"/>
       <c r="G224" s="1"/>
@@ -6504,7 +6501,7 @@
         <v>193</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F225" s="1"/>
       <c r="G225" s="1"/>
@@ -6520,7 +6517,7 @@
         <v>30</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F226" s="1"/>
       <c r="G226" s="1"/>
@@ -6529,31 +6526,31 @@
       <c r="B228" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C228" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="D228" s="6"/>
+      <c r="C228" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="D228" s="7"/>
       <c r="E228" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F228" s="7"/>
-      <c r="G228" s="7"/>
+      <c r="F228" s="6"/>
+      <c r="G228" s="6"/>
     </row>
     <row r="229" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B229" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C229" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="D229" s="7"/>
+      <c r="C229" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="D229" s="6"/>
       <c r="E229" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F229" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="G229" s="7" t="s">
+      <c r="F229" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="G229" s="6" t="s">
         <v>144</v>
       </c>
     </row>
@@ -6582,10 +6579,10 @@
         <v>1</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>14</v>
@@ -6600,17 +6597,17 @@
         <v>2</v>
       </c>
       <c r="C232" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D232" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="D232" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F232" s="1"/>
       <c r="G232" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="233" spans="2:7" x14ac:dyDescent="0.25">
@@ -6642,7 +6639,7 @@
         <v>168</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F234" s="1"/>
       <c r="G234" s="1"/>
@@ -6652,10 +6649,10 @@
         <v>5</v>
       </c>
       <c r="C235" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D235" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>21</v>
@@ -6668,10 +6665,10 @@
         <v>6</v>
       </c>
       <c r="C236" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D236" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="D236" s="1" t="s">
-        <v>295</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>21</v>
@@ -6684,10 +6681,10 @@
         <v>7</v>
       </c>
       <c r="C237" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D237" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>21</v>
@@ -6700,10 +6697,10 @@
         <v>8</v>
       </c>
       <c r="C238" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D238" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="D238" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>21</v>
@@ -6715,29 +6712,29 @@
       <c r="B240" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C240" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="D240" s="6"/>
+      <c r="C240" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D240" s="7"/>
       <c r="E240" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F240" s="7"/>
-      <c r="G240" s="7"/>
+      <c r="F240" s="6"/>
+      <c r="G240" s="6"/>
     </row>
     <row r="241" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B241" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C241" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="D241" s="7"/>
+      <c r="C241" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D241" s="6"/>
       <c r="E241" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F241" s="7"/>
-      <c r="G241" s="7"/>
+      <c r="F241" s="6"/>
+      <c r="G241" s="6"/>
     </row>
     <row r="242" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B242" s="2" t="s">
@@ -6764,10 +6761,10 @@
         <v>1</v>
       </c>
       <c r="C243" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D243" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>298</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>14</v>
@@ -6782,17 +6779,17 @@
         <v>2</v>
       </c>
       <c r="C244" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D244" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="D244" s="1" t="s">
-        <v>300</v>
-      </c>
       <c r="E244" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F244" s="1"/>
       <c r="G244" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="245" spans="2:7" x14ac:dyDescent="0.25">
@@ -6800,10 +6797,10 @@
         <v>3</v>
       </c>
       <c r="C245" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D245" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="D245" s="1" t="s">
-        <v>303</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>21</v>
@@ -6818,10 +6815,10 @@
         <v>4</v>
       </c>
       <c r="C246" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D246" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>305</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>21</v>
@@ -6834,13 +6831,13 @@
         <v>5</v>
       </c>
       <c r="C247" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D247" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="D247" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="E247" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F247" s="1"/>
       <c r="G247" s="1"/>
@@ -6850,13 +6847,13 @@
         <v>6</v>
       </c>
       <c r="C248" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D248" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D248" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="E248" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F248" s="1"/>
       <c r="G248" s="1"/>
@@ -6866,13 +6863,13 @@
         <v>7</v>
       </c>
       <c r="C249" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D249" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="D249" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="E249" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F249" s="1"/>
       <c r="G249" s="1"/>
@@ -6888,7 +6885,7 @@
         <v>30</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F250" s="1"/>
       <c r="G250" s="1"/>
@@ -6897,32 +6894,32 @@
       <c r="B252" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C252" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="D252" s="6"/>
+      <c r="C252" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D252" s="7"/>
       <c r="E252" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F252" s="7"/>
-      <c r="G252" s="7"/>
+      <c r="F252" s="6"/>
+      <c r="G252" s="6"/>
     </row>
     <row r="253" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B253" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C253" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D253" s="7"/>
+      <c r="C253" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="D253" s="6"/>
       <c r="E253" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F253" s="7" t="s">
+      <c r="F253" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="G253" s="7" t="s">
-        <v>314</v>
+      <c r="G253" s="6" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="254" spans="2:7" x14ac:dyDescent="0.25">
@@ -6950,10 +6947,10 @@
         <v>1</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>14</v>
@@ -6986,17 +6983,17 @@
         <v>3</v>
       </c>
       <c r="C257" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D257" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>298</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F257" s="1"/>
       <c r="G257" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="258" spans="2:7" x14ac:dyDescent="0.25">
@@ -7004,13 +7001,13 @@
         <v>4</v>
       </c>
       <c r="C258" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D258" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="D258" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="E258" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F258" s="1"/>
       <c r="G258" s="1"/>
@@ -7020,13 +7017,13 @@
         <v>5</v>
       </c>
       <c r="C259" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D259" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="D259" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="E259" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F259" s="1"/>
       <c r="G259" s="1"/>
@@ -7036,17 +7033,17 @@
         <v>6</v>
       </c>
       <c r="C260" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D260" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="D260" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="E260" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F260" s="1"/>
       <c r="G260" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="261" spans="2:7" x14ac:dyDescent="0.25">
@@ -7060,11 +7057,11 @@
         <v>193</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F261" s="1"/>
       <c r="G261" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="262" spans="2:7" x14ac:dyDescent="0.25">
@@ -7078,7 +7075,7 @@
         <v>30</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F262" s="1"/>
       <c r="G262" s="1"/>
@@ -7087,31 +7084,31 @@
       <c r="B264" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C264" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="D264" s="6"/>
+      <c r="C264" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="D264" s="7"/>
       <c r="E264" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F264" s="7"/>
-      <c r="G264" s="7"/>
+      <c r="F264" s="6"/>
+      <c r="G264" s="6"/>
     </row>
     <row r="265" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B265" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C265" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="D265" s="7"/>
+      <c r="C265" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="D265" s="6"/>
       <c r="E265" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F265" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="G265" s="7"/>
+      <c r="F265" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="G265" s="6"/>
     </row>
     <row r="266" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B266" s="2" t="s">
@@ -7138,10 +7135,10 @@
         <v>1</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>14</v>
@@ -7156,17 +7153,17 @@
         <v>2</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F268" s="1"/>
       <c r="G268" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="269" spans="2:7" x14ac:dyDescent="0.25">
@@ -7174,13 +7171,13 @@
         <v>3</v>
       </c>
       <c r="C269" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D269" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="D269" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="E269" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F269" s="1"/>
       <c r="G269" s="1"/>
@@ -7190,13 +7187,13 @@
         <v>4</v>
       </c>
       <c r="C270" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D270" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="D270" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="E270" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F270" s="1"/>
       <c r="G270" s="1"/>
@@ -7209,7 +7206,7 @@
         <v>157</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>21</v>
@@ -7222,17 +7219,17 @@
         <v>6</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>169</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F272" s="1"/>
       <c r="G272" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="273" spans="2:7" x14ac:dyDescent="0.25">
@@ -7243,10 +7240,10 @@
         <v>163</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F273" s="1"/>
       <c r="G273" s="1"/>
@@ -7262,7 +7259,7 @@
         <v>30</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F274" s="1"/>
       <c r="G274" s="1"/>
@@ -7272,13 +7269,13 @@
         <v>9</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F275" s="1"/>
       <c r="G275" s="1"/>
@@ -7287,29 +7284,29 @@
       <c r="B277" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C277" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="D277" s="6"/>
+      <c r="C277" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="D277" s="7"/>
       <c r="E277" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F277" s="7"/>
-      <c r="G277" s="7"/>
+      <c r="F277" s="6"/>
+      <c r="G277" s="6"/>
     </row>
     <row r="278" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B278" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C278" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="D278" s="7"/>
+      <c r="C278" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D278" s="6"/>
       <c r="E278" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F278" s="7"/>
-      <c r="G278" s="7"/>
+      <c r="F278" s="6"/>
+      <c r="G278" s="6"/>
     </row>
     <row r="279" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B279" s="2" t="s">
@@ -7336,10 +7333,10 @@
         <v>1</v>
       </c>
       <c r="C280" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D280" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>14</v>
@@ -7354,17 +7351,17 @@
         <v>2</v>
       </c>
       <c r="C281" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D281" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>342</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F281" s="1"/>
       <c r="G281" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="282" spans="2:7" x14ac:dyDescent="0.25">
@@ -7372,10 +7369,10 @@
         <v>3</v>
       </c>
       <c r="C282" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D282" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>14</v>
@@ -7388,17 +7385,17 @@
         <v>4</v>
       </c>
       <c r="C283" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D283" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F283" s="1"/>
       <c r="G283" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="284" spans="2:7" x14ac:dyDescent="0.25">
@@ -7406,17 +7403,17 @@
         <v>5</v>
       </c>
       <c r="C284" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D284" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="D284" s="1" t="s">
-        <v>350</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F284" s="1"/>
       <c r="G284" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="285" spans="2:7" x14ac:dyDescent="0.25">
@@ -7424,13 +7421,13 @@
         <v>6</v>
       </c>
       <c r="C285" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D285" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="D285" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="E285" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F285" s="1"/>
       <c r="G285" s="1"/>
@@ -7440,13 +7437,13 @@
         <v>7</v>
       </c>
       <c r="C286" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D286" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="D286" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="E286" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F286" s="1"/>
       <c r="G286" s="1"/>
@@ -7456,13 +7453,13 @@
         <v>8</v>
       </c>
       <c r="C287" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D287" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="D287" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="E287" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F287" s="1"/>
       <c r="G287" s="1"/>
@@ -7478,7 +7475,7 @@
         <v>30</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F288" s="1"/>
       <c r="G288" s="1"/>
@@ -7487,31 +7484,31 @@
       <c r="B290" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C290" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="D290" s="6"/>
+      <c r="C290" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="D290" s="7"/>
       <c r="E290" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F290" s="7"/>
-      <c r="G290" s="7"/>
+      <c r="F290" s="6"/>
+      <c r="G290" s="6"/>
     </row>
     <row r="291" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B291" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C291" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="D291" s="7"/>
+      <c r="C291" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="D291" s="6"/>
       <c r="E291" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F291" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="G291" s="7" t="s">
+      <c r="F291" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="G291" s="6" t="s">
         <v>144</v>
       </c>
     </row>
@@ -7540,10 +7537,10 @@
         <v>1</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>14</v>
@@ -7600,7 +7597,7 @@
         <v>168</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F296" s="1"/>
       <c r="G296" s="1"/>
@@ -7610,17 +7607,17 @@
         <v>5</v>
       </c>
       <c r="C297" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D297" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="D297" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="E297" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F297" s="1"/>
       <c r="G297" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="298" spans="2:7" x14ac:dyDescent="0.25">
@@ -7628,7 +7625,7 @@
         <v>6</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D298" s="1" t="s">
         <v>89</v>
@@ -7644,13 +7641,13 @@
         <v>7</v>
       </c>
       <c r="C299" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D299" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="D299" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="E299" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F299" s="1"/>
       <c r="G299" s="1"/>
@@ -7660,13 +7657,13 @@
         <v>8</v>
       </c>
       <c r="C300" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D300" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="D300" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="E300" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F300" s="1"/>
       <c r="G300" s="1"/>
@@ -7676,13 +7673,13 @@
         <v>9</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F301" s="1"/>
       <c r="G301" s="1"/>
@@ -7691,31 +7688,31 @@
       <c r="B303" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C303" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="D303" s="6"/>
+      <c r="C303" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="D303" s="7"/>
       <c r="E303" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F303" s="7"/>
-      <c r="G303" s="7"/>
+      <c r="F303" s="6"/>
+      <c r="G303" s="6"/>
     </row>
     <row r="304" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B304" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C304" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="D304" s="7"/>
+      <c r="C304" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D304" s="6"/>
       <c r="E304" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F304" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="G304" s="7"/>
+      <c r="F304" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="G304" s="6"/>
     </row>
     <row r="305" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B305" s="2" t="s">
@@ -7742,13 +7739,13 @@
         <v>1</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D306" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E306" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="E306" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="F306" s="1"/>
       <c r="G306" s="1" t="s">
@@ -7760,17 +7757,17 @@
         <v>2</v>
       </c>
       <c r="C307" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D307" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="D307" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="E307" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F307" s="1"/>
       <c r="G307" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="308" spans="2:7" x14ac:dyDescent="0.25">
@@ -7778,17 +7775,17 @@
         <v>3</v>
       </c>
       <c r="C308" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D308" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="D308" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="E308" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F308" s="1"/>
       <c r="G308" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="309" spans="2:7" x14ac:dyDescent="0.25">
@@ -7799,10 +7796,10 @@
         <v>76</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F309" s="1"/>
       <c r="G309" s="1"/>
@@ -7815,10 +7812,10 @@
         <v>114</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F310" s="1"/>
       <c r="G310" s="1"/>
@@ -7831,7 +7828,7 @@
         <v>230</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>14</v>
@@ -7844,13 +7841,13 @@
         <v>7</v>
       </c>
       <c r="C312" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D312" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="D312" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="E312" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F312" s="1"/>
       <c r="G312" s="1"/>
@@ -7866,7 +7863,7 @@
         <v>30</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F313" s="1"/>
       <c r="G313" s="1"/>
@@ -7882,7 +7879,7 @@
         <v>34</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F314" s="1"/>
       <c r="G314" s="1"/>
@@ -7891,32 +7888,32 @@
       <c r="B316" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C316" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="D316" s="6"/>
+      <c r="C316" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="D316" s="7"/>
       <c r="E316" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F316" s="7"/>
-      <c r="G316" s="7"/>
+      <c r="F316" s="6"/>
+      <c r="G316" s="6"/>
     </row>
     <row r="317" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B317" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C317" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="D317" s="7"/>
+      <c r="C317" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="D317" s="6"/>
       <c r="E317" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F317" s="7" t="s">
+      <c r="F317" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="G317" s="6" t="s">
         <v>384</v>
-      </c>
-      <c r="G317" s="7" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="318" spans="2:7" x14ac:dyDescent="0.25">
@@ -7944,13 +7941,13 @@
         <v>1</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F319" s="1"/>
       <c r="G319" s="1" t="s">
@@ -7962,17 +7959,17 @@
         <v>2</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F320" s="1"/>
       <c r="G320" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="321" spans="2:7" x14ac:dyDescent="0.25">
@@ -7980,17 +7977,17 @@
         <v>3</v>
       </c>
       <c r="C321" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D321" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="D321" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="E321" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F321" s="1"/>
       <c r="G321" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="322" spans="2:7" x14ac:dyDescent="0.25">
@@ -7998,13 +7995,13 @@
         <v>4</v>
       </c>
       <c r="C322" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D322" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="D322" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="E322" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F322" s="1"/>
       <c r="G322" s="1" t="s">
@@ -8019,10 +8016,10 @@
         <v>191</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F323" s="1"/>
       <c r="G323" s="1"/>
@@ -8032,13 +8029,13 @@
         <v>6</v>
       </c>
       <c r="C324" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D324" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D324" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="E324" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F324" s="1"/>
       <c r="G324" s="1"/>
@@ -8051,10 +8048,10 @@
         <v>151</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F325" s="1"/>
       <c r="G325" s="1"/>
@@ -8064,13 +8061,13 @@
         <v>8</v>
       </c>
       <c r="C326" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D326" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="D326" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="E326" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F326" s="1"/>
       <c r="G326" s="1"/>
@@ -8080,13 +8077,13 @@
         <v>9</v>
       </c>
       <c r="C327" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D327" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="D327" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="E327" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F327" s="1"/>
       <c r="G327" s="1"/>
@@ -8096,10 +8093,10 @@
         <v>10</v>
       </c>
       <c r="C328" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="D328" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>401</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>14</v>
@@ -8112,10 +8109,10 @@
         <v>11</v>
       </c>
       <c r="C329" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D329" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="D329" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>14</v>
@@ -8128,10 +8125,10 @@
         <v>12</v>
       </c>
       <c r="C330" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="D330" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="D330" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>14</v>
@@ -8150,11 +8147,11 @@
         <v>193</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F331" s="1"/>
       <c r="G331" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="332" spans="2:7" x14ac:dyDescent="0.25">
@@ -8168,7 +8165,7 @@
         <v>30</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F332" s="1"/>
       <c r="G332" s="1"/>
@@ -8184,7 +8181,7 @@
         <v>34</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F333" s="1"/>
       <c r="G333" s="1"/>
@@ -8193,31 +8190,31 @@
       <c r="B335" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C335" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="D335" s="6"/>
+      <c r="C335" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="D335" s="7"/>
       <c r="E335" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F335" s="7"/>
-      <c r="G335" s="7"/>
+      <c r="F335" s="6"/>
+      <c r="G335" s="6"/>
     </row>
     <row r="336" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B336" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C336" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="D336" s="7"/>
+      <c r="C336" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="D336" s="6"/>
       <c r="E336" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F336" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="G336" s="7"/>
+      <c r="F336" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="G336" s="6"/>
     </row>
     <row r="337" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B337" s="2" t="s">
@@ -8244,13 +8241,13 @@
         <v>1</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F338" s="1"/>
       <c r="G338" s="1" t="s">
@@ -8262,17 +8259,17 @@
         <v>2</v>
       </c>
       <c r="C339" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D339" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="D339" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="E339" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F339" s="1"/>
       <c r="G339" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="340" spans="2:7" x14ac:dyDescent="0.25">
@@ -8286,7 +8283,7 @@
         <v>72</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F340" s="1"/>
       <c r="G340" s="1"/>
@@ -8296,17 +8293,17 @@
         <v>4</v>
       </c>
       <c r="C341" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="D341" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="D341" s="1" t="s">
-        <v>415</v>
-      </c>
       <c r="E341" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F341" s="1"/>
       <c r="G341" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="342" spans="2:7" x14ac:dyDescent="0.25">
@@ -8314,13 +8311,13 @@
         <v>5</v>
       </c>
       <c r="C342" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D342" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="D342" s="1" t="s">
-        <v>418</v>
-      </c>
       <c r="E342" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F342" s="1"/>
       <c r="G342" s="1"/>
@@ -8330,13 +8327,13 @@
         <v>6</v>
       </c>
       <c r="C343" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D343" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D343" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="E343" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F343" s="1"/>
       <c r="G343" s="1"/>
@@ -8346,13 +8343,13 @@
         <v>7</v>
       </c>
       <c r="C344" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="D344" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="D344" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="E344" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F344" s="1"/>
       <c r="G344" s="1"/>
@@ -8368,7 +8365,7 @@
         <v>30</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F345" s="1"/>
       <c r="G345" s="1"/>
@@ -8377,32 +8374,32 @@
       <c r="B347" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C347" s="6" t="s">
-        <v>423</v>
-      </c>
-      <c r="D347" s="6"/>
+      <c r="C347" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="D347" s="7"/>
       <c r="E347" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F347" s="7"/>
-      <c r="G347" s="7"/>
+      <c r="F347" s="6"/>
+      <c r="G347" s="6"/>
     </row>
     <row r="348" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B348" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C348" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="D348" s="7"/>
+      <c r="C348" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="D348" s="6"/>
       <c r="E348" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F348" s="7" t="s">
+      <c r="F348" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="G348" s="6" t="s">
         <v>425</v>
-      </c>
-      <c r="G348" s="7" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="349" spans="2:7" x14ac:dyDescent="0.25">
@@ -8430,13 +8427,13 @@
         <v>1</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F350" s="1"/>
       <c r="G350" s="1" t="s">
@@ -8448,17 +8445,17 @@
         <v>2</v>
       </c>
       <c r="C351" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D351" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="D351" s="1" t="s">
-        <v>429</v>
-      </c>
       <c r="E351" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F351" s="1"/>
       <c r="G351" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="352" spans="2:7" x14ac:dyDescent="0.25">
@@ -8466,13 +8463,13 @@
         <v>3</v>
       </c>
       <c r="C352" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D352" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="D352" s="1" t="s">
-        <v>431</v>
-      </c>
       <c r="E352" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F352" s="1"/>
       <c r="G352" s="1"/>
@@ -8482,13 +8479,13 @@
         <v>4</v>
       </c>
       <c r="C353" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="D353" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="D353" s="1" t="s">
-        <v>433</v>
-      </c>
       <c r="E353" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F353" s="1"/>
       <c r="G353" s="1" t="s">
@@ -8500,13 +8497,13 @@
         <v>5</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D354" s="1" t="s">
         <v>192</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F354" s="1"/>
       <c r="G354" s="1"/>
@@ -8519,10 +8516,10 @@
         <v>151</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F355" s="1"/>
       <c r="G355" s="1"/>
@@ -8532,13 +8529,13 @@
         <v>7</v>
       </c>
       <c r="C356" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D356" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D356" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="E356" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F356" s="1"/>
       <c r="G356" s="1"/>
@@ -8548,17 +8545,17 @@
         <v>8</v>
       </c>
       <c r="C357" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D357" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="D357" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="E357" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F357" s="1"/>
       <c r="G357" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="358" spans="2:7" x14ac:dyDescent="0.25">
@@ -8566,17 +8563,17 @@
         <v>9</v>
       </c>
       <c r="C358" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D358" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="D358" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="E358" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F358" s="1"/>
       <c r="G358" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="359" spans="2:7" x14ac:dyDescent="0.25">
@@ -8590,11 +8587,11 @@
         <v>193</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F359" s="1"/>
       <c r="G359" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="360" spans="2:7" x14ac:dyDescent="0.25">
@@ -8608,7 +8605,7 @@
         <v>30</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F360" s="1"/>
       <c r="G360" s="1"/>
@@ -8624,7 +8621,7 @@
         <v>33</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F361" s="1"/>
       <c r="G361" s="1"/>
@@ -8633,29 +8630,29 @@
       <c r="B363" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C363" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="D363" s="6"/>
+      <c r="C363" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="D363" s="7"/>
       <c r="E363" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F363" s="7"/>
-      <c r="G363" s="7"/>
+      <c r="F363" s="6"/>
+      <c r="G363" s="6"/>
     </row>
     <row r="364" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B364" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C364" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="D364" s="7"/>
+      <c r="C364" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="D364" s="6"/>
       <c r="E364" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F364" s="7"/>
-      <c r="G364" s="7"/>
+      <c r="F364" s="6"/>
+      <c r="G364" s="6"/>
     </row>
     <row r="365" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B365" s="2" t="s">
@@ -8682,17 +8679,17 @@
         <v>1</v>
       </c>
       <c r="C366" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D366" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="D366" s="1" t="s">
-        <v>444</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F366" s="1"/>
       <c r="G366" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="367" spans="2:7" x14ac:dyDescent="0.25">
@@ -8703,16 +8700,16 @@
         <v>76</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F367" s="1">
         <v>50</v>
       </c>
       <c r="G367" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="368" spans="2:7" x14ac:dyDescent="0.25">
@@ -8720,17 +8717,17 @@
         <v>3</v>
       </c>
       <c r="C368" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D368" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="D368" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="E368" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F368" s="1"/>
       <c r="G368" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="369" spans="2:9" x14ac:dyDescent="0.25">
@@ -8738,7 +8735,7 @@
         <v>12</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D369" s="1"/>
       <c r="E369" s="1"/>
@@ -8750,7 +8747,7 @@
         <v>0</v>
       </c>
       <c r="C371" s="8" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D371" s="8"/>
       <c r="E371" s="3" t="s">
@@ -8765,7 +8762,7 @@
         <v>3</v>
       </c>
       <c r="C372" s="9" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D372" s="9"/>
       <c r="E372" s="3" t="s">
@@ -8801,17 +8798,17 @@
         <v>1</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D374" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E374" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F374" s="4"/>
       <c r="G374" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="I374"/>
     </row>
@@ -8820,17 +8817,17 @@
         <v>2</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E375" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F375" s="4"/>
       <c r="G375" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I375"/>
     </row>
@@ -8839,17 +8836,17 @@
         <v>3</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E376" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F376" s="4"/>
       <c r="G376" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I376"/>
     </row>
@@ -8858,7 +8855,7 @@
         <v>12</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D377" s="4"/>
       <c r="E377" s="4"/>
@@ -8870,32 +8867,32 @@
       <c r="B379" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C379" s="6" t="s">
-        <v>448</v>
-      </c>
-      <c r="D379" s="6"/>
+      <c r="C379" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="D379" s="7"/>
       <c r="E379" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F379" s="7"/>
-      <c r="G379" s="7"/>
+      <c r="F379" s="6"/>
+      <c r="G379" s="6"/>
     </row>
     <row r="380" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B380" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C380" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="D380" s="7"/>
+      <c r="C380" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="D380" s="6"/>
       <c r="E380" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F380" s="6" t="s">
-        <v>585</v>
-      </c>
-      <c r="G380" s="7" t="s">
-        <v>450</v>
+      <c r="F380" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="G380" s="6" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="381" spans="2:9" x14ac:dyDescent="0.25">
@@ -8923,17 +8920,17 @@
         <v>1</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F382" s="1"/>
       <c r="G382" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="383" spans="2:9" x14ac:dyDescent="0.25">
@@ -8947,7 +8944,7 @@
         <v>72</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F383" s="1"/>
       <c r="G383" s="1" t="s">
@@ -8959,7 +8956,7 @@
         <v>3</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D384" s="1" t="s">
         <v>17</v>
@@ -8980,16 +8977,16 @@
         <v>191</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F385" s="1">
         <v>120</v>
       </c>
       <c r="G385" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="386" spans="2:7" x14ac:dyDescent="0.25">
@@ -8997,19 +8994,19 @@
         <v>5</v>
       </c>
       <c r="C386" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="D386" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="D386" s="1" t="s">
-        <v>455</v>
-      </c>
       <c r="E386" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F386" s="1">
         <v>100</v>
       </c>
       <c r="G386" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="387" spans="2:7" x14ac:dyDescent="0.25">
@@ -9020,14 +9017,14 @@
         <v>151</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F387" s="1"/>
       <c r="G387" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="388" spans="2:7" x14ac:dyDescent="0.25">
@@ -9035,19 +9032,19 @@
         <v>7</v>
       </c>
       <c r="C388" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="D388" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="D388" s="1" t="s">
-        <v>457</v>
-      </c>
       <c r="E388" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F388" s="1">
         <v>255</v>
       </c>
       <c r="G388" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="389" spans="2:7" x14ac:dyDescent="0.25">
@@ -9055,13 +9052,13 @@
         <v>8</v>
       </c>
       <c r="C389" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="D389" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="D389" s="1" t="s">
-        <v>460</v>
-      </c>
       <c r="E389" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F389" s="1">
         <v>30</v>
@@ -9073,13 +9070,13 @@
         <v>9</v>
       </c>
       <c r="C390" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D390" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D390" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="E390" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F390" s="1">
         <v>255</v>
@@ -9091,13 +9088,13 @@
         <v>10</v>
       </c>
       <c r="C391" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="D391" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="D391" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="E391" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F391" s="1">
         <v>255</v>
@@ -9109,13 +9106,13 @@
         <v>11</v>
       </c>
       <c r="C392" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="D392" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="D392" s="1" t="s">
-        <v>464</v>
-      </c>
       <c r="E392" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F392" s="1"/>
       <c r="G392" s="1"/>
@@ -9125,13 +9122,13 @@
         <v>12</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F393" s="1"/>
       <c r="G393" s="1"/>
@@ -9141,17 +9138,17 @@
         <v>13</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D394" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F394" s="1"/>
       <c r="G394" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="395" spans="2:7" x14ac:dyDescent="0.25">
@@ -9162,14 +9159,14 @@
         <v>67</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F395" s="1"/>
       <c r="G395" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="396" spans="2:7" x14ac:dyDescent="0.25">
@@ -9183,11 +9180,11 @@
         <v>30</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F396" s="1"/>
       <c r="G396" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="397" spans="2:7" x14ac:dyDescent="0.25">
@@ -9201,11 +9198,11 @@
         <v>33</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F397" s="1"/>
       <c r="G397" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="398" spans="2:7" x14ac:dyDescent="0.25">
@@ -9213,13 +9210,13 @@
         <v>17</v>
       </c>
       <c r="C398" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D398" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="D398" s="1" t="s">
-        <v>470</v>
-      </c>
       <c r="E398" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F398" s="1"/>
       <c r="G398" s="1"/>
@@ -9229,13 +9226,13 @@
         <v>18</v>
       </c>
       <c r="C399" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="D399" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="D399" s="1" t="s">
+      <c r="E399" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="E399" s="1" t="s">
-        <v>558</v>
       </c>
       <c r="F399" s="1"/>
       <c r="G399" s="1"/>
@@ -9245,7 +9242,7 @@
         <v>12</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D400" s="1"/>
       <c r="E400" s="1"/>
@@ -9256,31 +9253,31 @@
       <c r="B402" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C402" s="6" t="s">
-        <v>472</v>
-      </c>
-      <c r="D402" s="6"/>
+      <c r="C402" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="D402" s="7"/>
       <c r="E402" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F402" s="7"/>
-      <c r="G402" s="7"/>
+      <c r="F402" s="6"/>
+      <c r="G402" s="6"/>
     </row>
     <row r="403" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B403" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C403" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="D403" s="7"/>
+      <c r="C403" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="D403" s="6"/>
       <c r="E403" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F403" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="G403" s="7"/>
+      <c r="F403" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="G403" s="6"/>
     </row>
     <row r="404" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B404" s="2" t="s">
@@ -9307,10 +9304,10 @@
         <v>1</v>
       </c>
       <c r="C405" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="D405" s="1" t="s">
         <v>473</v>
-      </c>
-      <c r="D405" s="1" t="s">
-        <v>474</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>14</v>
@@ -9343,19 +9340,19 @@
         <v>3</v>
       </c>
       <c r="C407" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="D407" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="D407" s="1" t="s">
-        <v>476</v>
-      </c>
       <c r="E407" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F407" s="1">
         <v>50</v>
       </c>
       <c r="G407" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="408" spans="2:7" x14ac:dyDescent="0.25">
@@ -9363,17 +9360,17 @@
         <v>4</v>
       </c>
       <c r="C408" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D408" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="D408" s="1" t="s">
-        <v>478</v>
-      </c>
       <c r="E408" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F408" s="1"/>
       <c r="G408" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="409" spans="2:7" x14ac:dyDescent="0.25">
@@ -9387,7 +9384,7 @@
         <v>30</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F409" s="1"/>
       <c r="G409" s="1" t="s">
@@ -9398,29 +9395,29 @@
       <c r="B411" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C411" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="D411" s="6"/>
+      <c r="C411" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="D411" s="7"/>
       <c r="E411" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F411" s="7"/>
-      <c r="G411" s="7"/>
+      <c r="F411" s="6"/>
+      <c r="G411" s="6"/>
     </row>
     <row r="412" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B412" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C412" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="D412" s="7"/>
+      <c r="C412" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D412" s="6"/>
       <c r="E412" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F412" s="7"/>
-      <c r="G412" s="7"/>
+      <c r="F412" s="6"/>
+      <c r="G412" s="6"/>
     </row>
     <row r="413" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B413" s="2" t="s">
@@ -9447,10 +9444,10 @@
         <v>1</v>
       </c>
       <c r="C414" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D414" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="D414" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>14</v>
@@ -9465,19 +9462,19 @@
         <v>2</v>
       </c>
       <c r="C415" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="D415" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="D415" s="1" t="s">
-        <v>482</v>
-      </c>
       <c r="E415" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F415" s="1">
         <v>100</v>
       </c>
       <c r="G415" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="416" spans="2:7" x14ac:dyDescent="0.25">
@@ -9485,19 +9482,19 @@
         <v>3</v>
       </c>
       <c r="C416" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D416" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="D416" s="1" t="s">
-        <v>485</v>
-      </c>
       <c r="E416" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F416" s="1">
         <v>50</v>
       </c>
       <c r="G416" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="417" spans="2:7" x14ac:dyDescent="0.25">
@@ -9505,17 +9502,17 @@
         <v>4</v>
       </c>
       <c r="C417" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="D417" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="D417" s="1" t="s">
-        <v>488</v>
-      </c>
       <c r="E417" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F417" s="1"/>
       <c r="G417" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="418" spans="2:7" x14ac:dyDescent="0.25">
@@ -9523,19 +9520,19 @@
         <v>5</v>
       </c>
       <c r="C418" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="D418" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="D418" s="1" t="s">
-        <v>491</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G418" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="419" spans="2:7" x14ac:dyDescent="0.25">
@@ -9543,17 +9540,17 @@
         <v>6</v>
       </c>
       <c r="C419" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D419" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="D419" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="E419" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F419" s="1"/>
       <c r="G419" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="420" spans="2:7" x14ac:dyDescent="0.25">
@@ -9567,7 +9564,7 @@
         <v>30</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F420" s="1"/>
       <c r="G420" s="1"/>
@@ -9576,31 +9573,31 @@
       <c r="B422" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C422" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="D422" s="6"/>
+      <c r="C422" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="D422" s="7"/>
       <c r="E422" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F422" s="7"/>
-      <c r="G422" s="7"/>
+      <c r="F422" s="6"/>
+      <c r="G422" s="6"/>
     </row>
     <row r="423" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B423" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C423" s="7" t="s">
-        <v>493</v>
-      </c>
-      <c r="D423" s="7"/>
+      <c r="C423" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="D423" s="6"/>
       <c r="E423" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F423" s="7" t="s">
-        <v>494</v>
-      </c>
-      <c r="G423" s="7"/>
+      <c r="F423" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="G423" s="6"/>
     </row>
     <row r="424" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B424" s="2" t="s">
@@ -9627,10 +9624,10 @@
         <v>1</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>14</v>
@@ -9645,17 +9642,17 @@
         <v>2</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F426" s="1"/>
       <c r="G426" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="427" spans="2:7" x14ac:dyDescent="0.25">
@@ -9663,17 +9660,17 @@
         <v>3</v>
       </c>
       <c r="C427" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="D427" s="1" t="s">
         <v>498</v>
-      </c>
-      <c r="D427" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F427" s="1"/>
       <c r="G427" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="428" spans="2:7" x14ac:dyDescent="0.25">
@@ -9681,19 +9678,19 @@
         <v>4</v>
       </c>
       <c r="C428" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="D428" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="D428" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="429" spans="2:7" x14ac:dyDescent="0.25">
@@ -9701,19 +9698,19 @@
         <v>5</v>
       </c>
       <c r="C429" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="D429" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="D429" s="1" t="s">
-        <v>505</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="430" spans="2:7" x14ac:dyDescent="0.25">
@@ -9724,10 +9721,10 @@
         <v>29</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F430" s="1"/>
       <c r="G430" s="1"/>
@@ -9736,31 +9733,31 @@
       <c r="B432" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C432" s="6" t="s">
-        <v>508</v>
-      </c>
-      <c r="D432" s="6"/>
+      <c r="C432" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="D432" s="7"/>
       <c r="E432" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F432" s="7"/>
-      <c r="G432" s="7"/>
+      <c r="F432" s="6"/>
+      <c r="G432" s="6"/>
     </row>
     <row r="433" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B433" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C433" s="7" t="s">
-        <v>509</v>
-      </c>
-      <c r="D433" s="7"/>
+      <c r="C433" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="D433" s="6"/>
       <c r="E433" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F433" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="G433" s="7"/>
+      <c r="F433" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="G433" s="6"/>
     </row>
     <row r="434" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B434" s="2" t="s">
@@ -9787,19 +9784,19 @@
         <v>1</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F435" s="1">
         <v>24</v>
       </c>
       <c r="G435" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="436" spans="2:7" x14ac:dyDescent="0.25">
@@ -9807,10 +9804,10 @@
         <v>2</v>
       </c>
       <c r="C436" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="D436" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="D436" s="1" t="s">
-        <v>514</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>14</v>
@@ -9828,13 +9825,13 @@
         <v>114</v>
       </c>
       <c r="D437" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="E437" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F437" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="E437" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="F437" s="1" t="s">
-        <v>516</v>
       </c>
       <c r="G437" s="1"/>
     </row>
@@ -9843,13 +9840,13 @@
         <v>4</v>
       </c>
       <c r="C438" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="D438" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="D438" s="1" t="s">
-        <v>518</v>
-      </c>
       <c r="E438" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F438" s="1">
         <v>500</v>
@@ -9858,6 +9855,136 @@
     </row>
   </sheetData>
   <mergeCells count="148">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="F116:G116"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="F141:G141"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="F167:G167"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="F168:G168"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="F175:G175"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="F142:G142"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="F153:G153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="F154:G154"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="F197:G197"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="F198:G198"/>
+    <mergeCell ref="C206:D206"/>
+    <mergeCell ref="F206:G206"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="F176:G176"/>
+    <mergeCell ref="C185:D185"/>
+    <mergeCell ref="F185:G185"/>
+    <mergeCell ref="C186:D186"/>
+    <mergeCell ref="F186:G186"/>
+    <mergeCell ref="C228:D228"/>
+    <mergeCell ref="F228:G228"/>
+    <mergeCell ref="C229:D229"/>
+    <mergeCell ref="F229:G229"/>
+    <mergeCell ref="C240:D240"/>
+    <mergeCell ref="F240:G240"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="F207:G207"/>
+    <mergeCell ref="C214:D214"/>
+    <mergeCell ref="F214:G214"/>
+    <mergeCell ref="C215:D215"/>
+    <mergeCell ref="F215:G215"/>
+    <mergeCell ref="C264:D264"/>
+    <mergeCell ref="F264:G264"/>
+    <mergeCell ref="C265:D265"/>
+    <mergeCell ref="F265:G265"/>
+    <mergeCell ref="C277:D277"/>
+    <mergeCell ref="F277:G277"/>
+    <mergeCell ref="C241:D241"/>
+    <mergeCell ref="F241:G241"/>
+    <mergeCell ref="C252:D252"/>
+    <mergeCell ref="F252:G252"/>
+    <mergeCell ref="C253:D253"/>
+    <mergeCell ref="F253:G253"/>
+    <mergeCell ref="C303:D303"/>
+    <mergeCell ref="F303:G303"/>
+    <mergeCell ref="C304:D304"/>
+    <mergeCell ref="F304:G304"/>
+    <mergeCell ref="C316:D316"/>
+    <mergeCell ref="F316:G316"/>
+    <mergeCell ref="C278:D278"/>
+    <mergeCell ref="F278:G278"/>
+    <mergeCell ref="C290:D290"/>
+    <mergeCell ref="F290:G290"/>
+    <mergeCell ref="C291:D291"/>
+    <mergeCell ref="F291:G291"/>
+    <mergeCell ref="C347:D347"/>
+    <mergeCell ref="F347:G347"/>
+    <mergeCell ref="C317:D317"/>
+    <mergeCell ref="F317:G317"/>
+    <mergeCell ref="C335:D335"/>
+    <mergeCell ref="F335:G335"/>
+    <mergeCell ref="C336:D336"/>
+    <mergeCell ref="F336:G336"/>
+    <mergeCell ref="C363:D363"/>
+    <mergeCell ref="F363:G363"/>
+    <mergeCell ref="C364:D364"/>
+    <mergeCell ref="F364:G364"/>
+    <mergeCell ref="C379:D379"/>
+    <mergeCell ref="F379:G379"/>
+    <mergeCell ref="C348:D348"/>
+    <mergeCell ref="F348:G348"/>
+    <mergeCell ref="C371:D371"/>
+    <mergeCell ref="F371:G371"/>
+    <mergeCell ref="C372:D372"/>
+    <mergeCell ref="F372:G372"/>
     <mergeCell ref="C380:D380"/>
     <mergeCell ref="F380:G380"/>
     <mergeCell ref="C402:D402"/>
@@ -9876,136 +10003,6 @@
     <mergeCell ref="F422:G422"/>
     <mergeCell ref="C423:D423"/>
     <mergeCell ref="F423:G423"/>
-    <mergeCell ref="C364:D364"/>
-    <mergeCell ref="F364:G364"/>
-    <mergeCell ref="C379:D379"/>
-    <mergeCell ref="F379:G379"/>
-    <mergeCell ref="C348:D348"/>
-    <mergeCell ref="F348:G348"/>
-    <mergeCell ref="C371:D371"/>
-    <mergeCell ref="F371:G371"/>
-    <mergeCell ref="C372:D372"/>
-    <mergeCell ref="F372:G372"/>
-    <mergeCell ref="C347:D347"/>
-    <mergeCell ref="F347:G347"/>
-    <mergeCell ref="C317:D317"/>
-    <mergeCell ref="F317:G317"/>
-    <mergeCell ref="C335:D335"/>
-    <mergeCell ref="F335:G335"/>
-    <mergeCell ref="C336:D336"/>
-    <mergeCell ref="F336:G336"/>
-    <mergeCell ref="C363:D363"/>
-    <mergeCell ref="F363:G363"/>
-    <mergeCell ref="C303:D303"/>
-    <mergeCell ref="F303:G303"/>
-    <mergeCell ref="C304:D304"/>
-    <mergeCell ref="F304:G304"/>
-    <mergeCell ref="C316:D316"/>
-    <mergeCell ref="F316:G316"/>
-    <mergeCell ref="C278:D278"/>
-    <mergeCell ref="F278:G278"/>
-    <mergeCell ref="C290:D290"/>
-    <mergeCell ref="F290:G290"/>
-    <mergeCell ref="C291:D291"/>
-    <mergeCell ref="F291:G291"/>
-    <mergeCell ref="C264:D264"/>
-    <mergeCell ref="F264:G264"/>
-    <mergeCell ref="C265:D265"/>
-    <mergeCell ref="F265:G265"/>
-    <mergeCell ref="C277:D277"/>
-    <mergeCell ref="F277:G277"/>
-    <mergeCell ref="C241:D241"/>
-    <mergeCell ref="F241:G241"/>
-    <mergeCell ref="C252:D252"/>
-    <mergeCell ref="F252:G252"/>
-    <mergeCell ref="C253:D253"/>
-    <mergeCell ref="F253:G253"/>
-    <mergeCell ref="C228:D228"/>
-    <mergeCell ref="F228:G228"/>
-    <mergeCell ref="C229:D229"/>
-    <mergeCell ref="F229:G229"/>
-    <mergeCell ref="C240:D240"/>
-    <mergeCell ref="F240:G240"/>
-    <mergeCell ref="C207:D207"/>
-    <mergeCell ref="F207:G207"/>
-    <mergeCell ref="C214:D214"/>
-    <mergeCell ref="F214:G214"/>
-    <mergeCell ref="C215:D215"/>
-    <mergeCell ref="F215:G215"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="F197:G197"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="F198:G198"/>
-    <mergeCell ref="C206:D206"/>
-    <mergeCell ref="F206:G206"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="F176:G176"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="F185:G185"/>
-    <mergeCell ref="C186:D186"/>
-    <mergeCell ref="F186:G186"/>
-    <mergeCell ref="C168:D168"/>
-    <mergeCell ref="F168:G168"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="F175:G175"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="F142:G142"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="F153:G153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="F154:G154"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="F141:G141"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="F130:G130"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="F167:G167"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="F103:G103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="F104:G104"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="F116:G116"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:G14"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Document/專題/db_diagram.xlsx
+++ b/Document/專題/db_diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\RentalManagementPlatform\Document\專題\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{851A35FB-FA46-43E8-898F-7961CA8FB4D8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C5A2C7-41D1-4B88-BEB1-FC06A242DC53}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="606">
   <si>
     <t>表格名稱</t>
   </si>
@@ -134,10 +134,6 @@
     <t>(FK) 對應 USER.user_id</t>
   </si>
   <si>
-    <t>中文：訂單_x000D_
-英文：BOOKING</t>
-  </si>
-  <si>
     <t>booking_id</t>
   </si>
   <si>
@@ -775,10 +771,6 @@
   </si>
   <si>
     <t>NOT NULL，default: SYSDATETIME()</t>
-  </si>
-  <si>
-    <t>中文：權限_x000D_
-英文：PERMISSIONS</t>
   </si>
   <si>
     <t>permission_id</t>
@@ -1914,6 +1906,72 @@
   </si>
   <si>
     <t>9,6</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATETIME2</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>(FK) 對應 USER.user_id</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>booking_id</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文：訂單
+英文：BOOKING</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>guest_id</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>permission_id</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文：權限
+英文：PERMISSIONS</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Null</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>admin</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>operators</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>suppliers_S</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>suppliers_E</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>hosts_S</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>hosts_E</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>tenants_S</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>tenants_E</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -1921,6 +1979,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="180" formatCode="yyyy/m/d\ h:mm;@"/>
+  </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -2272,7 +2333,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -2400,6 +2461,15 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -2531,7 +2601,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2561,6 +2631,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="5" borderId="4" xfId="9" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2607,7 +2686,25 @@
     <cellStyle name="壞" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="警告文字" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2917,7 +3014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:I438"/>
+  <dimension ref="B2:P438"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
@@ -2926,6 +3023,9 @@
     <col min="5" max="5" width="12.375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="35.75" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="62.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="12.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3028,7 +3128,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>22</v>
@@ -3048,7 +3148,7 @@
         <v>21</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>25</v>
@@ -3065,7 +3165,7 @@
         <v>27</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
@@ -3083,7 +3183,7 @@
         <v>30</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
@@ -3101,7 +3201,7 @@
         <v>33</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
@@ -3113,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>36</v>
+        <v>593</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="2" t="s">
@@ -3127,17 +3227,17 @@
         <v>3</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>37</v>
+        <v>592</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
@@ -3165,10 +3265,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>14</v>
@@ -3183,17 +3283,17 @@
         <v>2</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
@@ -3201,17 +3301,17 @@
         <v>3</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
@@ -3219,17 +3319,17 @@
         <v>4</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -3237,13 +3337,13 @@
         <v>5</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="E20" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -3253,17 +3353,17 @@
         <v>6</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="E21" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
@@ -3271,17 +3371,17 @@
         <v>7</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
@@ -3289,17 +3389,17 @@
         <v>8</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
@@ -3307,10 +3407,10 @@
         <v>9</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>21</v>
@@ -3323,10 +3423,10 @@
         <v>10</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>14</v>
@@ -3339,10 +3439,10 @@
         <v>11</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>14</v>
@@ -3355,17 +3455,17 @@
         <v>12</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="E27" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
@@ -3379,7 +3479,7 @@
         <v>30</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -3389,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="2" t="s">
@@ -3403,7 +3503,7 @@
         <v>3</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="2" t="s">
@@ -3432,15 +3532,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>14</v>
@@ -3450,217 +3550,244 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B34" s="1">
         <v>2</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>520</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
         <v>3</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="E35" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B36" s="1">
         <v>4</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B37" s="1">
         <v>5</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="E37" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B38" s="1">
         <v>6</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="E38" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B39" s="1">
         <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E39" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B40" s="1">
         <v>8</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+        <v>519</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B41" s="1">
         <v>9</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="E41" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B42" s="1">
         <v>10</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>528</v>
-      </c>
       <c r="E42" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B43" s="1">
         <v>11</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>529</v>
-      </c>
       <c r="E43" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B44" s="1">
         <v>12</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B45" s="1">
         <v>13</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>530</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>532</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="J45" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="L45" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="M45" s="10" t="s">
+        <v>602</v>
+      </c>
+      <c r="N45" s="10" t="s">
+        <v>603</v>
+      </c>
+      <c r="O45" s="10" t="s">
+        <v>604</v>
+      </c>
+      <c r="P45" s="10" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B46" s="1">
         <v>14</v>
       </c>
@@ -3671,14 +3798,38 @@
         <v>30</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="I46" s="10">
+        <v>45292.001388888886</v>
+      </c>
+      <c r="J46" s="10">
+        <v>45292.001388888886</v>
+      </c>
+      <c r="K46" s="12">
+        <v>45323</v>
+      </c>
+      <c r="L46" s="12">
+        <v>45897</v>
+      </c>
+      <c r="M46" s="12">
+        <v>45897</v>
+      </c>
+      <c r="N46" s="12">
+        <v>45897</v>
+      </c>
+      <c r="O46" s="12">
+        <v>45897</v>
+      </c>
+      <c r="P46" s="12">
+        <v>45897</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B47" s="1">
         <v>15</v>
       </c>
@@ -3689,17 +3840,41 @@
         <v>34</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
+      <c r="I47" s="12">
+        <v>45897</v>
+      </c>
+      <c r="J47" s="12">
+        <v>45897</v>
+      </c>
+      <c r="K47" s="12">
+        <v>45323</v>
+      </c>
+      <c r="L47" s="12">
+        <v>45897</v>
+      </c>
+      <c r="M47" s="12">
+        <v>45897</v>
+      </c>
+      <c r="N47" s="12">
+        <v>45897</v>
+      </c>
+      <c r="O47" s="12">
+        <v>45897</v>
+      </c>
+      <c r="P47" s="12">
+        <v>45897</v>
+      </c>
     </row>
     <row r="49" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D49" s="7"/>
       <c r="E49" s="2" t="s">
@@ -3713,14 +3888,14 @@
         <v>3</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G50" s="6"/>
     </row>
@@ -3749,10 +3924,10 @@
         <v>1</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>14</v>
@@ -3767,17 +3942,17 @@
         <v>2</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
@@ -3785,17 +3960,17 @@
         <v>3</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
@@ -3803,17 +3978,17 @@
         <v>4</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="E55" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3821,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D57" s="7"/>
       <c r="E57" s="2" t="s">
@@ -3835,7 +4010,7 @@
         <v>3</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="2" t="s">
@@ -3869,10 +4044,10 @@
         <v>1</v>
       </c>
       <c r="C60" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>14</v>
@@ -3887,17 +4062,17 @@
         <v>2</v>
       </c>
       <c r="C61" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="E61" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3905,7 +4080,7 @@
         <v>0</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D63" s="7"/>
       <c r="E63" s="2" t="s">
@@ -3919,7 +4094,7 @@
         <v>3</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="2" t="s">
@@ -3953,10 +4128,10 @@
         <v>1</v>
       </c>
       <c r="C66" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>14</v>
@@ -3971,17 +4146,17 @@
         <v>2</v>
       </c>
       <c r="C67" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="E67" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="68" spans="2:9" x14ac:dyDescent="0.25">
@@ -3989,13 +4164,13 @@
         <v>3</v>
       </c>
       <c r="C68" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="E68" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
@@ -4005,17 +4180,17 @@
         <v>4</v>
       </c>
       <c r="C69" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="E69" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="70" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4023,17 +4198,17 @@
         <v>5</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D70" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="E70" s="4" t="s">
         <v>560</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>562</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="I70"/>
     </row>
@@ -4042,17 +4217,17 @@
         <v>6</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F71" s="4"/>
       <c r="G71" s="4" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="I71"/>
     </row>
@@ -4061,17 +4236,17 @@
         <v>7</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F72" s="4"/>
       <c r="G72" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="I72"/>
     </row>
@@ -4080,17 +4255,17 @@
         <v>8</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F73" s="4"/>
       <c r="G73" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="I73"/>
     </row>
@@ -4099,17 +4274,17 @@
         <v>9</v>
       </c>
       <c r="C74" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="E74" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.25">
@@ -4117,17 +4292,17 @@
         <v>10</v>
       </c>
       <c r="C75" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.25">
@@ -4135,13 +4310,13 @@
         <v>11</v>
       </c>
       <c r="C76" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
@@ -4151,17 +4326,17 @@
         <v>12</v>
       </c>
       <c r="C77" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.25">
@@ -4169,13 +4344,13 @@
         <v>13</v>
       </c>
       <c r="C78" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="E78" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
@@ -4185,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D80" s="8"/>
       <c r="E80" s="3" t="s">
@@ -4200,17 +4375,17 @@
         <v>3</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I81"/>
     </row>
@@ -4240,10 +4415,10 @@
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>14</v>
@@ -4259,17 +4434,17 @@
         <v>2</v>
       </c>
       <c r="C84" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I84"/>
     </row>
@@ -4278,17 +4453,17 @@
         <v>3</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="I85"/>
     </row>
@@ -4297,7 +4472,7 @@
         <v>0</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D87" s="7"/>
       <c r="E87" s="2" t="s">
@@ -4311,17 +4486,17 @@
         <v>3</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F88" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G88" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.25">
@@ -4349,10 +4524,10 @@
         <v>1</v>
       </c>
       <c r="C90" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>14</v>
@@ -4367,17 +4542,17 @@
         <v>2</v>
       </c>
       <c r="C91" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.25">
@@ -4385,10 +4560,10 @@
         <v>3</v>
       </c>
       <c r="C92" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>14</v>
@@ -4403,13 +4578,13 @@
         <v>4</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
@@ -4419,13 +4594,13 @@
         <v>5</v>
       </c>
       <c r="C94" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
@@ -4435,7 +4610,7 @@
         <v>0</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="2" t="s">
@@ -4456,7 +4631,7 @@
         <v>5</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G97" s="6"/>
     </row>
@@ -4503,17 +4678,17 @@
         <v>2</v>
       </c>
       <c r="C100" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F100" s="1"/>
       <c r="G100" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="101" spans="2:9" x14ac:dyDescent="0.25">
@@ -4521,17 +4696,17 @@
         <v>3</v>
       </c>
       <c r="C101" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D101" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F101" s="1"/>
       <c r="G101" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="103" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4539,7 +4714,7 @@
         <v>0</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D103" s="8"/>
       <c r="E103" s="3" t="s">
@@ -4553,17 +4728,17 @@
         <v>3</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D104" s="9"/>
       <c r="E104" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G104" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="105" spans="2:9" x14ac:dyDescent="0.25">
@@ -4591,10 +4766,10 @@
         <v>1</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>14</v>
@@ -4609,17 +4784,17 @@
         <v>2</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="4" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="I107"/>
     </row>
@@ -4628,17 +4803,17 @@
         <v>3</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F108" s="4"/>
       <c r="G108" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="109" spans="2:9" x14ac:dyDescent="0.25">
@@ -4646,17 +4821,17 @@
         <v>4</v>
       </c>
       <c r="C109" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D109" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="D109" s="4" t="s">
-        <v>148</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F109" s="4"/>
       <c r="G109" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="110" spans="2:9" x14ac:dyDescent="0.25">
@@ -4664,17 +4839,17 @@
         <v>5</v>
       </c>
       <c r="C110" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D110" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="D110" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F110" s="4"/>
       <c r="G110" s="4" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="111" spans="2:9" x14ac:dyDescent="0.25">
@@ -4682,17 +4857,17 @@
         <v>6</v>
       </c>
       <c r="C111" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D111" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="4" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="112" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -4700,17 +4875,17 @@
         <v>7</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="I112"/>
     </row>
@@ -4719,17 +4894,17 @@
         <v>8</v>
       </c>
       <c r="C113" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D113" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="D113" s="4" t="s">
-        <v>152</v>
-      </c>
       <c r="E113" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F113" s="4"/>
       <c r="G113" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="114" spans="2:7" x14ac:dyDescent="0.25">
@@ -4743,7 +4918,7 @@
         <v>30</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="4"/>
@@ -4753,7 +4928,7 @@
         <v>0</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D116" s="7"/>
       <c r="E116" s="2" t="s">
@@ -4767,14 +4942,14 @@
         <v>3</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G117" s="6"/>
     </row>
@@ -4803,10 +4978,10 @@
         <v>1</v>
       </c>
       <c r="C119" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>14</v>
@@ -4821,17 +4996,17 @@
         <v>2</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F120" s="1"/>
       <c r="G120" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="121" spans="2:7" x14ac:dyDescent="0.25">
@@ -4839,17 +5014,17 @@
         <v>3</v>
       </c>
       <c r="C121" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F121" s="1"/>
       <c r="G121" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="122" spans="2:7" x14ac:dyDescent="0.25">
@@ -4857,17 +5032,17 @@
         <v>4</v>
       </c>
       <c r="C122" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D122" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F122" s="1"/>
       <c r="G122" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="123" spans="2:7" x14ac:dyDescent="0.25">
@@ -4875,13 +5050,13 @@
         <v>5</v>
       </c>
       <c r="C123" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D123" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="E123" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
@@ -4891,13 +5066,13 @@
         <v>6</v>
       </c>
       <c r="C124" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D124" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="E124" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
@@ -4907,13 +5082,13 @@
         <v>7</v>
       </c>
       <c r="C125" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D125" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="E125" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
@@ -4923,17 +5098,17 @@
         <v>8</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F126" s="1"/>
       <c r="G126" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="127" spans="2:7" x14ac:dyDescent="0.25">
@@ -4947,7 +5122,7 @@
         <v>30</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>
@@ -4957,7 +5132,7 @@
         <v>0</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D129" s="7"/>
       <c r="E129" s="2" t="s">
@@ -4971,14 +5146,14 @@
         <v>3</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D130" s="6"/>
       <c r="E130" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G130" s="6"/>
     </row>
@@ -5007,10 +5182,10 @@
         <v>1</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>14</v>
@@ -5025,17 +5200,17 @@
         <v>2</v>
       </c>
       <c r="C133" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F133" s="1"/>
       <c r="G133" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="134" spans="2:7" x14ac:dyDescent="0.25">
@@ -5043,13 +5218,13 @@
         <v>3</v>
       </c>
       <c r="C134" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D134" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="E134" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
@@ -5059,17 +5234,17 @@
         <v>4</v>
       </c>
       <c r="C135" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D135" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="E135" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F135" s="1"/>
       <c r="G135" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="136" spans="2:7" x14ac:dyDescent="0.25">
@@ -5077,17 +5252,17 @@
         <v>5</v>
       </c>
       <c r="C136" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F136" s="1"/>
       <c r="G136" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="137" spans="2:7" x14ac:dyDescent="0.25">
@@ -5095,13 +5270,13 @@
         <v>6</v>
       </c>
       <c r="C137" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D137" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
@@ -5111,13 +5286,13 @@
         <v>7</v>
       </c>
       <c r="C138" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D138" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F138" s="1"/>
       <c r="G138" s="1"/>
@@ -5133,7 +5308,7 @@
         <v>30</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
@@ -5143,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D141" s="7"/>
       <c r="E141" s="2" t="s">
@@ -5157,17 +5332,17 @@
         <v>3</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D142" s="6"/>
       <c r="E142" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="143" spans="2:7" x14ac:dyDescent="0.25">
@@ -5195,10 +5370,10 @@
         <v>1</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>14</v>
@@ -5213,17 +5388,17 @@
         <v>2</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F145" s="1"/>
       <c r="G145" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="146" spans="2:7" x14ac:dyDescent="0.25">
@@ -5231,10 +5406,10 @@
         <v>3</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>14</v>
@@ -5249,10 +5424,10 @@
         <v>4</v>
       </c>
       <c r="C147" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>201</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>14</v>
@@ -5267,17 +5442,17 @@
         <v>5</v>
       </c>
       <c r="C148" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F148" s="1"/>
       <c r="G148" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="149" spans="2:7" x14ac:dyDescent="0.25">
@@ -5285,17 +5460,17 @@
         <v>6</v>
       </c>
       <c r="C149" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D149" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="E149" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F149" s="1"/>
       <c r="G149" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="150" spans="2:7" x14ac:dyDescent="0.25">
@@ -5303,17 +5478,17 @@
         <v>7</v>
       </c>
       <c r="C150" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F150" s="1"/>
       <c r="G150" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="151" spans="2:7" x14ac:dyDescent="0.25">
@@ -5327,7 +5502,7 @@
         <v>30</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F151" s="1"/>
       <c r="G151" s="1"/>
@@ -5337,7 +5512,7 @@
         <v>0</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D153" s="7"/>
       <c r="E153" s="2" t="s">
@@ -5351,17 +5526,17 @@
         <v>3</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D154" s="6"/>
       <c r="E154" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="155" spans="2:7" x14ac:dyDescent="0.25">
@@ -5389,10 +5564,10 @@
         <v>1</v>
       </c>
       <c r="C156" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>14</v>
@@ -5417,7 +5592,7 @@
       </c>
       <c r="F157" s="1"/>
       <c r="G157" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="158" spans="2:7" x14ac:dyDescent="0.25">
@@ -5425,17 +5600,17 @@
         <v>3</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F158" s="1"/>
       <c r="G158" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="159" spans="2:7" x14ac:dyDescent="0.25">
@@ -5443,17 +5618,17 @@
         <v>4</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="160" spans="2:7" x14ac:dyDescent="0.25">
@@ -5461,17 +5636,17 @@
         <v>5</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F160" s="1"/>
       <c r="G160" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="161" spans="2:7" x14ac:dyDescent="0.25">
@@ -5479,17 +5654,17 @@
         <v>6</v>
       </c>
       <c r="C161" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F161" s="1"/>
       <c r="G161" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="162" spans="2:7" x14ac:dyDescent="0.25">
@@ -5497,17 +5672,17 @@
         <v>7</v>
       </c>
       <c r="C162" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>219</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F162" s="1"/>
       <c r="G162" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="163" spans="2:7" x14ac:dyDescent="0.25">
@@ -5515,17 +5690,17 @@
         <v>8</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F163" s="1"/>
       <c r="G163" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="164" spans="2:7" x14ac:dyDescent="0.25">
@@ -5539,7 +5714,7 @@
         <v>30</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>244</v>
+        <v>590</v>
       </c>
       <c r="F164" s="1"/>
       <c r="G164" s="1"/>
@@ -5555,7 +5730,7 @@
         <v>34</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F165" s="1"/>
       <c r="G165" s="1"/>
@@ -5565,7 +5740,7 @@
         <v>0</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D167" s="7"/>
       <c r="E167" s="2" t="s">
@@ -5579,14 +5754,14 @@
         <v>3</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D168" s="6"/>
       <c r="E168" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G168" s="6"/>
     </row>
@@ -5615,10 +5790,10 @@
         <v>1</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>14</v>
@@ -5633,17 +5808,17 @@
         <v>2</v>
       </c>
       <c r="C171" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F171" s="1"/>
       <c r="G171" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="172" spans="2:7" x14ac:dyDescent="0.25">
@@ -5651,17 +5826,17 @@
         <v>3</v>
       </c>
       <c r="C172" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D172" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="E172" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F172" s="1"/>
       <c r="G172" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="173" spans="2:7" x14ac:dyDescent="0.25">
@@ -5669,17 +5844,17 @@
         <v>4</v>
       </c>
       <c r="C173" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F173" s="1"/>
       <c r="G173" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="175" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5687,7 +5862,7 @@
         <v>0</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D175" s="7"/>
       <c r="E175" s="2" t="s">
@@ -5701,7 +5876,7 @@
         <v>3</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D176" s="6"/>
       <c r="E176" s="2" t="s">
@@ -5710,7 +5885,7 @@
       <c r="F176" s="6"/>
       <c r="G176" s="6"/>
     </row>
-    <row r="177" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B177" s="2" t="s">
         <v>7</v>
       </c>
@@ -5730,83 +5905,83 @@
         <v>12</v>
       </c>
     </row>
-    <row r="178" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B178" s="1">
         <v>1</v>
       </c>
       <c r="C178" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F178" s="1"/>
       <c r="G178" s="1" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="179" spans="2:7" x14ac:dyDescent="0.25">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="179" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B179" s="1">
         <v>2</v>
       </c>
       <c r="C179" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D179" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F179" s="1">
         <v>50</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="180" spans="2:7" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="180" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B180" s="1">
         <v>3</v>
       </c>
       <c r="C180" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D180" s="1" t="s">
+      <c r="E180" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="E180" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="F180" s="1">
         <v>100</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="181" spans="2:7" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="181" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B181" s="1">
         <v>4</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F181" s="1">
         <v>500</v>
       </c>
       <c r="G181" s="1"/>
     </row>
-    <row r="182" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B182" s="1">
         <v>5</v>
       </c>
@@ -5817,14 +5992,17 @@
         <v>30</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F182" s="1"/>
       <c r="G182" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="183" spans="2:7" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+      <c r="I182" s="10">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="183" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B183" s="1">
         <v>6</v>
       </c>
@@ -5835,19 +6013,22 @@
         <v>33</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F183" s="1"/>
       <c r="G183" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="185" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+      <c r="I183" s="10">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="185" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B185" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>246</v>
+        <v>596</v>
       </c>
       <c r="D185" s="7"/>
       <c r="E185" s="2" t="s">
@@ -5856,12 +6037,12 @@
       <c r="F185" s="6"/>
       <c r="G185" s="6"/>
     </row>
-    <row r="186" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B186" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>247</v>
+        <v>595</v>
       </c>
       <c r="D186" s="6"/>
       <c r="E186" s="2" t="s">
@@ -5870,7 +6051,7 @@
       <c r="F186" s="6"/>
       <c r="G186" s="6"/>
     </row>
-    <row r="187" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B187" s="2" t="s">
         <v>7</v>
       </c>
@@ -5890,123 +6071,123 @@
         <v>12</v>
       </c>
     </row>
-    <row r="188" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B188" s="1">
         <v>1</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F188" s="1"/>
       <c r="G188" s="1" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="189" spans="2:7" x14ac:dyDescent="0.25">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="189" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B189" s="1">
         <v>2</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F189" s="1">
         <v>100</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="190" spans="2:7" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="190" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B190" s="1">
         <v>3</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F190" s="1">
         <v>200</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="191" spans="2:7" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="191" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B191" s="1">
         <v>4</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F191" s="1">
         <v>50</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="192" spans="2:7" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="192" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B192" s="1">
         <v>5</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F192" s="1">
         <v>50</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="193" spans="2:7" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="193" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B193" s="1">
         <v>6</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F193" s="1">
         <v>500</v>
       </c>
       <c r="G193" s="1"/>
     </row>
-    <row r="194" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B194" s="1">
         <v>7</v>
       </c>
@@ -6017,14 +6198,17 @@
         <v>30</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F194" s="1"/>
       <c r="G194" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="195" spans="2:7" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+      <c r="I194" s="10">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="195" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B195" s="1">
         <v>8</v>
       </c>
@@ -6035,19 +6219,22 @@
         <v>33</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F195" s="1"/>
       <c r="G195" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="197" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+      <c r="I195" s="10">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="197" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B197" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D197" s="7"/>
       <c r="E197" s="2" t="s">
@@ -6056,25 +6243,25 @@
       <c r="F197" s="6"/>
       <c r="G197" s="6"/>
     </row>
-    <row r="198" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B198" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D198" s="6"/>
       <c r="E198" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="199" spans="2:7" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="199" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B199" s="2" t="s">
         <v>7</v>
       </c>
@@ -6094,79 +6281,79 @@
         <v>12</v>
       </c>
     </row>
-    <row r="200" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B200" s="1">
         <v>1</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F200" s="1"/>
       <c r="G200" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="201" spans="2:7" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="201" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B201" s="1">
         <v>2</v>
       </c>
       <c r="C201" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D201" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F201" s="1"/>
       <c r="G201" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="202" spans="2:7" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="202" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B202" s="1">
         <v>3</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F202" s="1"/>
       <c r="G202" s="1" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="203" spans="2:7" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="203" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B203" s="1">
         <v>4</v>
       </c>
       <c r="C203" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E203" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>268</v>
       </c>
       <c r="F203" s="1"/>
       <c r="G203" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="204" spans="2:7" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="204" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B204" s="1">
         <v>5</v>
       </c>
@@ -6177,19 +6364,22 @@
         <v>30</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F204" s="1"/>
       <c r="G204" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="206" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+      <c r="I204" s="10">
+        <v>45292.000694444447</v>
+      </c>
+    </row>
+    <row r="206" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B206" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D206" s="7"/>
       <c r="E206" s="2" t="s">
@@ -6198,25 +6388,25 @@
       <c r="F206" s="6"/>
       <c r="G206" s="6"/>
     </row>
-    <row r="207" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B207" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D207" s="6"/>
       <c r="E207" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G207" s="6" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="208" spans="2:7" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="208" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B208" s="2" t="s">
         <v>7</v>
       </c>
@@ -6236,15 +6426,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="209" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B209" s="1">
         <v>1</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>14</v>
@@ -6254,15 +6444,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="210" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B210" s="1">
         <v>2</v>
       </c>
       <c r="C210" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D210" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>14</v>
@@ -6272,25 +6462,25 @@
         <v>35</v>
       </c>
     </row>
-    <row r="211" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B211" s="1">
         <v>3</v>
       </c>
       <c r="C211" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D211" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F211" s="1"/>
       <c r="G211" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="212" spans="2:7" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="212" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B212" s="1">
         <v>4</v>
       </c>
@@ -6301,19 +6491,20 @@
         <v>30</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F212" s="1"/>
       <c r="G212" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="214" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+      <c r="I212" s="10"/>
+    </row>
+    <row r="214" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B214" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D214" s="7"/>
       <c r="E214" s="2" t="s">
@@ -6322,23 +6513,23 @@
       <c r="F214" s="6"/>
       <c r="G214" s="6"/>
     </row>
-    <row r="215" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B215" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D215" s="6"/>
       <c r="E215" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G215" s="6"/>
     </row>
-    <row r="216" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B216" s="2" t="s">
         <v>7</v>
       </c>
@@ -6358,15 +6549,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="217" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B217" s="1">
         <v>1</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>14</v>
@@ -6376,15 +6567,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="218" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B218" s="1">
         <v>2</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>14</v>
@@ -6394,47 +6585,47 @@
         <v>35</v>
       </c>
     </row>
-    <row r="219" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B219" s="1">
         <v>3</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F219" s="1"/>
       <c r="G219" s="1"/>
     </row>
-    <row r="220" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B220" s="1">
         <v>4</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F220" s="1"/>
       <c r="G220" s="1"/>
     </row>
-    <row r="221" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B221" s="1">
         <v>5</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>21</v>
@@ -6442,15 +6633,15 @@
       <c r="F221" s="1"/>
       <c r="G221" s="1"/>
     </row>
-    <row r="222" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B222" s="1">
         <v>6</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>21</v>
@@ -6458,15 +6649,15 @@
       <c r="F222" s="1"/>
       <c r="G222" s="1"/>
     </row>
-    <row r="223" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B223" s="1">
         <v>7</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>21</v>
@@ -6474,18 +6665,18 @@
       <c r="F223" s="1"/>
       <c r="G223" s="1"/>
     </row>
-    <row r="224" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B224" s="1">
         <v>8</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F224" s="1"/>
       <c r="G224" s="1"/>
@@ -6495,13 +6686,13 @@
         <v>9</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F225" s="1"/>
       <c r="G225" s="1"/>
@@ -6517,7 +6708,7 @@
         <v>30</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F226" s="1"/>
       <c r="G226" s="1"/>
@@ -6527,7 +6718,7 @@
         <v>0</v>
       </c>
       <c r="C228" s="7" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D228" s="7"/>
       <c r="E228" s="2" t="s">
@@ -6541,17 +6732,17 @@
         <v>3</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D229" s="6"/>
       <c r="E229" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F229" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G229" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="230" spans="2:7" x14ac:dyDescent="0.25">
@@ -6579,10 +6770,10 @@
         <v>1</v>
       </c>
       <c r="C231" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D231" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="D231" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="E231" s="1" t="s">
         <v>14</v>
@@ -6597,17 +6788,17 @@
         <v>2</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F232" s="1"/>
       <c r="G232" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="233" spans="2:7" x14ac:dyDescent="0.25">
@@ -6615,17 +6806,17 @@
         <v>3</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F233" s="1"/>
       <c r="G233" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="234" spans="2:7" x14ac:dyDescent="0.25">
@@ -6633,13 +6824,13 @@
         <v>4</v>
       </c>
       <c r="C234" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D234" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D234" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="E234" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F234" s="1"/>
       <c r="G234" s="1"/>
@@ -6649,10 +6840,10 @@
         <v>5</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E235" s="1" t="s">
         <v>21</v>
@@ -6665,10 +6856,10 @@
         <v>6</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>21</v>
@@ -6681,10 +6872,10 @@
         <v>7</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>21</v>
@@ -6697,10 +6888,10 @@
         <v>8</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>21</v>
@@ -6713,7 +6904,7 @@
         <v>0</v>
       </c>
       <c r="C240" s="7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D240" s="7"/>
       <c r="E240" s="2" t="s">
@@ -6727,7 +6918,7 @@
         <v>3</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D241" s="6"/>
       <c r="E241" s="2" t="s">
@@ -6761,10 +6952,10 @@
         <v>1</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>14</v>
@@ -6779,17 +6970,17 @@
         <v>2</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F244" s="1"/>
       <c r="G244" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="245" spans="2:7" x14ac:dyDescent="0.25">
@@ -6797,17 +6988,17 @@
         <v>3</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E245" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F245" s="1"/>
       <c r="G245" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="246" spans="2:7" x14ac:dyDescent="0.25">
@@ -6815,10 +7006,10 @@
         <v>4</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>21</v>
@@ -6831,13 +7022,13 @@
         <v>5</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F247" s="1"/>
       <c r="G247" s="1"/>
@@ -6847,13 +7038,13 @@
         <v>6</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F248" s="1"/>
       <c r="G248" s="1"/>
@@ -6863,13 +7054,13 @@
         <v>7</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F249" s="1"/>
       <c r="G249" s="1"/>
@@ -6885,7 +7076,7 @@
         <v>30</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F250" s="1"/>
       <c r="G250" s="1"/>
@@ -6895,7 +7086,7 @@
         <v>0</v>
       </c>
       <c r="C252" s="7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D252" s="7"/>
       <c r="E252" s="2" t="s">
@@ -6909,17 +7100,17 @@
         <v>3</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D253" s="6"/>
       <c r="E253" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F253" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G253" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="254" spans="2:7" x14ac:dyDescent="0.25">
@@ -6947,10 +7138,10 @@
         <v>1</v>
       </c>
       <c r="C255" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D255" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="D255" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>14</v>
@@ -6965,10 +7156,10 @@
         <v>2</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>14</v>
@@ -6983,17 +7174,17 @@
         <v>3</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F257" s="1"/>
       <c r="G257" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="258" spans="2:7" x14ac:dyDescent="0.25">
@@ -7001,13 +7192,13 @@
         <v>4</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F258" s="1"/>
       <c r="G258" s="1"/>
@@ -7017,13 +7208,13 @@
         <v>5</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F259" s="1"/>
       <c r="G259" s="1"/>
@@ -7033,17 +7224,17 @@
         <v>6</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F260" s="1"/>
       <c r="G260" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="261" spans="2:7" x14ac:dyDescent="0.25">
@@ -7051,17 +7242,17 @@
         <v>7</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F261" s="1"/>
       <c r="G261" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="262" spans="2:7" x14ac:dyDescent="0.25">
@@ -7075,7 +7266,7 @@
         <v>30</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F262" s="1"/>
       <c r="G262" s="1"/>
@@ -7085,7 +7276,7 @@
         <v>0</v>
       </c>
       <c r="C264" s="7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D264" s="7"/>
       <c r="E264" s="2" t="s">
@@ -7099,14 +7290,14 @@
         <v>3</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D265" s="6"/>
       <c r="E265" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F265" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G265" s="6"/>
     </row>
@@ -7135,10 +7326,10 @@
         <v>1</v>
       </c>
       <c r="C267" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D267" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="D267" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>14</v>
@@ -7153,17 +7344,17 @@
         <v>2</v>
       </c>
       <c r="C268" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D268" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F268" s="1"/>
       <c r="G268" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="269" spans="2:7" x14ac:dyDescent="0.25">
@@ -7171,13 +7362,13 @@
         <v>3</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F269" s="1"/>
       <c r="G269" s="1"/>
@@ -7187,13 +7378,13 @@
         <v>4</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F270" s="1"/>
       <c r="G270" s="1"/>
@@ -7203,10 +7394,10 @@
         <v>5</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>21</v>
@@ -7219,17 +7410,17 @@
         <v>6</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F272" s="1"/>
       <c r="G272" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="273" spans="2:7" x14ac:dyDescent="0.25">
@@ -7237,13 +7428,13 @@
         <v>7</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F273" s="1"/>
       <c r="G273" s="1"/>
@@ -7259,7 +7450,7 @@
         <v>30</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F274" s="1"/>
       <c r="G274" s="1"/>
@@ -7269,13 +7460,13 @@
         <v>9</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F275" s="1"/>
       <c r="G275" s="1"/>
@@ -7285,7 +7476,7 @@
         <v>0</v>
       </c>
       <c r="C277" s="7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D277" s="7"/>
       <c r="E277" s="2" t="s">
@@ -7299,7 +7490,7 @@
         <v>3</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D278" s="6"/>
       <c r="E278" s="2" t="s">
@@ -7333,10 +7524,10 @@
         <v>1</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>14</v>
@@ -7351,17 +7542,17 @@
         <v>2</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F281" s="1"/>
       <c r="G281" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="282" spans="2:7" x14ac:dyDescent="0.25">
@@ -7369,10 +7560,10 @@
         <v>3</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>14</v>
@@ -7385,17 +7576,17 @@
         <v>4</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F283" s="1"/>
       <c r="G283" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="284" spans="2:7" x14ac:dyDescent="0.25">
@@ -7403,17 +7594,17 @@
         <v>5</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F284" s="1"/>
       <c r="G284" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="285" spans="2:7" x14ac:dyDescent="0.25">
@@ -7421,13 +7612,13 @@
         <v>6</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F285" s="1"/>
       <c r="G285" s="1"/>
@@ -7437,13 +7628,13 @@
         <v>7</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F286" s="1"/>
       <c r="G286" s="1"/>
@@ -7453,13 +7644,13 @@
         <v>8</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F287" s="1"/>
       <c r="G287" s="1"/>
@@ -7475,7 +7666,7 @@
         <v>30</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F288" s="1"/>
       <c r="G288" s="1"/>
@@ -7485,7 +7676,7 @@
         <v>0</v>
       </c>
       <c r="C290" s="7" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D290" s="7"/>
       <c r="E290" s="2" t="s">
@@ -7499,17 +7690,17 @@
         <v>3</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D291" s="6"/>
       <c r="E291" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F291" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G291" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="292" spans="2:7" x14ac:dyDescent="0.25">
@@ -7537,10 +7728,10 @@
         <v>1</v>
       </c>
       <c r="C293" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D293" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>358</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>14</v>
@@ -7555,17 +7746,17 @@
         <v>2</v>
       </c>
       <c r="C294" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D294" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F294" s="1"/>
       <c r="G294" s="1" t="s">
-        <v>35</v>
+        <v>591</v>
       </c>
     </row>
     <row r="295" spans="2:7" x14ac:dyDescent="0.25">
@@ -7573,17 +7764,17 @@
         <v>3</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F295" s="1"/>
       <c r="G295" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="296" spans="2:7" x14ac:dyDescent="0.25">
@@ -7591,13 +7782,13 @@
         <v>4</v>
       </c>
       <c r="C296" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D296" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D296" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="E296" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F296" s="1"/>
       <c r="G296" s="1"/>
@@ -7607,17 +7798,17 @@
         <v>5</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F297" s="1"/>
       <c r="G297" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="298" spans="2:7" x14ac:dyDescent="0.25">
@@ -7625,10 +7816,10 @@
         <v>6</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>14</v>
@@ -7641,13 +7832,13 @@
         <v>7</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F299" s="1"/>
       <c r="G299" s="1"/>
@@ -7657,13 +7848,13 @@
         <v>8</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F300" s="1"/>
       <c r="G300" s="1"/>
@@ -7673,13 +7864,13 @@
         <v>9</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F301" s="1"/>
       <c r="G301" s="1"/>
@@ -7689,7 +7880,7 @@
         <v>0</v>
       </c>
       <c r="C303" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D303" s="7"/>
       <c r="E303" s="2" t="s">
@@ -7703,14 +7894,14 @@
         <v>3</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D304" s="6"/>
       <c r="E304" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F304" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G304" s="6"/>
     </row>
@@ -7739,13 +7930,13 @@
         <v>1</v>
       </c>
       <c r="C306" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D306" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="D306" s="1" t="s">
-        <v>370</v>
-      </c>
       <c r="E306" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F306" s="1"/>
       <c r="G306" s="1" t="s">
@@ -7757,17 +7948,17 @@
         <v>2</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F307" s="1"/>
       <c r="G307" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="308" spans="2:7" x14ac:dyDescent="0.25">
@@ -7775,17 +7966,17 @@
         <v>3</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F308" s="1"/>
       <c r="G308" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="309" spans="2:7" x14ac:dyDescent="0.25">
@@ -7793,13 +7984,13 @@
         <v>4</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F309" s="1"/>
       <c r="G309" s="1"/>
@@ -7809,13 +8000,13 @@
         <v>5</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F310" s="1"/>
       <c r="G310" s="1"/>
@@ -7825,10 +8016,10 @@
         <v>6</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E311" s="1" t="s">
         <v>14</v>
@@ -7841,13 +8032,13 @@
         <v>7</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F312" s="1"/>
       <c r="G312" s="1"/>
@@ -7863,7 +8054,7 @@
         <v>30</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F313" s="1"/>
       <c r="G313" s="1"/>
@@ -7879,7 +8070,7 @@
         <v>34</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F314" s="1"/>
       <c r="G314" s="1"/>
@@ -7889,7 +8080,7 @@
         <v>0</v>
       </c>
       <c r="C316" s="7" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D316" s="7"/>
       <c r="E316" s="2" t="s">
@@ -7903,17 +8094,17 @@
         <v>3</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D317" s="6"/>
       <c r="E317" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F317" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G317" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="318" spans="2:7" x14ac:dyDescent="0.25">
@@ -7941,13 +8132,13 @@
         <v>1</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F319" s="1"/>
       <c r="G319" s="1" t="s">
@@ -7959,17 +8150,17 @@
         <v>2</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F320" s="1"/>
       <c r="G320" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="321" spans="2:7" x14ac:dyDescent="0.25">
@@ -7977,17 +8168,17 @@
         <v>3</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F321" s="1"/>
       <c r="G321" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="322" spans="2:7" x14ac:dyDescent="0.25">
@@ -7995,13 +8186,13 @@
         <v>4</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F322" s="1"/>
       <c r="G322" s="1" t="s">
@@ -8013,13 +8204,13 @@
         <v>5</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F323" s="1"/>
       <c r="G323" s="1"/>
@@ -8029,13 +8220,13 @@
         <v>6</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F324" s="1"/>
       <c r="G324" s="1"/>
@@ -8045,13 +8236,13 @@
         <v>7</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F325" s="1"/>
       <c r="G325" s="1"/>
@@ -8061,13 +8252,13 @@
         <v>8</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F326" s="1"/>
       <c r="G326" s="1"/>
@@ -8077,13 +8268,13 @@
         <v>9</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F327" s="1"/>
       <c r="G327" s="1"/>
@@ -8093,10 +8284,10 @@
         <v>10</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E328" s="1" t="s">
         <v>14</v>
@@ -8109,10 +8300,10 @@
         <v>11</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>14</v>
@@ -8125,10 +8316,10 @@
         <v>12</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>14</v>
@@ -8141,17 +8332,17 @@
         <v>13</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F331" s="1"/>
       <c r="G331" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="332" spans="2:7" x14ac:dyDescent="0.25">
@@ -8165,7 +8356,7 @@
         <v>30</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F332" s="1"/>
       <c r="G332" s="1"/>
@@ -8181,7 +8372,7 @@
         <v>34</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F333" s="1"/>
       <c r="G333" s="1"/>
@@ -8191,7 +8382,7 @@
         <v>0</v>
       </c>
       <c r="C335" s="7" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D335" s="7"/>
       <c r="E335" s="2" t="s">
@@ -8205,14 +8396,14 @@
         <v>3</v>
       </c>
       <c r="C336" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D336" s="6"/>
       <c r="E336" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F336" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="G336" s="6"/>
     </row>
@@ -8241,13 +8432,13 @@
         <v>1</v>
       </c>
       <c r="C338" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="D338" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D338" s="1" t="s">
-        <v>409</v>
-      </c>
       <c r="E338" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F338" s="1"/>
       <c r="G338" s="1" t="s">
@@ -8259,17 +8450,17 @@
         <v>2</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F339" s="1"/>
       <c r="G339" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="340" spans="2:7" x14ac:dyDescent="0.25">
@@ -8277,13 +8468,13 @@
         <v>3</v>
       </c>
       <c r="C340" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D340" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D340" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="E340" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F340" s="1"/>
       <c r="G340" s="1"/>
@@ -8293,17 +8484,17 @@
         <v>4</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F341" s="1"/>
       <c r="G341" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="342" spans="2:7" x14ac:dyDescent="0.25">
@@ -8311,13 +8502,13 @@
         <v>5</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F342" s="1"/>
       <c r="G342" s="1"/>
@@ -8327,13 +8518,13 @@
         <v>6</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F343" s="1"/>
       <c r="G343" s="1"/>
@@ -8343,13 +8534,13 @@
         <v>7</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F344" s="1"/>
       <c r="G344" s="1"/>
@@ -8365,7 +8556,7 @@
         <v>30</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F345" s="1"/>
       <c r="G345" s="1"/>
@@ -8375,7 +8566,7 @@
         <v>0</v>
       </c>
       <c r="C347" s="7" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D347" s="7"/>
       <c r="E347" s="2" t="s">
@@ -8389,17 +8580,17 @@
         <v>3</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D348" s="6"/>
       <c r="E348" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F348" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="G348" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="349" spans="2:7" x14ac:dyDescent="0.25">
@@ -8427,13 +8618,13 @@
         <v>1</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F350" s="1"/>
       <c r="G350" s="1" t="s">
@@ -8445,17 +8636,17 @@
         <v>2</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F351" s="1"/>
       <c r="G351" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="352" spans="2:7" x14ac:dyDescent="0.25">
@@ -8463,13 +8654,13 @@
         <v>3</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F352" s="1"/>
       <c r="G352" s="1"/>
@@ -8479,13 +8670,13 @@
         <v>4</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F353" s="1"/>
       <c r="G353" s="1" t="s">
@@ -8497,13 +8688,13 @@
         <v>5</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F354" s="1"/>
       <c r="G354" s="1"/>
@@ -8513,13 +8704,13 @@
         <v>6</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F355" s="1"/>
       <c r="G355" s="1"/>
@@ -8529,13 +8720,13 @@
         <v>7</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F356" s="1"/>
       <c r="G356" s="1"/>
@@ -8545,17 +8736,17 @@
         <v>8</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F357" s="1"/>
       <c r="G357" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="358" spans="2:7" x14ac:dyDescent="0.25">
@@ -8563,17 +8754,17 @@
         <v>9</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F358" s="1"/>
       <c r="G358" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="359" spans="2:7" x14ac:dyDescent="0.25">
@@ -8581,17 +8772,17 @@
         <v>10</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F359" s="1"/>
       <c r="G359" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="360" spans="2:7" x14ac:dyDescent="0.25">
@@ -8605,7 +8796,7 @@
         <v>30</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F360" s="1"/>
       <c r="G360" s="1"/>
@@ -8621,7 +8812,7 @@
         <v>33</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F361" s="1"/>
       <c r="G361" s="1"/>
@@ -8631,7 +8822,7 @@
         <v>0</v>
       </c>
       <c r="C363" s="7" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D363" s="7"/>
       <c r="E363" s="2" t="s">
@@ -8645,7 +8836,7 @@
         <v>3</v>
       </c>
       <c r="C364" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D364" s="6"/>
       <c r="E364" s="2" t="s">
@@ -8679,17 +8870,17 @@
         <v>1</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F366" s="1"/>
       <c r="G366" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="367" spans="2:7" x14ac:dyDescent="0.25">
@@ -8697,19 +8888,19 @@
         <v>2</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F367" s="1">
         <v>50</v>
       </c>
       <c r="G367" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="368" spans="2:7" x14ac:dyDescent="0.25">
@@ -8717,17 +8908,17 @@
         <v>3</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F368" s="1"/>
       <c r="G368" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="369" spans="2:9" x14ac:dyDescent="0.25">
@@ -8735,7 +8926,7 @@
         <v>12</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D369" s="1"/>
       <c r="E369" s="1"/>
@@ -8747,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="C371" s="8" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D371" s="8"/>
       <c r="E371" s="3" t="s">
@@ -8762,7 +8953,7 @@
         <v>3</v>
       </c>
       <c r="C372" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D372" s="9"/>
       <c r="E372" s="3" t="s">
@@ -8798,17 +8989,17 @@
         <v>1</v>
       </c>
       <c r="C374" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="D374" s="4" t="s">
         <v>547</v>
-      </c>
-      <c r="D374" s="4" t="s">
-        <v>549</v>
       </c>
       <c r="E374" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F374" s="4"/>
       <c r="G374" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I374"/>
     </row>
@@ -8817,17 +9008,17 @@
         <v>2</v>
       </c>
       <c r="C375" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="D375" s="4" t="s">
         <v>548</v>
-      </c>
-      <c r="D375" s="4" t="s">
-        <v>550</v>
       </c>
       <c r="E375" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F375" s="4"/>
       <c r="G375" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="I375"/>
     </row>
@@ -8836,17 +9027,17 @@
         <v>3</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E376" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F376" s="4"/>
       <c r="G376" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="I376"/>
     </row>
@@ -8855,7 +9046,7 @@
         <v>12</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D377" s="4"/>
       <c r="E377" s="4"/>
@@ -8868,7 +9059,7 @@
         <v>0</v>
       </c>
       <c r="C379" s="7" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D379" s="7"/>
       <c r="E379" s="2" t="s">
@@ -8882,17 +9073,17 @@
         <v>3</v>
       </c>
       <c r="C380" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D380" s="6"/>
       <c r="E380" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F380" s="7" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="G380" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="381" spans="2:9" x14ac:dyDescent="0.25">
@@ -8920,17 +9111,17 @@
         <v>1</v>
       </c>
       <c r="C382" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D382" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D382" s="1" t="s">
-        <v>450</v>
-      </c>
       <c r="E382" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F382" s="1"/>
       <c r="G382" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="383" spans="2:9" x14ac:dyDescent="0.25">
@@ -8938,13 +9129,13 @@
         <v>2</v>
       </c>
       <c r="C383" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D383" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D383" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="E383" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F383" s="1"/>
       <c r="G383" s="1" t="s">
@@ -8956,7 +9147,7 @@
         <v>3</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D384" s="1" t="s">
         <v>17</v>
@@ -8974,19 +9165,19 @@
         <v>4</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F385" s="1">
         <v>120</v>
       </c>
       <c r="G385" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="386" spans="2:7" x14ac:dyDescent="0.25">
@@ -8994,19 +9185,19 @@
         <v>5</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F386" s="1">
         <v>100</v>
       </c>
       <c r="G386" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="387" spans="2:7" x14ac:dyDescent="0.25">
@@ -9014,17 +9205,17 @@
         <v>6</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F387" s="1"/>
       <c r="G387" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="388" spans="2:7" x14ac:dyDescent="0.25">
@@ -9032,19 +9223,19 @@
         <v>7</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F388" s="1">
         <v>255</v>
       </c>
       <c r="G388" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="389" spans="2:7" x14ac:dyDescent="0.25">
@@ -9052,13 +9243,13 @@
         <v>8</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F389" s="1">
         <v>30</v>
@@ -9070,13 +9261,13 @@
         <v>9</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F390" s="1">
         <v>255</v>
@@ -9088,13 +9279,13 @@
         <v>10</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F391" s="1">
         <v>255</v>
@@ -9106,13 +9297,13 @@
         <v>11</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F392" s="1"/>
       <c r="G392" s="1"/>
@@ -9122,13 +9313,13 @@
         <v>12</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F393" s="1"/>
       <c r="G393" s="1"/>
@@ -9138,17 +9329,17 @@
         <v>13</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D394" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F394" s="1"/>
       <c r="G394" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="395" spans="2:7" x14ac:dyDescent="0.25">
@@ -9156,17 +9347,17 @@
         <v>14</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F395" s="1"/>
       <c r="G395" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="396" spans="2:7" x14ac:dyDescent="0.25">
@@ -9180,11 +9371,11 @@
         <v>30</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F396" s="1"/>
       <c r="G396" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="397" spans="2:7" x14ac:dyDescent="0.25">
@@ -9198,11 +9389,11 @@
         <v>33</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F397" s="1"/>
       <c r="G397" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="398" spans="2:7" x14ac:dyDescent="0.25">
@@ -9210,13 +9401,13 @@
         <v>17</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F398" s="1"/>
       <c r="G398" s="1"/>
@@ -9226,13 +9417,13 @@
         <v>18</v>
       </c>
       <c r="C399" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="D399" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="E399" s="1" t="s">
         <v>555</v>
-      </c>
-      <c r="D399" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="E399" s="1" t="s">
-        <v>557</v>
       </c>
       <c r="F399" s="1"/>
       <c r="G399" s="1"/>
@@ -9242,19 +9433,19 @@
         <v>12</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D400" s="1"/>
       <c r="E400" s="1"/>
       <c r="F400" s="1"/>
       <c r="G400" s="1"/>
     </row>
-    <row r="402" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B402" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C402" s="7" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D402" s="7"/>
       <c r="E402" s="2" t="s">
@@ -9263,23 +9454,23 @@
       <c r="F402" s="6"/>
       <c r="G402" s="6"/>
     </row>
-    <row r="403" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B403" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C403" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D403" s="6"/>
       <c r="E403" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F403" s="6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G403" s="6"/>
     </row>
-    <row r="404" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B404" s="2" t="s">
         <v>7</v>
       </c>
@@ -9299,15 +9490,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="405" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B405" s="1">
         <v>1</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>14</v>
@@ -9317,15 +9508,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="406" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B406" s="1">
         <v>2</v>
       </c>
       <c r="C406" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D406" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="D406" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>14</v>
@@ -9335,45 +9526,45 @@
         <v>35</v>
       </c>
     </row>
-    <row r="407" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B407" s="1">
         <v>3</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F407" s="1">
         <v>50</v>
       </c>
       <c r="G407" s="1" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="408" spans="2:7" x14ac:dyDescent="0.25">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="408" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B408" s="1">
         <v>4</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D408" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F408" s="1"/>
       <c r="G408" s="1" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="409" spans="2:7" x14ac:dyDescent="0.25">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="409" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B409" s="1">
         <v>5</v>
       </c>
@@ -9384,19 +9575,22 @@
         <v>30</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F409" s="1"/>
       <c r="G409" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="411" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I409" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="411" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B411" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C411" s="7" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D411" s="7"/>
       <c r="E411" s="2" t="s">
@@ -9405,12 +9599,12 @@
       <c r="F411" s="6"/>
       <c r="G411" s="6"/>
     </row>
-    <row r="412" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B412" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C412" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D412" s="6"/>
       <c r="E412" s="2" t="s">
@@ -9419,7 +9613,7 @@
       <c r="F412" s="6"/>
       <c r="G412" s="6"/>
     </row>
-    <row r="413" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B413" s="2" t="s">
         <v>7</v>
       </c>
@@ -9439,15 +9633,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="414" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B414" s="1">
         <v>1</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>14</v>
@@ -9457,103 +9651,103 @@
         <v>15</v>
       </c>
     </row>
-    <row r="415" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B415" s="1">
         <v>2</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F415" s="1">
         <v>100</v>
       </c>
       <c r="G415" s="1" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="416" spans="2:7" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="416" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B416" s="1">
         <v>3</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F416" s="1">
         <v>50</v>
       </c>
       <c r="G416" s="1" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="417" spans="2:7" x14ac:dyDescent="0.25">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="417" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B417" s="1">
         <v>4</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F417" s="1"/>
       <c r="G417" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="418" spans="2:7" x14ac:dyDescent="0.25">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="418" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B418" s="1">
         <v>5</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F418" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="G418" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="G418" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="419" spans="2:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="419" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B419" s="1">
         <v>6</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F419" s="1"/>
       <c r="G419" s="1" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="420" spans="2:7" x14ac:dyDescent="0.25">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="420" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B420" s="1">
         <v>7</v>
       </c>
@@ -9564,17 +9758,20 @@
         <v>30</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F420" s="1"/>
       <c r="G420" s="1"/>
-    </row>
-    <row r="422" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I420" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="422" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B422" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C422" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D422" s="7"/>
       <c r="E422" s="2" t="s">
@@ -9583,23 +9780,23 @@
       <c r="F422" s="6"/>
       <c r="G422" s="6"/>
     </row>
-    <row r="423" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B423" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C423" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D423" s="6"/>
       <c r="E423" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F423" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G423" s="6"/>
     </row>
-    <row r="424" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B424" s="2" t="s">
         <v>7</v>
       </c>
@@ -9619,15 +9816,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="425" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B425" s="1">
         <v>1</v>
       </c>
       <c r="C425" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D425" s="1" t="s">
         <v>492</v>
-      </c>
-      <c r="D425" s="1" t="s">
-        <v>494</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>14</v>
@@ -9637,83 +9834,83 @@
         <v>15</v>
       </c>
     </row>
-    <row r="426" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B426" s="1">
         <v>2</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F426" s="1"/>
       <c r="G426" s="1" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="427" spans="2:7" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="427" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B427" s="1">
         <v>3</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F427" s="1"/>
       <c r="G427" s="1" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="428" spans="2:7" x14ac:dyDescent="0.25">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="428" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B428" s="1">
         <v>4</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="429" spans="2:7" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="429" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B429" s="1">
         <v>5</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="430" spans="2:7" x14ac:dyDescent="0.25">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="430" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B430" s="1">
         <v>6</v>
       </c>
@@ -9721,20 +9918,23 @@
         <v>29</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F430" s="1"/>
       <c r="G430" s="1"/>
-    </row>
-    <row r="432" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I430" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="432" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B432" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C432" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D432" s="7"/>
       <c r="E432" s="2" t="s">
@@ -9748,14 +9948,14 @@
         <v>3</v>
       </c>
       <c r="C433" s="6" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D433" s="6"/>
       <c r="E433" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F433" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G433" s="6"/>
     </row>
@@ -9784,19 +9984,19 @@
         <v>1</v>
       </c>
       <c r="C435" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D435" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="D435" s="1" t="s">
-        <v>510</v>
-      </c>
       <c r="E435" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F435" s="1">
         <v>24</v>
       </c>
       <c r="G435" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="436" spans="2:7" x14ac:dyDescent="0.25">
@@ -9804,17 +10004,17 @@
         <v>2</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F436" s="1"/>
       <c r="G436" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="437" spans="2:7" x14ac:dyDescent="0.25">
@@ -9822,16 +10022,16 @@
         <v>3</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G437" s="1"/>
     </row>
@@ -9840,13 +10040,13 @@
         <v>4</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F438" s="1">
         <v>500</v>
@@ -10005,6 +10205,16 @@
     <mergeCell ref="F423:G423"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"DATETIME2"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:G999 I40">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="USER.user_id">
+      <formula>NOT(ISERROR(SEARCH("USER.user_id",B1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Document/專題/db_diagram.xlsx
+++ b/Document/專題/db_diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\RentalManagementPlatform\Document\專題\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE122EB-4B70-4E2F-B6FC-CBCAAD86F1E3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CBDBB0-405F-413B-B707-E7D1629092EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2184,7 +2184,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/m/d\ h:mm;@"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2843,7 +2843,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2889,18 +2889,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="8">
       <alignment vertical="center"/>
     </xf>
@@ -2910,11 +2898,23 @@
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="7">
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2922,7 +2922,10 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" xfId="7" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3306,7 +3309,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:P438"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="40.5" bestFit="1" customWidth="1"/>
@@ -3320,37 +3323,37 @@
     <col min="13" max="16" width="12.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="82.5" customHeight="1">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="20" t="s">
         <v>590</v>
       </c>
-      <c r="D2" s="16"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+    </row>
+    <row r="3" spans="2:9">
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="15"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="15"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G3" s="21"/>
+    </row>
+    <row r="4" spans="2:9">
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
@@ -3370,7 +3373,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -3388,7 +3391,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -3406,7 +3409,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -3426,7 +3429,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -3446,7 +3449,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -3464,7 +3467,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9">
       <c r="B10" s="1">
         <v>6</v>
       </c>
@@ -3485,7 +3488,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9">
       <c r="B11" s="1">
         <v>7</v>
       </c>
@@ -3506,39 +3509,39 @@
         <v>592</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" ht="16.5" customHeight="1">
       <c r="B13" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="20" t="s">
         <v>572</v>
       </c>
-      <c r="D13" s="16"/>
+      <c r="D13" s="20"/>
       <c r="E13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+    </row>
+    <row r="14" spans="2:9">
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="21" t="s">
         <v>571</v>
       </c>
-      <c r="D14" s="15"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="20" t="s">
         <v>567</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="21" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9">
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
@@ -3558,7 +3561,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9">
       <c r="B16" s="1">
         <v>1</v>
       </c>
@@ -3576,7 +3579,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9">
       <c r="B17" s="1">
         <v>2</v>
       </c>
@@ -3594,7 +3597,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9">
       <c r="B18" s="1">
         <v>3</v>
       </c>
@@ -3612,7 +3615,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9">
       <c r="B19" s="1">
         <v>4</v>
       </c>
@@ -3630,7 +3633,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9">
       <c r="B20" s="1">
         <v>5</v>
       </c>
@@ -3646,7 +3649,7 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9">
       <c r="B21" s="1">
         <v>6</v>
       </c>
@@ -3667,7 +3670,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9">
       <c r="B22" s="1">
         <v>7</v>
       </c>
@@ -3688,7 +3691,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9">
       <c r="B23" s="1">
         <v>8</v>
       </c>
@@ -3706,7 +3709,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9">
       <c r="B24" s="1">
         <v>9</v>
       </c>
@@ -3722,7 +3725,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9">
       <c r="B25" s="1">
         <v>10</v>
       </c>
@@ -3738,7 +3741,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9">
       <c r="B26" s="1">
         <v>11</v>
       </c>
@@ -3754,7 +3757,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9">
       <c r="B27" s="1">
         <v>12</v>
       </c>
@@ -3772,7 +3775,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9">
       <c r="B28" s="1">
         <v>13</v>
       </c>
@@ -3791,35 +3794,35 @@
         <v>606</v>
       </c>
     </row>
-    <row r="30" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9" ht="16.5" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="16"/>
+      <c r="D30" s="20"/>
       <c r="E30" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+    </row>
+    <row r="31" spans="2:9">
       <c r="B31" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="D31" s="15"/>
+      <c r="D31" s="21"/>
       <c r="E31" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+    </row>
+    <row r="32" spans="2:9">
       <c r="B32" s="2" t="s">
         <v>6</v>
       </c>
@@ -3839,7 +3842,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:16">
       <c r="B33" s="1">
         <v>1</v>
       </c>
@@ -3857,7 +3860,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:16">
       <c r="B34" s="1">
         <v>2</v>
       </c>
@@ -3875,7 +3878,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:16">
       <c r="B35" s="1">
         <v>3</v>
       </c>
@@ -3893,7 +3896,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:16">
       <c r="B36" s="1">
         <v>4</v>
       </c>
@@ -3911,7 +3914,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:16">
       <c r="B37" s="1">
         <v>5</v>
       </c>
@@ -3929,7 +3932,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:16">
       <c r="B38" s="1">
         <v>6</v>
       </c>
@@ -3947,7 +3950,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:16">
       <c r="B39" s="1">
         <v>7</v>
       </c>
@@ -3963,7 +3966,7 @@
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:16">
       <c r="B40" s="1">
         <v>8</v>
       </c>
@@ -3984,7 +3987,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:16">
       <c r="B41" s="1">
         <v>9</v>
       </c>
@@ -4002,7 +4005,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:16">
       <c r="B42" s="1">
         <v>10</v>
       </c>
@@ -4018,7 +4021,7 @@
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:16">
       <c r="B43" s="1">
         <v>11</v>
       </c>
@@ -4034,7 +4037,7 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:16">
       <c r="B44" s="1">
         <v>12</v>
       </c>
@@ -4052,7 +4055,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:16">
       <c r="B45" s="1">
         <v>13</v>
       </c>
@@ -4094,7 +4097,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:16">
       <c r="B46" s="1">
         <v>14</v>
       </c>
@@ -4136,7 +4139,7 @@
         <v>45897</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:16">
       <c r="B47" s="1">
         <v>15</v>
       </c>
@@ -4176,37 +4179,37 @@
         <v>45897</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:7" ht="16.5" customHeight="1">
       <c r="B49" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="D49" s="16"/>
+      <c r="D49" s="20"/>
       <c r="E49" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F49" s="21"/>
+      <c r="G49" s="21"/>
+    </row>
+    <row r="50" spans="2:7">
       <c r="B50" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="C50" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="D50" s="15"/>
+      <c r="D50" s="21"/>
       <c r="E50" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F50" s="15" t="s">
+      <c r="F50" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="G50" s="15"/>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G50" s="21"/>
+    </row>
+    <row r="51" spans="2:7">
       <c r="B51" s="2" t="s">
         <v>6</v>
       </c>
@@ -4226,7 +4229,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:7">
       <c r="B52" s="1">
         <v>1</v>
       </c>
@@ -4244,7 +4247,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:7">
       <c r="B53" s="1">
         <v>2</v>
       </c>
@@ -4262,7 +4265,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:7">
       <c r="B54" s="1">
         <v>3</v>
       </c>
@@ -4280,7 +4283,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:7">
       <c r="B55" s="1">
         <v>4</v>
       </c>
@@ -4298,35 +4301,35 @@
         <v>98</v>
       </c>
     </row>
-    <row r="57" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:7" ht="16.5" customHeight="1">
       <c r="B57" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C57" s="16" t="s">
+      <c r="C57" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="16"/>
+      <c r="D57" s="20"/>
       <c r="E57" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-    </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F57" s="21"/>
+      <c r="G57" s="21"/>
+    </row>
+    <row r="58" spans="2:7">
       <c r="B58" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="C58" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="D58" s="15"/>
+      <c r="D58" s="21"/>
       <c r="E58" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15"/>
-    </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+    </row>
+    <row r="59" spans="2:7">
       <c r="B59" s="2" t="s">
         <v>6</v>
       </c>
@@ -4346,7 +4349,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:7">
       <c r="B60" s="1">
         <v>1</v>
       </c>
@@ -4364,7 +4367,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:7">
       <c r="B61" s="1">
         <v>2</v>
       </c>
@@ -4382,35 +4385,35 @@
         <v>104</v>
       </c>
     </row>
-    <row r="63" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:7" ht="16.5" customHeight="1">
       <c r="B63" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C63" s="16" t="s">
+      <c r="C63" s="20" t="s">
         <v>547</v>
       </c>
-      <c r="D63" s="16"/>
+      <c r="D63" s="20"/>
       <c r="E63" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-    </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F63" s="21"/>
+      <c r="G63" s="21"/>
+    </row>
+    <row r="64" spans="2:7">
       <c r="B64" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="C64" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D64" s="15"/>
+      <c r="D64" s="21"/>
       <c r="E64" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F64" s="15"/>
-      <c r="G64" s="15"/>
-    </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
+    </row>
+    <row r="65" spans="2:9">
       <c r="B65" s="2" t="s">
         <v>6</v>
       </c>
@@ -4430,7 +4433,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9">
       <c r="B66" s="1">
         <v>1</v>
       </c>
@@ -4448,7 +4451,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9">
       <c r="B67" s="1">
         <v>2</v>
       </c>
@@ -4466,7 +4469,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9">
       <c r="B68" s="1">
         <v>3</v>
       </c>
@@ -4482,7 +4485,7 @@
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9">
       <c r="B69" s="1">
         <v>4</v>
       </c>
@@ -4500,7 +4503,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="70" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" s="5" customFormat="1">
       <c r="B70" s="4">
         <v>5</v>
       </c>
@@ -4519,7 +4522,7 @@
       </c>
       <c r="I70"/>
     </row>
-    <row r="71" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" s="5" customFormat="1">
       <c r="B71" s="4">
         <v>6</v>
       </c>
@@ -4538,7 +4541,7 @@
       </c>
       <c r="I71"/>
     </row>
-    <row r="72" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9" s="5" customFormat="1">
       <c r="B72" s="4">
         <v>7</v>
       </c>
@@ -4559,7 +4562,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="73" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9" s="5" customFormat="1">
       <c r="B73" s="4">
         <v>8</v>
       </c>
@@ -4580,7 +4583,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:9">
       <c r="B74" s="1">
         <v>9</v>
       </c>
@@ -4598,7 +4601,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:9">
       <c r="B75" s="1">
         <v>10</v>
       </c>
@@ -4616,7 +4619,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9">
       <c r="B76" s="1">
         <v>11</v>
       </c>
@@ -4635,7 +4638,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9">
       <c r="B77" s="1">
         <v>12</v>
       </c>
@@ -4653,60 +4656,60 @@
         <v>123</v>
       </c>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B78" s="1">
+    <row r="78" spans="2:9" s="10" customFormat="1">
+      <c r="B78" s="26">
         <v>13</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D78" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="E78" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
       <c r="I78" s="10" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="80" spans="2:9" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9" s="5" customFormat="1" ht="16.5" customHeight="1">
       <c r="B80" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C80" s="17" t="s">
+      <c r="C80" s="22" t="s">
         <v>548</v>
       </c>
-      <c r="D80" s="17"/>
+      <c r="D80" s="22"/>
       <c r="E80" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F80" s="18"/>
-      <c r="G80" s="18"/>
+      <c r="F80" s="23"/>
+      <c r="G80" s="23"/>
       <c r="I80"/>
     </row>
-    <row r="81" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9" s="5" customFormat="1">
       <c r="B81" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C81" s="18" t="s">
+      <c r="C81" s="23" t="s">
         <v>542</v>
       </c>
-      <c r="D81" s="18"/>
+      <c r="D81" s="23"/>
       <c r="E81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F81" s="17" t="s">
+      <c r="F81" s="22" t="s">
         <v>546</v>
       </c>
-      <c r="G81" s="18" t="s">
+      <c r="G81" s="23" t="s">
         <v>37</v>
       </c>
       <c r="I81"/>
     </row>
-    <row r="82" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9" s="5" customFormat="1">
       <c r="B82" s="3" t="s">
         <v>6</v>
       </c>
@@ -4727,7 +4730,7 @@
       </c>
       <c r="I82"/>
     </row>
-    <row r="83" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" s="5" customFormat="1">
       <c r="B83" s="4">
         <v>1</v>
       </c>
@@ -4746,7 +4749,7 @@
       </c>
       <c r="I83"/>
     </row>
-    <row r="84" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" s="5" customFormat="1">
       <c r="B84" s="4">
         <v>2</v>
       </c>
@@ -4765,7 +4768,7 @@
       </c>
       <c r="I84"/>
     </row>
-    <row r="85" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9" s="5" customFormat="1">
       <c r="B85" s="4">
         <v>3</v>
       </c>
@@ -4784,39 +4787,39 @@
       </c>
       <c r="I85"/>
     </row>
-    <row r="87" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9" ht="16.5" customHeight="1">
       <c r="B87" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C87" s="16" t="s">
+      <c r="C87" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="D87" s="16"/>
+      <c r="D87" s="20"/>
       <c r="E87" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F87" s="15"/>
-      <c r="G87" s="15"/>
-    </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F87" s="21"/>
+      <c r="G87" s="21"/>
+    </row>
+    <row r="88" spans="2:9">
       <c r="B88" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C88" s="15" t="s">
+      <c r="C88" s="21" t="s">
         <v>604</v>
       </c>
-      <c r="D88" s="15"/>
+      <c r="D88" s="21"/>
       <c r="E88" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F88" s="15" t="s">
+      <c r="F88" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="G88" s="15" t="s">
+      <c r="G88" s="21" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9">
       <c r="B89" s="2" t="s">
         <v>6</v>
       </c>
@@ -4836,7 +4839,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9">
       <c r="B90" s="1">
         <v>1</v>
       </c>
@@ -4854,7 +4857,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9">
       <c r="B91" s="1">
         <v>2</v>
       </c>
@@ -4872,7 +4875,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9">
       <c r="B92" s="1">
         <v>3</v>
       </c>
@@ -4890,7 +4893,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9">
       <c r="B93" s="1">
         <v>4</v>
       </c>
@@ -4909,7 +4912,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9">
       <c r="B94" s="1">
         <v>5</v>
       </c>
@@ -4928,37 +4931,37 @@
         <v>605</v>
       </c>
     </row>
-    <row r="96" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9" ht="16.5" customHeight="1">
       <c r="B96" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C96" s="16" t="s">
+      <c r="C96" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="D96" s="16"/>
+      <c r="D96" s="20"/>
       <c r="E96" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F96" s="15"/>
-      <c r="G96" s="15"/>
-    </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F96" s="21"/>
+      <c r="G96" s="21"/>
+    </row>
+    <row r="97" spans="2:9">
       <c r="B97" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C97" s="15" t="s">
+      <c r="C97" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D97" s="15"/>
+      <c r="D97" s="21"/>
       <c r="E97" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F97" s="15" t="s">
+      <c r="F97" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="G97" s="15"/>
-    </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G97" s="21"/>
+    </row>
+    <row r="98" spans="2:9">
       <c r="B98" s="2" t="s">
         <v>6</v>
       </c>
@@ -4978,7 +4981,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9">
       <c r="B99" s="1">
         <v>1</v>
       </c>
@@ -4996,7 +4999,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9">
       <c r="B100" s="1">
         <v>2</v>
       </c>
@@ -5014,7 +5017,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9">
       <c r="B101" s="1">
         <v>3</v>
       </c>
@@ -5032,39 +5035,39 @@
         <v>136</v>
       </c>
     </row>
-    <row r="103" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" ht="16.5" customHeight="1">
       <c r="B103" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C103" s="17" t="s">
+      <c r="C103" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="D103" s="17"/>
+      <c r="D103" s="22"/>
       <c r="E103" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F103" s="18"/>
-      <c r="G103" s="18"/>
-    </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F103" s="23"/>
+      <c r="G103" s="23"/>
+    </row>
+    <row r="104" spans="2:9">
       <c r="B104" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C104" s="18" t="s">
+      <c r="C104" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="D104" s="18"/>
+      <c r="D104" s="23"/>
       <c r="E104" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F104" s="17" t="s">
+      <c r="F104" s="22" t="s">
         <v>566</v>
       </c>
-      <c r="G104" s="18" t="s">
+      <c r="G104" s="23" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:9">
       <c r="B105" s="3" t="s">
         <v>6</v>
       </c>
@@ -5084,7 +5087,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:9">
       <c r="B106" s="4">
         <v>1</v>
       </c>
@@ -5102,7 +5105,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="107" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:9" s="5" customFormat="1">
       <c r="B107" s="4">
         <v>2</v>
       </c>
@@ -5121,7 +5124,7 @@
       </c>
       <c r="I107"/>
     </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:9">
       <c r="B108" s="4">
         <v>3</v>
       </c>
@@ -5139,7 +5142,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:9">
       <c r="B109" s="4">
         <v>4</v>
       </c>
@@ -5157,7 +5160,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:9">
       <c r="B110" s="4">
         <v>5</v>
       </c>
@@ -5175,7 +5178,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:9">
       <c r="B111" s="4">
         <v>6</v>
       </c>
@@ -5193,7 +5196,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="112" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:9" s="5" customFormat="1">
       <c r="B112" s="4">
         <v>7</v>
       </c>
@@ -5212,7 +5215,7 @@
       </c>
       <c r="I112"/>
     </row>
-    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:9">
       <c r="B113" s="4">
         <v>8</v>
       </c>
@@ -5230,7 +5233,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:9">
       <c r="B114" s="4">
         <v>9</v>
       </c>
@@ -5249,37 +5252,37 @@
         <v>589</v>
       </c>
     </row>
-    <row r="116" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:9" ht="16.5" customHeight="1">
       <c r="B116" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C116" s="16" t="s">
+      <c r="C116" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="D116" s="16"/>
+      <c r="D116" s="20"/>
       <c r="E116" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F116" s="15"/>
-      <c r="G116" s="15"/>
-    </row>
-    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F116" s="21"/>
+      <c r="G116" s="21"/>
+    </row>
+    <row r="117" spans="2:9">
       <c r="B117" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C117" s="15" t="s">
+      <c r="C117" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="D117" s="15"/>
+      <c r="D117" s="21"/>
       <c r="E117" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F117" s="15" t="s">
+      <c r="F117" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="G117" s="15"/>
-    </row>
-    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G117" s="21"/>
+    </row>
+    <row r="118" spans="2:9">
       <c r="B118" s="2" t="s">
         <v>6</v>
       </c>
@@ -5299,7 +5302,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:9">
       <c r="B119" s="1">
         <v>1</v>
       </c>
@@ -5317,7 +5320,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:9">
       <c r="B120" s="1">
         <v>2</v>
       </c>
@@ -5335,7 +5338,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:9">
       <c r="B121" s="1">
         <v>3</v>
       </c>
@@ -5353,7 +5356,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:9">
       <c r="B122" s="1">
         <v>4</v>
       </c>
@@ -5371,7 +5374,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:9">
       <c r="B123" s="1">
         <v>5</v>
       </c>
@@ -5390,7 +5393,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:9">
       <c r="B124" s="1">
         <v>6</v>
       </c>
@@ -5407,7 +5410,7 @@
       <c r="G124" s="1"/>
       <c r="I124" s="12"/>
     </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:9">
       <c r="B125" s="1">
         <v>7</v>
       </c>
@@ -5424,7 +5427,7 @@
       <c r="G125" s="1"/>
       <c r="I125" s="12"/>
     </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:9">
       <c r="B126" s="1">
         <v>8</v>
       </c>
@@ -5443,7 +5446,7 @@
       </c>
       <c r="I126" s="12"/>
     </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:9">
       <c r="B127" s="1">
         <v>9</v>
       </c>
@@ -5462,37 +5465,37 @@
         <v>610</v>
       </c>
     </row>
-    <row r="129" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:9" ht="16.5" customHeight="1">
       <c r="B129" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C129" s="16" t="s">
+      <c r="C129" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="D129" s="16"/>
+      <c r="D129" s="20"/>
       <c r="E129" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F129" s="15"/>
-      <c r="G129" s="15"/>
-    </row>
-    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F129" s="21"/>
+      <c r="G129" s="21"/>
+    </row>
+    <row r="130" spans="2:9">
       <c r="B130" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C130" s="15" t="s">
+      <c r="C130" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="D130" s="15"/>
+      <c r="D130" s="21"/>
       <c r="E130" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F130" s="15" t="s">
+      <c r="F130" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="G130" s="15"/>
-    </row>
-    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G130" s="21"/>
+    </row>
+    <row r="131" spans="2:9">
       <c r="B131" s="2" t="s">
         <v>6</v>
       </c>
@@ -5512,7 +5515,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:9">
       <c r="B132" s="1">
         <v>1</v>
       </c>
@@ -5530,7 +5533,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:9">
       <c r="B133" s="1">
         <v>2</v>
       </c>
@@ -5548,7 +5551,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:9">
       <c r="B134" s="1">
         <v>3</v>
       </c>
@@ -5564,7 +5567,7 @@
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
     </row>
-    <row r="135" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:9">
       <c r="B135" s="1">
         <v>4</v>
       </c>
@@ -5582,7 +5585,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="136" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:9">
       <c r="B136" s="1">
         <v>5</v>
       </c>
@@ -5600,7 +5603,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="137" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:9">
       <c r="B137" s="1">
         <v>6</v>
       </c>
@@ -5616,7 +5619,7 @@
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
     </row>
-    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:9">
       <c r="B138" s="1">
         <v>7</v>
       </c>
@@ -5632,7 +5635,7 @@
       <c r="F138" s="1"/>
       <c r="G138" s="1"/>
     </row>
-    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:9">
       <c r="B139" s="1">
         <v>8</v>
       </c>
@@ -5651,39 +5654,39 @@
         <v>611</v>
       </c>
     </row>
-    <row r="141" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:9" ht="16.5" customHeight="1">
       <c r="B141" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C141" s="16" t="s">
+      <c r="C141" s="20" t="s">
         <v>587</v>
       </c>
-      <c r="D141" s="16"/>
+      <c r="D141" s="20"/>
       <c r="E141" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F141" s="15"/>
-      <c r="G141" s="15"/>
-    </row>
-    <row r="142" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F141" s="21"/>
+      <c r="G141" s="21"/>
+    </row>
+    <row r="142" spans="2:9">
       <c r="B142" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C142" s="15" t="s">
+      <c r="C142" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="D142" s="15"/>
+      <c r="D142" s="21"/>
       <c r="E142" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F142" s="16" t="s">
+      <c r="F142" s="20" t="s">
         <v>565</v>
       </c>
-      <c r="G142" s="15" t="s">
+      <c r="G142" s="21" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="143" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:9">
       <c r="B143" s="2" t="s">
         <v>6</v>
       </c>
@@ -5703,7 +5706,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:9">
       <c r="B144" s="1">
         <v>1</v>
       </c>
@@ -5721,7 +5724,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="145" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:9">
       <c r="B145" s="1">
         <v>2</v>
       </c>
@@ -5739,7 +5742,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:9">
       <c r="B146" s="1">
         <v>3</v>
       </c>
@@ -5757,7 +5760,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="147" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:9">
       <c r="B147" s="1">
         <v>4</v>
       </c>
@@ -5775,7 +5778,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="148" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:9">
       <c r="B148" s="1">
         <v>5</v>
       </c>
@@ -5793,7 +5796,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="149" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:9">
       <c r="B149" s="1">
         <v>6</v>
       </c>
@@ -5811,7 +5814,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:9">
       <c r="B150" s="1">
         <v>7</v>
       </c>
@@ -5829,7 +5832,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="151" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:9">
       <c r="B151" s="1">
         <v>8</v>
       </c>
@@ -5848,39 +5851,39 @@
         <v>588</v>
       </c>
     </row>
-    <row r="153" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:9" ht="16.5" customHeight="1">
       <c r="B153" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C153" s="16" t="s">
+      <c r="C153" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="D153" s="16"/>
+      <c r="D153" s="20"/>
       <c r="E153" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F153" s="15"/>
-      <c r="G153" s="15"/>
-    </row>
-    <row r="154" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F153" s="21"/>
+      <c r="G153" s="21"/>
+    </row>
+    <row r="154" spans="2:9">
       <c r="B154" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C154" s="15" t="s">
+      <c r="C154" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D154" s="15"/>
+      <c r="D154" s="21"/>
       <c r="E154" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F154" s="15" t="s">
+      <c r="F154" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="G154" s="15" t="s">
+      <c r="G154" s="21" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="155" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:9">
       <c r="B155" s="2" t="s">
         <v>6</v>
       </c>
@@ -5900,7 +5903,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="156" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:9">
       <c r="B156" s="1">
         <v>1</v>
       </c>
@@ -5918,7 +5921,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="157" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:9">
       <c r="B157" s="1">
         <v>2</v>
       </c>
@@ -5936,7 +5939,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="158" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:9">
       <c r="B158" s="1">
         <v>3</v>
       </c>
@@ -5954,7 +5957,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="159" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:9">
       <c r="B159" s="1">
         <v>4</v>
       </c>
@@ -5972,7 +5975,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="160" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:9">
       <c r="B160" s="1">
         <v>5</v>
       </c>
@@ -5990,7 +5993,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="161" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:9">
       <c r="B161" s="1">
         <v>6</v>
       </c>
@@ -6008,7 +6011,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="162" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:9">
       <c r="B162" s="1">
         <v>7</v>
       </c>
@@ -6026,7 +6029,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="163" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:9">
       <c r="B163" s="1">
         <v>8</v>
       </c>
@@ -6044,7 +6047,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:9">
       <c r="B164" s="1">
         <v>9</v>
       </c>
@@ -6063,7 +6066,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="165" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:9">
       <c r="B165" s="1">
         <v>10</v>
       </c>
@@ -6082,37 +6085,37 @@
         <v>586</v>
       </c>
     </row>
-    <row r="167" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:9" ht="16.5" customHeight="1">
       <c r="B167" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C167" s="16" t="s">
+      <c r="C167" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="D167" s="16"/>
+      <c r="D167" s="20"/>
       <c r="E167" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F167" s="15"/>
-      <c r="G167" s="15"/>
-    </row>
-    <row r="168" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F167" s="21"/>
+      <c r="G167" s="21"/>
+    </row>
+    <row r="168" spans="2:9">
       <c r="B168" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C168" s="15" t="s">
+      <c r="C168" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="D168" s="15"/>
+      <c r="D168" s="21"/>
       <c r="E168" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F168" s="15" t="s">
+      <c r="F168" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="G168" s="15"/>
-    </row>
-    <row r="169" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G168" s="21"/>
+    </row>
+    <row r="169" spans="2:9">
       <c r="B169" s="2" t="s">
         <v>6</v>
       </c>
@@ -6132,7 +6135,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:9">
       <c r="B170" s="1">
         <v>1</v>
       </c>
@@ -6150,7 +6153,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="171" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:9">
       <c r="B171" s="1">
         <v>2</v>
       </c>
@@ -6168,7 +6171,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="172" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:9">
       <c r="B172" s="1">
         <v>3</v>
       </c>
@@ -6186,7 +6189,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="173" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:9">
       <c r="B173" s="1">
         <v>4</v>
       </c>
@@ -6204,35 +6207,35 @@
         <v>226</v>
       </c>
     </row>
-    <row r="175" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:9" ht="16.5" customHeight="1">
       <c r="B175" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C175" s="16" t="s">
+      <c r="C175" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="D175" s="16"/>
+      <c r="D175" s="20"/>
       <c r="E175" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F175" s="15"/>
-      <c r="G175" s="15"/>
-    </row>
-    <row r="176" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F175" s="21"/>
+      <c r="G175" s="21"/>
+    </row>
+    <row r="176" spans="2:9">
       <c r="B176" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C176" s="15" t="s">
+      <c r="C176" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="D176" s="15"/>
+      <c r="D176" s="21"/>
       <c r="E176" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F176" s="15"/>
-      <c r="G176" s="15"/>
-    </row>
-    <row r="177" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F176" s="21"/>
+      <c r="G176" s="21"/>
+    </row>
+    <row r="177" spans="2:9">
       <c r="B177" s="2" t="s">
         <v>6</v>
       </c>
@@ -6252,7 +6255,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="178" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:9">
       <c r="B178" s="1">
         <v>1</v>
       </c>
@@ -6270,7 +6273,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="179" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:9">
       <c r="B179" s="1">
         <v>2</v>
       </c>
@@ -6290,7 +6293,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="180" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:9">
       <c r="B180" s="1">
         <v>3</v>
       </c>
@@ -6310,7 +6313,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="181" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:9">
       <c r="B181" s="1">
         <v>4</v>
       </c>
@@ -6328,7 +6331,7 @@
       </c>
       <c r="G181" s="1"/>
     </row>
-    <row r="182" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:9">
       <c r="B182" s="1">
         <v>5</v>
       </c>
@@ -6349,7 +6352,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="183" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:9">
       <c r="B183" s="1">
         <v>6</v>
       </c>
@@ -6370,35 +6373,35 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="185" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:9" ht="16.5" customHeight="1">
       <c r="B185" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C185" s="16" t="s">
+      <c r="C185" s="20" t="s">
         <v>575</v>
       </c>
-      <c r="D185" s="16"/>
+      <c r="D185" s="20"/>
       <c r="E185" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F185" s="15"/>
-      <c r="G185" s="15"/>
-    </row>
-    <row r="186" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F185" s="21"/>
+      <c r="G185" s="21"/>
+    </row>
+    <row r="186" spans="2:9">
       <c r="B186" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C186" s="15" t="s">
+      <c r="C186" s="21" t="s">
         <v>574</v>
       </c>
-      <c r="D186" s="15"/>
+      <c r="D186" s="21"/>
       <c r="E186" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F186" s="15"/>
-      <c r="G186" s="15"/>
-    </row>
-    <row r="187" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F186" s="21"/>
+      <c r="G186" s="21"/>
+    </row>
+    <row r="187" spans="2:9">
       <c r="B187" s="2" t="s">
         <v>6</v>
       </c>
@@ -6418,7 +6421,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="188" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:9">
       <c r="B188" s="1">
         <v>1</v>
       </c>
@@ -6436,7 +6439,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="189" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:9">
       <c r="B189" s="1">
         <v>2</v>
       </c>
@@ -6456,7 +6459,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="190" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:9">
       <c r="B190" s="1">
         <v>3</v>
       </c>
@@ -6476,7 +6479,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="191" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:9">
       <c r="B191" s="1">
         <v>4</v>
       </c>
@@ -6496,7 +6499,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="192" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:9">
       <c r="B192" s="1">
         <v>5</v>
       </c>
@@ -6516,7 +6519,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="193" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:9">
       <c r="B193" s="1">
         <v>6</v>
       </c>
@@ -6534,7 +6537,7 @@
       </c>
       <c r="G193" s="1"/>
     </row>
-    <row r="194" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:9">
       <c r="B194" s="1">
         <v>7</v>
       </c>
@@ -6555,7 +6558,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="195" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:9">
       <c r="B195" s="1">
         <v>8</v>
       </c>
@@ -6576,39 +6579,39 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="197" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:9" ht="16.5" customHeight="1">
       <c r="B197" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C197" s="16" t="s">
+      <c r="C197" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="D197" s="16"/>
+      <c r="D197" s="20"/>
       <c r="E197" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F197" s="15"/>
-      <c r="G197" s="15"/>
-    </row>
-    <row r="198" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F197" s="21"/>
+      <c r="G197" s="21"/>
+    </row>
+    <row r="198" spans="2:9">
       <c r="B198" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C198" s="15" t="s">
+      <c r="C198" s="21" t="s">
         <v>511</v>
       </c>
-      <c r="D198" s="15"/>
+      <c r="D198" s="21"/>
       <c r="E198" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F198" s="15" t="s">
+      <c r="F198" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="G198" s="15" t="s">
+      <c r="G198" s="21" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="199" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:9">
       <c r="B199" s="2" t="s">
         <v>6</v>
       </c>
@@ -6628,7 +6631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="200" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:9">
       <c r="B200" s="1">
         <v>1</v>
       </c>
@@ -6646,7 +6649,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="201" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:9">
       <c r="B201" s="1">
         <v>2</v>
       </c>
@@ -6664,7 +6667,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="202" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:9">
       <c r="B202" s="1">
         <v>3</v>
       </c>
@@ -6682,7 +6685,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="203" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:9">
       <c r="B203" s="1">
         <v>4</v>
       </c>
@@ -6700,7 +6703,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="204" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:9">
       <c r="B204" s="1">
         <v>5</v>
       </c>
@@ -6721,39 +6724,39 @@
         <v>45292.000694444447</v>
       </c>
     </row>
-    <row r="206" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:9" ht="16.5" customHeight="1">
       <c r="B206" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C206" s="16" t="s">
+      <c r="C206" s="20" t="s">
         <v>512</v>
       </c>
-      <c r="D206" s="16"/>
+      <c r="D206" s="20"/>
       <c r="E206" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F206" s="15"/>
-      <c r="G206" s="15"/>
-    </row>
-    <row r="207" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F206" s="21"/>
+      <c r="G206" s="21"/>
+    </row>
+    <row r="207" spans="2:9">
       <c r="B207" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C207" s="15" t="s">
+      <c r="C207" s="21" t="s">
         <v>535</v>
       </c>
-      <c r="D207" s="15"/>
+      <c r="D207" s="21"/>
       <c r="E207" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F207" s="15" t="s">
+      <c r="F207" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="G207" s="15" t="s">
+      <c r="G207" s="21" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="208" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:9">
       <c r="B208" s="2" t="s">
         <v>6</v>
       </c>
@@ -6773,7 +6776,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="209" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:9">
       <c r="B209" s="1">
         <v>1</v>
       </c>
@@ -6791,7 +6794,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="210" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:9">
       <c r="B210" s="1">
         <v>2</v>
       </c>
@@ -6809,7 +6812,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="211" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:9">
       <c r="B211" s="1">
         <v>3</v>
       </c>
@@ -6827,7 +6830,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="212" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:9">
       <c r="B212" s="1">
         <v>4</v>
       </c>
@@ -6848,37 +6851,37 @@
         <v>593</v>
       </c>
     </row>
-    <row r="214" spans="2:9" s="26" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B214" s="23" t="s">
+    <row r="214" spans="2:9" s="19" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B214" s="18" t="s">
         <v>0</v>
       </c>
       <c r="C214" s="24" t="s">
         <v>624</v>
       </c>
       <c r="D214" s="24"/>
-      <c r="E214" s="23" t="s">
+      <c r="E214" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F214" s="25"/>
       <c r="G214" s="25"/>
     </row>
-    <row r="215" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:9">
       <c r="B215" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C215" s="15" t="s">
+      <c r="C215" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="D215" s="15"/>
+      <c r="D215" s="21"/>
       <c r="E215" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F215" s="15" t="s">
+      <c r="F215" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="G215" s="15"/>
-    </row>
-    <row r="216" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G215" s="21"/>
+    </row>
+    <row r="216" spans="2:9">
       <c r="B216" s="2" t="s">
         <v>6</v>
       </c>
@@ -6898,7 +6901,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="217" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:9">
       <c r="B217" s="1">
         <v>1</v>
       </c>
@@ -6916,7 +6919,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="218" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:9">
       <c r="B218" s="1">
         <v>2</v>
       </c>
@@ -6934,7 +6937,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="219" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:9">
       <c r="B219" s="1">
         <v>3</v>
       </c>
@@ -6949,9 +6952,9 @@
       </c>
       <c r="F219" s="1"/>
       <c r="G219" s="1"/>
-      <c r="I219" s="19"/>
-    </row>
-    <row r="220" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I219" s="15"/>
+    </row>
+    <row r="220" spans="2:9">
       <c r="B220" s="1">
         <v>4</v>
       </c>
@@ -6966,9 +6969,9 @@
       </c>
       <c r="F220" s="1"/>
       <c r="G220" s="1"/>
-      <c r="I220" s="19"/>
-    </row>
-    <row r="221" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I220" s="15"/>
+    </row>
+    <row r="221" spans="2:9">
       <c r="B221" s="1">
         <v>5</v>
       </c>
@@ -6984,7 +6987,7 @@
       <c r="F221" s="1"/>
       <c r="G221" s="1"/>
     </row>
-    <row r="222" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:9">
       <c r="B222" s="1">
         <v>6</v>
       </c>
@@ -7000,7 +7003,7 @@
       <c r="F222" s="1"/>
       <c r="G222" s="1"/>
     </row>
-    <row r="223" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:9">
       <c r="B223" s="1">
         <v>7</v>
       </c>
@@ -7016,7 +7019,7 @@
       <c r="F223" s="1"/>
       <c r="G223" s="1"/>
     </row>
-    <row r="224" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:9">
       <c r="B224" s="1">
         <v>8</v>
       </c>
@@ -7031,9 +7034,9 @@
       </c>
       <c r="F224" s="1"/>
       <c r="G224" s="1"/>
-      <c r="I224" s="19"/>
-    </row>
-    <row r="225" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I224" s="15"/>
+    </row>
+    <row r="225" spans="2:9">
       <c r="B225" s="1">
         <v>9</v>
       </c>
@@ -7049,7 +7052,7 @@
       <c r="F225" s="1"/>
       <c r="G225" s="1"/>
     </row>
-    <row r="226" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:9">
       <c r="B226" s="1">
         <v>10</v>
       </c>
@@ -7064,41 +7067,41 @@
       </c>
       <c r="F226" s="1"/>
       <c r="G226" s="1"/>
-      <c r="I226" s="19"/>
-    </row>
-    <row r="228" spans="2:9" s="26" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B228" s="23" t="s">
+      <c r="I226" s="15"/>
+    </row>
+    <row r="228" spans="2:9" s="19" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B228" s="18" t="s">
         <v>0</v>
       </c>
       <c r="C228" s="24" t="s">
         <v>631</v>
       </c>
       <c r="D228" s="24"/>
-      <c r="E228" s="23" t="s">
+      <c r="E228" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F228" s="25"/>
       <c r="G228" s="25"/>
     </row>
-    <row r="229" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:9">
       <c r="B229" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C229" s="15" t="s">
+      <c r="C229" s="21" t="s">
         <v>630</v>
       </c>
-      <c r="D229" s="15"/>
+      <c r="D229" s="21"/>
       <c r="E229" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F229" s="15" t="s">
+      <c r="F229" s="21" t="s">
         <v>280</v>
       </c>
-      <c r="G229" s="15" t="s">
+      <c r="G229" s="21" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="230" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:9">
       <c r="B230" s="2" t="s">
         <v>6</v>
       </c>
@@ -7118,7 +7121,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="231" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:9">
       <c r="B231" s="1">
         <v>1</v>
       </c>
@@ -7136,7 +7139,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="232" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:9">
       <c r="B232" s="1">
         <v>2</v>
       </c>
@@ -7154,7 +7157,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="233" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:9">
       <c r="B233" s="1">
         <v>3</v>
       </c>
@@ -7172,7 +7175,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="234" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:9">
       <c r="B234" s="1">
         <v>4</v>
       </c>
@@ -7188,7 +7191,7 @@
       <c r="F234" s="1"/>
       <c r="G234" s="1"/>
     </row>
-    <row r="235" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:9">
       <c r="B235" s="1">
         <v>5</v>
       </c>
@@ -7204,7 +7207,7 @@
       <c r="F235" s="1"/>
       <c r="G235" s="1"/>
     </row>
-    <row r="236" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:9">
       <c r="B236" s="1">
         <v>6</v>
       </c>
@@ -7220,7 +7223,7 @@
       <c r="F236" s="1"/>
       <c r="G236" s="1"/>
     </row>
-    <row r="237" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:9">
       <c r="B237" s="1">
         <v>7</v>
       </c>
@@ -7236,7 +7239,7 @@
       <c r="F237" s="1"/>
       <c r="G237" s="1"/>
     </row>
-    <row r="238" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:9">
       <c r="B238" s="1">
         <v>8</v>
       </c>
@@ -7252,35 +7255,35 @@
       <c r="F238" s="1"/>
       <c r="G238" s="1"/>
     </row>
-    <row r="240" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:9" ht="16.5" customHeight="1">
       <c r="B240" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C240" s="16" t="s">
+      <c r="C240" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="D240" s="16"/>
+      <c r="D240" s="20"/>
       <c r="E240" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F240" s="15"/>
-      <c r="G240" s="15"/>
-    </row>
-    <row r="241" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F240" s="21"/>
+      <c r="G240" s="21"/>
+    </row>
+    <row r="241" spans="2:9">
       <c r="B241" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C241" s="15" t="s">
+      <c r="C241" s="21" t="s">
         <v>285</v>
       </c>
-      <c r="D241" s="15"/>
+      <c r="D241" s="21"/>
       <c r="E241" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F241" s="15"/>
-      <c r="G241" s="15"/>
-    </row>
-    <row r="242" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F241" s="21"/>
+      <c r="G241" s="21"/>
+    </row>
+    <row r="242" spans="2:9">
       <c r="B242" s="2" t="s">
         <v>6</v>
       </c>
@@ -7300,7 +7303,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="243" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:9">
       <c r="B243" s="1">
         <v>1</v>
       </c>
@@ -7318,7 +7321,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="244" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:9">
       <c r="B244" s="1">
         <v>2</v>
       </c>
@@ -7336,7 +7339,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="245" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:9">
       <c r="B245" s="1">
         <v>3</v>
       </c>
@@ -7354,7 +7357,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="246" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:9">
       <c r="B246" s="1">
         <v>4</v>
       </c>
@@ -7370,7 +7373,7 @@
       <c r="F246" s="1"/>
       <c r="G246" s="1"/>
     </row>
-    <row r="247" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:9">
       <c r="B247" s="1">
         <v>5</v>
       </c>
@@ -7386,7 +7389,7 @@
       <c r="F247" s="1"/>
       <c r="G247" s="1"/>
     </row>
-    <row r="248" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:9">
       <c r="B248" s="1">
         <v>6</v>
       </c>
@@ -7402,7 +7405,7 @@
       <c r="F248" s="1"/>
       <c r="G248" s="1"/>
     </row>
-    <row r="249" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:9">
       <c r="B249" s="1">
         <v>7</v>
       </c>
@@ -7418,7 +7421,7 @@
       <c r="F249" s="1"/>
       <c r="G249" s="1"/>
     </row>
-    <row r="250" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:9">
       <c r="B250" s="1">
         <v>8</v>
       </c>
@@ -7437,39 +7440,39 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="252" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:9" ht="16.5" customHeight="1">
       <c r="B252" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C252" s="16" t="s">
+      <c r="C252" s="20" t="s">
         <v>638</v>
       </c>
-      <c r="D252" s="16"/>
+      <c r="D252" s="20"/>
       <c r="E252" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F252" s="15"/>
-      <c r="G252" s="15"/>
-    </row>
-    <row r="253" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F252" s="21"/>
+      <c r="G252" s="21"/>
+    </row>
+    <row r="253" spans="2:9">
       <c r="B253" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C253" s="15" t="s">
+      <c r="C253" s="21" t="s">
         <v>637</v>
       </c>
-      <c r="D253" s="15"/>
+      <c r="D253" s="21"/>
       <c r="E253" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F253" s="15" t="s">
+      <c r="F253" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="G253" s="15" t="s">
+      <c r="G253" s="21" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="254" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:9">
       <c r="B254" s="2" t="s">
         <v>6</v>
       </c>
@@ -7489,7 +7492,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="255" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:9">
       <c r="B255" s="1">
         <v>1</v>
       </c>
@@ -7507,7 +7510,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="256" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:9">
       <c r="B256" s="1">
         <v>2</v>
       </c>
@@ -7525,7 +7528,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="257" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:9">
       <c r="B257" s="1">
         <v>3</v>
       </c>
@@ -7543,7 +7546,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="258" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:9">
       <c r="B258" s="1">
         <v>4</v>
       </c>
@@ -7558,11 +7561,11 @@
       </c>
       <c r="F258" s="1"/>
       <c r="G258" s="1"/>
-      <c r="I258" s="19" t="s">
+      <c r="I258" s="15" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="259" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:9">
       <c r="B259" s="1">
         <v>5</v>
       </c>
@@ -7577,11 +7580,11 @@
       </c>
       <c r="F259" s="1"/>
       <c r="G259" s="1"/>
-      <c r="I259" s="19" t="s">
+      <c r="I259" s="15" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="260" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:9">
       <c r="B260" s="1">
         <v>6</v>
       </c>
@@ -7599,7 +7602,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="261" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:9">
       <c r="B261" s="1">
         <v>7</v>
       </c>
@@ -7617,7 +7620,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="262" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:9">
       <c r="B262" s="1">
         <v>8</v>
       </c>
@@ -7632,41 +7635,41 @@
       </c>
       <c r="F262" s="1"/>
       <c r="G262" s="1"/>
-      <c r="I262" s="19" t="s">
+      <c r="I262" s="15" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="264" spans="2:9" s="26" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B264" s="23" t="s">
+    <row r="264" spans="2:9" s="19" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B264" s="18" t="s">
         <v>0</v>
       </c>
       <c r="C264" s="24" t="s">
         <v>629</v>
       </c>
       <c r="D264" s="24"/>
-      <c r="E264" s="23" t="s">
+      <c r="E264" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F264" s="25"/>
       <c r="G264" s="25"/>
     </row>
-    <row r="265" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:9">
       <c r="B265" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C265" s="15" t="s">
+      <c r="C265" s="21" t="s">
         <v>628</v>
       </c>
-      <c r="D265" s="15"/>
+      <c r="D265" s="21"/>
       <c r="E265" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F265" s="15" t="s">
+      <c r="F265" s="21" t="s">
         <v>311</v>
       </c>
-      <c r="G265" s="15"/>
-    </row>
-    <row r="266" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G265" s="21"/>
+    </row>
+    <row r="266" spans="2:9">
       <c r="B266" s="2" t="s">
         <v>6</v>
       </c>
@@ -7686,7 +7689,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="267" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:9">
       <c r="B267" s="1">
         <v>1</v>
       </c>
@@ -7704,7 +7707,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="268" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:9">
       <c r="B268" s="1">
         <v>2</v>
       </c>
@@ -7722,45 +7725,45 @@
         <v>313</v>
       </c>
     </row>
-    <row r="269" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B269" s="1">
+    <row r="269" spans="2:9" s="10" customFormat="1">
+      <c r="B269" s="26">
         <v>3</v>
       </c>
-      <c r="C269" s="1" t="s">
+      <c r="C269" s="26" t="s">
         <v>314</v>
       </c>
-      <c r="D269" s="1" t="s">
+      <c r="D269" s="26" t="s">
         <v>315</v>
       </c>
-      <c r="E269" s="1" t="s">
+      <c r="E269" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="F269" s="1"/>
-      <c r="G269" s="1"/>
-      <c r="I269" s="22" t="s">
+      <c r="F269" s="26"/>
+      <c r="G269" s="26"/>
+      <c r="I269" s="27" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="270" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B270" s="1">
+    <row r="270" spans="2:9" s="10" customFormat="1">
+      <c r="B270" s="26">
         <v>4</v>
       </c>
-      <c r="C270" s="1" t="s">
+      <c r="C270" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="D270" s="1" t="s">
+      <c r="D270" s="26" t="s">
         <v>317</v>
       </c>
-      <c r="E270" s="1" t="s">
+      <c r="E270" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="F270" s="1"/>
-      <c r="G270" s="1"/>
-      <c r="I270" s="22" t="s">
+      <c r="F270" s="26"/>
+      <c r="G270" s="26"/>
+      <c r="I270" s="27" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="271" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:9">
       <c r="B271" s="1">
         <v>5</v>
       </c>
@@ -7776,7 +7779,7 @@
       <c r="F271" s="1"/>
       <c r="G271" s="1"/>
     </row>
-    <row r="272" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:9">
       <c r="B272" s="1">
         <v>6</v>
       </c>
@@ -7794,7 +7797,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="273" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:9">
       <c r="B273" s="1">
         <v>7</v>
       </c>
@@ -7809,9 +7812,9 @@
       </c>
       <c r="F273" s="1"/>
       <c r="G273" s="1"/>
-      <c r="I273" s="19"/>
-    </row>
-    <row r="274" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I273" s="15"/>
+    </row>
+    <row r="274" spans="2:9">
       <c r="B274" s="1">
         <v>8</v>
       </c>
@@ -7826,9 +7829,9 @@
       </c>
       <c r="F274" s="1"/>
       <c r="G274" s="1"/>
-      <c r="I274" s="19"/>
-    </row>
-    <row r="275" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I274" s="15"/>
+    </row>
+    <row r="275" spans="2:9">
       <c r="B275" s="1">
         <v>9</v>
       </c>
@@ -7844,35 +7847,35 @@
       <c r="F275" s="1"/>
       <c r="G275" s="1"/>
     </row>
-    <row r="277" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:9" ht="16.5" customHeight="1">
       <c r="B277" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C277" s="16" t="s">
+      <c r="C277" s="20" t="s">
         <v>595</v>
       </c>
-      <c r="D277" s="16"/>
+      <c r="D277" s="20"/>
       <c r="E277" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F277" s="15"/>
-      <c r="G277" s="15"/>
-    </row>
-    <row r="278" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F277" s="21"/>
+      <c r="G277" s="21"/>
+    </row>
+    <row r="278" spans="2:9">
       <c r="B278" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C278" s="15" t="s">
+      <c r="C278" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="D278" s="15"/>
+      <c r="D278" s="21"/>
       <c r="E278" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F278" s="15"/>
-      <c r="G278" s="15"/>
-    </row>
-    <row r="279" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F278" s="21"/>
+      <c r="G278" s="21"/>
+    </row>
+    <row r="279" spans="2:9">
       <c r="B279" s="2" t="s">
         <v>6</v>
       </c>
@@ -7892,7 +7895,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="280" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:9">
       <c r="B280" s="1">
         <v>1</v>
       </c>
@@ -7910,7 +7913,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="281" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:9">
       <c r="B281" s="1">
         <v>2</v>
       </c>
@@ -7928,7 +7931,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="282" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:9">
       <c r="B282" s="1">
         <v>3</v>
       </c>
@@ -7944,7 +7947,7 @@
       <c r="F282" s="1"/>
       <c r="G282" s="1"/>
     </row>
-    <row r="283" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:9">
       <c r="B283" s="1">
         <v>4</v>
       </c>
@@ -7962,7 +7965,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="284" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:9">
       <c r="B284" s="1">
         <v>5</v>
       </c>
@@ -7980,7 +7983,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="285" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:9">
       <c r="B285" s="1">
         <v>6</v>
       </c>
@@ -7999,7 +8002,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="286" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:9">
       <c r="B286" s="1">
         <v>7</v>
       </c>
@@ -8018,7 +8021,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="287" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:9">
       <c r="B287" s="1">
         <v>8</v>
       </c>
@@ -8034,7 +8037,7 @@
       <c r="F287" s="1"/>
       <c r="G287" s="1"/>
     </row>
-    <row r="288" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:9">
       <c r="B288" s="1">
         <v>9</v>
       </c>
@@ -8053,39 +8056,39 @@
         <v>45292.000694444447</v>
       </c>
     </row>
-    <row r="290" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:9" ht="16.5" customHeight="1">
       <c r="B290" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C290" s="16" t="s">
+      <c r="C290" s="20" t="s">
         <v>596</v>
       </c>
-      <c r="D290" s="16"/>
+      <c r="D290" s="20"/>
       <c r="E290" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F290" s="15"/>
-      <c r="G290" s="15"/>
-    </row>
-    <row r="291" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F290" s="21"/>
+      <c r="G290" s="21"/>
+    </row>
+    <row r="291" spans="2:9">
       <c r="B291" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C291" s="15" t="s">
+      <c r="C291" s="21" t="s">
         <v>338</v>
       </c>
-      <c r="D291" s="15"/>
+      <c r="D291" s="21"/>
       <c r="E291" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F291" s="15" t="s">
+      <c r="F291" s="21" t="s">
         <v>339</v>
       </c>
-      <c r="G291" s="15" t="s">
+      <c r="G291" s="21" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="292" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:9">
       <c r="B292" s="2" t="s">
         <v>6</v>
       </c>
@@ -8105,7 +8108,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="293" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:9">
       <c r="B293" s="1">
         <v>1</v>
       </c>
@@ -8123,7 +8126,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="294" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:9">
       <c r="B294" s="1">
         <v>2</v>
       </c>
@@ -8141,7 +8144,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="295" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:9">
       <c r="B295" s="1">
         <v>3</v>
       </c>
@@ -8159,7 +8162,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="296" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:9">
       <c r="B296" s="1">
         <v>4</v>
       </c>
@@ -8175,7 +8178,7 @@
       <c r="F296" s="1"/>
       <c r="G296" s="1"/>
     </row>
-    <row r="297" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:9">
       <c r="B297" s="1">
         <v>5</v>
       </c>
@@ -8193,7 +8196,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="298" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:9">
       <c r="B298" s="1">
         <v>6</v>
       </c>
@@ -8209,7 +8212,7 @@
       <c r="F298" s="1"/>
       <c r="G298" s="1"/>
     </row>
-    <row r="299" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:9">
       <c r="B299" s="1">
         <v>7</v>
       </c>
@@ -8228,7 +8231,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="300" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:9">
       <c r="B300" s="1">
         <v>8</v>
       </c>
@@ -8247,7 +8250,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="301" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:9">
       <c r="B301" s="1">
         <v>9</v>
       </c>
@@ -8263,37 +8266,37 @@
       <c r="F301" s="1"/>
       <c r="G301" s="1"/>
     </row>
-    <row r="303" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:9" ht="16.5" customHeight="1">
       <c r="B303" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C303" s="16" t="s">
+      <c r="C303" s="20" t="s">
         <v>348</v>
       </c>
-      <c r="D303" s="16"/>
+      <c r="D303" s="20"/>
       <c r="E303" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F303" s="15"/>
-      <c r="G303" s="15"/>
-    </row>
-    <row r="304" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F303" s="21"/>
+      <c r="G303" s="21"/>
+    </row>
+    <row r="304" spans="2:9">
       <c r="B304" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C304" s="15" t="s">
+      <c r="C304" s="21" t="s">
         <v>349</v>
       </c>
-      <c r="D304" s="15"/>
+      <c r="D304" s="21"/>
       <c r="E304" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F304" s="15" t="s">
+      <c r="F304" s="21" t="s">
         <v>350</v>
       </c>
-      <c r="G304" s="15"/>
-    </row>
-    <row r="305" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G304" s="21"/>
+    </row>
+    <row r="305" spans="2:9">
       <c r="B305" s="2" t="s">
         <v>6</v>
       </c>
@@ -8313,7 +8316,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="306" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:9">
       <c r="B306" s="1">
         <v>1</v>
       </c>
@@ -8331,7 +8334,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="307" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:9">
       <c r="B307" s="1">
         <v>2</v>
       </c>
@@ -8349,7 +8352,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="308" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:9">
       <c r="B308" s="1">
         <v>3</v>
       </c>
@@ -8367,7 +8370,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="309" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:9">
       <c r="B309" s="1">
         <v>4</v>
       </c>
@@ -8383,7 +8386,7 @@
       <c r="F309" s="1"/>
       <c r="G309" s="1"/>
     </row>
-    <row r="310" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:9">
       <c r="B310" s="1">
         <v>5</v>
       </c>
@@ -8399,7 +8402,7 @@
       <c r="F310" s="1"/>
       <c r="G310" s="1"/>
     </row>
-    <row r="311" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:9">
       <c r="B311" s="1">
         <v>6</v>
       </c>
@@ -8415,7 +8418,7 @@
       <c r="F311" s="1"/>
       <c r="G311" s="1"/>
     </row>
-    <row r="312" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:9">
       <c r="B312" s="1">
         <v>7</v>
       </c>
@@ -8431,7 +8434,7 @@
       <c r="F312" s="1"/>
       <c r="G312" s="1"/>
     </row>
-    <row r="313" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:9">
       <c r="B313" s="1">
         <v>8</v>
       </c>
@@ -8450,7 +8453,7 @@
         <v>45292.000694444447</v>
       </c>
     </row>
-    <row r="314" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:9">
       <c r="B314" s="1">
         <v>9</v>
       </c>
@@ -8469,39 +8472,39 @@
         <v>45292.000694444447</v>
       </c>
     </row>
-    <row r="316" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:9" ht="16.5" customHeight="1">
       <c r="B316" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C316" s="16" t="s">
+      <c r="C316" s="20" t="s">
         <v>597</v>
       </c>
-      <c r="D316" s="16"/>
+      <c r="D316" s="20"/>
       <c r="E316" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F316" s="15"/>
-      <c r="G316" s="15"/>
-    </row>
-    <row r="317" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F316" s="21"/>
+      <c r="G316" s="21"/>
+    </row>
+    <row r="317" spans="2:9">
       <c r="B317" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C317" s="15" t="s">
+      <c r="C317" s="21" t="s">
         <v>362</v>
       </c>
-      <c r="D317" s="15"/>
+      <c r="D317" s="21"/>
       <c r="E317" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F317" s="15" t="s">
+      <c r="F317" s="21" t="s">
         <v>363</v>
       </c>
-      <c r="G317" s="15" t="s">
+      <c r="G317" s="21" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="318" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:9">
       <c r="B318" s="2" t="s">
         <v>6</v>
       </c>
@@ -8521,7 +8524,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="319" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:9">
       <c r="B319" s="1">
         <v>1</v>
       </c>
@@ -8539,7 +8542,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="320" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:9">
       <c r="B320" s="1">
         <v>2</v>
       </c>
@@ -8557,7 +8560,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="321" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:9">
       <c r="B321" s="1">
         <v>3</v>
       </c>
@@ -8575,7 +8578,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="322" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:9">
       <c r="B322" s="1">
         <v>4</v>
       </c>
@@ -8593,7 +8596,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="323" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:9">
       <c r="B323" s="1">
         <v>5</v>
       </c>
@@ -8609,7 +8612,7 @@
       <c r="F323" s="1"/>
       <c r="G323" s="1"/>
     </row>
-    <row r="324" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:9">
       <c r="B324" s="1">
         <v>6</v>
       </c>
@@ -8625,7 +8628,7 @@
       <c r="F324" s="1"/>
       <c r="G324" s="1"/>
     </row>
-    <row r="325" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:9">
       <c r="B325" s="1">
         <v>7</v>
       </c>
@@ -8641,7 +8644,7 @@
       <c r="F325" s="1"/>
       <c r="G325" s="1"/>
     </row>
-    <row r="326" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:9">
       <c r="B326" s="1">
         <v>8</v>
       </c>
@@ -8657,7 +8660,7 @@
       <c r="F326" s="1"/>
       <c r="G326" s="1"/>
     </row>
-    <row r="327" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:9">
       <c r="B327" s="1">
         <v>9</v>
       </c>
@@ -8676,7 +8679,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="328" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:9">
       <c r="B328" s="1">
         <v>10</v>
       </c>
@@ -8692,7 +8695,7 @@
       <c r="F328" s="1"/>
       <c r="G328" s="1"/>
     </row>
-    <row r="329" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:9">
       <c r="B329" s="1">
         <v>11</v>
       </c>
@@ -8708,7 +8711,7 @@
       <c r="F329" s="1"/>
       <c r="G329" s="1"/>
     </row>
-    <row r="330" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:9">
       <c r="B330" s="1">
         <v>12</v>
       </c>
@@ -8724,7 +8727,7 @@
       <c r="F330" s="1"/>
       <c r="G330" s="1"/>
     </row>
-    <row r="331" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:9">
       <c r="B331" s="1">
         <v>13</v>
       </c>
@@ -8742,7 +8745,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="332" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:9">
       <c r="B332" s="1">
         <v>14</v>
       </c>
@@ -8761,7 +8764,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="333" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:9">
       <c r="B333" s="1">
         <v>15</v>
       </c>
@@ -8780,37 +8783,37 @@
         <v>599</v>
       </c>
     </row>
-    <row r="335" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:9" ht="16.5" customHeight="1">
       <c r="B335" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C335" s="16" t="s">
+      <c r="C335" s="20" t="s">
         <v>386</v>
       </c>
-      <c r="D335" s="16"/>
+      <c r="D335" s="20"/>
       <c r="E335" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F335" s="15"/>
-      <c r="G335" s="15"/>
-    </row>
-    <row r="336" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F335" s="21"/>
+      <c r="G335" s="21"/>
+    </row>
+    <row r="336" spans="2:9">
       <c r="B336" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C336" s="15" t="s">
+      <c r="C336" s="21" t="s">
         <v>616</v>
       </c>
-      <c r="D336" s="15"/>
+      <c r="D336" s="21"/>
       <c r="E336" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F336" s="15" t="s">
+      <c r="F336" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="G336" s="15"/>
-    </row>
-    <row r="337" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G336" s="21"/>
+    </row>
+    <row r="337" spans="2:7">
       <c r="B337" s="2" t="s">
         <v>6</v>
       </c>
@@ -8830,7 +8833,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="338" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:7">
       <c r="B338" s="1">
         <v>1</v>
       </c>
@@ -8848,7 +8851,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="339" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:7">
       <c r="B339" s="1">
         <v>2</v>
       </c>
@@ -8866,7 +8869,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="340" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:7">
       <c r="B340" s="1">
         <v>3</v>
       </c>
@@ -8882,7 +8885,7 @@
       <c r="F340" s="1"/>
       <c r="G340" s="1"/>
     </row>
-    <row r="341" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:7">
       <c r="B341" s="1">
         <v>4</v>
       </c>
@@ -8900,7 +8903,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="342" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:7">
       <c r="B342" s="1">
         <v>5</v>
       </c>
@@ -8916,7 +8919,7 @@
       <c r="F342" s="1"/>
       <c r="G342" s="1"/>
     </row>
-    <row r="343" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:7">
       <c r="B343" s="1">
         <v>6</v>
       </c>
@@ -8932,7 +8935,7 @@
       <c r="F343" s="1"/>
       <c r="G343" s="1"/>
     </row>
-    <row r="344" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:7">
       <c r="B344" s="1">
         <v>7</v>
       </c>
@@ -8948,7 +8951,7 @@
       <c r="F344" s="1"/>
       <c r="G344" s="1"/>
     </row>
-    <row r="345" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:7">
       <c r="B345" s="1">
         <v>8</v>
       </c>
@@ -8964,39 +8967,39 @@
       <c r="F345" s="1"/>
       <c r="G345" s="1"/>
     </row>
-    <row r="347" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:7" ht="16.5" customHeight="1">
       <c r="B347" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C347" s="16" t="s">
+      <c r="C347" s="20" t="s">
         <v>402</v>
       </c>
-      <c r="D347" s="16"/>
+      <c r="D347" s="20"/>
       <c r="E347" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F347" s="15"/>
-      <c r="G347" s="15"/>
-    </row>
-    <row r="348" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F347" s="21"/>
+      <c r="G347" s="21"/>
+    </row>
+    <row r="348" spans="2:7">
       <c r="B348" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C348" s="15" t="s">
+      <c r="C348" s="21" t="s">
         <v>403</v>
       </c>
-      <c r="D348" s="15"/>
+      <c r="D348" s="21"/>
       <c r="E348" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F348" s="15" t="s">
+      <c r="F348" s="21" t="s">
         <v>404</v>
       </c>
-      <c r="G348" s="15" t="s">
+      <c r="G348" s="21" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="349" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:7">
       <c r="B349" s="2" t="s">
         <v>6</v>
       </c>
@@ -9016,7 +9019,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="350" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:7">
       <c r="B350" s="1">
         <v>1</v>
       </c>
@@ -9034,25 +9037,25 @@
         <v>14</v>
       </c>
     </row>
-    <row r="351" spans="2:7" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B351" s="20">
+    <row r="351" spans="2:7" s="17" customFormat="1">
+      <c r="B351" s="16">
         <v>2</v>
       </c>
-      <c r="C351" s="20" t="s">
+      <c r="C351" s="16" t="s">
         <v>617</v>
       </c>
-      <c r="D351" s="20" t="s">
+      <c r="D351" s="16" t="s">
         <v>615</v>
       </c>
-      <c r="E351" s="20" t="s">
+      <c r="E351" s="16" t="s">
         <v>352</v>
       </c>
-      <c r="F351" s="20"/>
-      <c r="G351" s="20" t="s">
+      <c r="F351" s="16"/>
+      <c r="G351" s="16" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="352" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:7">
       <c r="B352" s="1">
         <v>3</v>
       </c>
@@ -9068,7 +9071,7 @@
       <c r="F352" s="1"/>
       <c r="G352" s="1"/>
     </row>
-    <row r="353" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:9">
       <c r="B353" s="1">
         <v>4</v>
       </c>
@@ -9086,7 +9089,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="354" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:9">
       <c r="B354" s="1">
         <v>5</v>
       </c>
@@ -9102,7 +9105,7 @@
       <c r="F354" s="1"/>
       <c r="G354" s="1"/>
     </row>
-    <row r="355" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:9">
       <c r="B355" s="1">
         <v>6</v>
       </c>
@@ -9118,7 +9121,7 @@
       <c r="F355" s="1"/>
       <c r="G355" s="1"/>
     </row>
-    <row r="356" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:9">
       <c r="B356" s="1">
         <v>7</v>
       </c>
@@ -9134,7 +9137,7 @@
       <c r="F356" s="1"/>
       <c r="G356" s="1"/>
     </row>
-    <row r="357" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:9">
       <c r="B357" s="1">
         <v>8</v>
       </c>
@@ -9152,7 +9155,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="358" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:9">
       <c r="B358" s="1">
         <v>9</v>
       </c>
@@ -9170,7 +9173,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="359" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:9">
       <c r="B359" s="1">
         <v>10</v>
       </c>
@@ -9188,7 +9191,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="360" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:9">
       <c r="B360" s="1">
         <v>11</v>
       </c>
@@ -9207,7 +9210,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="361" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:9">
       <c r="B361" s="1">
         <v>12</v>
       </c>
@@ -9226,35 +9229,35 @@
         <v>619</v>
       </c>
     </row>
-    <row r="363" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:9" ht="16.5" customHeight="1">
       <c r="B363" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C363" s="16" t="s">
+      <c r="C363" s="20" t="s">
         <v>419</v>
       </c>
-      <c r="D363" s="16"/>
+      <c r="D363" s="20"/>
       <c r="E363" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F363" s="15"/>
-      <c r="G363" s="15"/>
-    </row>
-    <row r="364" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F363" s="21"/>
+      <c r="G363" s="21"/>
+    </row>
+    <row r="364" spans="2:9">
       <c r="B364" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C364" s="15" t="s">
+      <c r="C364" s="21" t="s">
         <v>420</v>
       </c>
-      <c r="D364" s="15"/>
+      <c r="D364" s="21"/>
       <c r="E364" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F364" s="15"/>
-      <c r="G364" s="15"/>
-    </row>
-    <row r="365" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F364" s="21"/>
+      <c r="G364" s="21"/>
+    </row>
+    <row r="365" spans="2:9">
       <c r="B365" s="2" t="s">
         <v>6</v>
       </c>
@@ -9274,7 +9277,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="366" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:9">
       <c r="B366" s="1">
         <v>1</v>
       </c>
@@ -9292,7 +9295,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="367" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:9">
       <c r="B367" s="1">
         <v>2</v>
       </c>
@@ -9312,7 +9315,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="368" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:9">
       <c r="B368" s="1">
         <v>3</v>
       </c>
@@ -9330,7 +9333,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="369" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:9">
       <c r="B369" s="1" t="s">
         <v>11</v>
       </c>
@@ -9342,37 +9345,37 @@
       <c r="F369" s="1"/>
       <c r="G369" s="1"/>
     </row>
-    <row r="371" spans="2:9" s="5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:9" s="5" customFormat="1" ht="16.5" customHeight="1">
       <c r="B371" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C371" s="17" t="s">
+      <c r="C371" s="22" t="s">
         <v>522</v>
       </c>
-      <c r="D371" s="17"/>
+      <c r="D371" s="22"/>
       <c r="E371" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F371" s="18"/>
-      <c r="G371" s="18"/>
+      <c r="F371" s="23"/>
+      <c r="G371" s="23"/>
       <c r="I371"/>
     </row>
-    <row r="372" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:9" s="5" customFormat="1">
       <c r="B372" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C372" s="18" t="s">
+      <c r="C372" s="23" t="s">
         <v>420</v>
       </c>
-      <c r="D372" s="18"/>
+      <c r="D372" s="23"/>
       <c r="E372" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F372" s="18"/>
-      <c r="G372" s="18"/>
+      <c r="F372" s="23"/>
+      <c r="G372" s="23"/>
       <c r="I372"/>
     </row>
-    <row r="373" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:9" s="5" customFormat="1">
       <c r="B373" s="3" t="s">
         <v>6</v>
       </c>
@@ -9393,7 +9396,7 @@
       </c>
       <c r="I373"/>
     </row>
-    <row r="374" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:9" s="5" customFormat="1">
       <c r="B374" s="4">
         <v>1</v>
       </c>
@@ -9412,7 +9415,7 @@
       </c>
       <c r="I374"/>
     </row>
-    <row r="375" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:9" s="5" customFormat="1">
       <c r="B375" s="4">
         <v>2</v>
       </c>
@@ -9431,7 +9434,7 @@
       </c>
       <c r="I375"/>
     </row>
-    <row r="376" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:9" s="5" customFormat="1">
       <c r="B376" s="4">
         <v>3</v>
       </c>
@@ -9450,7 +9453,7 @@
       </c>
       <c r="I376"/>
     </row>
-    <row r="377" spans="2:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:9" s="5" customFormat="1">
       <c r="B377" s="4" t="s">
         <v>11</v>
       </c>
@@ -9463,39 +9466,39 @@
       <c r="G377" s="4"/>
       <c r="I377"/>
     </row>
-    <row r="379" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:9" ht="16.5" customHeight="1">
       <c r="B379" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C379" s="16" t="s">
+      <c r="C379" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="D379" s="16"/>
+      <c r="D379" s="20"/>
       <c r="E379" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F379" s="15"/>
-      <c r="G379" s="15"/>
-    </row>
-    <row r="380" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F379" s="21"/>
+      <c r="G379" s="21"/>
+    </row>
+    <row r="380" spans="2:9">
       <c r="B380" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C380" s="15" t="s">
+      <c r="C380" s="21" t="s">
         <v>426</v>
       </c>
-      <c r="D380" s="15"/>
+      <c r="D380" s="21"/>
       <c r="E380" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F380" s="16" t="s">
+      <c r="F380" s="20" t="s">
         <v>561</v>
       </c>
-      <c r="G380" s="15" t="s">
+      <c r="G380" s="21" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="381" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:9">
       <c r="B381" s="2" t="s">
         <v>6</v>
       </c>
@@ -9515,7 +9518,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="382" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:9">
       <c r="B382" s="1">
         <v>1</v>
       </c>
@@ -9533,7 +9536,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="383" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:9">
       <c r="B383" s="1">
         <v>2</v>
       </c>
@@ -9551,7 +9554,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="384" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:9">
       <c r="B384" s="1">
         <v>3</v>
       </c>
@@ -9569,7 +9572,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="385" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:9">
       <c r="B385" s="1">
         <v>4</v>
       </c>
@@ -9589,7 +9592,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="386" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:9">
       <c r="B386" s="1">
         <v>5</v>
       </c>
@@ -9609,7 +9612,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="387" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:9">
       <c r="B387" s="1">
         <v>6</v>
       </c>
@@ -9627,7 +9630,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="388" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:9">
       <c r="B388" s="1">
         <v>7</v>
       </c>
@@ -9647,7 +9650,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="389" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:9">
       <c r="B389" s="1">
         <v>8</v>
       </c>
@@ -9665,7 +9668,7 @@
       </c>
       <c r="G389" s="1"/>
     </row>
-    <row r="390" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:9">
       <c r="B390" s="1">
         <v>9</v>
       </c>
@@ -9683,7 +9686,7 @@
       </c>
       <c r="G390" s="1"/>
     </row>
-    <row r="391" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:9">
       <c r="B391" s="1">
         <v>10</v>
       </c>
@@ -9701,7 +9704,7 @@
       </c>
       <c r="G391" s="1"/>
     </row>
-    <row r="392" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:9">
       <c r="B392" s="1">
         <v>11</v>
       </c>
@@ -9720,7 +9723,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="393" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:9">
       <c r="B393" s="1">
         <v>12</v>
       </c>
@@ -9739,7 +9742,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="394" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:9">
       <c r="B394" s="1">
         <v>13</v>
       </c>
@@ -9757,7 +9760,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="395" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:9">
       <c r="B395" s="1">
         <v>14</v>
       </c>
@@ -9775,7 +9778,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="396" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:9">
       <c r="B396" s="1">
         <v>15</v>
       </c>
@@ -9796,7 +9799,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="397" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:9">
       <c r="B397" s="1">
         <v>16</v>
       </c>
@@ -9817,7 +9820,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="398" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:9">
       <c r="B398" s="1">
         <v>17</v>
       </c>
@@ -9836,7 +9839,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="399" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:9">
       <c r="B399" s="1">
         <v>18</v>
       </c>
@@ -9852,7 +9855,7 @@
       <c r="F399" s="1"/>
       <c r="G399" s="1"/>
     </row>
-    <row r="400" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:9">
       <c r="B400" s="1" t="s">
         <v>11</v>
       </c>
@@ -9864,37 +9867,37 @@
       <c r="F400" s="1"/>
       <c r="G400" s="1"/>
     </row>
-    <row r="402" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:9" ht="16.5" customHeight="1">
       <c r="B402" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C402" s="16" t="s">
+      <c r="C402" s="20" t="s">
         <v>448</v>
       </c>
-      <c r="D402" s="16"/>
+      <c r="D402" s="20"/>
       <c r="E402" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F402" s="15"/>
-      <c r="G402" s="15"/>
-    </row>
-    <row r="403" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F402" s="21"/>
+      <c r="G402" s="21"/>
+    </row>
+    <row r="403" spans="2:9">
       <c r="B403" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C403" s="15" t="s">
+      <c r="C403" s="21" t="s">
         <v>449</v>
       </c>
-      <c r="D403" s="15"/>
+      <c r="D403" s="21"/>
       <c r="E403" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F403" s="15" t="s">
+      <c r="F403" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="G403" s="15"/>
-    </row>
-    <row r="404" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G403" s="21"/>
+    </row>
+    <row r="404" spans="2:9">
       <c r="B404" s="2" t="s">
         <v>6</v>
       </c>
@@ -9914,7 +9917,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="405" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:9">
       <c r="B405" s="1">
         <v>1</v>
       </c>
@@ -9932,7 +9935,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="406" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:9">
       <c r="B406" s="1">
         <v>2</v>
       </c>
@@ -9950,7 +9953,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="407" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:9">
       <c r="B407" s="1">
         <v>3</v>
       </c>
@@ -9970,7 +9973,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="408" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:9">
       <c r="B408" s="1">
         <v>4</v>
       </c>
@@ -9988,7 +9991,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="409" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:9">
       <c r="B409" s="1">
         <v>5</v>
       </c>
@@ -10009,35 +10012,35 @@
         <v>576</v>
       </c>
     </row>
-    <row r="411" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:9" ht="16.5" customHeight="1">
       <c r="B411" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C411" s="16" t="s">
+      <c r="C411" s="20" t="s">
         <v>456</v>
       </c>
-      <c r="D411" s="16"/>
+      <c r="D411" s="20"/>
       <c r="E411" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F411" s="15"/>
-      <c r="G411" s="15"/>
-    </row>
-    <row r="412" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F411" s="21"/>
+      <c r="G411" s="21"/>
+    </row>
+    <row r="412" spans="2:9">
       <c r="B412" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C412" s="15" t="s">
+      <c r="C412" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="D412" s="15"/>
+      <c r="D412" s="21"/>
       <c r="E412" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F412" s="15"/>
-      <c r="G412" s="15"/>
-    </row>
-    <row r="413" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F412" s="21"/>
+      <c r="G412" s="21"/>
+    </row>
+    <row r="413" spans="2:9">
       <c r="B413" s="2" t="s">
         <v>6</v>
       </c>
@@ -10057,7 +10060,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="414" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:9">
       <c r="B414" s="1">
         <v>1</v>
       </c>
@@ -10075,7 +10078,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="415" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:9">
       <c r="B415" s="1">
         <v>2</v>
       </c>
@@ -10095,7 +10098,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="416" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:9">
       <c r="B416" s="1">
         <v>3</v>
       </c>
@@ -10115,7 +10118,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="417" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:9">
       <c r="B417" s="1">
         <v>4</v>
       </c>
@@ -10133,7 +10136,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="418" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:9">
       <c r="B418" s="1">
         <v>5</v>
       </c>
@@ -10153,7 +10156,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="419" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:9">
       <c r="B419" s="1">
         <v>6</v>
       </c>
@@ -10171,7 +10174,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="420" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:9">
       <c r="B420" s="1">
         <v>7</v>
       </c>
@@ -10190,37 +10193,37 @@
         <v>576</v>
       </c>
     </row>
-    <row r="422" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:9" ht="16.5" customHeight="1">
       <c r="B422" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C422" s="16" t="s">
+      <c r="C422" s="20" t="s">
         <v>468</v>
       </c>
-      <c r="D422" s="16"/>
+      <c r="D422" s="20"/>
       <c r="E422" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F422" s="15"/>
-      <c r="G422" s="15"/>
-    </row>
-    <row r="423" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="F422" s="21"/>
+      <c r="G422" s="21"/>
+    </row>
+    <row r="423" spans="2:9">
       <c r="B423" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C423" s="15" t="s">
+      <c r="C423" s="21" t="s">
         <v>469</v>
       </c>
-      <c r="D423" s="15"/>
+      <c r="D423" s="21"/>
       <c r="E423" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F423" s="15" t="s">
+      <c r="F423" s="21" t="s">
         <v>470</v>
       </c>
-      <c r="G423" s="15"/>
-    </row>
-    <row r="424" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="G423" s="21"/>
+    </row>
+    <row r="424" spans="2:9">
       <c r="B424" s="2" t="s">
         <v>6</v>
       </c>
@@ -10240,7 +10243,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="425" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:9">
       <c r="B425" s="1">
         <v>1</v>
       </c>
@@ -10258,7 +10261,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="426" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:9">
       <c r="B426" s="1">
         <v>2</v>
       </c>
@@ -10276,7 +10279,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="427" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:9">
       <c r="B427" s="1">
         <v>3</v>
       </c>
@@ -10294,7 +10297,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="428" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:9">
       <c r="B428" s="1">
         <v>4</v>
       </c>
@@ -10314,7 +10317,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="429" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:9">
       <c r="B429" s="1">
         <v>5</v>
       </c>
@@ -10334,7 +10337,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="430" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:9">
       <c r="B430" s="1">
         <v>6</v>
       </c>
@@ -10353,37 +10356,37 @@
         <v>576</v>
       </c>
     </row>
-    <row r="432" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:9" ht="16.5" customHeight="1">
       <c r="B432" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C432" s="16" t="s">
+      <c r="C432" s="20" t="s">
         <v>484</v>
       </c>
-      <c r="D432" s="16"/>
+      <c r="D432" s="20"/>
       <c r="E432" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F432" s="15"/>
-      <c r="G432" s="15"/>
-    </row>
-    <row r="433" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F432" s="21"/>
+      <c r="G432" s="21"/>
+    </row>
+    <row r="433" spans="2:7">
       <c r="B433" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C433" s="15" t="s">
+      <c r="C433" s="21" t="s">
         <v>485</v>
       </c>
-      <c r="D433" s="15"/>
+      <c r="D433" s="21"/>
       <c r="E433" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F433" s="15" t="s">
+      <c r="F433" s="21" t="s">
         <v>486</v>
       </c>
-      <c r="G433" s="15"/>
-    </row>
-    <row r="434" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G433" s="21"/>
+    </row>
+    <row r="434" spans="2:7">
       <c r="B434" s="2" t="s">
         <v>6</v>
       </c>
@@ -10403,7 +10406,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="435" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:7">
       <c r="B435" s="1">
         <v>1</v>
       </c>
@@ -10423,7 +10426,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="436" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:7">
       <c r="B436" s="1">
         <v>2</v>
       </c>
@@ -10441,7 +10444,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="437" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:7">
       <c r="B437" s="1">
         <v>3</v>
       </c>
@@ -10459,7 +10462,7 @@
       </c>
       <c r="G437" s="1"/>
     </row>
-    <row r="438" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:7">
       <c r="B438" s="1">
         <v>4</v>
       </c>
@@ -10479,136 +10482,6 @@
     </row>
   </sheetData>
   <mergeCells count="148">
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="F103:G103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="F104:G104"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="F116:G116"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="F141:G141"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="F130:G130"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="F167:G167"/>
-    <mergeCell ref="C168:D168"/>
-    <mergeCell ref="F168:G168"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="F175:G175"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="F142:G142"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="F153:G153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="F154:G154"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="F197:G197"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="F198:G198"/>
-    <mergeCell ref="C206:D206"/>
-    <mergeCell ref="F206:G206"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="F176:G176"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="F185:G185"/>
-    <mergeCell ref="C186:D186"/>
-    <mergeCell ref="F186:G186"/>
-    <mergeCell ref="C228:D228"/>
-    <mergeCell ref="F228:G228"/>
-    <mergeCell ref="C229:D229"/>
-    <mergeCell ref="F229:G229"/>
-    <mergeCell ref="C240:D240"/>
-    <mergeCell ref="F240:G240"/>
-    <mergeCell ref="C207:D207"/>
-    <mergeCell ref="F207:G207"/>
-    <mergeCell ref="C214:D214"/>
-    <mergeCell ref="F214:G214"/>
-    <mergeCell ref="C215:D215"/>
-    <mergeCell ref="F215:G215"/>
-    <mergeCell ref="C264:D264"/>
-    <mergeCell ref="F264:G264"/>
-    <mergeCell ref="C265:D265"/>
-    <mergeCell ref="F265:G265"/>
-    <mergeCell ref="C277:D277"/>
-    <mergeCell ref="F277:G277"/>
-    <mergeCell ref="C241:D241"/>
-    <mergeCell ref="F241:G241"/>
-    <mergeCell ref="C252:D252"/>
-    <mergeCell ref="F252:G252"/>
-    <mergeCell ref="C253:D253"/>
-    <mergeCell ref="F253:G253"/>
-    <mergeCell ref="C303:D303"/>
-    <mergeCell ref="F303:G303"/>
-    <mergeCell ref="C304:D304"/>
-    <mergeCell ref="F304:G304"/>
-    <mergeCell ref="C316:D316"/>
-    <mergeCell ref="F316:G316"/>
-    <mergeCell ref="C278:D278"/>
-    <mergeCell ref="F278:G278"/>
-    <mergeCell ref="C290:D290"/>
-    <mergeCell ref="F290:G290"/>
-    <mergeCell ref="C291:D291"/>
-    <mergeCell ref="F291:G291"/>
-    <mergeCell ref="C347:D347"/>
-    <mergeCell ref="F347:G347"/>
-    <mergeCell ref="C317:D317"/>
-    <mergeCell ref="F317:G317"/>
-    <mergeCell ref="C335:D335"/>
-    <mergeCell ref="F335:G335"/>
-    <mergeCell ref="C336:D336"/>
-    <mergeCell ref="F336:G336"/>
-    <mergeCell ref="C363:D363"/>
-    <mergeCell ref="F363:G363"/>
-    <mergeCell ref="C364:D364"/>
-    <mergeCell ref="F364:G364"/>
-    <mergeCell ref="C379:D379"/>
-    <mergeCell ref="F379:G379"/>
-    <mergeCell ref="C348:D348"/>
-    <mergeCell ref="F348:G348"/>
-    <mergeCell ref="C371:D371"/>
-    <mergeCell ref="F371:G371"/>
-    <mergeCell ref="C372:D372"/>
-    <mergeCell ref="F372:G372"/>
     <mergeCell ref="C380:D380"/>
     <mergeCell ref="F380:G380"/>
     <mergeCell ref="C402:D402"/>
@@ -10627,6 +10500,136 @@
     <mergeCell ref="F422:G422"/>
     <mergeCell ref="C423:D423"/>
     <mergeCell ref="F423:G423"/>
+    <mergeCell ref="C364:D364"/>
+    <mergeCell ref="F364:G364"/>
+    <mergeCell ref="C379:D379"/>
+    <mergeCell ref="F379:G379"/>
+    <mergeCell ref="C348:D348"/>
+    <mergeCell ref="F348:G348"/>
+    <mergeCell ref="C371:D371"/>
+    <mergeCell ref="F371:G371"/>
+    <mergeCell ref="C372:D372"/>
+    <mergeCell ref="F372:G372"/>
+    <mergeCell ref="C347:D347"/>
+    <mergeCell ref="F347:G347"/>
+    <mergeCell ref="C317:D317"/>
+    <mergeCell ref="F317:G317"/>
+    <mergeCell ref="C335:D335"/>
+    <mergeCell ref="F335:G335"/>
+    <mergeCell ref="C336:D336"/>
+    <mergeCell ref="F336:G336"/>
+    <mergeCell ref="C363:D363"/>
+    <mergeCell ref="F363:G363"/>
+    <mergeCell ref="C303:D303"/>
+    <mergeCell ref="F303:G303"/>
+    <mergeCell ref="C304:D304"/>
+    <mergeCell ref="F304:G304"/>
+    <mergeCell ref="C316:D316"/>
+    <mergeCell ref="F316:G316"/>
+    <mergeCell ref="C278:D278"/>
+    <mergeCell ref="F278:G278"/>
+    <mergeCell ref="C290:D290"/>
+    <mergeCell ref="F290:G290"/>
+    <mergeCell ref="C291:D291"/>
+    <mergeCell ref="F291:G291"/>
+    <mergeCell ref="C264:D264"/>
+    <mergeCell ref="F264:G264"/>
+    <mergeCell ref="C265:D265"/>
+    <mergeCell ref="F265:G265"/>
+    <mergeCell ref="C277:D277"/>
+    <mergeCell ref="F277:G277"/>
+    <mergeCell ref="C241:D241"/>
+    <mergeCell ref="F241:G241"/>
+    <mergeCell ref="C252:D252"/>
+    <mergeCell ref="F252:G252"/>
+    <mergeCell ref="C253:D253"/>
+    <mergeCell ref="F253:G253"/>
+    <mergeCell ref="C228:D228"/>
+    <mergeCell ref="F228:G228"/>
+    <mergeCell ref="C229:D229"/>
+    <mergeCell ref="F229:G229"/>
+    <mergeCell ref="C240:D240"/>
+    <mergeCell ref="F240:G240"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="F207:G207"/>
+    <mergeCell ref="C214:D214"/>
+    <mergeCell ref="F214:G214"/>
+    <mergeCell ref="C215:D215"/>
+    <mergeCell ref="F215:G215"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="F197:G197"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="F198:G198"/>
+    <mergeCell ref="C206:D206"/>
+    <mergeCell ref="F206:G206"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="F176:G176"/>
+    <mergeCell ref="C185:D185"/>
+    <mergeCell ref="F185:G185"/>
+    <mergeCell ref="C186:D186"/>
+    <mergeCell ref="F186:G186"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="F168:G168"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="F175:G175"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="F142:G142"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="F153:G153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="F154:G154"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="F141:G141"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="F167:G167"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="F116:G116"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:G14"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="E1:E1048576">

--- a/Document/專題/db_diagram.xlsx
+++ b/Document/專題/db_diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\RentalManagementPlatform\Document\專題\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CBDBB0-405F-413B-B707-E7D1629092EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4112F1-DB0D-4E4F-AC77-11CFA67041EF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="db" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">db!$I$2:$I$438</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">db!$I$2:$I$439</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="642">
   <si>
     <t>表格名稱</t>
   </si>
@@ -2100,10 +2100,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>到期不續訂</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>1.USER.user_id(role=host) → 2.HOST_SUBSCRIPTION.created_at → 3.HOST_SUBSCRIPTION.start_date</t>
   </si>
   <si>
@@ -2174,6 +2170,22 @@
   <si>
     <t>中文：房東訂閱
 英文：HOST_SUBSCRIPTION</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>到期不續訂(NN)</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>is_deleted</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>軟刪除</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>BIT</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -2376,7 +2388,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2571,6 +2583,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2843,7 +2867,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2904,11 +2928,17 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" xfId="7" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2922,10 +2952,16 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" xfId="7" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3308,7 +3344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:P438"/>
+  <dimension ref="B2:P439"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
@@ -3327,31 +3363,31 @@
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="23" t="s">
         <v>590</v>
       </c>
-      <c r="D2" s="20"/>
+      <c r="D2" s="23"/>
       <c r="E2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
     </row>
     <row r="3" spans="2:9">
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="21"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="21"/>
+      <c r="G3" s="22"/>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="2" t="s">
@@ -3513,31 +3549,31 @@
       <c r="B13" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="23" t="s">
         <v>572</v>
       </c>
-      <c r="D13" s="20"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
     </row>
     <row r="14" spans="2:9">
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="22" t="s">
         <v>571</v>
       </c>
-      <c r="D14" s="21"/>
+      <c r="D14" s="22"/>
       <c r="E14" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="23" t="s">
         <v>567</v>
       </c>
-      <c r="G14" s="21" t="s">
+      <c r="G14" s="22" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3675,7 +3711,7 @@
         <v>7</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>53</v>
@@ -3762,7 +3798,7 @@
         <v>12</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>65</v>
@@ -3772,7 +3808,7 @@
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="28" spans="2:9">
@@ -3798,29 +3834,29 @@
       <c r="B30" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="20"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
     </row>
     <row r="31" spans="2:9">
       <c r="B31" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="D31" s="21"/>
+      <c r="D31" s="22"/>
       <c r="E31" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
     </row>
     <row r="32" spans="2:9">
       <c r="B32" s="2" t="s">
@@ -3914,21 +3950,21 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="2:16">
-      <c r="B37" s="1">
+    <row r="37" spans="2:16" s="29" customFormat="1">
+      <c r="B37" s="28">
         <v>5</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="28" t="s">
         <v>261</v>
       </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1" t="s">
+      <c r="F37" s="28"/>
+      <c r="G37" s="28" t="s">
         <v>77</v>
       </c>
     </row>
@@ -4183,31 +4219,31 @@
       <c r="B49" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C49" s="20" t="s">
+      <c r="C49" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="D49" s="20"/>
+      <c r="D49" s="23"/>
       <c r="E49" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F49" s="21"/>
-      <c r="G49" s="21"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
     </row>
     <row r="50" spans="2:7">
       <c r="B50" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C50" s="21" t="s">
+      <c r="C50" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="D50" s="21"/>
+      <c r="D50" s="22"/>
       <c r="E50" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F50" s="21" t="s">
+      <c r="F50" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="G50" s="21"/>
+      <c r="G50" s="22"/>
     </row>
     <row r="51" spans="2:7">
       <c r="B51" s="2" t="s">
@@ -4305,29 +4341,29 @@
       <c r="B57" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C57" s="20" t="s">
+      <c r="C57" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="20"/>
+      <c r="D57" s="23"/>
       <c r="E57" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F57" s="21"/>
-      <c r="G57" s="21"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
     </row>
     <row r="58" spans="2:7">
       <c r="B58" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C58" s="21" t="s">
+      <c r="C58" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="D58" s="21"/>
+      <c r="D58" s="22"/>
       <c r="E58" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
     </row>
     <row r="59" spans="2:7">
       <c r="B59" s="2" t="s">
@@ -4389,29 +4425,29 @@
       <c r="B63" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C63" s="20" t="s">
+      <c r="C63" s="23" t="s">
         <v>547</v>
       </c>
-      <c r="D63" s="20"/>
+      <c r="D63" s="23"/>
       <c r="E63" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
     </row>
     <row r="64" spans="2:7">
       <c r="B64" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C64" s="21" t="s">
+      <c r="C64" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D64" s="21"/>
+      <c r="D64" s="22"/>
       <c r="E64" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
     </row>
     <row r="65" spans="2:9">
       <c r="B65" s="2" t="s">
@@ -4656,271 +4692,268 @@
         <v>123</v>
       </c>
     </row>
-    <row r="78" spans="2:9" s="10" customFormat="1">
-      <c r="B78" s="26">
+    <row r="78" spans="2:9" s="31" customFormat="1">
+      <c r="B78" s="30">
         <v>13</v>
       </c>
-      <c r="C78" s="26" t="s">
+      <c r="C78" s="30" t="s">
+        <v>639</v>
+      </c>
+      <c r="D78" s="30" t="s">
+        <v>640</v>
+      </c>
+      <c r="E78" s="30" t="s">
+        <v>641</v>
+      </c>
+      <c r="F78" s="30"/>
+      <c r="G78" s="30"/>
+    </row>
+    <row r="79" spans="2:9" s="10" customFormat="1">
+      <c r="B79" s="20">
+        <v>13</v>
+      </c>
+      <c r="C79" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D78" s="26" t="s">
+      <c r="D79" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="E78" s="26" t="s">
+      <c r="E79" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="F78" s="26"/>
-      <c r="G78" s="26"/>
-      <c r="I78" s="10" t="s">
+      <c r="F79" s="20"/>
+      <c r="G79" s="20"/>
+      <c r="I79" s="10" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="80" spans="2:9" s="5" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B80" s="3" t="s">
+    <row r="81" spans="2:9" s="5" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B81" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C80" s="22" t="s">
+      <c r="C81" s="24" t="s">
         <v>548</v>
       </c>
-      <c r="D80" s="22"/>
-      <c r="E80" s="3" t="s">
+      <c r="D81" s="24"/>
+      <c r="E81" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F80" s="23"/>
-      <c r="G80" s="23"/>
-      <c r="I80"/>
-    </row>
-    <row r="81" spans="2:9" s="5" customFormat="1">
-      <c r="B81" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C81" s="23" t="s">
-        <v>542</v>
-      </c>
-      <c r="D81" s="23"/>
-      <c r="E81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F81" s="22" t="s">
-        <v>546</v>
-      </c>
-      <c r="G81" s="23" t="s">
-        <v>37</v>
-      </c>
+      <c r="F81" s="25"/>
+      <c r="G81" s="25"/>
       <c r="I81"/>
     </row>
     <row r="82" spans="2:9" s="5" customFormat="1">
       <c r="B82" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C82" s="25" t="s">
+        <v>542</v>
+      </c>
+      <c r="D82" s="25"/>
+      <c r="E82" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F82" s="24" t="s">
+        <v>546</v>
+      </c>
+      <c r="G82" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="I82"/>
+    </row>
+    <row r="83" spans="2:9" s="5" customFormat="1">
+      <c r="B83" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="E83" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="F83" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G82" s="3" t="s">
+      <c r="G83" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="I82"/>
-    </row>
-    <row r="83" spans="2:9" s="5" customFormat="1">
-      <c r="B83" s="4">
-        <v>1</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="I83"/>
     </row>
     <row r="84" spans="2:9" s="5" customFormat="1">
       <c r="B84" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>39</v>
+        <v>542</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="4" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="I84"/>
     </row>
     <row r="85" spans="2:9" s="5" customFormat="1">
       <c r="B85" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>543</v>
+        <v>39</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>544</v>
+        <v>40</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I85"/>
+    </row>
+    <row r="86" spans="2:9" s="5" customFormat="1">
+      <c r="B86" s="4">
+        <v>3</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4" t="s">
         <v>545</v>
       </c>
-      <c r="I85"/>
-    </row>
-    <row r="87" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B87" s="2" t="s">
+      <c r="I86"/>
+    </row>
+    <row r="88" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B88" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C87" s="20" t="s">
+      <c r="C88" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="D87" s="20"/>
-      <c r="E87" s="2" t="s">
+      <c r="D88" s="23"/>
+      <c r="E88" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F87" s="21"/>
-      <c r="G87" s="21"/>
-    </row>
-    <row r="88" spans="2:9">
-      <c r="B88" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C88" s="21" t="s">
-        <v>604</v>
-      </c>
-      <c r="D88" s="21"/>
-      <c r="E88" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F88" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="G88" s="21" t="s">
-        <v>37</v>
-      </c>
+      <c r="F88" s="22"/>
+      <c r="G88" s="22"/>
     </row>
     <row r="89" spans="2:9">
       <c r="B89" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C89" s="22" t="s">
+        <v>604</v>
+      </c>
+      <c r="D89" s="22"/>
+      <c r="E89" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G89" s="22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9">
+      <c r="B90" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C90" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D89" s="2" t="s">
+      <c r="D90" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E89" s="2" t="s">
+      <c r="E90" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F89" s="2" t="s">
+      <c r="F90" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G89" s="2" t="s">
+      <c r="G90" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="90" spans="2:9">
-      <c r="B90" s="1">
-        <v>1</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="91" spans="2:9">
       <c r="B91" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>39</v>
+        <v>604</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F91" s="1"/>
       <c r="G91" s="1" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92" spans="2:9">
       <c r="B92" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F92" s="1"/>
       <c r="G92" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="93" spans="2:9">
       <c r="B93" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>238</v>
+        <v>13</v>
       </c>
       <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
-      <c r="I93" s="10" t="s">
-        <v>605</v>
+      <c r="G93" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="94" spans="2:9">
       <c r="B94" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>238</v>
@@ -4931,494 +4964,496 @@
         <v>605</v>
       </c>
     </row>
-    <row r="96" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B96" s="2" t="s">
+    <row r="95" spans="2:9">
+      <c r="B95" s="1">
+        <v>5</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="I95" s="10" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="97" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B97" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C96" s="20" t="s">
+      <c r="C97" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="D96" s="20"/>
-      <c r="E96" s="2" t="s">
+      <c r="D97" s="23"/>
+      <c r="E97" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F96" s="21"/>
-      <c r="G96" s="21"/>
-    </row>
-    <row r="97" spans="2:9">
-      <c r="B97" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C97" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="D97" s="21"/>
-      <c r="E97" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F97" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="G97" s="21"/>
+      <c r="F97" s="22"/>
+      <c r="G97" s="22"/>
     </row>
     <row r="98" spans="2:9">
       <c r="B98" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C98" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98" s="22"/>
+      <c r="E98" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F98" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="G98" s="22"/>
+    </row>
+    <row r="99" spans="2:9">
+      <c r="B99" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C99" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="D99" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E98" s="2" t="s">
+      <c r="E99" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F98" s="2" t="s">
+      <c r="F99" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G98" s="2" t="s">
+      <c r="G99" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="99" spans="2:9">
-      <c r="B99" s="1">
-        <v>1</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="100" spans="2:9">
       <c r="B100" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F100" s="1"/>
       <c r="G100" s="1" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101" spans="2:9">
       <c r="B101" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="F101" s="1"/>
       <c r="G101" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="102" spans="2:9">
+      <c r="B102" s="1">
+        <v>3</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="103" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B103" s="3" t="s">
+    <row r="104" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B104" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C103" s="22" t="s">
+      <c r="C104" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="D103" s="22"/>
-      <c r="E103" s="3" t="s">
+      <c r="D104" s="24"/>
+      <c r="E104" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F103" s="23"/>
-      <c r="G103" s="23"/>
-    </row>
-    <row r="104" spans="2:9">
-      <c r="B104" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C104" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="D104" s="23"/>
-      <c r="E104" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F104" s="22" t="s">
-        <v>566</v>
-      </c>
-      <c r="G104" s="23" t="s">
-        <v>139</v>
-      </c>
+      <c r="F104" s="25"/>
+      <c r="G104" s="25"/>
     </row>
     <row r="105" spans="2:9">
       <c r="B105" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C105" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="D105" s="25"/>
+      <c r="E105" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F105" s="24" t="s">
+        <v>566</v>
+      </c>
+      <c r="G105" s="25" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="106" spans="2:9">
+      <c r="B106" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C106" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D105" s="3" t="s">
+      <c r="D106" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E105" s="3" t="s">
+      <c r="E106" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F105" s="3" t="s">
+      <c r="F106" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G105" s="3" t="s">
+      <c r="G106" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="2:9">
-      <c r="B106" s="4">
+    <row r="107" spans="2:9">
+      <c r="B107" s="4">
         <v>1</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C107" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="D106" s="4" t="s">
+      <c r="D107" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F106" s="4"/>
-      <c r="G106" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="107" spans="2:9" s="5" customFormat="1">
-      <c r="B107" s="4">
-        <v>2</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="D107" s="4" t="s">
-        <v>514</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="I107"/>
-    </row>
-    <row r="108" spans="2:9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="2:9" s="5" customFormat="1">
       <c r="B108" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>35</v>
+        <v>513</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F108" s="4"/>
       <c r="G108" s="4" t="s">
-        <v>141</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="I108"/>
     </row>
     <row r="109" spans="2:9">
       <c r="B109" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>142</v>
+        <v>35</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>143</v>
+        <v>515</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F109" s="4"/>
       <c r="G109" s="4" t="s">
-        <v>520</v>
+        <v>141</v>
       </c>
     </row>
     <row r="110" spans="2:9">
       <c r="B110" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>45</v>
+        <v>142</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F110" s="4"/>
       <c r="G110" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="111" spans="2:9">
       <c r="B111" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>145</v>
+        <v>46</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="4" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="112" spans="2:9" s="5" customFormat="1">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="112" spans="2:9">
       <c r="B112" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>516</v>
+        <v>144</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>517</v>
+        <v>145</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="I112"/>
-    </row>
-    <row r="113" spans="2:9">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="113" spans="2:9" s="5" customFormat="1">
       <c r="B113" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>146</v>
+        <v>516</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>147</v>
+        <v>517</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="F113" s="4"/>
       <c r="G113" s="4" t="s">
-        <v>148</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="I113"/>
     </row>
     <row r="114" spans="2:9">
       <c r="B114" s="4">
+        <v>8</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="F114" s="4"/>
+      <c r="G114" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="115" spans="2:9">
+      <c r="B115" s="4">
         <v>9</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C115" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D114" s="4" t="s">
+      <c r="D115" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E114" s="4" t="s">
+      <c r="E115" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="F114" s="4"/>
-      <c r="G114" s="4"/>
-      <c r="I114" t="s">
+      <c r="F115" s="4"/>
+      <c r="G115" s="4"/>
+      <c r="I115" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="116" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B116" s="2" t="s">
+    <row r="117" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B117" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C116" s="20" t="s">
+      <c r="C117" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="D116" s="20"/>
-      <c r="E116" s="2" t="s">
+      <c r="D117" s="23"/>
+      <c r="E117" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F116" s="21"/>
-      <c r="G116" s="21"/>
-    </row>
-    <row r="117" spans="2:9">
-      <c r="B117" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C117" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="D117" s="21"/>
-      <c r="E117" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F117" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="G117" s="21"/>
+      <c r="F117" s="22"/>
+      <c r="G117" s="22"/>
     </row>
     <row r="118" spans="2:9">
       <c r="B118" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C118" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D118" s="22"/>
+      <c r="E118" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F118" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G118" s="22"/>
+    </row>
+    <row r="119" spans="2:9">
+      <c r="B119" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C119" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="D119" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E118" s="2" t="s">
+      <c r="E119" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F118" s="2" t="s">
+      <c r="F119" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G118" s="2" t="s">
+      <c r="G119" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="119" spans="2:9">
-      <c r="B119" s="1">
-        <v>1</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F119" s="1"/>
-      <c r="G119" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="120" spans="2:9">
       <c r="B120" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>38</v>
+        <v>151</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F120" s="1"/>
       <c r="G120" s="1" t="s">
-        <v>92</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121" spans="2:9">
       <c r="B121" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>152</v>
+        <v>35</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>153</v>
+        <v>38</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F121" s="1"/>
       <c r="G121" s="1" t="s">
-        <v>154</v>
+        <v>92</v>
       </c>
     </row>
     <row r="122" spans="2:9">
       <c r="B122" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="F122" s="1"/>
       <c r="G122" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="123" spans="2:9">
       <c r="B123" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F123" s="1"/>
-      <c r="G123" s="1"/>
-      <c r="I123" s="12" t="s">
-        <v>609</v>
+      <c r="G123" s="1" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="124" spans="2:9">
       <c r="B124" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
-      <c r="I124" s="12"/>
+      <c r="I124" s="12" t="s">
+        <v>609</v>
+      </c>
     </row>
     <row r="125" spans="2:9">
       <c r="B125" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>235</v>
@@ -5429,205 +5464,206 @@
     </row>
     <row r="126" spans="2:9">
       <c r="B126" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>64</v>
+        <v>162</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F126" s="1"/>
-      <c r="G126" s="1" t="s">
-        <v>165</v>
-      </c>
+      <c r="G126" s="1"/>
       <c r="I126" s="12"/>
     </row>
     <row r="127" spans="2:9">
       <c r="B127" s="1">
+        <v>8</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F127" s="1"/>
+      <c r="G127" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I127" s="12"/>
+    </row>
+    <row r="128" spans="2:9">
+      <c r="B128" s="1">
         <v>9</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C128" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D128" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E127" s="1" t="s">
+      <c r="E128" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F127" s="1"/>
-      <c r="G127" s="1"/>
-      <c r="I127" s="12" t="s">
+      <c r="F128" s="1"/>
+      <c r="G128" s="1"/>
+      <c r="I128" s="12" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="129" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B129" s="2" t="s">
+    <row r="130" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B130" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C129" s="20" t="s">
+      <c r="C130" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="D129" s="20"/>
-      <c r="E129" s="2" t="s">
+      <c r="D130" s="23"/>
+      <c r="E130" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F129" s="21"/>
-      <c r="G129" s="21"/>
-    </row>
-    <row r="130" spans="2:9">
-      <c r="B130" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C130" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="D130" s="21"/>
-      <c r="E130" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F130" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="G130" s="21"/>
+      <c r="F130" s="22"/>
+      <c r="G130" s="22"/>
     </row>
     <row r="131" spans="2:9">
       <c r="B131" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C131" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="D131" s="22"/>
+      <c r="E131" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F131" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="G131" s="22"/>
+    </row>
+    <row r="132" spans="2:9">
+      <c r="B132" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C132" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D131" s="2" t="s">
+      <c r="D132" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E131" s="2" t="s">
+      <c r="E132" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F131" s="2" t="s">
+      <c r="F132" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G131" s="2" t="s">
+      <c r="G132" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="132" spans="2:9">
-      <c r="B132" s="1">
-        <v>1</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F132" s="1"/>
-      <c r="G132" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="133" spans="2:9">
       <c r="B133" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F133" s="1"/>
       <c r="G133" s="1" t="s">
-        <v>170</v>
+        <v>14</v>
       </c>
     </row>
     <row r="134" spans="2:9">
       <c r="B134" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="F134" s="1"/>
-      <c r="G134" s="1"/>
+      <c r="G134" s="1" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="135" spans="2:9">
       <c r="B135" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F135" s="1"/>
-      <c r="G135" s="1" t="s">
-        <v>175</v>
-      </c>
+      <c r="G135" s="1"/>
     </row>
     <row r="136" spans="2:9">
       <c r="B136" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F136" s="1"/>
       <c r="G136" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="137" spans="2:9">
       <c r="B137" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F137" s="1"/>
-      <c r="G137" s="1"/>
+      <c r="G137" s="1" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="138" spans="2:9">
       <c r="B138" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>235</v>
@@ -5637,138 +5673,136 @@
     </row>
     <row r="139" spans="2:9">
       <c r="B139" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>28</v>
+        <v>181</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>29</v>
+        <v>182</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
-      <c r="I139" t="s">
+    </row>
+    <row r="140" spans="2:9">
+      <c r="B140" s="1">
+        <v>8</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F140" s="1"/>
+      <c r="G140" s="1"/>
+      <c r="I140" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="141" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B141" s="2" t="s">
+    <row r="142" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B142" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C141" s="20" t="s">
+      <c r="C142" s="23" t="s">
         <v>587</v>
       </c>
-      <c r="D141" s="20"/>
-      <c r="E141" s="2" t="s">
+      <c r="D142" s="23"/>
+      <c r="E142" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F141" s="21"/>
-      <c r="G141" s="21"/>
-    </row>
-    <row r="142" spans="2:9">
-      <c r="B142" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C142" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="D142" s="21"/>
-      <c r="E142" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F142" s="20" t="s">
-        <v>565</v>
-      </c>
-      <c r="G142" s="21" t="s">
-        <v>190</v>
-      </c>
+      <c r="F142" s="22"/>
+      <c r="G142" s="22"/>
     </row>
     <row r="143" spans="2:9">
       <c r="B143" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C143" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="D143" s="22"/>
+      <c r="E143" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F143" s="23" t="s">
+        <v>565</v>
+      </c>
+      <c r="G143" s="22" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="144" spans="2:9">
+      <c r="B144" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C143" s="2" t="s">
+      <c r="C144" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D143" s="2" t="s">
+      <c r="D144" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E143" s="2" t="s">
+      <c r="E144" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F143" s="2" t="s">
+      <c r="F144" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G143" s="2" t="s">
+      <c r="G144" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="144" spans="2:9">
-      <c r="B144" s="1">
-        <v>1</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F144" s="1"/>
-      <c r="G144" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="145" spans="2:9">
       <c r="B145" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>38</v>
+        <v>191</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F145" s="1"/>
       <c r="G145" s="1" t="s">
-        <v>192</v>
+        <v>14</v>
       </c>
     </row>
     <row r="146" spans="2:9">
       <c r="B146" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>184</v>
+        <v>35</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>193</v>
+        <v>38</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F146" s="1"/>
       <c r="G146" s="1" t="s">
-        <v>34</v>
+        <v>192</v>
       </c>
     </row>
     <row r="147" spans="2:9">
       <c r="B147" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>13</v>
@@ -5780,587 +5814,584 @@
     </row>
     <row r="148" spans="2:9">
       <c r="B148" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>45</v>
+        <v>194</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>46</v>
+        <v>195</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F148" s="1"/>
       <c r="G148" s="1" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="149" spans="2:9">
       <c r="B149" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>196</v>
+        <v>45</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>197</v>
+        <v>46</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="F149" s="1"/>
       <c r="G149" s="1" t="s">
-        <v>198</v>
+        <v>47</v>
       </c>
     </row>
     <row r="150" spans="2:9">
       <c r="B150" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>13</v>
+        <v>235</v>
       </c>
       <c r="F150" s="1"/>
       <c r="G150" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="151" spans="2:9">
       <c r="B151" s="1">
+        <v>7</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F151" s="1"/>
+      <c r="G151" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="152" spans="2:9">
+      <c r="B152" s="1">
         <v>8</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="C152" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D151" s="1" t="s">
+      <c r="D152" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E151" s="1" t="s">
+      <c r="E152" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F151" s="1"/>
-      <c r="G151" s="1"/>
-      <c r="I151" t="s">
+      <c r="F152" s="1"/>
+      <c r="G152" s="1"/>
+      <c r="I152" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="153" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B153" s="2" t="s">
+    <row r="154" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B154" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C153" s="20" t="s">
+      <c r="C154" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="D153" s="20"/>
-      <c r="E153" s="2" t="s">
+      <c r="D154" s="23"/>
+      <c r="E154" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F153" s="21"/>
-      <c r="G153" s="21"/>
-    </row>
-    <row r="154" spans="2:9">
-      <c r="B154" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C154" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="D154" s="21"/>
-      <c r="E154" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F154" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="G154" s="21" t="s">
-        <v>190</v>
-      </c>
+      <c r="F154" s="22"/>
+      <c r="G154" s="22"/>
     </row>
     <row r="155" spans="2:9">
       <c r="B155" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C155" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D155" s="22"/>
+      <c r="E155" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F155" s="22" t="s">
+        <v>203</v>
+      </c>
+      <c r="G155" s="22" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="156" spans="2:9">
+      <c r="B156" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C155" s="2" t="s">
+      <c r="C156" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D155" s="2" t="s">
+      <c r="D156" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E155" s="2" t="s">
+      <c r="E156" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F155" s="2" t="s">
+      <c r="F156" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G155" s="2" t="s">
+      <c r="G156" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="156" spans="2:9">
-      <c r="B156" s="1">
-        <v>1</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F156" s="1"/>
-      <c r="G156" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="157" spans="2:9">
       <c r="B157" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F157" s="1"/>
       <c r="G157" s="1" t="s">
-        <v>204</v>
+        <v>14</v>
       </c>
     </row>
     <row r="158" spans="2:9">
       <c r="B158" s="1">
+        <v>2</v>
+      </c>
+      <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C158" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="D158" s="1" t="s">
-        <v>193</v>
+        <v>12</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F158" s="1"/>
       <c r="G158" s="1" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
     </row>
     <row r="159" spans="2:9">
       <c r="B159" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="1" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
     </row>
     <row r="160" spans="2:9">
       <c r="B160" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>110</v>
+        <v>186</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F160" s="1"/>
       <c r="G160" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="161" spans="2:9">
       <c r="B161" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>209</v>
+        <v>110</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>13</v>
+        <v>235</v>
       </c>
       <c r="F161" s="1"/>
       <c r="G161" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="162" spans="2:9">
       <c r="B162" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F162" s="1"/>
       <c r="G162" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="163" spans="2:9">
       <c r="B163" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>64</v>
+        <v>212</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="F163" s="1"/>
       <c r="G163" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="164" spans="2:9">
       <c r="B164" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>29</v>
+        <v>215</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>569</v>
+        <v>235</v>
       </c>
       <c r="F164" s="1"/>
-      <c r="G164" s="1"/>
-      <c r="I164" t="s">
-        <v>585</v>
+      <c r="G164" s="1" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="165" spans="2:9">
       <c r="B165" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>238</v>
+        <v>569</v>
       </c>
       <c r="F165" s="1"/>
       <c r="G165" s="1"/>
       <c r="I165" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="166" spans="2:9">
+      <c r="B166" s="1">
+        <v>10</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F166" s="1"/>
+      <c r="G166" s="1"/>
+      <c r="I166" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="167" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B167" s="2" t="s">
+    <row r="168" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B168" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C167" s="20" t="s">
+      <c r="C168" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="D167" s="20"/>
-      <c r="E167" s="2" t="s">
+      <c r="D168" s="23"/>
+      <c r="E168" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F167" s="21"/>
-      <c r="G167" s="21"/>
-    </row>
-    <row r="168" spans="2:9">
-      <c r="B168" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C168" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="D168" s="21"/>
-      <c r="E168" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F168" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="G168" s="21"/>
+      <c r="F168" s="22"/>
+      <c r="G168" s="22"/>
     </row>
     <row r="169" spans="2:9">
       <c r="B169" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C169" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="D169" s="22"/>
+      <c r="E169" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F169" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="G169" s="22"/>
+    </row>
+    <row r="170" spans="2:9">
+      <c r="B170" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C169" s="2" t="s">
+      <c r="C170" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D169" s="2" t="s">
+      <c r="D170" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E169" s="2" t="s">
+      <c r="E170" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F169" s="2" t="s">
+      <c r="F170" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G169" s="2" t="s">
+      <c r="G170" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="170" spans="2:9">
-      <c r="B170" s="1">
-        <v>1</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F170" s="1"/>
-      <c r="G170" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="171" spans="2:9">
       <c r="B171" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>45</v>
+        <v>218</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>46</v>
+        <v>220</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F171" s="1"/>
       <c r="G171" s="1" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
     </row>
     <row r="172" spans="2:9">
       <c r="B172" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>221</v>
+        <v>45</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>222</v>
+        <v>46</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="F172" s="1"/>
       <c r="G172" s="1" t="s">
-        <v>223</v>
+        <v>47</v>
       </c>
     </row>
     <row r="173" spans="2:9">
       <c r="B173" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>13</v>
+        <v>235</v>
       </c>
       <c r="F173" s="1"/>
       <c r="G173" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="174" spans="2:9">
+      <c r="B174" s="1">
+        <v>4</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F174" s="1"/>
+      <c r="G174" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="175" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B175" s="2" t="s">
+    <row r="176" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B176" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C175" s="20" t="s">
+      <c r="C176" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="D175" s="20"/>
-      <c r="E175" s="2" t="s">
+      <c r="D176" s="23"/>
+      <c r="E176" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F175" s="21"/>
-      <c r="G175" s="21"/>
-    </row>
-    <row r="176" spans="2:9">
-      <c r="B176" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C176" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="D176" s="21"/>
-      <c r="E176" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F176" s="21"/>
-      <c r="G176" s="21"/>
+      <c r="F176" s="22"/>
+      <c r="G176" s="22"/>
     </row>
     <row r="177" spans="2:9">
       <c r="B177" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C177" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="D177" s="22"/>
+      <c r="E177" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F177" s="22"/>
+      <c r="G177" s="22"/>
+    </row>
+    <row r="178" spans="2:9">
+      <c r="B178" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C177" s="2" t="s">
+      <c r="C178" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D177" s="2" t="s">
+      <c r="D178" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E177" s="2" t="s">
+      <c r="E178" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F177" s="2" t="s">
+      <c r="F178" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G177" s="2" t="s">
+      <c r="G178" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="178" spans="2:9">
-      <c r="B178" s="1">
-        <v>1</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F178" s="1"/>
-      <c r="G178" s="1" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="179" spans="2:9">
       <c r="B179" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F179" s="1">
-        <v>50</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F179" s="1"/>
       <c r="G179" s="1" t="s">
-        <v>232</v>
+        <v>564</v>
       </c>
     </row>
     <row r="180" spans="2:9">
       <c r="B180" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F180" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="181" spans="2:9">
       <c r="B181" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>110</v>
+        <v>233</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F181" s="1">
-        <v>500</v>
-      </c>
-      <c r="G181" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="182" spans="2:9">
       <c r="B182" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>29</v>
+        <v>237</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F182" s="1"/>
-      <c r="G182" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="I182" s="6">
-        <v>45292</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="F182" s="1">
+        <v>500</v>
+      </c>
+      <c r="G182" s="1"/>
     </row>
     <row r="183" spans="2:9">
       <c r="B183" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>238</v>
@@ -6373,127 +6404,128 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="185" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B185" s="2" t="s">
+    <row r="184" spans="2:9">
+      <c r="B184" s="1">
+        <v>6</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F184" s="1"/>
+      <c r="G184" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I184" s="6">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="186" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B186" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C185" s="20" t="s">
+      <c r="C186" s="23" t="s">
         <v>575</v>
       </c>
-      <c r="D185" s="20"/>
-      <c r="E185" s="2" t="s">
+      <c r="D186" s="23"/>
+      <c r="E186" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F185" s="21"/>
-      <c r="G185" s="21"/>
-    </row>
-    <row r="186" spans="2:9">
-      <c r="B186" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C186" s="21" t="s">
-        <v>574</v>
-      </c>
-      <c r="D186" s="21"/>
-      <c r="E186" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F186" s="21"/>
-      <c r="G186" s="21"/>
+      <c r="F186" s="22"/>
+      <c r="G186" s="22"/>
     </row>
     <row r="187" spans="2:9">
       <c r="B187" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C187" s="22" t="s">
+        <v>574</v>
+      </c>
+      <c r="D187" s="22"/>
+      <c r="E187" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F187" s="22"/>
+      <c r="G187" s="22"/>
+    </row>
+    <row r="188" spans="2:9">
+      <c r="B188" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C187" s="2" t="s">
+      <c r="C188" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D187" s="2" t="s">
+      <c r="D188" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E187" s="2" t="s">
+      <c r="E188" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F187" s="2" t="s">
+      <c r="F188" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G187" s="2" t="s">
+      <c r="G188" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="188" spans="2:9">
-      <c r="B188" s="1">
-        <v>1</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F188" s="1"/>
-      <c r="G188" s="1" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="189" spans="2:9">
       <c r="B189" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F189" s="1">
-        <v>100</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F189" s="1"/>
       <c r="G189" s="1" t="s">
-        <v>232</v>
+        <v>564</v>
       </c>
     </row>
     <row r="190" spans="2:9">
       <c r="B190" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F190" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="191" spans="2:9">
       <c r="B191" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F191" s="1">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>236</v>
@@ -6501,13 +6533,13 @@
     </row>
     <row r="192" spans="2:9">
       <c r="B192" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>235</v>
@@ -6521,52 +6553,51 @@
     </row>
     <row r="193" spans="2:9">
       <c r="B193" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>110</v>
+        <v>248</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F193" s="1">
-        <v>500</v>
-      </c>
-      <c r="G193" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="194" spans="2:9">
       <c r="B194" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>29</v>
+        <v>250</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F194" s="1"/>
-      <c r="G194" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="I194" s="6">
-        <v>45292</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="F194" s="1">
+        <v>500</v>
+      </c>
+      <c r="G194" s="1"/>
     </row>
     <row r="195" spans="2:9">
       <c r="B195" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>238</v>
@@ -6579,390 +6610,394 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="197" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B197" s="2" t="s">
+    <row r="196" spans="2:9">
+      <c r="B196" s="1">
+        <v>8</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F196" s="1"/>
+      <c r="G196" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I196" s="6">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="198" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B198" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C197" s="20" t="s">
+      <c r="C198" s="23" t="s">
         <v>251</v>
       </c>
-      <c r="D197" s="20"/>
-      <c r="E197" s="2" t="s">
+      <c r="D198" s="23"/>
+      <c r="E198" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F197" s="21"/>
-      <c r="G197" s="21"/>
-    </row>
-    <row r="198" spans="2:9">
-      <c r="B198" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C198" s="21" t="s">
-        <v>511</v>
-      </c>
-      <c r="D198" s="21"/>
-      <c r="E198" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F198" s="21" t="s">
-        <v>252</v>
-      </c>
-      <c r="G198" s="21" t="s">
-        <v>253</v>
-      </c>
+      <c r="F198" s="22"/>
+      <c r="G198" s="22"/>
     </row>
     <row r="199" spans="2:9">
       <c r="B199" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C199" s="22" t="s">
+        <v>511</v>
+      </c>
+      <c r="D199" s="22"/>
+      <c r="E199" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F199" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="G199" s="22" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="200" spans="2:9">
+      <c r="B200" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C199" s="2" t="s">
+      <c r="C200" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D199" s="2" t="s">
+      <c r="D200" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E199" s="2" t="s">
+      <c r="E200" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F199" s="2" t="s">
+      <c r="F200" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G199" s="2" t="s">
+      <c r="G200" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="200" spans="2:9">
-      <c r="B200" s="1">
-        <v>1</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F200" s="1"/>
-      <c r="G200" s="1" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="201" spans="2:9">
       <c r="B201" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F201" s="1"/>
       <c r="G201" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="202" spans="2:9">
       <c r="B202" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F202" s="1"/>
       <c r="G202" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="203" spans="2:9">
       <c r="B203" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>261</v>
+        <v>13</v>
       </c>
       <c r="F203" s="1"/>
       <c r="G203" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="204" spans="2:9">
       <c r="B204" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>28</v>
+        <v>259</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>29</v>
+        <v>260</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="F204" s="1"/>
       <c r="G204" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="205" spans="2:9">
+      <c r="B205" s="1">
+        <v>5</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F205" s="1"/>
+      <c r="G205" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="I204" s="6">
+      <c r="I205" s="6">
         <v>45292.000694444447</v>
       </c>
     </row>
-    <row r="206" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B206" s="2" t="s">
+    <row r="207" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B207" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C206" s="20" t="s">
+      <c r="C207" s="23" t="s">
         <v>512</v>
       </c>
-      <c r="D206" s="20"/>
-      <c r="E206" s="2" t="s">
+      <c r="D207" s="23"/>
+      <c r="E207" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F206" s="21"/>
-      <c r="G206" s="21"/>
-    </row>
-    <row r="207" spans="2:9">
-      <c r="B207" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C207" s="21" t="s">
-        <v>535</v>
-      </c>
-      <c r="D207" s="21"/>
-      <c r="E207" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F207" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="G207" s="21" t="s">
-        <v>265</v>
-      </c>
+      <c r="F207" s="22"/>
+      <c r="G207" s="22"/>
     </row>
     <row r="208" spans="2:9">
       <c r="B208" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C208" s="22" t="s">
+        <v>535</v>
+      </c>
+      <c r="D208" s="22"/>
+      <c r="E208" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F208" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="G208" s="22" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="209" spans="2:9">
+      <c r="B209" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C208" s="2" t="s">
+      <c r="C209" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D208" s="2" t="s">
+      <c r="D209" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E208" s="2" t="s">
+      <c r="E209" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F208" s="2" t="s">
+      <c r="F209" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G208" s="2" t="s">
+      <c r="G209" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="209" spans="2:9">
-      <c r="B209" s="1">
-        <v>1</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="E209" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F209" s="1"/>
-      <c r="G209" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="210" spans="2:9">
       <c r="B210" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>67</v>
+        <v>263</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>68</v>
+        <v>266</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F210" s="1"/>
       <c r="G210" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="211" spans="2:9">
       <c r="B211" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>228</v>
+        <v>67</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>229</v>
+        <v>68</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F211" s="1"/>
       <c r="G211" s="1" t="s">
-        <v>257</v>
+        <v>34</v>
       </c>
     </row>
     <row r="212" spans="2:9">
       <c r="B212" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>28</v>
+        <v>228</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>29</v>
+        <v>229</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>238</v>
+        <v>13</v>
       </c>
       <c r="F212" s="1"/>
       <c r="G212" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="213" spans="2:9">
+      <c r="B213" s="1">
+        <v>4</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F213" s="1"/>
+      <c r="G213" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="I212" s="6" t="s">
+      <c r="I213" s="6" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="214" spans="2:9" s="19" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B214" s="18" t="s">
+    <row r="215" spans="2:9" s="19" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B215" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C214" s="24" t="s">
-        <v>624</v>
-      </c>
-      <c r="D214" s="24"/>
-      <c r="E214" s="18" t="s">
+      <c r="C215" s="26" t="s">
+        <v>623</v>
+      </c>
+      <c r="D215" s="26"/>
+      <c r="E215" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="F214" s="25"/>
-      <c r="G214" s="25"/>
-    </row>
-    <row r="215" spans="2:9">
-      <c r="B215" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C215" s="21" t="s">
-        <v>267</v>
-      </c>
-      <c r="D215" s="21"/>
-      <c r="E215" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F215" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="G215" s="21"/>
+      <c r="F215" s="27"/>
+      <c r="G215" s="27"/>
     </row>
     <row r="216" spans="2:9">
       <c r="B216" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C216" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="D216" s="22"/>
+      <c r="E216" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F216" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="G216" s="22"/>
+    </row>
+    <row r="217" spans="2:9">
+      <c r="B217" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C216" s="2" t="s">
+      <c r="C217" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D216" s="2" t="s">
+      <c r="D217" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E216" s="2" t="s">
+      <c r="E217" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F216" s="2" t="s">
+      <c r="F217" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G216" s="2" t="s">
+      <c r="G217" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="217" spans="2:9">
-      <c r="B217" s="1">
-        <v>1</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="D217" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E217" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F217" s="1"/>
-      <c r="G217" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="218" spans="2:9">
       <c r="B218" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>184</v>
+        <v>624</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>193</v>
+        <v>268</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F218" s="1"/>
       <c r="G218" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="219" spans="2:9">
       <c r="B219" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>269</v>
+        <v>184</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>270</v>
+        <v>193</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>238</v>
+        <v>13</v>
       </c>
       <c r="F219" s="1"/>
-      <c r="G219" s="1"/>
-      <c r="I219" s="15"/>
+      <c r="G219" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="220" spans="2:9">
       <c r="B220" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>238</v>
@@ -6973,29 +7008,30 @@
     </row>
     <row r="221" spans="2:9">
       <c r="B221" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>20</v>
+        <v>238</v>
       </c>
       <c r="F221" s="1"/>
       <c r="G221" s="1"/>
+      <c r="I221" s="15"/>
     </row>
     <row r="222" spans="2:9">
       <c r="B222" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>20</v>
@@ -7005,13 +7041,13 @@
     </row>
     <row r="223" spans="2:9">
       <c r="B223" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>20</v>
@@ -7021,201 +7057,201 @@
     </row>
     <row r="224" spans="2:9">
       <c r="B224" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>158</v>
+        <v>277</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>238</v>
+        <v>20</v>
       </c>
       <c r="F224" s="1"/>
       <c r="G224" s="1"/>
-      <c r="I224" s="15"/>
     </row>
     <row r="225" spans="2:9">
       <c r="B225" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>64</v>
+        <v>158</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>188</v>
+        <v>279</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F225" s="1"/>
       <c r="G225" s="1"/>
+      <c r="I225" s="15"/>
     </row>
     <row r="226" spans="2:9">
       <c r="B226" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>29</v>
+        <v>188</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F226" s="1"/>
       <c r="G226" s="1"/>
-      <c r="I226" s="15"/>
-    </row>
-    <row r="228" spans="2:9" s="19" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B228" s="18" t="s">
+    </row>
+    <row r="227" spans="2:9">
+      <c r="B227" s="1">
+        <v>10</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F227" s="1"/>
+      <c r="G227" s="1"/>
+      <c r="I227" s="15"/>
+    </row>
+    <row r="229" spans="2:9" s="19" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B229" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C228" s="24" t="s">
-        <v>631</v>
-      </c>
-      <c r="D228" s="24"/>
-      <c r="E228" s="18" t="s">
+      <c r="C229" s="26" t="s">
+        <v>630</v>
+      </c>
+      <c r="D229" s="26"/>
+      <c r="E229" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="F228" s="25"/>
-      <c r="G228" s="25"/>
-    </row>
-    <row r="229" spans="2:9">
-      <c r="B229" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C229" s="21" t="s">
-        <v>630</v>
-      </c>
-      <c r="D229" s="21"/>
-      <c r="E229" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F229" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="G229" s="21" t="s">
-        <v>139</v>
-      </c>
+      <c r="F229" s="27"/>
+      <c r="G229" s="27"/>
     </row>
     <row r="230" spans="2:9">
       <c r="B230" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C230" s="22" t="s">
+        <v>629</v>
+      </c>
+      <c r="D230" s="22"/>
+      <c r="E230" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F230" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="G230" s="22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="231" spans="2:9">
+      <c r="B231" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C230" s="2" t="s">
+      <c r="C231" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D230" s="2" t="s">
+      <c r="D231" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E230" s="2" t="s">
+      <c r="E231" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F230" s="2" t="s">
+      <c r="F231" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G230" s="2" t="s">
+      <c r="G231" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="231" spans="2:9">
-      <c r="B231" s="1">
-        <v>1</v>
-      </c>
-      <c r="C231" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="D231" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="E231" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F231" s="1"/>
-      <c r="G231" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="232" spans="2:9">
       <c r="B232" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>267</v>
+        <v>629</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F232" s="1"/>
       <c r="G232" s="1" t="s">
-        <v>282</v>
+        <v>14</v>
       </c>
     </row>
     <row r="233" spans="2:9">
       <c r="B233" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>35</v>
+        <v>267</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F233" s="1"/>
       <c r="G233" s="1" t="s">
-        <v>92</v>
+        <v>282</v>
       </c>
     </row>
     <row r="234" spans="2:9">
       <c r="B234" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>162</v>
+        <v>35</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>163</v>
+        <v>38</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="F234" s="1"/>
-      <c r="G234" s="1"/>
+      <c r="G234" s="1" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="235" spans="2:9">
       <c r="B235" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>273</v>
+        <v>162</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>274</v>
+        <v>163</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>20</v>
+        <v>235</v>
       </c>
       <c r="F235" s="1"/>
       <c r="G235" s="1"/>
     </row>
     <row r="236" spans="2:9">
       <c r="B236" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>634</v>
+        <v>274</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>20</v>
@@ -7225,13 +7261,13 @@
     </row>
     <row r="237" spans="2:9">
       <c r="B237" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>276</v>
+        <v>633</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>20</v>
@@ -7241,13 +7277,13 @@
     </row>
     <row r="238" spans="2:9">
       <c r="B238" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>20</v>
@@ -7255,149 +7291,149 @@
       <c r="F238" s="1"/>
       <c r="G238" s="1"/>
     </row>
-    <row r="240" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B240" s="2" t="s">
+    <row r="239" spans="2:9">
+      <c r="B239" s="1">
+        <v>8</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F239" s="1"/>
+      <c r="G239" s="1"/>
+    </row>
+    <row r="241" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B241" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C240" s="20" t="s">
+      <c r="C241" s="23" t="s">
         <v>284</v>
       </c>
-      <c r="D240" s="20"/>
-      <c r="E240" s="2" t="s">
+      <c r="D241" s="23"/>
+      <c r="E241" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F240" s="21"/>
-      <c r="G240" s="21"/>
-    </row>
-    <row r="241" spans="2:9">
-      <c r="B241" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C241" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="D241" s="21"/>
-      <c r="E241" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F241" s="21"/>
-      <c r="G241" s="21"/>
+      <c r="F241" s="22"/>
+      <c r="G241" s="22"/>
     </row>
     <row r="242" spans="2:9">
       <c r="B242" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C242" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="D242" s="22"/>
+      <c r="E242" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F242" s="22"/>
+      <c r="G242" s="22"/>
+    </row>
+    <row r="243" spans="2:9">
+      <c r="B243" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C242" s="2" t="s">
+      <c r="C243" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D242" s="2" t="s">
+      <c r="D243" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E242" s="2" t="s">
+      <c r="E243" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F242" s="2" t="s">
+      <c r="F243" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G242" s="2" t="s">
+      <c r="G243" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="243" spans="2:9">
-      <c r="B243" s="1">
-        <v>1</v>
-      </c>
-      <c r="C243" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="E243" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F243" s="1"/>
-      <c r="G243" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="244" spans="2:9">
       <c r="B244" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="F244" s="1"/>
       <c r="G244" s="1" t="s">
-        <v>289</v>
+        <v>14</v>
       </c>
     </row>
     <row r="245" spans="2:9">
       <c r="B245" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>20</v>
+        <v>235</v>
       </c>
       <c r="F245" s="1"/>
       <c r="G245" s="1" t="s">
-        <v>154</v>
+        <v>289</v>
       </c>
     </row>
     <row r="246" spans="2:9">
       <c r="B246" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F246" s="1"/>
-      <c r="G246" s="1"/>
+      <c r="G246" s="1" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="247" spans="2:9">
       <c r="B247" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="F247" s="1"/>
       <c r="G247" s="1"/>
     </row>
     <row r="248" spans="2:9">
       <c r="B248" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>261</v>
@@ -7407,13 +7443,13 @@
     </row>
     <row r="249" spans="2:9">
       <c r="B249" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>261</v>
@@ -7423,157 +7459,154 @@
     </row>
     <row r="250" spans="2:9">
       <c r="B250" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>28</v>
+        <v>298</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>29</v>
+        <v>299</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="F250" s="1"/>
       <c r="G250" s="1"/>
-      <c r="I250" s="14">
+    </row>
+    <row r="251" spans="2:9">
+      <c r="B251" s="1">
+        <v>8</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F251" s="1"/>
+      <c r="G251" s="1"/>
+      <c r="I251" s="14">
         <v>45292</v>
       </c>
     </row>
-    <row r="252" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B252" s="2" t="s">
+    <row r="253" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B253" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C252" s="20" t="s">
-        <v>638</v>
-      </c>
-      <c r="D252" s="20"/>
-      <c r="E252" s="2" t="s">
+      <c r="C253" s="23" t="s">
+        <v>637</v>
+      </c>
+      <c r="D253" s="23"/>
+      <c r="E253" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F252" s="21"/>
-      <c r="G252" s="21"/>
-    </row>
-    <row r="253" spans="2:9">
-      <c r="B253" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C253" s="21" t="s">
-        <v>637</v>
-      </c>
-      <c r="D253" s="21"/>
-      <c r="E253" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F253" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="G253" s="21" t="s">
-        <v>301</v>
-      </c>
+      <c r="F253" s="22"/>
+      <c r="G253" s="22"/>
     </row>
     <row r="254" spans="2:9">
       <c r="B254" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C254" s="22" t="s">
+        <v>636</v>
+      </c>
+      <c r="D254" s="22"/>
+      <c r="E254" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F254" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="G254" s="22" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="255" spans="2:9">
+      <c r="B255" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C254" s="2" t="s">
+      <c r="C255" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D254" s="2" t="s">
+      <c r="D255" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E254" s="2" t="s">
+      <c r="E255" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F254" s="2" t="s">
+      <c r="F255" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G254" s="2" t="s">
+      <c r="G255" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="255" spans="2:9">
-      <c r="B255" s="1">
-        <v>1</v>
-      </c>
-      <c r="C255" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="D255" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="E255" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F255" s="1"/>
-      <c r="G255" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="256" spans="2:9">
       <c r="B256" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>184</v>
+        <v>300</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>193</v>
+        <v>302</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F256" s="1"/>
       <c r="G256" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="257" spans="2:9">
       <c r="B257" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>285</v>
+        <v>184</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>286</v>
+        <v>193</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F257" s="1"/>
       <c r="G257" s="1" t="s">
-        <v>303</v>
+        <v>34</v>
       </c>
     </row>
     <row r="258" spans="2:9">
       <c r="B258" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>633</v>
+        <v>285</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>238</v>
+        <v>13</v>
       </c>
       <c r="F258" s="1"/>
-      <c r="G258" s="1"/>
-      <c r="I258" s="15" t="s">
-        <v>621</v>
+      <c r="G258" s="1" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="259" spans="2:9">
       <c r="B259" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>305</v>
+        <v>632</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>238</v>
@@ -7581,248 +7614,250 @@
       <c r="F259" s="1"/>
       <c r="G259" s="1"/>
       <c r="I259" s="15" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="260" spans="2:9">
       <c r="B260" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="F260" s="1"/>
-      <c r="G260" s="1" t="s">
-        <v>620</v>
+      <c r="G260" s="1"/>
+      <c r="I260" s="15" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="261" spans="2:9">
       <c r="B261" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>64</v>
+        <v>307</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>188</v>
+        <v>308</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="F261" s="1"/>
       <c r="G261" s="1" t="s">
-        <v>309</v>
+        <v>638</v>
       </c>
     </row>
     <row r="262" spans="2:9">
       <c r="B262" s="1">
+        <v>7</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F262" s="1"/>
+      <c r="G262" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="263" spans="2:9">
+      <c r="B263" s="1">
         <v>8</v>
       </c>
-      <c r="C262" s="1" t="s">
+      <c r="C263" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D262" s="1" t="s">
+      <c r="D263" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E262" s="1" t="s">
+      <c r="E263" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F262" s="1"/>
-      <c r="G262" s="1"/>
-      <c r="I262" s="15" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="264" spans="2:9" s="19" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B264" s="18" t="s">
+      <c r="F263" s="1"/>
+      <c r="G263" s="1"/>
+      <c r="I263" s="15" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="265" spans="2:9" s="19" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B265" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C264" s="24" t="s">
-        <v>629</v>
-      </c>
-      <c r="D264" s="24"/>
-      <c r="E264" s="18" t="s">
+      <c r="C265" s="26" t="s">
+        <v>628</v>
+      </c>
+      <c r="D265" s="26"/>
+      <c r="E265" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="F264" s="25"/>
-      <c r="G264" s="25"/>
-    </row>
-    <row r="265" spans="2:9">
-      <c r="B265" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C265" s="21" t="s">
-        <v>628</v>
-      </c>
-      <c r="D265" s="21"/>
-      <c r="E265" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F265" s="21" t="s">
-        <v>311</v>
-      </c>
-      <c r="G265" s="21"/>
+      <c r="F265" s="27"/>
+      <c r="G265" s="27"/>
     </row>
     <row r="266" spans="2:9">
       <c r="B266" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C266" s="22" t="s">
+        <v>627</v>
+      </c>
+      <c r="D266" s="22"/>
+      <c r="E266" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F266" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="G266" s="22"/>
+    </row>
+    <row r="267" spans="2:9">
+      <c r="B267" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C266" s="2" t="s">
+      <c r="C267" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D266" s="2" t="s">
+      <c r="D267" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E266" s="2" t="s">
+      <c r="E267" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F266" s="2" t="s">
+      <c r="F267" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G266" s="2" t="s">
+      <c r="G267" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="267" spans="2:9">
-      <c r="B267" s="1">
-        <v>1</v>
-      </c>
-      <c r="C267" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D267" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="E267" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F267" s="1"/>
-      <c r="G267" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="268" spans="2:9">
       <c r="B268" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F268" s="1"/>
       <c r="G268" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="269" spans="2:9">
+      <c r="B269" s="1">
+        <v>2</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F269" s="1"/>
+      <c r="G269" s="1" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="269" spans="2:9" s="10" customFormat="1">
-      <c r="B269" s="26">
+    <row r="270" spans="2:9" s="10" customFormat="1">
+      <c r="B270" s="20">
         <v>3</v>
       </c>
-      <c r="C269" s="26" t="s">
+      <c r="C270" s="20" t="s">
         <v>314</v>
       </c>
-      <c r="D269" s="26" t="s">
+      <c r="D270" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="E269" s="26" t="s">
+      <c r="E270" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="F269" s="26"/>
-      <c r="G269" s="26"/>
-      <c r="I269" s="27" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="270" spans="2:9" s="10" customFormat="1">
-      <c r="B270" s="26">
+      <c r="F270" s="20"/>
+      <c r="G270" s="20"/>
+      <c r="I270" s="21" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="271" spans="2:9" s="10" customFormat="1">
+      <c r="B271" s="20">
         <v>4</v>
       </c>
-      <c r="C270" s="26" t="s">
+      <c r="C271" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="D270" s="26" t="s">
+      <c r="D271" s="20" t="s">
         <v>317</v>
       </c>
-      <c r="E270" s="26" t="s">
+      <c r="E271" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="F270" s="26"/>
-      <c r="G270" s="26"/>
-      <c r="I270" s="27" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="271" spans="2:9">
-      <c r="B271" s="1">
-        <v>5</v>
-      </c>
-      <c r="C271" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D271" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E271" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F271" s="1"/>
-      <c r="G271" s="1"/>
+      <c r="F271" s="20"/>
+      <c r="G271" s="20"/>
+      <c r="I271" s="21" t="s">
+        <v>626</v>
+      </c>
     </row>
     <row r="272" spans="2:9">
       <c r="B272" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>319</v>
+        <v>152</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>164</v>
+        <v>318</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="F272" s="1"/>
-      <c r="G272" s="1" t="s">
-        <v>632</v>
-      </c>
+      <c r="G272" s="1"/>
     </row>
     <row r="273" spans="2:9">
       <c r="B273" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>158</v>
+        <v>319</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>279</v>
+        <v>164</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F273" s="1"/>
-      <c r="G273" s="1"/>
-      <c r="I273" s="15"/>
+      <c r="G273" s="1" t="s">
+        <v>631</v>
+      </c>
     </row>
     <row r="274" spans="2:9">
       <c r="B274" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>28</v>
+        <v>158</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>29</v>
+        <v>279</v>
       </c>
       <c r="E274" s="1" t="s">
         <v>238</v>
@@ -7833,184 +7868,182 @@
     </row>
     <row r="275" spans="2:9">
       <c r="B275" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>320</v>
+        <v>28</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F275" s="1"/>
       <c r="G275" s="1"/>
-    </row>
-    <row r="277" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B277" s="2" t="s">
+      <c r="I275" s="15"/>
+    </row>
+    <row r="276" spans="2:9">
+      <c r="B276" s="1">
+        <v>9</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F276" s="1"/>
+      <c r="G276" s="1"/>
+    </row>
+    <row r="278" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B278" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C277" s="20" t="s">
+      <c r="C278" s="23" t="s">
         <v>595</v>
       </c>
-      <c r="D277" s="20"/>
-      <c r="E277" s="2" t="s">
+      <c r="D278" s="23"/>
+      <c r="E278" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F277" s="21"/>
-      <c r="G277" s="21"/>
-    </row>
-    <row r="278" spans="2:9">
-      <c r="B278" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C278" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="D278" s="21"/>
-      <c r="E278" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F278" s="21"/>
-      <c r="G278" s="21"/>
+      <c r="F278" s="22"/>
+      <c r="G278" s="22"/>
     </row>
     <row r="279" spans="2:9">
       <c r="B279" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C279" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="D279" s="22"/>
+      <c r="E279" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F279" s="22"/>
+      <c r="G279" s="22"/>
+    </row>
+    <row r="280" spans="2:9">
+      <c r="B280" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C279" s="2" t="s">
+      <c r="C280" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D279" s="2" t="s">
+      <c r="D280" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E279" s="2" t="s">
+      <c r="E280" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F279" s="2" t="s">
+      <c r="F280" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G279" s="2" t="s">
+      <c r="G280" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="280" spans="2:9">
-      <c r="B280" s="1">
-        <v>1</v>
-      </c>
-      <c r="C280" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="E280" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F280" s="1"/>
-      <c r="G280" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="281" spans="2:9">
       <c r="B281" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F281" s="1"/>
       <c r="G281" s="1" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="282" spans="2:9">
       <c r="B282" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F282" s="1"/>
-      <c r="G282" s="1"/>
+      <c r="G282" s="1" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="283" spans="2:9">
       <c r="B283" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F283" s="1"/>
-      <c r="G283" s="1" t="s">
-        <v>330</v>
-      </c>
+      <c r="G283" s="1"/>
     </row>
     <row r="284" spans="2:9">
       <c r="B284" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F284" s="1"/>
       <c r="G284" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="285" spans="2:9">
       <c r="B285" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>238</v>
+        <v>20</v>
       </c>
       <c r="F285" s="1"/>
-      <c r="G285" s="1"/>
-      <c r="I285" t="s">
-        <v>594</v>
+      <c r="G285" s="1" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="286" spans="2:9">
       <c r="B286" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>238</v>
@@ -8023,223 +8056,223 @@
     </row>
     <row r="287" spans="2:9">
       <c r="B287" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>298</v>
+        <v>336</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>299</v>
+        <v>337</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>261</v>
+        <v>238</v>
       </c>
       <c r="F287" s="1"/>
       <c r="G287" s="1"/>
+      <c r="I287" t="s">
+        <v>594</v>
+      </c>
     </row>
     <row r="288" spans="2:9">
       <c r="B288" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>28</v>
+        <v>298</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>29</v>
+        <v>299</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="F288" s="1"/>
       <c r="G288" s="1"/>
-      <c r="I288" s="9">
+    </row>
+    <row r="289" spans="2:9">
+      <c r="B289" s="1">
+        <v>9</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F289" s="1"/>
+      <c r="G289" s="1"/>
+      <c r="I289" s="9">
         <v>45292.000694444447</v>
       </c>
     </row>
-    <row r="290" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B290" s="2" t="s">
+    <row r="291" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B291" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C290" s="20" t="s">
+      <c r="C291" s="23" t="s">
         <v>596</v>
       </c>
-      <c r="D290" s="20"/>
-      <c r="E290" s="2" t="s">
+      <c r="D291" s="23"/>
+      <c r="E291" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F290" s="21"/>
-      <c r="G290" s="21"/>
-    </row>
-    <row r="291" spans="2:9">
-      <c r="B291" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C291" s="21" t="s">
-        <v>338</v>
-      </c>
-      <c r="D291" s="21"/>
-      <c r="E291" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F291" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="G291" s="21" t="s">
-        <v>139</v>
-      </c>
+      <c r="F291" s="22"/>
+      <c r="G291" s="22"/>
     </row>
     <row r="292" spans="2:9">
       <c r="B292" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C292" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="D292" s="22"/>
+      <c r="E292" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F292" s="22" t="s">
+        <v>339</v>
+      </c>
+      <c r="G292" s="22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="293" spans="2:9">
+      <c r="B293" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C292" s="2" t="s">
+      <c r="C293" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D292" s="2" t="s">
+      <c r="D293" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E292" s="2" t="s">
+      <c r="E293" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F292" s="2" t="s">
+      <c r="F293" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G292" s="2" t="s">
+      <c r="G293" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="293" spans="2:9">
-      <c r="B293" s="1">
-        <v>1</v>
-      </c>
-      <c r="C293" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E293" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F293" s="1"/>
-      <c r="G293" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="294" spans="2:9">
       <c r="B294" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>42</v>
+        <v>338</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>43</v>
+        <v>340</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F294" s="1"/>
       <c r="G294" s="1" t="s">
-        <v>570</v>
+        <v>14</v>
       </c>
     </row>
     <row r="295" spans="2:9">
       <c r="B295" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F295" s="1"/>
       <c r="G295" s="1" t="s">
-        <v>92</v>
+        <v>570</v>
       </c>
     </row>
     <row r="296" spans="2:9">
       <c r="B296" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>162</v>
+        <v>35</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>163</v>
+        <v>38</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="F296" s="1"/>
-      <c r="G296" s="1"/>
+      <c r="G296" s="1" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="297" spans="2:9">
       <c r="B297" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>341</v>
+        <v>162</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>342</v>
+        <v>163</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F297" s="1"/>
-      <c r="G297" s="1" t="s">
-        <v>343</v>
-      </c>
+      <c r="G297" s="1"/>
     </row>
     <row r="298" spans="2:9">
       <c r="B298" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>85</v>
+        <v>342</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>13</v>
+        <v>235</v>
       </c>
       <c r="F298" s="1"/>
-      <c r="G298" s="1"/>
+      <c r="G298" s="1" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="299" spans="2:9">
       <c r="B299" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>612</v>
+        <v>85</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>238</v>
+        <v>13</v>
       </c>
       <c r="F299" s="1"/>
       <c r="G299" s="1"/>
-      <c r="I299" t="s">
-        <v>614</v>
-      </c>
     </row>
     <row r="300" spans="2:9">
       <c r="B300" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>347</v>
+        <v>612</v>
       </c>
       <c r="E300" s="1" t="s">
         <v>238</v>
@@ -8247,154 +8280,157 @@
       <c r="F300" s="1"/>
       <c r="G300" s="1"/>
       <c r="I300" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="301" spans="2:9">
       <c r="B301" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>11</v>
+        <v>347</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F301" s="1"/>
       <c r="G301" s="1"/>
-    </row>
-    <row r="303" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B303" s="2" t="s">
+      <c r="I301" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="302" spans="2:9">
+      <c r="B302" s="1">
+        <v>9</v>
+      </c>
+      <c r="C302" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E302" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F302" s="1"/>
+      <c r="G302" s="1"/>
+    </row>
+    <row r="304" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B304" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C303" s="20" t="s">
+      <c r="C304" s="23" t="s">
         <v>348</v>
       </c>
-      <c r="D303" s="20"/>
-      <c r="E303" s="2" t="s">
+      <c r="D304" s="23"/>
+      <c r="E304" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F303" s="21"/>
-      <c r="G303" s="21"/>
-    </row>
-    <row r="304" spans="2:9">
-      <c r="B304" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C304" s="21" t="s">
-        <v>349</v>
-      </c>
-      <c r="D304" s="21"/>
-      <c r="E304" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F304" s="21" t="s">
-        <v>350</v>
-      </c>
-      <c r="G304" s="21"/>
+      <c r="F304" s="22"/>
+      <c r="G304" s="22"/>
     </row>
     <row r="305" spans="2:9">
       <c r="B305" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C305" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="D305" s="22"/>
+      <c r="E305" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F305" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="G305" s="22"/>
+    </row>
+    <row r="306" spans="2:9">
+      <c r="B306" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C305" s="2" t="s">
+      <c r="C306" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D305" s="2" t="s">
+      <c r="D306" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E305" s="2" t="s">
+      <c r="E306" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F305" s="2" t="s">
+      <c r="F306" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G305" s="2" t="s">
+      <c r="G306" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="306" spans="2:9">
-      <c r="B306" s="1">
-        <v>1</v>
-      </c>
-      <c r="C306" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="E306" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F306" s="1"/>
-      <c r="G306" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="307" spans="2:9">
       <c r="B307" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>235</v>
+        <v>352</v>
       </c>
       <c r="F307" s="1"/>
       <c r="G307" s="1" t="s">
-        <v>355</v>
+        <v>14</v>
       </c>
     </row>
     <row r="308" spans="2:9">
       <c r="B308" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>352</v>
+        <v>235</v>
       </c>
       <c r="F308" s="1"/>
       <c r="G308" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="309" spans="2:9">
       <c r="B309" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>72</v>
+        <v>356</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>235</v>
+        <v>352</v>
       </c>
       <c r="F309" s="1"/>
-      <c r="G309" s="1"/>
+      <c r="G309" s="1" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="310" spans="2:9">
       <c r="B310" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E310" s="1" t="s">
         <v>235</v>
@@ -8404,64 +8440,61 @@
     </row>
     <row r="311" spans="2:9">
       <c r="B311" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>224</v>
+        <v>110</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>13</v>
+        <v>235</v>
       </c>
       <c r="F311" s="1"/>
       <c r="G311" s="1"/>
     </row>
     <row r="312" spans="2:9">
       <c r="B312" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>298</v>
+        <v>224</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>299</v>
+        <v>361</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>261</v>
+        <v>13</v>
       </c>
       <c r="F312" s="1"/>
       <c r="G312" s="1"/>
     </row>
     <row r="313" spans="2:9">
       <c r="B313" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>28</v>
+        <v>298</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>29</v>
+        <v>299</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="F313" s="1"/>
       <c r="G313" s="1"/>
-      <c r="I313" s="9">
-        <v>45292.000694444447</v>
-      </c>
     </row>
     <row r="314" spans="2:9">
       <c r="B314" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>238</v>
@@ -8472,155 +8505,158 @@
         <v>45292.000694444447</v>
       </c>
     </row>
-    <row r="316" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B316" s="2" t="s">
+    <row r="315" spans="2:9">
+      <c r="B315" s="1">
+        <v>9</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E315" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F315" s="1"/>
+      <c r="G315" s="1"/>
+      <c r="I315" s="9">
+        <v>45292.000694444447</v>
+      </c>
+    </row>
+    <row r="317" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B317" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C316" s="20" t="s">
+      <c r="C317" s="23" t="s">
         <v>597</v>
       </c>
-      <c r="D316" s="20"/>
-      <c r="E316" s="2" t="s">
+      <c r="D317" s="23"/>
+      <c r="E317" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F316" s="21"/>
-      <c r="G316" s="21"/>
-    </row>
-    <row r="317" spans="2:9">
-      <c r="B317" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C317" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="D317" s="21"/>
-      <c r="E317" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F317" s="21" t="s">
-        <v>363</v>
-      </c>
-      <c r="G317" s="21" t="s">
-        <v>364</v>
-      </c>
+      <c r="F317" s="22"/>
+      <c r="G317" s="22"/>
     </row>
     <row r="318" spans="2:9">
       <c r="B318" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C318" s="22" t="s">
+        <v>362</v>
+      </c>
+      <c r="D318" s="22"/>
+      <c r="E318" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F318" s="22" t="s">
+        <v>363</v>
+      </c>
+      <c r="G318" s="22" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="319" spans="2:9">
+      <c r="B319" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C318" s="2" t="s">
+      <c r="C319" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D318" s="2" t="s">
+      <c r="D319" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E318" s="2" t="s">
+      <c r="E319" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F318" s="2" t="s">
+      <c r="F319" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G318" s="2" t="s">
+      <c r="G319" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="319" spans="2:9">
-      <c r="B319" s="1">
-        <v>1</v>
-      </c>
-      <c r="C319" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="D319" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="E319" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F319" s="1"/>
-      <c r="G319" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="320" spans="2:9">
       <c r="B320" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>235</v>
+        <v>352</v>
       </c>
       <c r="F320" s="1"/>
       <c r="G320" s="1" t="s">
-        <v>355</v>
+        <v>14</v>
       </c>
     </row>
     <row r="321" spans="2:9">
       <c r="B321" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>352</v>
+        <v>235</v>
       </c>
       <c r="F321" s="1"/>
       <c r="G321" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="322" spans="2:9">
       <c r="B322" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F322" s="1"/>
       <c r="G322" s="1" t="s">
-        <v>34</v>
+        <v>358</v>
       </c>
     </row>
     <row r="323" spans="2:9">
       <c r="B323" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>186</v>
+        <v>369</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>235</v>
+        <v>352</v>
       </c>
       <c r="F323" s="1"/>
-      <c r="G323" s="1"/>
+      <c r="G323" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="324" spans="2:9">
       <c r="B324" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>372</v>
+        <v>186</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E324" s="1" t="s">
         <v>235</v>
@@ -8630,13 +8666,13 @@
     </row>
     <row r="325" spans="2:9">
       <c r="B325" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>146</v>
+        <v>372</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E325" s="1" t="s">
         <v>235</v>
@@ -8646,64 +8682,64 @@
     </row>
     <row r="326" spans="2:9">
       <c r="B326" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>375</v>
+        <v>146</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="F326" s="1"/>
       <c r="G326" s="1"/>
     </row>
     <row r="327" spans="2:9">
       <c r="B327" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="F327" s="1"/>
       <c r="G327" s="1"/>
-      <c r="I327" t="s">
-        <v>599</v>
-      </c>
     </row>
     <row r="328" spans="2:9">
       <c r="B328" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>13</v>
+        <v>238</v>
       </c>
       <c r="F328" s="1"/>
       <c r="G328" s="1"/>
+      <c r="I328" t="s">
+        <v>599</v>
+      </c>
     </row>
     <row r="329" spans="2:9">
       <c r="B329" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E329" s="1" t="s">
         <v>13</v>
@@ -8713,13 +8749,13 @@
     </row>
     <row r="330" spans="2:9">
       <c r="B330" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>13</v>
@@ -8729,50 +8765,47 @@
     </row>
     <row r="331" spans="2:9">
       <c r="B331" s="1">
+        <v>12</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E331" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C331" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D331" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E331" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="F331" s="1"/>
-      <c r="G331" s="1" t="s">
-        <v>385</v>
-      </c>
+      <c r="G331" s="1"/>
     </row>
     <row r="332" spans="2:9">
       <c r="B332" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>29</v>
+        <v>188</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F332" s="1"/>
-      <c r="G332" s="1"/>
-      <c r="I332" t="s">
-        <v>598</v>
+      <c r="G332" s="1" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="333" spans="2:9">
       <c r="B333" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E333" s="1" t="s">
         <v>238</v>
@@ -8780,154 +8813,157 @@
       <c r="F333" s="1"/>
       <c r="G333" s="1"/>
       <c r="I333" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="334" spans="2:9">
+      <c r="B334" s="1">
+        <v>15</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E334" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F334" s="1"/>
+      <c r="G334" s="1"/>
+      <c r="I334" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="335" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B335" s="2" t="s">
+    <row r="336" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B336" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C335" s="20" t="s">
+      <c r="C336" s="23" t="s">
         <v>386</v>
       </c>
-      <c r="D335" s="20"/>
-      <c r="E335" s="2" t="s">
+      <c r="D336" s="23"/>
+      <c r="E336" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F335" s="21"/>
-      <c r="G335" s="21"/>
-    </row>
-    <row r="336" spans="2:9">
-      <c r="B336" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C336" s="21" t="s">
-        <v>616</v>
-      </c>
-      <c r="D336" s="21"/>
-      <c r="E336" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F336" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="G336" s="21"/>
+      <c r="F336" s="22"/>
+      <c r="G336" s="22"/>
     </row>
     <row r="337" spans="2:7">
       <c r="B337" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C337" s="22" t="s">
+        <v>616</v>
+      </c>
+      <c r="D337" s="22"/>
+      <c r="E337" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F337" s="22" t="s">
+        <v>388</v>
+      </c>
+      <c r="G337" s="22"/>
+    </row>
+    <row r="338" spans="2:7">
+      <c r="B338" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C337" s="2" t="s">
+      <c r="C338" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D337" s="2" t="s">
+      <c r="D338" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E337" s="2" t="s">
+      <c r="E338" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F337" s="2" t="s">
+      <c r="F338" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G337" s="2" t="s">
+      <c r="G338" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="338" spans="2:7">
-      <c r="B338" s="1">
-        <v>1</v>
-      </c>
-      <c r="C338" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="E338" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F338" s="1"/>
-      <c r="G338" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="339" spans="2:7">
       <c r="B339" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F339" s="1"/>
       <c r="G339" s="1" t="s">
-        <v>392</v>
+        <v>14</v>
       </c>
     </row>
     <row r="340" spans="2:7">
       <c r="B340" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>67</v>
+        <v>390</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>68</v>
+        <v>391</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F340" s="1"/>
-      <c r="G340" s="1"/>
+      <c r="G340" s="1" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="341" spans="2:7">
       <c r="B341" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>393</v>
+        <v>67</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>394</v>
+        <v>68</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>235</v>
+        <v>352</v>
       </c>
       <c r="F341" s="1"/>
-      <c r="G341" s="1" t="s">
-        <v>395</v>
-      </c>
+      <c r="G341" s="1"/>
     </row>
     <row r="342" spans="2:7">
       <c r="B342" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F342" s="1"/>
-      <c r="G342" s="1"/>
+      <c r="G342" s="1" t="s">
+        <v>395</v>
+      </c>
     </row>
     <row r="343" spans="2:7">
       <c r="B343" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>235</v>
@@ -8937,183 +8973,183 @@
     </row>
     <row r="344" spans="2:7">
       <c r="B344" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="F344" s="1"/>
       <c r="G344" s="1"/>
     </row>
     <row r="345" spans="2:7">
       <c r="B345" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>28</v>
+        <v>400</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>29</v>
+        <v>401</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="F345" s="1"/>
       <c r="G345" s="1"/>
     </row>
-    <row r="347" spans="2:7" ht="16.5" customHeight="1">
-      <c r="B347" s="2" t="s">
+    <row r="346" spans="2:7">
+      <c r="B346" s="1">
+        <v>8</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E346" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F346" s="1"/>
+      <c r="G346" s="1"/>
+    </row>
+    <row r="348" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B348" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C347" s="20" t="s">
+      <c r="C348" s="23" t="s">
         <v>402</v>
       </c>
-      <c r="D347" s="20"/>
-      <c r="E347" s="2" t="s">
+      <c r="D348" s="23"/>
+      <c r="E348" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F347" s="21"/>
-      <c r="G347" s="21"/>
-    </row>
-    <row r="348" spans="2:7">
-      <c r="B348" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C348" s="21" t="s">
-        <v>403</v>
-      </c>
-      <c r="D348" s="21"/>
-      <c r="E348" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F348" s="21" t="s">
-        <v>404</v>
-      </c>
-      <c r="G348" s="21" t="s">
-        <v>405</v>
-      </c>
+      <c r="F348" s="22"/>
+      <c r="G348" s="22"/>
     </row>
     <row r="349" spans="2:7">
       <c r="B349" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C349" s="22" t="s">
+        <v>403</v>
+      </c>
+      <c r="D349" s="22"/>
+      <c r="E349" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F349" s="22" t="s">
+        <v>404</v>
+      </c>
+      <c r="G349" s="22" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="350" spans="2:7">
+      <c r="B350" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C349" s="2" t="s">
+      <c r="C350" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D349" s="2" t="s">
+      <c r="D350" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E349" s="2" t="s">
+      <c r="E350" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F349" s="2" t="s">
+      <c r="F350" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G349" s="2" t="s">
+      <c r="G350" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="350" spans="2:7">
-      <c r="B350" s="1">
+    <row r="351" spans="2:7">
+      <c r="B351" s="1">
         <v>1</v>
       </c>
-      <c r="C350" s="1" t="s">
+      <c r="C351" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="D350" s="1" t="s">
+      <c r="D351" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="E350" s="1" t="s">
+      <c r="E351" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="F350" s="1"/>
-      <c r="G350" s="1" t="s">
+      <c r="F351" s="1"/>
+      <c r="G351" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="351" spans="2:7" s="17" customFormat="1">
-      <c r="B351" s="16">
+    <row r="352" spans="2:7" s="17" customFormat="1">
+      <c r="B352" s="16">
         <v>2</v>
       </c>
-      <c r="C351" s="16" t="s">
+      <c r="C352" s="16" t="s">
         <v>617</v>
       </c>
-      <c r="D351" s="16" t="s">
+      <c r="D352" s="16" t="s">
         <v>615</v>
       </c>
-      <c r="E351" s="16" t="s">
+      <c r="E352" s="16" t="s">
         <v>352</v>
       </c>
-      <c r="F351" s="16"/>
-      <c r="G351" s="16" t="s">
+      <c r="F352" s="16"/>
+      <c r="G352" s="16" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="352" spans="2:7">
-      <c r="B352" s="1">
-        <v>3</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="E352" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F352" s="1"/>
-      <c r="G352" s="1"/>
     </row>
     <row r="353" spans="2:9">
       <c r="B353" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F353" s="1"/>
-      <c r="G353" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="G353" s="1"/>
     </row>
     <row r="354" spans="2:9">
       <c r="B354" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>187</v>
+        <v>410</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>235</v>
+        <v>352</v>
       </c>
       <c r="F354" s="1"/>
-      <c r="G354" s="1"/>
+      <c r="G354" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="355" spans="2:9">
       <c r="B355" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>146</v>
+        <v>411</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>374</v>
+        <v>187</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>235</v>
@@ -9123,13 +9159,13 @@
     </row>
     <row r="356" spans="2:9">
       <c r="B356" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>398</v>
+        <v>146</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>235</v>
@@ -9139,86 +9175,83 @@
     </row>
     <row r="357" spans="2:9">
       <c r="B357" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F357" s="1"/>
-      <c r="G357" s="1" t="s">
-        <v>414</v>
-      </c>
+      <c r="G357" s="1"/>
     </row>
     <row r="358" spans="2:9">
       <c r="B358" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F358" s="1"/>
       <c r="G358" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="359" spans="2:9">
       <c r="B359" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>64</v>
+        <v>415</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>188</v>
+        <v>416</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F359" s="1"/>
       <c r="G359" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="360" spans="2:9">
       <c r="B360" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>29</v>
+        <v>188</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F360" s="1"/>
-      <c r="G360" s="1"/>
-      <c r="I360" t="s">
-        <v>618</v>
+      <c r="G360" s="1" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="361" spans="2:9">
       <c r="B361" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>238</v>
@@ -9226,223 +9259,223 @@
       <c r="F361" s="1"/>
       <c r="G361" s="1"/>
       <c r="I361" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="362" spans="2:9">
+      <c r="B362" s="1">
+        <v>12</v>
+      </c>
+      <c r="C362" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E362" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F362" s="1"/>
+      <c r="G362" s="1"/>
+      <c r="I362" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="363" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B363" s="2" t="s">
+    <row r="364" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B364" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C363" s="20" t="s">
+      <c r="C364" s="23" t="s">
         <v>419</v>
       </c>
-      <c r="D363" s="20"/>
-      <c r="E363" s="2" t="s">
+      <c r="D364" s="23"/>
+      <c r="E364" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F363" s="21"/>
-      <c r="G363" s="21"/>
-    </row>
-    <row r="364" spans="2:9">
-      <c r="B364" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C364" s="21" t="s">
-        <v>420</v>
-      </c>
-      <c r="D364" s="21"/>
-      <c r="E364" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F364" s="21"/>
-      <c r="G364" s="21"/>
+      <c r="F364" s="22"/>
+      <c r="G364" s="22"/>
     </row>
     <row r="365" spans="2:9">
       <c r="B365" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C365" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="D365" s="22"/>
+      <c r="E365" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F365" s="22"/>
+      <c r="G365" s="22"/>
+    </row>
+    <row r="366" spans="2:9">
+      <c r="B366" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C365" s="2" t="s">
+      <c r="C366" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D365" s="2" t="s">
+      <c r="D366" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E365" s="2" t="s">
+      <c r="E366" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F365" s="2" t="s">
+      <c r="F366" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G365" s="2" t="s">
+      <c r="G366" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="366" spans="2:9">
-      <c r="B366" s="1">
-        <v>1</v>
-      </c>
-      <c r="C366" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D366" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="E366" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F366" s="1"/>
-      <c r="G366" s="1" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="367" spans="2:9">
       <c r="B367" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>72</v>
+        <v>420</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>359</v>
+        <v>421</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F367" s="1">
-        <v>50</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F367" s="1"/>
       <c r="G367" s="1" t="s">
-        <v>422</v>
+        <v>563</v>
       </c>
     </row>
     <row r="368" spans="2:9">
       <c r="B368" s="1">
+        <v>2</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="E368" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F368" s="1">
+        <v>50</v>
+      </c>
+      <c r="G368" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="369" spans="2:9">
+      <c r="B369" s="1">
         <v>3</v>
       </c>
-      <c r="C368" s="1" t="s">
+      <c r="C369" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="D368" s="1" t="s">
+      <c r="D369" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="E368" s="1" t="s">
+      <c r="E369" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="F368" s="1"/>
-      <c r="G368" s="1" t="s">
+      <c r="F369" s="1"/>
+      <c r="G369" s="1" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="369" spans="2:9">
-      <c r="B369" s="1" t="s">
+    <row r="370" spans="2:9">
+      <c r="B370" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C369" s="1" t="s">
+      <c r="C370" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="D369" s="1"/>
-      <c r="E369" s="1"/>
-      <c r="F369" s="1"/>
-      <c r="G369" s="1"/>
-    </row>
-    <row r="371" spans="2:9" s="5" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B371" s="3" t="s">
+      <c r="D370" s="1"/>
+      <c r="E370" s="1"/>
+      <c r="F370" s="1"/>
+      <c r="G370" s="1"/>
+    </row>
+    <row r="372" spans="2:9" s="5" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B372" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C371" s="22" t="s">
+      <c r="C372" s="24" t="s">
         <v>522</v>
       </c>
-      <c r="D371" s="22"/>
-      <c r="E371" s="3" t="s">
+      <c r="D372" s="24"/>
+      <c r="E372" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F371" s="23"/>
-      <c r="G371" s="23"/>
-      <c r="I371"/>
-    </row>
-    <row r="372" spans="2:9" s="5" customFormat="1">
-      <c r="B372" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C372" s="23" t="s">
-        <v>420</v>
-      </c>
-      <c r="D372" s="23"/>
-      <c r="E372" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F372" s="23"/>
-      <c r="G372" s="23"/>
+      <c r="F372" s="25"/>
+      <c r="G372" s="25"/>
       <c r="I372"/>
     </row>
     <row r="373" spans="2:9" s="5" customFormat="1">
       <c r="B373" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C373" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="D373" s="25"/>
+      <c r="E373" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F373" s="25"/>
+      <c r="G373" s="25"/>
+      <c r="I373"/>
+    </row>
+    <row r="374" spans="2:9" s="5" customFormat="1">
+      <c r="B374" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C373" s="3" t="s">
+      <c r="C374" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D373" s="3" t="s">
+      <c r="D374" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E373" s="3" t="s">
+      <c r="E374" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F373" s="3" t="s">
+      <c r="F374" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G373" s="3" t="s">
+      <c r="G374" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="I373"/>
-    </row>
-    <row r="374" spans="2:9" s="5" customFormat="1">
-      <c r="B374" s="4">
-        <v>1</v>
-      </c>
-      <c r="C374" s="4" t="s">
-        <v>524</v>
-      </c>
-      <c r="D374" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="E374" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F374" s="4"/>
-      <c r="G374" s="4" t="s">
-        <v>562</v>
       </c>
       <c r="I374"/>
     </row>
     <row r="375" spans="2:9" s="5" customFormat="1">
       <c r="B375" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E375" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F375" s="4"/>
       <c r="G375" s="4" t="s">
-        <v>529</v>
+        <v>562</v>
       </c>
       <c r="I375"/>
     </row>
     <row r="376" spans="2:9" s="5" customFormat="1">
       <c r="B376" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E376" s="4" t="s">
         <v>13</v>
@@ -9454,159 +9487,158 @@
       <c r="I376"/>
     </row>
     <row r="377" spans="2:9" s="5" customFormat="1">
-      <c r="B377" s="4" t="s">
+      <c r="B377" s="4">
+        <v>3</v>
+      </c>
+      <c r="C377" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="D377" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="E377" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F377" s="4"/>
+      <c r="G377" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="I377"/>
+    </row>
+    <row r="378" spans="2:9" s="5" customFormat="1">
+      <c r="B378" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C377" s="4" t="s">
+      <c r="C378" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="D377" s="4"/>
-      <c r="E377" s="4"/>
-      <c r="F377" s="4"/>
-      <c r="G377" s="4"/>
-      <c r="I377"/>
-    </row>
-    <row r="379" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B379" s="2" t="s">
+      <c r="D378" s="4"/>
+      <c r="E378" s="4"/>
+      <c r="F378" s="4"/>
+      <c r="G378" s="4"/>
+      <c r="I378"/>
+    </row>
+    <row r="380" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B380" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C379" s="20" t="s">
+      <c r="C380" s="23" t="s">
         <v>425</v>
       </c>
-      <c r="D379" s="20"/>
-      <c r="E379" s="2" t="s">
+      <c r="D380" s="23"/>
+      <c r="E380" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F379" s="21"/>
-      <c r="G379" s="21"/>
-    </row>
-    <row r="380" spans="2:9">
-      <c r="B380" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C380" s="21" t="s">
-        <v>426</v>
-      </c>
-      <c r="D380" s="21"/>
-      <c r="E380" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F380" s="20" t="s">
-        <v>561</v>
-      </c>
-      <c r="G380" s="21" t="s">
-        <v>427</v>
-      </c>
+      <c r="F380" s="22"/>
+      <c r="G380" s="22"/>
     </row>
     <row r="381" spans="2:9">
       <c r="B381" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C381" s="22" t="s">
+        <v>426</v>
+      </c>
+      <c r="D381" s="22"/>
+      <c r="E381" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F381" s="23" t="s">
+        <v>561</v>
+      </c>
+      <c r="G381" s="22" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="382" spans="2:9">
+      <c r="B382" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C381" s="2" t="s">
+      <c r="C382" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D381" s="2" t="s">
+      <c r="D382" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E381" s="2" t="s">
+      <c r="E382" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F381" s="2" t="s">
+      <c r="F382" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G381" s="2" t="s">
+      <c r="G382" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="382" spans="2:9">
-      <c r="B382" s="1">
-        <v>1</v>
-      </c>
-      <c r="C382" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="D382" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="E382" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="F382" s="1"/>
-      <c r="G382" s="1" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="383" spans="2:9">
       <c r="B383" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>67</v>
+        <v>426</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>68</v>
+        <v>428</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>352</v>
+        <v>531</v>
       </c>
       <c r="F383" s="1"/>
       <c r="G383" s="1" t="s">
-        <v>34</v>
+        <v>429</v>
       </c>
     </row>
     <row r="384" spans="2:9">
       <c r="B384" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>430</v>
+        <v>67</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>13</v>
+        <v>352</v>
       </c>
       <c r="F384" s="1"/>
       <c r="G384" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="385" spans="2:9">
       <c r="B385" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>186</v>
+        <v>430</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>371</v>
+        <v>16</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F385" s="1">
-        <v>120</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F385" s="1"/>
       <c r="G385" s="1" t="s">
-        <v>236</v>
+        <v>17</v>
       </c>
     </row>
     <row r="386" spans="2:9">
       <c r="B386" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>431</v>
+        <v>186</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>432</v>
+        <v>371</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F386" s="1">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G386" s="1" t="s">
         <v>236</v>
@@ -9614,87 +9646,89 @@
     </row>
     <row r="387" spans="2:9">
       <c r="B387" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>146</v>
+        <v>431</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>374</v>
+        <v>432</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F387" s="1"/>
+      <c r="F387" s="1">
+        <v>100</v>
+      </c>
       <c r="G387" s="1" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="388" spans="2:9">
       <c r="B388" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>433</v>
+        <v>146</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>434</v>
+        <v>374</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F388" s="1">
-        <v>255</v>
-      </c>
+      <c r="F388" s="1"/>
       <c r="G388" s="1" t="s">
-        <v>435</v>
+        <v>236</v>
       </c>
     </row>
     <row r="389" spans="2:9">
       <c r="B389" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F389" s="1">
-        <v>30</v>
-      </c>
-      <c r="G389" s="1"/>
+        <v>255</v>
+      </c>
+      <c r="G389" s="1" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="390" spans="2:9">
       <c r="B390" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>398</v>
+        <v>436</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>399</v>
+        <v>437</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F390" s="1">
-        <v>255</v>
+        <v>30</v>
       </c>
       <c r="G390" s="1"/>
     </row>
     <row r="391" spans="2:9">
       <c r="B391" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>438</v>
+        <v>398</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>439</v>
+        <v>399</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>235</v>
@@ -9706,32 +9740,31 @@
     </row>
     <row r="392" spans="2:9">
       <c r="B392" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>602</v>
+        <v>438</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F392" s="1"/>
+        <v>235</v>
+      </c>
+      <c r="F392" s="1">
+        <v>255</v>
+      </c>
       <c r="G392" s="1"/>
-      <c r="I392" t="s">
-        <v>603</v>
-      </c>
     </row>
     <row r="393" spans="2:9">
       <c r="B393" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>441</v>
+        <v>602</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>347</v>
+        <v>440</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>238</v>
@@ -9739,75 +9772,73 @@
       <c r="F393" s="1"/>
       <c r="G393" s="1"/>
       <c r="I393" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="394" spans="2:9">
       <c r="B394" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D394" s="1" t="s">
-        <v>380</v>
+        <v>347</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>13</v>
+        <v>238</v>
       </c>
       <c r="F394" s="1"/>
-      <c r="G394" s="1" t="s">
-        <v>443</v>
+      <c r="G394" s="1"/>
+      <c r="I394" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="395" spans="2:9">
       <c r="B395" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>64</v>
+        <v>442</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>536</v>
+        <v>380</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="F395" s="1"/>
       <c r="G395" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="396" spans="2:9">
       <c r="B396" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>29</v>
+        <v>536</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F396" s="1"/>
       <c r="G396" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="I396" t="s">
-        <v>598</v>
+        <v>444</v>
       </c>
     </row>
     <row r="397" spans="2:9">
       <c r="B397" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>238</v>
@@ -9817,515 +9848,516 @@
         <v>236</v>
       </c>
       <c r="I397" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="398" spans="2:9">
       <c r="B398" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>445</v>
+        <v>31</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>446</v>
+        <v>32</v>
       </c>
       <c r="E398" s="1" t="s">
         <v>238</v>
       </c>
       <c r="F398" s="1"/>
-      <c r="G398" s="1"/>
+      <c r="G398" s="1" t="s">
+        <v>236</v>
+      </c>
       <c r="I398" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="399" spans="2:9">
       <c r="B399" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>532</v>
+        <v>445</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>533</v>
+        <v>446</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>534</v>
+        <v>238</v>
       </c>
       <c r="F399" s="1"/>
       <c r="G399" s="1"/>
+      <c r="I399" t="s">
+        <v>600</v>
+      </c>
     </row>
     <row r="400" spans="2:9">
-      <c r="B400" s="1" t="s">
-        <v>11</v>
+      <c r="B400" s="1">
+        <v>18</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="D400" s="1"/>
-      <c r="E400" s="1"/>
+        <v>532</v>
+      </c>
+      <c r="D400" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="E400" s="1" t="s">
+        <v>534</v>
+      </c>
       <c r="F400" s="1"/>
       <c r="G400" s="1"/>
     </row>
-    <row r="402" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B402" s="2" t="s">
+    <row r="401" spans="2:9">
+      <c r="B401" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C401" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D401" s="1"/>
+      <c r="E401" s="1"/>
+      <c r="F401" s="1"/>
+      <c r="G401" s="1"/>
+    </row>
+    <row r="403" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B403" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C402" s="20" t="s">
+      <c r="C403" s="23" t="s">
         <v>448</v>
       </c>
-      <c r="D402" s="20"/>
-      <c r="E402" s="2" t="s">
+      <c r="D403" s="23"/>
+      <c r="E403" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F402" s="21"/>
-      <c r="G402" s="21"/>
-    </row>
-    <row r="403" spans="2:9">
-      <c r="B403" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C403" s="21" t="s">
-        <v>449</v>
-      </c>
-      <c r="D403" s="21"/>
-      <c r="E403" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F403" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="G403" s="21"/>
+      <c r="F403" s="22"/>
+      <c r="G403" s="22"/>
     </row>
     <row r="404" spans="2:9">
       <c r="B404" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C404" s="22" t="s">
+        <v>449</v>
+      </c>
+      <c r="D404" s="22"/>
+      <c r="E404" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F404" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="G404" s="22"/>
+    </row>
+    <row r="405" spans="2:9">
+      <c r="B405" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C404" s="2" t="s">
+      <c r="C405" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D404" s="2" t="s">
+      <c r="D405" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E404" s="2" t="s">
+      <c r="E405" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F404" s="2" t="s">
+      <c r="F405" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G404" s="2" t="s">
+      <c r="G405" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="405" spans="2:9">
-      <c r="B405" s="1">
-        <v>1</v>
-      </c>
-      <c r="C405" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D405" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="E405" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F405" s="1"/>
-      <c r="G405" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="406" spans="2:9">
       <c r="B406" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>67</v>
+        <v>449</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>68</v>
+        <v>450</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F406" s="1"/>
       <c r="G406" s="1" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="407" spans="2:9">
       <c r="B407" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>451</v>
+        <v>67</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>452</v>
+        <v>68</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F407" s="1">
-        <v>50</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F407" s="1"/>
       <c r="G407" s="1" t="s">
-        <v>560</v>
+        <v>34</v>
       </c>
     </row>
     <row r="408" spans="2:9">
       <c r="B408" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D408" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F408" s="1"/>
+      <c r="F408" s="1">
+        <v>50</v>
+      </c>
       <c r="G408" s="1" t="s">
-        <v>455</v>
+        <v>560</v>
       </c>
     </row>
     <row r="409" spans="2:9">
       <c r="B409" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>28</v>
+        <v>453</v>
       </c>
       <c r="D409" s="1" t="s">
-        <v>29</v>
+        <v>454</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F409" s="1"/>
       <c r="G409" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="410" spans="2:9">
+      <c r="B410" s="1">
+        <v>5</v>
+      </c>
+      <c r="C410" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D410" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E410" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F410" s="1"/>
+      <c r="G410" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I409" t="s">
+      <c r="I410" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="411" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B411" s="2" t="s">
+    <row r="412" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B412" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C411" s="20" t="s">
+      <c r="C412" s="23" t="s">
         <v>456</v>
       </c>
-      <c r="D411" s="20"/>
-      <c r="E411" s="2" t="s">
+      <c r="D412" s="23"/>
+      <c r="E412" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F411" s="21"/>
-      <c r="G411" s="21"/>
-    </row>
-    <row r="412" spans="2:9">
-      <c r="B412" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C412" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="D412" s="21"/>
-      <c r="E412" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F412" s="21"/>
-      <c r="G412" s="21"/>
+      <c r="F412" s="22"/>
+      <c r="G412" s="22"/>
     </row>
     <row r="413" spans="2:9">
       <c r="B413" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C413" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="D413" s="22"/>
+      <c r="E413" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F413" s="22"/>
+      <c r="G413" s="22"/>
+    </row>
+    <row r="414" spans="2:9">
+      <c r="B414" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C413" s="2" t="s">
+      <c r="C414" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D413" s="2" t="s">
+      <c r="D414" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E413" s="2" t="s">
+      <c r="E414" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F413" s="2" t="s">
+      <c r="F414" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G413" s="2" t="s">
+      <c r="G414" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="414" spans="2:9">
-      <c r="B414" s="1">
-        <v>1</v>
-      </c>
-      <c r="C414" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="D414" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="E414" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F414" s="1"/>
-      <c r="G414" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="415" spans="2:9">
       <c r="B415" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>457</v>
+        <v>321</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>458</v>
+        <v>322</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F415" s="1">
-        <v>100</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F415" s="1"/>
       <c r="G415" s="1" t="s">
-        <v>459</v>
+        <v>14</v>
       </c>
     </row>
     <row r="416" spans="2:9">
       <c r="B416" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>235</v>
       </c>
       <c r="F416" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G416" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="417" spans="2:9">
       <c r="B417" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F417" s="1"/>
+      <c r="F417" s="1">
+        <v>50</v>
+      </c>
       <c r="G417" s="1" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="418" spans="2:9">
       <c r="B418" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F418" s="1" t="s">
-        <v>557</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="F418" s="1"/>
       <c r="G418" s="1" t="s">
-        <v>559</v>
+        <v>465</v>
       </c>
     </row>
     <row r="419" spans="2:9">
       <c r="B419" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>298</v>
+        <v>466</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>299</v>
+        <v>467</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="F419" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="F419" s="1" t="s">
+        <v>557</v>
+      </c>
       <c r="G419" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="420" spans="2:9">
       <c r="B420" s="1">
+        <v>6</v>
+      </c>
+      <c r="C420" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D420" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E420" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="F420" s="1"/>
+      <c r="G420" s="1" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="421" spans="2:9">
+      <c r="B421" s="1">
         <v>7</v>
       </c>
-      <c r="C420" s="1" t="s">
+      <c r="C421" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D420" s="1" t="s">
+      <c r="D421" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E420" s="1" t="s">
+      <c r="E421" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F420" s="1"/>
-      <c r="G420" s="1"/>
-      <c r="I420" t="s">
+      <c r="F421" s="1"/>
+      <c r="G421" s="1"/>
+      <c r="I421" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="422" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B422" s="2" t="s">
+    <row r="423" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B423" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C422" s="20" t="s">
+      <c r="C423" s="23" t="s">
         <v>468</v>
       </c>
-      <c r="D422" s="20"/>
-      <c r="E422" s="2" t="s">
+      <c r="D423" s="23"/>
+      <c r="E423" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F422" s="21"/>
-      <c r="G422" s="21"/>
-    </row>
-    <row r="423" spans="2:9">
-      <c r="B423" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C423" s="21" t="s">
-        <v>469</v>
-      </c>
-      <c r="D423" s="21"/>
-      <c r="E423" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F423" s="21" t="s">
-        <v>470</v>
-      </c>
-      <c r="G423" s="21"/>
+      <c r="F423" s="22"/>
+      <c r="G423" s="22"/>
     </row>
     <row r="424" spans="2:9">
       <c r="B424" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C424" s="22" t="s">
+        <v>469</v>
+      </c>
+      <c r="D424" s="22"/>
+      <c r="E424" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F424" s="22" t="s">
+        <v>470</v>
+      </c>
+      <c r="G424" s="22"/>
+    </row>
+    <row r="425" spans="2:9">
+      <c r="B425" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C424" s="2" t="s">
+      <c r="C425" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D424" s="2" t="s">
+      <c r="D425" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E424" s="2" t="s">
+      <c r="E425" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F424" s="2" t="s">
+      <c r="F425" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G424" s="2" t="s">
+      <c r="G425" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="425" spans="2:9">
-      <c r="B425" s="1">
-        <v>1</v>
-      </c>
-      <c r="C425" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="D425" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="E425" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F425" s="1"/>
-      <c r="G425" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="426" spans="2:9">
       <c r="B426" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>321</v>
+        <v>469</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F426" s="1"/>
       <c r="G426" s="1" t="s">
-        <v>473</v>
+        <v>14</v>
       </c>
     </row>
     <row r="427" spans="2:9">
       <c r="B427" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>474</v>
+        <v>321</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F427" s="1"/>
       <c r="G427" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="428" spans="2:9">
       <c r="B428" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F428" s="1" t="s">
-        <v>556</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F428" s="1"/>
       <c r="G428" s="1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="429" spans="2:9">
       <c r="B429" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>20</v>
@@ -10334,288 +10366,174 @@
         <v>556</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="430" spans="2:9">
       <c r="B430" s="1">
+        <v>5</v>
+      </c>
+      <c r="C430" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="D430" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="E430" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F430" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="G430" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="431" spans="2:9">
+      <c r="B431" s="1">
         <v>6</v>
       </c>
-      <c r="C430" s="1" t="s">
+      <c r="C431" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D430" s="1" t="s">
+      <c r="D431" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="E430" s="1" t="s">
+      <c r="E431" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F430" s="1"/>
-      <c r="G430" s="1"/>
-      <c r="I430" t="s">
+      <c r="F431" s="1"/>
+      <c r="G431" s="1"/>
+      <c r="I431" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="432" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B432" s="2" t="s">
+    <row r="433" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B433" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C432" s="20" t="s">
+      <c r="C433" s="23" t="s">
         <v>484</v>
       </c>
-      <c r="D432" s="20"/>
-      <c r="E432" s="2" t="s">
+      <c r="D433" s="23"/>
+      <c r="E433" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F432" s="21"/>
-      <c r="G432" s="21"/>
-    </row>
-    <row r="433" spans="2:7">
-      <c r="B433" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C433" s="21" t="s">
-        <v>485</v>
-      </c>
-      <c r="D433" s="21"/>
-      <c r="E433" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F433" s="21" t="s">
-        <v>486</v>
-      </c>
-      <c r="G433" s="21"/>
+      <c r="F433" s="22"/>
+      <c r="G433" s="22"/>
     </row>
     <row r="434" spans="2:7">
       <c r="B434" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C434" s="22" t="s">
+        <v>485</v>
+      </c>
+      <c r="D434" s="22"/>
+      <c r="E434" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F434" s="22" t="s">
+        <v>486</v>
+      </c>
+      <c r="G434" s="22"/>
+    </row>
+    <row r="435" spans="2:7">
+      <c r="B435" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C434" s="2" t="s">
+      <c r="C435" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D434" s="2" t="s">
+      <c r="D435" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E434" s="2" t="s">
+      <c r="E435" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F434" s="2" t="s">
+      <c r="F435" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G434" s="2" t="s">
+      <c r="G435" s="2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="435" spans="2:7">
-      <c r="B435" s="1">
-        <v>1</v>
-      </c>
-      <c r="C435" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="D435" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="E435" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F435" s="1">
-        <v>24</v>
-      </c>
-      <c r="G435" s="1" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="436" spans="2:7">
       <c r="B436" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F436" s="1"/>
+        <v>235</v>
+      </c>
+      <c r="F436" s="1">
+        <v>24</v>
+      </c>
       <c r="G436" s="1" t="s">
-        <v>47</v>
+        <v>488</v>
       </c>
     </row>
     <row r="437" spans="2:7">
       <c r="B437" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>110</v>
+        <v>489</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F437" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="G437" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="F437" s="1"/>
+      <c r="G437" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="438" spans="2:7">
       <c r="B438" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>493</v>
+        <v>110</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="F438" s="1">
+      <c r="F438" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="G438" s="1"/>
+    </row>
+    <row r="439" spans="2:7">
+      <c r="B439" s="1">
+        <v>4</v>
+      </c>
+      <c r="C439" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D439" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="E439" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F439" s="1">
         <v>500</v>
       </c>
-      <c r="G438" s="1"/>
+      <c r="G439" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="148">
-    <mergeCell ref="C380:D380"/>
-    <mergeCell ref="F380:G380"/>
-    <mergeCell ref="C402:D402"/>
-    <mergeCell ref="F402:G402"/>
-    <mergeCell ref="C403:D403"/>
-    <mergeCell ref="F403:G403"/>
-    <mergeCell ref="C411:D411"/>
-    <mergeCell ref="F411:G411"/>
-    <mergeCell ref="C433:D433"/>
-    <mergeCell ref="F433:G433"/>
-    <mergeCell ref="C432:D432"/>
-    <mergeCell ref="F432:G432"/>
-    <mergeCell ref="C412:D412"/>
-    <mergeCell ref="F412:G412"/>
-    <mergeCell ref="C422:D422"/>
-    <mergeCell ref="F422:G422"/>
-    <mergeCell ref="C423:D423"/>
-    <mergeCell ref="F423:G423"/>
-    <mergeCell ref="C364:D364"/>
-    <mergeCell ref="F364:G364"/>
-    <mergeCell ref="C379:D379"/>
-    <mergeCell ref="F379:G379"/>
-    <mergeCell ref="C348:D348"/>
-    <mergeCell ref="F348:G348"/>
-    <mergeCell ref="C371:D371"/>
-    <mergeCell ref="F371:G371"/>
-    <mergeCell ref="C372:D372"/>
-    <mergeCell ref="F372:G372"/>
-    <mergeCell ref="C347:D347"/>
-    <mergeCell ref="F347:G347"/>
-    <mergeCell ref="C317:D317"/>
-    <mergeCell ref="F317:G317"/>
-    <mergeCell ref="C335:D335"/>
-    <mergeCell ref="F335:G335"/>
-    <mergeCell ref="C336:D336"/>
-    <mergeCell ref="F336:G336"/>
-    <mergeCell ref="C363:D363"/>
-    <mergeCell ref="F363:G363"/>
-    <mergeCell ref="C303:D303"/>
-    <mergeCell ref="F303:G303"/>
-    <mergeCell ref="C304:D304"/>
-    <mergeCell ref="F304:G304"/>
-    <mergeCell ref="C316:D316"/>
-    <mergeCell ref="F316:G316"/>
-    <mergeCell ref="C278:D278"/>
-    <mergeCell ref="F278:G278"/>
-    <mergeCell ref="C290:D290"/>
-    <mergeCell ref="F290:G290"/>
-    <mergeCell ref="C291:D291"/>
-    <mergeCell ref="F291:G291"/>
-    <mergeCell ref="C264:D264"/>
-    <mergeCell ref="F264:G264"/>
-    <mergeCell ref="C265:D265"/>
-    <mergeCell ref="F265:G265"/>
-    <mergeCell ref="C277:D277"/>
-    <mergeCell ref="F277:G277"/>
-    <mergeCell ref="C241:D241"/>
-    <mergeCell ref="F241:G241"/>
-    <mergeCell ref="C252:D252"/>
-    <mergeCell ref="F252:G252"/>
-    <mergeCell ref="C253:D253"/>
-    <mergeCell ref="F253:G253"/>
-    <mergeCell ref="C228:D228"/>
-    <mergeCell ref="F228:G228"/>
-    <mergeCell ref="C229:D229"/>
-    <mergeCell ref="F229:G229"/>
-    <mergeCell ref="C240:D240"/>
-    <mergeCell ref="F240:G240"/>
-    <mergeCell ref="C207:D207"/>
-    <mergeCell ref="F207:G207"/>
-    <mergeCell ref="C214:D214"/>
-    <mergeCell ref="F214:G214"/>
-    <mergeCell ref="C215:D215"/>
-    <mergeCell ref="F215:G215"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="F197:G197"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="F198:G198"/>
-    <mergeCell ref="C206:D206"/>
-    <mergeCell ref="F206:G206"/>
-    <mergeCell ref="C176:D176"/>
-    <mergeCell ref="F176:G176"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="F185:G185"/>
-    <mergeCell ref="C186:D186"/>
-    <mergeCell ref="F186:G186"/>
-    <mergeCell ref="C168:D168"/>
-    <mergeCell ref="F168:G168"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="F175:G175"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="F142:G142"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="F153:G153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="F154:G154"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="F141:G141"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="F130:G130"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="F167:G167"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="F103:G103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="F104:G104"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="F116:G116"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="F81:G81"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="F2:G2"/>
@@ -10630,6 +10548,140 @@
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="F14:G14"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="F142:G142"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="F118:G118"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="F131:G131"/>
+    <mergeCell ref="C168:D168"/>
+    <mergeCell ref="F168:G168"/>
+    <mergeCell ref="C169:D169"/>
+    <mergeCell ref="F169:G169"/>
+    <mergeCell ref="C176:D176"/>
+    <mergeCell ref="F176:G176"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="F143:G143"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="F154:G154"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="F155:G155"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="F198:G198"/>
+    <mergeCell ref="C199:D199"/>
+    <mergeCell ref="F199:G199"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="F207:G207"/>
+    <mergeCell ref="C177:D177"/>
+    <mergeCell ref="F177:G177"/>
+    <mergeCell ref="C186:D186"/>
+    <mergeCell ref="F186:G186"/>
+    <mergeCell ref="C187:D187"/>
+    <mergeCell ref="F187:G187"/>
+    <mergeCell ref="C229:D229"/>
+    <mergeCell ref="F229:G229"/>
+    <mergeCell ref="C230:D230"/>
+    <mergeCell ref="F230:G230"/>
+    <mergeCell ref="C241:D241"/>
+    <mergeCell ref="F241:G241"/>
+    <mergeCell ref="C208:D208"/>
+    <mergeCell ref="F208:G208"/>
+    <mergeCell ref="C215:D215"/>
+    <mergeCell ref="F215:G215"/>
+    <mergeCell ref="C216:D216"/>
+    <mergeCell ref="F216:G216"/>
+    <mergeCell ref="C265:D265"/>
+    <mergeCell ref="F265:G265"/>
+    <mergeCell ref="C266:D266"/>
+    <mergeCell ref="F266:G266"/>
+    <mergeCell ref="C278:D278"/>
+    <mergeCell ref="F278:G278"/>
+    <mergeCell ref="C242:D242"/>
+    <mergeCell ref="F242:G242"/>
+    <mergeCell ref="C253:D253"/>
+    <mergeCell ref="F253:G253"/>
+    <mergeCell ref="C254:D254"/>
+    <mergeCell ref="F254:G254"/>
+    <mergeCell ref="C304:D304"/>
+    <mergeCell ref="F304:G304"/>
+    <mergeCell ref="C305:D305"/>
+    <mergeCell ref="F305:G305"/>
+    <mergeCell ref="C317:D317"/>
+    <mergeCell ref="F317:G317"/>
+    <mergeCell ref="C279:D279"/>
+    <mergeCell ref="F279:G279"/>
+    <mergeCell ref="C291:D291"/>
+    <mergeCell ref="F291:G291"/>
+    <mergeCell ref="C292:D292"/>
+    <mergeCell ref="F292:G292"/>
+    <mergeCell ref="C348:D348"/>
+    <mergeCell ref="F348:G348"/>
+    <mergeCell ref="C318:D318"/>
+    <mergeCell ref="F318:G318"/>
+    <mergeCell ref="C336:D336"/>
+    <mergeCell ref="F336:G336"/>
+    <mergeCell ref="C337:D337"/>
+    <mergeCell ref="F337:G337"/>
+    <mergeCell ref="C364:D364"/>
+    <mergeCell ref="F364:G364"/>
+    <mergeCell ref="C365:D365"/>
+    <mergeCell ref="F365:G365"/>
+    <mergeCell ref="C380:D380"/>
+    <mergeCell ref="F380:G380"/>
+    <mergeCell ref="C349:D349"/>
+    <mergeCell ref="F349:G349"/>
+    <mergeCell ref="C372:D372"/>
+    <mergeCell ref="F372:G372"/>
+    <mergeCell ref="C373:D373"/>
+    <mergeCell ref="F373:G373"/>
+    <mergeCell ref="C381:D381"/>
+    <mergeCell ref="F381:G381"/>
+    <mergeCell ref="C403:D403"/>
+    <mergeCell ref="F403:G403"/>
+    <mergeCell ref="C404:D404"/>
+    <mergeCell ref="F404:G404"/>
+    <mergeCell ref="C412:D412"/>
+    <mergeCell ref="F412:G412"/>
+    <mergeCell ref="C434:D434"/>
+    <mergeCell ref="F434:G434"/>
+    <mergeCell ref="C433:D433"/>
+    <mergeCell ref="F433:G433"/>
+    <mergeCell ref="C413:D413"/>
+    <mergeCell ref="F413:G413"/>
+    <mergeCell ref="C423:D423"/>
+    <mergeCell ref="F423:G423"/>
+    <mergeCell ref="C424:D424"/>
+    <mergeCell ref="F424:G424"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="E1:E1048576">
@@ -10637,7 +10689,7 @@
       <formula>"DATETIME2"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:G999 I40 I10:I11">
+  <conditionalFormatting sqref="I40 I10:I11 B1:G1000">
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="USER.user_id">
       <formula>NOT(ISERROR(SEARCH("USER.user_id",B1)))</formula>
     </cfRule>

--- a/Document/專題/db_diagram.xlsx
+++ b/Document/專題/db_diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\RentalManagementPlatform\Document\專題\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53A0DE4-AB61-4076-9852-471A5881C457}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8BB5DB1-14CF-4331-96A0-42DA009AD2B9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="662">
   <si>
     <t>表格名稱</t>
   </si>
@@ -251,15 +251,6 @@
     <t>例：王小明</t>
   </si>
   <si>
-    <t>auto_subscribe</t>
-  </si>
-  <si>
-    <t>自動訂閱</t>
-  </si>
-  <si>
-    <t>true/false</t>
-  </si>
-  <si>
     <t>password_hash</t>
   </si>
   <si>
@@ -400,12 +391,6 @@
     <t>例：滿2000才可用</t>
   </si>
   <si>
-    <t>start_at</t>
-  </si>
-  <si>
-    <t>生效時間</t>
-  </si>
-  <si>
     <t>中文：優惠券發放紀錄_x000D_
 英文：COUPON_GUEST</t>
   </si>
@@ -903,9 +888,6 @@
   </si>
   <si>
     <t>方案名稱</t>
-  </si>
-  <si>
-    <t>例：房東 Pro 月費方案</t>
   </si>
   <si>
     <t>monthly_fee</t>
@@ -2251,6 +2233,46 @@
   </si>
   <si>
     <t>驗證碼</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>is_deleted</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>BIT</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否已刪除</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>photo_type</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>照片類型</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>NVARCHAR</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>例：cover/gallery</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT NULL例：房東 Pro 月費方案</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT NULL單位：TWD</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>NOT NULL</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -2453,7 +2475,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2648,18 +2670,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2932,7 +2942,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2999,23 +3009,11 @@
     <xf numFmtId="0" fontId="7" fillId="33" borderId="0" xfId="7" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3074,7 +3072,41 @@
     <cellStyle name="壞" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="警告文字" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="15">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3120,16 +3152,6 @@
       <fill>
         <patternFill>
           <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3503,31 +3525,31 @@
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27" t="s">
-        <v>590</v>
-      </c>
-      <c r="D2" s="27"/>
+      <c r="C2" s="22" t="s">
+        <v>584</v>
+      </c>
+      <c r="D2" s="22"/>
       <c r="E2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" spans="2:9">
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="26"/>
+      <c r="D3" s="23"/>
       <c r="E3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="26"/>
+      <c r="G3" s="23"/>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="2" t="s">
@@ -3599,7 +3621,7 @@
         <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>21</v>
@@ -3619,7 +3641,7 @@
         <v>20</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>24</v>
@@ -3636,7 +3658,7 @@
         <v>26</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
@@ -3654,14 +3676,14 @@
         <v>29</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
     </row>
     <row r="11" spans="2:9">
@@ -3675,45 +3697,45 @@
         <v>32</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="16.5" customHeight="1">
       <c r="B13" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="27" t="s">
-        <v>572</v>
-      </c>
-      <c r="D13" s="27"/>
+      <c r="C13" s="22" t="s">
+        <v>566</v>
+      </c>
+      <c r="D13" s="22"/>
       <c r="E13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
     </row>
     <row r="14" spans="2:9">
       <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="26" t="s">
-        <v>571</v>
-      </c>
-      <c r="D14" s="26"/>
+      <c r="C14" s="23" t="s">
+        <v>565</v>
+      </c>
+      <c r="D14" s="23"/>
       <c r="E14" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="27" t="s">
-        <v>567</v>
-      </c>
-      <c r="G14" s="26" t="s">
+      <c r="F14" s="22" t="s">
+        <v>561</v>
+      </c>
+      <c r="G14" s="23" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3778,7 +3800,7 @@
         <v>3</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>43</v>
@@ -3820,7 +3842,7 @@
         <v>49</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -3836,14 +3858,14 @@
         <v>51</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
         <v>52</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
     </row>
     <row r="22" spans="2:9">
@@ -3851,20 +3873,20 @@
         <v>7</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
         <v>54</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
     </row>
     <row r="23" spans="2:9">
@@ -3938,17 +3960,17 @@
         <v>12</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
     </row>
     <row r="28" spans="2:9">
@@ -3962,41 +3984,41 @@
         <v>29</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="I28" s="12" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
     </row>
     <row r="30" spans="2:9" ht="16.5" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="27" t="s">
+      <c r="C30" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="27"/>
+      <c r="D30" s="22"/>
       <c r="E30" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
     </row>
     <row r="31" spans="2:9">
       <c r="B31" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="C31" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="D31" s="26"/>
+      <c r="D31" s="23"/>
       <c r="E31" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
     </row>
     <row r="32" spans="2:9">
       <c r="B32" s="2" t="s">
@@ -4041,17 +4063,17 @@
         <v>2</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
     </row>
     <row r="35" spans="2:16">
@@ -4065,7 +4087,7 @@
         <v>70</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1" t="s">
@@ -4083,28 +4105,28 @@
         <v>73</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="2:16" s="23" customFormat="1">
-      <c r="B37" s="22">
+    <row r="37" spans="2:16">
+      <c r="B37" s="1">
         <v>5</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="C37" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="D37" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E37" s="22" t="s">
-        <v>261</v>
-      </c>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22" t="s">
+      <c r="E37" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1" t="s">
         <v>77</v>
       </c>
     </row>
@@ -4113,54 +4135,54 @@
         <v>6</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>78</v>
+        <v>493</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>235</v>
+        <v>494</v>
+      </c>
+      <c r="E38" t="s">
+        <v>230</v>
       </c>
       <c r="F38" s="1"/>
-      <c r="G38" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="G38" s="1"/>
     </row>
     <row r="39" spans="2:16">
       <c r="B39" s="1">
         <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="E39" t="s">
-        <v>235</v>
+        <v>496</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>233</v>
       </c>
       <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
+      <c r="G39" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>570</v>
+      </c>
     </row>
     <row r="40" spans="2:16">
       <c r="B40" s="1">
         <v>8</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>501</v>
+        <v>78</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>502</v>
+        <v>79</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>576</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="2:16">
@@ -4168,31 +4190,29 @@
         <v>9</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>82</v>
+        <v>499</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>235</v>
+        <v>491</v>
       </c>
       <c r="F41" s="1"/>
-      <c r="G41" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="G41" s="1"/>
     </row>
     <row r="42" spans="2:16">
       <c r="B42" s="1">
         <v>10</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -4202,33 +4222,59 @@
         <v>11</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>504</v>
+        <v>81</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>506</v>
+        <v>82</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>497</v>
+        <v>13</v>
       </c>
       <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
+      <c r="G43" s="1" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="44" spans="2:16">
       <c r="B44" s="1">
         <v>12</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>84</v>
+        <v>501</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>85</v>
+        <v>502</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>13</v>
+        <v>503</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1" t="s">
-        <v>86</v>
+        <v>504</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="P44" s="6" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="45" spans="2:16">
@@ -4236,41 +4282,41 @@
         <v>13</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>507</v>
+        <v>645</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>508</v>
+        <v>646</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>509</v>
+        <v>233</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>577</v>
-      </c>
-      <c r="J45" s="6" t="s">
-        <v>578</v>
-      </c>
-      <c r="K45" s="6" t="s">
-        <v>579</v>
-      </c>
-      <c r="L45" s="6" t="s">
-        <v>580</v>
-      </c>
-      <c r="M45" s="6" t="s">
-        <v>581</v>
-      </c>
-      <c r="N45" s="6" t="s">
-        <v>582</v>
-      </c>
-      <c r="O45" s="6" t="s">
-        <v>583</v>
-      </c>
-      <c r="P45" s="6" t="s">
-        <v>584</v>
+        <v>84</v>
+      </c>
+      <c r="I45" s="6">
+        <v>45292.001388888886</v>
+      </c>
+      <c r="J45" s="6">
+        <v>45292.001388888886</v>
+      </c>
+      <c r="K45" s="8">
+        <v>45323</v>
+      </c>
+      <c r="L45" s="8">
+        <v>45897</v>
+      </c>
+      <c r="M45" s="8">
+        <v>45897</v>
+      </c>
+      <c r="N45" s="8">
+        <v>45897</v>
+      </c>
+      <c r="O45" s="8">
+        <v>45897</v>
+      </c>
+      <c r="P45" s="8">
+        <v>45897</v>
       </c>
     </row>
     <row r="46" spans="2:16">
@@ -4278,23 +4324,21 @@
         <v>14</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>651</v>
+        <v>31</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>652</v>
+        <v>33</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F46" s="1"/>
-      <c r="G46" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I46" s="6">
-        <v>45292.001388888886</v>
-      </c>
-      <c r="J46" s="6">
-        <v>45292.001388888886</v>
+      <c r="G46" s="1"/>
+      <c r="I46" s="8">
+        <v>45897</v>
+      </c>
+      <c r="J46" s="8">
+        <v>45897</v>
       </c>
       <c r="K46" s="8">
         <v>45323</v>
@@ -4315,272 +4359,250 @@
         <v>45897</v>
       </c>
     </row>
-    <row r="47" spans="2:16">
-      <c r="B47" s="1">
-        <v>15</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="I47" s="8">
-        <v>45897</v>
-      </c>
-      <c r="J47" s="8">
-        <v>45897</v>
-      </c>
-      <c r="K47" s="8">
-        <v>45323</v>
-      </c>
-      <c r="L47" s="8">
-        <v>45897</v>
-      </c>
-      <c r="M47" s="8">
-        <v>45897</v>
-      </c>
-      <c r="N47" s="8">
-        <v>45897</v>
-      </c>
-      <c r="O47" s="8">
-        <v>45897</v>
-      </c>
-      <c r="P47" s="8">
-        <v>45897</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" ht="16.5" customHeight="1">
+    <row r="48" spans="2:16" ht="16.5" customHeight="1">
+      <c r="B48" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>639</v>
+      </c>
+      <c r="D48" s="22"/>
+      <c r="E48" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="23"/>
+      <c r="G48" s="23"/>
+    </row>
+    <row r="49" spans="2:7">
       <c r="B49" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C49" s="27" t="s">
-        <v>645</v>
-      </c>
-      <c r="D49" s="27"/>
+        <v>2</v>
+      </c>
+      <c r="C49" s="23" t="s">
+        <v>640</v>
+      </c>
+      <c r="D49" s="23"/>
       <c r="E49" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
+        <v>4</v>
+      </c>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
     </row>
     <row r="50" spans="2:7">
       <c r="B50" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="26" t="s">
-        <v>646</v>
-      </c>
-      <c r="D50" s="26"/>
+        <v>6</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E50" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F50" s="26"/>
-      <c r="G50" s="26"/>
+        <v>9</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="51" spans="2:7">
-      <c r="B51" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>11</v>
+      <c r="B51" s="1">
+        <v>1</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="52" spans="2:7">
       <c r="B52" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F52" s="1"/>
-      <c r="G52" s="1" t="s">
-        <v>643</v>
-      </c>
+      <c r="G52" s="1"/>
     </row>
     <row r="53" spans="2:7">
       <c r="B53" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
     </row>
     <row r="54" spans="2:7">
       <c r="B54" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
     </row>
     <row r="55" spans="2:7">
       <c r="B55" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
     </row>
     <row r="56" spans="2:7">
       <c r="B56" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
     </row>
-    <row r="57" spans="2:7">
-      <c r="B57" s="1">
-        <v>6</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-    </row>
-    <row r="59" spans="2:7" ht="16.5" customHeight="1">
+    <row r="58" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B58" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D58" s="22"/>
+      <c r="E58" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F58" s="23"/>
+      <c r="G58" s="23"/>
+    </row>
+    <row r="59" spans="2:7">
       <c r="B59" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C59" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="D59" s="27"/>
+        <v>2</v>
+      </c>
+      <c r="C59" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D59" s="23"/>
       <c r="E59" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F59" s="26"/>
-      <c r="G59" s="26"/>
+        <v>4</v>
+      </c>
+      <c r="F59" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="G59" s="23"/>
     </row>
     <row r="60" spans="2:7">
       <c r="B60" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="D60" s="26"/>
+        <v>6</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E60" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F60" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="G60" s="26"/>
+        <v>9</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="61" spans="2:7">
-      <c r="B61" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>11</v>
+      <c r="B61" s="1">
+        <v>1</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="2:7">
       <c r="B62" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>91</v>
+        <v>38</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1" t="s">
-        <v>14</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="2:7">
       <c r="B63" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1" t="s">
@@ -4589,7 +4611,7 @@
     </row>
     <row r="64" spans="2:7">
       <c r="B64" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>93</v>
@@ -4598,184 +4620,184 @@
         <v>94</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="65" spans="2:9">
-      <c r="B65" s="1">
+    <row r="66" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B66" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C66" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D66" s="22"/>
+      <c r="E66" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F66" s="23"/>
+      <c r="G66" s="23"/>
+    </row>
+    <row r="67" spans="2:9">
+      <c r="B67" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C67" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="D67" s="23"/>
+      <c r="E67" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="67" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B67" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C67" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="D67" s="27"/>
-      <c r="E67" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F67" s="26"/>
-      <c r="G67" s="26"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="23"/>
     </row>
     <row r="68" spans="2:9">
       <c r="B68" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C68" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="D68" s="26"/>
+        <v>6</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E68" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F68" s="26"/>
-      <c r="G68" s="26"/>
+        <v>9</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="69" spans="2:9">
-      <c r="B69" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>11</v>
+      <c r="B69" s="1">
+        <v>1</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="70" spans="2:9">
       <c r="B70" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="71" spans="2:9">
-      <c r="B71" s="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B72" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C72" s="22" t="s">
+        <v>541</v>
+      </c>
+      <c r="D72" s="22"/>
+      <c r="E72" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F72" s="23"/>
+      <c r="G72" s="23"/>
+    </row>
+    <row r="73" spans="2:9">
+      <c r="B73" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="73" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B73" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C73" s="27" t="s">
-        <v>547</v>
-      </c>
-      <c r="D73" s="27"/>
+      <c r="C73" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D73" s="23"/>
       <c r="E73" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F73" s="26"/>
-      <c r="G73" s="26"/>
+        <v>4</v>
+      </c>
+      <c r="F73" s="23"/>
+      <c r="G73" s="23"/>
     </row>
     <row r="74" spans="2:9">
       <c r="B74" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C74" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9">
+      <c r="B75" s="1">
+        <v>1</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D74" s="26"/>
-      <c r="E74" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F74" s="26"/>
-      <c r="G74" s="26"/>
-    </row>
-    <row r="75" spans="2:9">
-      <c r="B75" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>11</v>
+      <c r="D75" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="76" spans="2:9">
       <c r="B76" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>39</v>
+        <v>102</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76" s="1" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
     </row>
     <row r="77" spans="2:9">
       <c r="B77" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>105</v>
@@ -4784,130 +4806,130 @@
         <v>106</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F77" s="1"/>
-      <c r="G77" s="1" t="s">
-        <v>107</v>
-      </c>
+      <c r="G77" s="1"/>
     </row>
     <row r="78" spans="2:9">
       <c r="B78" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C78" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="E78" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-    </row>
-    <row r="79" spans="2:9">
-      <c r="B79" s="1">
-        <v>4</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1" t="s">
-        <v>112</v>
-      </c>
+    </row>
+    <row r="79" spans="2:9" s="5" customFormat="1">
+      <c r="B79" s="4">
+        <v>5</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="I79"/>
     </row>
     <row r="80" spans="2:9" s="5" customFormat="1">
       <c r="B80" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="4" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="I80"/>
     </row>
     <row r="81" spans="2:9" s="5" customFormat="1">
       <c r="B81" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>539</v>
+        <v>233</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="4" t="s">
-        <v>550</v>
-      </c>
-      <c r="I81"/>
+        <v>545</v>
+      </c>
+      <c r="I81" s="11" t="s">
+        <v>599</v>
+      </c>
     </row>
     <row r="82" spans="2:9" s="5" customFormat="1">
       <c r="B82" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="4" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="I82" s="11" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="83" spans="2:9" s="5" customFormat="1">
-      <c r="B83" s="4">
-        <v>8</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="F83" s="4"/>
-      <c r="G83" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="I83" s="11" t="s">
-        <v>605</v>
+        <v>599</v>
+      </c>
+    </row>
+    <row r="83" spans="2:9">
+      <c r="B83" s="1">
+        <v>9</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="84" spans="2:9">
       <c r="B84" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>113</v>
@@ -4916,7 +4938,7 @@
         <v>114</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="F84" s="1"/>
       <c r="G84" s="1" t="s">
@@ -4925,7 +4947,7 @@
     </row>
     <row r="85" spans="2:9">
       <c r="B85" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>116</v>
@@ -4934,769 +4956,769 @@
         <v>117</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="F85" s="1"/>
-      <c r="G85" s="1" t="s">
-        <v>118</v>
+      <c r="G85" s="1"/>
+      <c r="I85" s="10" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="86" spans="2:9">
       <c r="B86" s="1">
+        <v>12</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" s="5" customFormat="1">
+      <c r="B87" s="4">
+        <v>13</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+    </row>
+    <row r="89" spans="2:9" s="5" customFormat="1" ht="16.5" customHeight="1">
+      <c r="B89" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C89" s="24" t="s">
+        <v>542</v>
+      </c>
+      <c r="D89" s="24"/>
+      <c r="E89" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F89" s="25"/>
+      <c r="G89" s="25"/>
+      <c r="I89"/>
+    </row>
+    <row r="90" spans="2:9" s="5" customFormat="1">
+      <c r="B90" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C90" s="25" t="s">
+        <v>536</v>
+      </c>
+      <c r="D90" s="25"/>
+      <c r="E90" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F90" s="24" t="s">
+        <v>540</v>
+      </c>
+      <c r="G90" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="I90"/>
+    </row>
+    <row r="91" spans="2:9" s="5" customFormat="1">
+      <c r="B91" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G91" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="I86" s="10" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="87" spans="2:9">
-      <c r="B87" s="1">
-        <v>12</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D87" s="1" t="s">
+      <c r="I91"/>
+    </row>
+    <row r="92" spans="2:9" s="5" customFormat="1">
+      <c r="B92" s="4">
+        <v>1</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="88" spans="2:9" s="25" customFormat="1">
-      <c r="B88" s="24">
+      <c r="E92" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C88" s="24" t="s">
-        <v>639</v>
-      </c>
-      <c r="D88" s="24" t="s">
-        <v>640</v>
-      </c>
-      <c r="E88" s="24" t="s">
-        <v>641</v>
-      </c>
-      <c r="F88" s="24"/>
-      <c r="G88" s="24"/>
-    </row>
-    <row r="89" spans="2:9" s="10" customFormat="1">
-      <c r="B89" s="20">
+      <c r="F92" s="4"/>
+      <c r="G92" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I92"/>
+    </row>
+    <row r="93" spans="2:9" s="5" customFormat="1">
+      <c r="B93" s="4">
+        <v>2</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E93" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C89" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="D89" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="E89" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="F89" s="20"/>
-      <c r="G89" s="20"/>
-      <c r="I89" s="10" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="91" spans="2:9" s="5" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B91" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C91" s="28" t="s">
-        <v>548</v>
-      </c>
-      <c r="D91" s="28"/>
-      <c r="E91" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F91" s="29"/>
-      <c r="G91" s="29"/>
-      <c r="I91"/>
-    </row>
-    <row r="92" spans="2:9" s="5" customFormat="1">
-      <c r="B92" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C92" s="29" t="s">
-        <v>542</v>
-      </c>
-      <c r="D92" s="29"/>
-      <c r="E92" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F92" s="28" t="s">
-        <v>546</v>
-      </c>
-      <c r="G92" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="I92"/>
-    </row>
-    <row r="93" spans="2:9" s="5" customFormat="1">
-      <c r="B93" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>11</v>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="I93"/>
     </row>
     <row r="94" spans="2:9" s="5" customFormat="1">
       <c r="B94" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>127</v>
+        <v>538</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F94" s="4"/>
       <c r="G94" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="I94"/>
+    </row>
+    <row r="96" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B96" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C96" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="D96" s="22"/>
+      <c r="E96" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F96" s="23"/>
+      <c r="G96" s="23"/>
+    </row>
+    <row r="97" spans="2:9">
+      <c r="B97" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C97" s="23" t="s">
+        <v>598</v>
+      </c>
+      <c r="D97" s="23"/>
+      <c r="E97" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F97" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="G97" s="23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="98" spans="2:9">
+      <c r="B98" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="2:9">
+      <c r="B99" s="1">
+        <v>1</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I94"/>
-    </row>
-    <row r="95" spans="2:9" s="5" customFormat="1">
-      <c r="B95" s="4">
+    </row>
+    <row r="100" spans="2:9">
+      <c r="B100" s="1">
         <v>2</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C100" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D95" s="4" t="s">
+      <c r="D100" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E95" s="4" t="s">
+      <c r="E100" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4" t="s">
+      <c r="F100" s="1"/>
+      <c r="G100" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="I95"/>
-    </row>
-    <row r="96" spans="2:9" s="5" customFormat="1">
-      <c r="B96" s="4">
-        <v>3</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>543</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="I96"/>
-    </row>
-    <row r="98" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B98" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C98" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="D98" s="27"/>
-      <c r="E98" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F98" s="26"/>
-      <c r="G98" s="26"/>
-    </row>
-    <row r="99" spans="2:9">
-      <c r="B99" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C99" s="26" t="s">
-        <v>604</v>
-      </c>
-      <c r="D99" s="26"/>
-      <c r="E99" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F99" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="G99" s="26" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="100" spans="2:9">
-      <c r="B100" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="101" spans="2:9">
       <c r="B101" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>604</v>
+        <v>42</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>127</v>
+        <v>43</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F101" s="1"/>
       <c r="G101" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="102" spans="2:9">
       <c r="B102" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>13</v>
+        <v>233</v>
       </c>
       <c r="F102" s="1"/>
-      <c r="G102" s="1" t="s">
-        <v>41</v>
+      <c r="G102" s="1"/>
+      <c r="I102" s="10" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="103" spans="2:9">
       <c r="B103" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="E103" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="I103" s="10" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="105" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B105" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C105" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D105" s="22"/>
+      <c r="E105" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F105" s="23"/>
+      <c r="G105" s="23"/>
+    </row>
+    <row r="106" spans="2:9">
+      <c r="B106" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C106" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D106" s="23"/>
+      <c r="E106" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F106" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="G106" s="23"/>
+    </row>
+    <row r="107" spans="2:9">
+      <c r="B107" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="2:9">
+      <c r="B108" s="1">
+        <v>1</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E108" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F103" s="1"/>
-      <c r="G103" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="104" spans="2:9">
-      <c r="B104" s="1">
-        <v>4</v>
-      </c>
-      <c r="C104" s="1" t="s">
+      <c r="F108" s="1"/>
+      <c r="G108" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="109" spans="2:9">
+      <c r="B109" s="1">
+        <v>2</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F109" s="1"/>
+      <c r="G109" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F104" s="1"/>
-      <c r="G104" s="1"/>
-      <c r="I104" s="10" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="105" spans="2:9">
-      <c r="B105" s="1">
-        <v>5</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F105" s="1"/>
-      <c r="G105" s="1"/>
-      <c r="I105" s="10" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="107" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B107" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C107" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="D107" s="27"/>
-      <c r="E107" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F107" s="26"/>
-      <c r="G107" s="26"/>
-    </row>
-    <row r="108" spans="2:9">
-      <c r="B108" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C108" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="D108" s="26"/>
-      <c r="E108" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F108" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="G108" s="26"/>
-    </row>
-    <row r="109" spans="2:9">
-      <c r="B109" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="110" spans="2:9">
       <c r="B110" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="F110" s="1"/>
       <c r="G110" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="112" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B112" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C112" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="D112" s="24"/>
+      <c r="E112" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F112" s="25"/>
+      <c r="G112" s="25"/>
+    </row>
+    <row r="113" spans="2:9">
+      <c r="B113" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C113" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="D113" s="25"/>
+      <c r="E113" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F113" s="24" t="s">
+        <v>560</v>
+      </c>
+      <c r="G113" s="25" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="114" spans="2:9">
+      <c r="B114" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" spans="2:9">
+      <c r="B115" s="4">
+        <v>1</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F115" s="4"/>
+      <c r="G115" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="111" spans="2:9">
-      <c r="B111" s="1">
+    <row r="116" spans="2:9" s="5" customFormat="1">
+      <c r="B116" s="4">
         <v>2</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E111" s="1" t="s">
+      <c r="C116" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="E116" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F111" s="1"/>
-      <c r="G111" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="112" spans="2:9">
-      <c r="B112" s="1">
-        <v>3</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F112" s="1"/>
-      <c r="G112" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="114" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B114" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C114" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="D114" s="28"/>
-      <c r="E114" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F114" s="29"/>
-      <c r="G114" s="29"/>
-    </row>
-    <row r="115" spans="2:9">
-      <c r="B115" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C115" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="D115" s="29"/>
-      <c r="E115" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F115" s="28" t="s">
-        <v>566</v>
-      </c>
-      <c r="G115" s="29" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="116" spans="2:9">
-      <c r="B116" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G116" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="F116" s="4"/>
+      <c r="G116" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="I116"/>
     </row>
     <row r="117" spans="2:9">
       <c r="B117" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>140</v>
+        <v>509</v>
       </c>
       <c r="E117" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F117" s="4"/>
       <c r="G117" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="118" spans="2:9" s="5" customFormat="1">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="118" spans="2:9">
       <c r="B118" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>513</v>
+        <v>137</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>514</v>
+        <v>138</v>
       </c>
       <c r="E118" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F118" s="4"/>
       <c r="G118" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="I118"/>
+        <v>514</v>
+      </c>
     </row>
     <row r="119" spans="2:9">
       <c r="B119" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>515</v>
+        <v>46</v>
       </c>
       <c r="E119" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F119" s="4"/>
       <c r="G119" s="4" t="s">
-        <v>141</v>
+        <v>513</v>
       </c>
     </row>
     <row r="120" spans="2:9">
       <c r="B120" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E120" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F120" s="4"/>
       <c r="G120" s="4" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="121" spans="2:9">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="121" spans="2:9" s="5" customFormat="1">
       <c r="B121" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>45</v>
+        <v>510</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>46</v>
+        <v>511</v>
       </c>
       <c r="E121" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F121" s="4"/>
       <c r="G121" s="4" t="s">
-        <v>519</v>
-      </c>
+        <v>515</v>
+      </c>
+      <c r="I121"/>
     </row>
     <row r="122" spans="2:9">
       <c r="B122" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="F122" s="4"/>
       <c r="G122" s="4" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="123" spans="2:9" s="5" customFormat="1">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="123" spans="2:9">
       <c r="B123" s="4">
+        <v>9</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F123" s="4"/>
+      <c r="G123" s="4"/>
+      <c r="I123" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="125" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B125" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C125" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="D125" s="22"/>
+      <c r="E125" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F125" s="23"/>
+      <c r="G125" s="23"/>
+    </row>
+    <row r="126" spans="2:9">
+      <c r="B126" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C126" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="D126" s="23"/>
+      <c r="E126" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F126" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="G126" s="23"/>
+    </row>
+    <row r="127" spans="2:9">
+      <c r="B127" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C123" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="E123" s="4" t="s">
+      <c r="D127" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="2:9">
+      <c r="B128" s="1">
+        <v>1</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E128" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F123" s="4"/>
-      <c r="G123" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="I123"/>
-    </row>
-    <row r="124" spans="2:9">
-      <c r="B124" s="4">
-        <v>8</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="E124" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="F124" s="4"/>
-      <c r="G124" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="125" spans="2:9">
-      <c r="B125" s="4">
-        <v>9</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D125" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E125" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="F125" s="4"/>
-      <c r="G125" s="4"/>
-      <c r="I125" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="127" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B127" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C127" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="D127" s="27"/>
-      <c r="E127" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F127" s="26"/>
-      <c r="G127" s="26"/>
-    </row>
-    <row r="128" spans="2:9">
-      <c r="B128" s="2" t="s">
+      <c r="F128" s="1"/>
+      <c r="G128" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="129" spans="2:9">
+      <c r="B129" s="1">
         <v>2</v>
       </c>
-      <c r="C128" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="D128" s="26"/>
-      <c r="E128" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F128" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="G128" s="26"/>
-    </row>
-    <row r="129" spans="2:9">
-      <c r="B129" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G129" s="2" t="s">
-        <v>11</v>
+      <c r="C129" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="130" spans="2:9">
       <c r="B130" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F130" s="1"/>
       <c r="G130" s="1" t="s">
-        <v>14</v>
+        <v>149</v>
       </c>
     </row>
     <row r="131" spans="2:9">
       <c r="B131" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>38</v>
+        <v>151</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="F131" s="1"/>
       <c r="G131" s="1" t="s">
-        <v>92</v>
+        <v>152</v>
       </c>
     </row>
     <row r="132" spans="2:9">
       <c r="B132" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="F132" s="1"/>
-      <c r="G132" s="1" t="s">
-        <v>154</v>
+      <c r="G132" s="1"/>
+      <c r="I132" s="12" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="133" spans="2:9">
       <c r="B133" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>155</v>
@@ -5705,184 +5727,181 @@
         <v>156</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F133" s="1"/>
-      <c r="G133" s="1" t="s">
-        <v>157</v>
-      </c>
+      <c r="G133" s="1"/>
+      <c r="I133" s="12"/>
     </row>
     <row r="134" spans="2:9">
       <c r="B134" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C134" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D134" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="E134" s="1" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
-      <c r="I134" s="12" t="s">
-        <v>609</v>
-      </c>
+      <c r="I134" s="12"/>
     </row>
     <row r="135" spans="2:9">
       <c r="B135" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C135" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F135" s="1"/>
+      <c r="G135" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D135" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F135" s="1"/>
-      <c r="G135" s="1"/>
       <c r="I135" s="12"/>
     </row>
     <row r="136" spans="2:9">
       <c r="B136" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>162</v>
+        <v>28</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>163</v>
+        <v>29</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F136" s="1"/>
       <c r="G136" s="1"/>
-      <c r="I136" s="12"/>
-    </row>
-    <row r="137" spans="2:9">
-      <c r="B137" s="1">
+      <c r="I136" s="12" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="138" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B138" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C138" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="D138" s="22"/>
+      <c r="E138" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F138" s="23"/>
+      <c r="G138" s="23"/>
+    </row>
+    <row r="139" spans="2:9">
+      <c r="B139" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C139" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="D139" s="23"/>
+      <c r="E139" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F139" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="G139" s="23"/>
+    </row>
+    <row r="140" spans="2:9">
+      <c r="B140" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D140" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D137" s="1" t="s">
+      <c r="E140" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="2:9">
+      <c r="B141" s="1">
+        <v>1</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E137" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F137" s="1"/>
-      <c r="G137" s="1" t="s">
+      <c r="E141" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F141" s="1"/>
+      <c r="G141" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="142" spans="2:9">
+      <c r="B142" s="1">
+        <v>2</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F142" s="1"/>
+      <c r="G142" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="I137" s="12"/>
-    </row>
-    <row r="138" spans="2:9">
-      <c r="B138" s="1">
-        <v>9</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F138" s="1"/>
-      <c r="G138" s="1"/>
-      <c r="I138" s="12" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="140" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B140" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C140" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="D140" s="27"/>
-      <c r="E140" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F140" s="26"/>
-      <c r="G140" s="26"/>
-    </row>
-    <row r="141" spans="2:9">
-      <c r="B141" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C141" s="26" t="s">
-        <v>167</v>
-      </c>
-      <c r="D141" s="26"/>
-      <c r="E141" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F141" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="G141" s="26"/>
-    </row>
-    <row r="142" spans="2:9">
-      <c r="B142" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G142" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="143" spans="2:9">
       <c r="B143" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C143" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D143" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E143" s="1" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="F143" s="1"/>
-      <c r="G143" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="G143" s="1"/>
     </row>
     <row r="144" spans="2:9">
       <c r="B144" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="F144" s="1"/>
       <c r="G144" s="1" t="s">
@@ -5891,7 +5910,7 @@
     </row>
     <row r="145" spans="2:9">
       <c r="B145" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>171</v>
@@ -5900,32 +5919,32 @@
         <v>172</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F145" s="1"/>
-      <c r="G145" s="1"/>
+      <c r="G145" s="1" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="146" spans="2:9">
       <c r="B146" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F146" s="1"/>
-      <c r="G146" s="1" t="s">
-        <v>175</v>
-      </c>
+      <c r="G146" s="1"/>
     </row>
     <row r="147" spans="2:9">
       <c r="B147" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>176</v>
@@ -5934,379 +5953,381 @@
         <v>177</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F147" s="1"/>
-      <c r="G147" s="1" t="s">
-        <v>178</v>
-      </c>
+      <c r="G147" s="1"/>
     </row>
     <row r="148" spans="2:9">
       <c r="B148" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>179</v>
+        <v>28</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>180</v>
+        <v>29</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F148" s="1"/>
       <c r="G148" s="1"/>
-    </row>
-    <row r="149" spans="2:9">
-      <c r="B149" s="1">
+      <c r="I148" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="150" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B150" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C150" s="22" t="s">
+        <v>581</v>
+      </c>
+      <c r="D150" s="22"/>
+      <c r="E150" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F150" s="23"/>
+      <c r="G150" s="23"/>
+    </row>
+    <row r="151" spans="2:9">
+      <c r="B151" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C151" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="D151" s="23"/>
+      <c r="E151" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F151" s="22" t="s">
+        <v>559</v>
+      </c>
+      <c r="G151" s="23" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="152" spans="2:9">
+      <c r="B152" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C149" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F149" s="1"/>
-      <c r="G149" s="1"/>
-    </row>
-    <row r="150" spans="2:9">
-      <c r="B150" s="1">
+      <c r="D152" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F150" s="1"/>
-      <c r="G150" s="1"/>
-      <c r="I150" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="152" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B152" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C152" s="27" t="s">
-        <v>587</v>
-      </c>
-      <c r="D152" s="27"/>
       <c r="E152" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="2:9">
+      <c r="B153" s="1">
         <v>1</v>
       </c>
-      <c r="F152" s="26"/>
-      <c r="G152" s="26"/>
-    </row>
-    <row r="153" spans="2:9">
-      <c r="B153" s="2" t="s">
+      <c r="C153" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F153" s="1"/>
+      <c r="G153" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="154" spans="2:9">
+      <c r="B154" s="1">
         <v>2</v>
       </c>
-      <c r="C153" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="D153" s="26"/>
-      <c r="E153" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F153" s="27" t="s">
-        <v>565</v>
-      </c>
-      <c r="G153" s="26" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="154" spans="2:9">
-      <c r="B154" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G154" s="2" t="s">
-        <v>11</v>
+      <c r="C154" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F154" s="1"/>
+      <c r="G154" s="1" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="155" spans="2:9">
       <c r="B155" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F155" s="1"/>
       <c r="G155" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="156" spans="2:9">
       <c r="B156" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F156" s="1"/>
       <c r="G156" s="1" t="s">
-        <v>192</v>
+        <v>34</v>
       </c>
     </row>
     <row r="157" spans="2:9">
       <c r="B157" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>184</v>
+        <v>45</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>193</v>
+        <v>46</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F157" s="1"/>
       <c r="G157" s="1" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="158" spans="2:9">
       <c r="B158" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="F158" s="1"/>
       <c r="G158" s="1" t="s">
-        <v>34</v>
+        <v>193</v>
       </c>
     </row>
     <row r="159" spans="2:9">
       <c r="B159" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>45</v>
+        <v>194</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>46</v>
+        <v>195</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F159" s="1"/>
       <c r="G159" s="1" t="s">
-        <v>47</v>
+        <v>196</v>
       </c>
     </row>
     <row r="160" spans="2:9">
       <c r="B160" s="1">
+        <v>8</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1"/>
+      <c r="I160" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="162" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B162" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C162" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="D162" s="22"/>
+      <c r="E162" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F162" s="23"/>
+      <c r="G162" s="23"/>
+    </row>
+    <row r="163" spans="2:9">
+      <c r="B163" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C163" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D163" s="23"/>
+      <c r="E163" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F163" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="G163" s="23" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="164" spans="2:9">
+      <c r="B164" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="F160" s="1"/>
-      <c r="G160" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="161" spans="2:9">
-      <c r="B161" s="1">
+      <c r="C164" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C161" s="1" t="s">
+      <c r="D164" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="2:9">
+      <c r="B165" s="1">
+        <v>1</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F165" s="1"/>
+      <c r="G165" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="166" spans="2:9">
+      <c r="B166" s="1">
+        <v>2</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F166" s="1"/>
+      <c r="G166" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F161" s="1"/>
-      <c r="G161" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="162" spans="2:9">
-      <c r="B162" s="1">
-        <v>8</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F162" s="1"/>
-      <c r="G162" s="1"/>
-      <c r="I162" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="164" spans="2:9" ht="16.5" customHeight="1">
-      <c r="B164" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C164" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="D164" s="27"/>
-      <c r="E164" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F164" s="26"/>
-      <c r="G164" s="26"/>
-    </row>
-    <row r="165" spans="2:9">
-      <c r="B165" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C165" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="D165" s="26"/>
-      <c r="E165" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F165" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="G165" s="26" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="166" spans="2:9">
-      <c r="B166" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F166" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G166" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="167" spans="2:9">
       <c r="B167" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>45</v>
+        <v>179</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>46</v>
+        <v>188</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F167" s="1"/>
       <c r="G167" s="1" t="s">
-        <v>14</v>
+        <v>180</v>
       </c>
     </row>
     <row r="168" spans="2:9">
       <c r="B168" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>3</v>
+        <v>181</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>12</v>
+        <v>200</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="F168" s="1"/>
       <c r="G168" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="169" spans="2:9">
       <c r="B169" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="F169" s="1"/>
       <c r="G169" s="1" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
     </row>
     <row r="170" spans="2:9">
       <c r="B170" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>205</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="F170" s="1"/>
       <c r="G170" s="1" t="s">
@@ -6315,34 +6336,34 @@
     </row>
     <row r="171" spans="2:9">
       <c r="B171" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>110</v>
+        <v>207</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="F171" s="1"/>
       <c r="G171" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="172" spans="2:9">
       <c r="B172" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>209</v>
+        <v>64</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>210</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="F172" s="1"/>
       <c r="G172" s="1" t="s">
@@ -6351,227 +6372,228 @@
     </row>
     <row r="173" spans="2:9">
       <c r="B173" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>212</v>
+        <v>28</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>213</v>
+        <v>29</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>20</v>
+        <v>563</v>
       </c>
       <c r="F173" s="1"/>
-      <c r="G173" s="1" t="s">
-        <v>214</v>
+      <c r="G173" s="1"/>
+      <c r="I173" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="174" spans="2:9">
       <c r="B174" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>215</v>
+        <v>33</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F174" s="1"/>
-      <c r="G174" s="1" t="s">
-        <v>216</v>
+      <c r="G174" s="1"/>
+      <c r="I174" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="175" spans="2:9">
       <c r="B175" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>28</v>
+        <v>652</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>29</v>
+        <v>654</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>569</v>
+        <v>653</v>
       </c>
       <c r="F175" s="1"/>
       <c r="G175" s="1"/>
       <c r="I175" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="176" spans="2:9">
-      <c r="B176" s="1">
-        <v>10</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F176" s="1"/>
-      <c r="G176" s="1"/>
-      <c r="I176" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="178" spans="2:7" ht="16.5" customHeight="1">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="177" spans="2:7" ht="16.5" customHeight="1">
+      <c r="B177" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C177" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="D177" s="22"/>
+      <c r="E177" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F177" s="23"/>
+      <c r="G177" s="23"/>
+    </row>
+    <row r="178" spans="2:7">
       <c r="B178" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C178" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="D178" s="27"/>
+        <v>2</v>
+      </c>
+      <c r="C178" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="D178" s="23"/>
       <c r="E178" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F178" s="26"/>
-      <c r="G178" s="26"/>
+        <v>4</v>
+      </c>
+      <c r="F178" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="G178" s="23"/>
     </row>
     <row r="179" spans="2:7">
       <c r="B179" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C179" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="D179" s="26"/>
+        <v>6</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="E179" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F179" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="G179" s="26"/>
+        <v>9</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="180" spans="2:7">
-      <c r="B180" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E180" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F180" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G180" s="2" t="s">
-        <v>11</v>
+      <c r="B180" s="1">
+        <v>1</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F180" s="1"/>
+      <c r="G180" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="181" spans="2:7">
       <c r="B181" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>218</v>
+        <v>45</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>220</v>
+        <v>46</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F181" s="1"/>
       <c r="G181" s="1" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
     <row r="182" spans="2:7">
       <c r="B182" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>46</v>
+        <v>217</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="F182" s="1"/>
       <c r="G182" s="1" t="s">
-        <v>47</v>
+        <v>218</v>
       </c>
     </row>
     <row r="183" spans="2:7">
       <c r="B183" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="F183" s="1"/>
       <c r="G183" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="184" spans="2:7">
       <c r="B184" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>224</v>
+        <v>655</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>225</v>
+        <v>656</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>13</v>
+        <v>657</v>
       </c>
       <c r="F184" s="1"/>
       <c r="G184" s="1" t="s">
-        <v>226</v>
+        <v>658</v>
       </c>
     </row>
     <row r="186" spans="2:7" ht="16.5" customHeight="1">
       <c r="B186" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C186" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="D186" s="27"/>
+      <c r="C186" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="D186" s="22"/>
       <c r="E186" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F186" s="26"/>
-      <c r="G186" s="26"/>
+      <c r="F186" s="23"/>
+      <c r="G186" s="23"/>
     </row>
     <row r="187" spans="2:7">
       <c r="B187" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C187" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="D187" s="26"/>
+      <c r="C187" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="D187" s="23"/>
       <c r="E187" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F187" s="26"/>
-      <c r="G187" s="26"/>
+      <c r="F187" s="23"/>
+      <c r="G187" s="23"/>
     </row>
     <row r="188" spans="2:7">
       <c r="B188" s="2" t="s">
@@ -6598,17 +6620,17 @@
         <v>1</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F189" s="1"/>
       <c r="G189" s="1" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
     </row>
     <row r="190" spans="2:7">
@@ -6616,19 +6638,19 @@
         <v>2</v>
       </c>
       <c r="C190" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E190" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="F190" s="1">
         <v>50</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="191" spans="2:7">
@@ -6636,19 +6658,19 @@
         <v>3</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F191" s="1">
         <v>100</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="192" spans="2:7">
@@ -6656,13 +6678,13 @@
         <v>4</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F192" s="1">
         <v>500</v>
@@ -6680,11 +6702,11 @@
         <v>29</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F193" s="1"/>
       <c r="G193" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="I193" s="6">
         <v>45292</v>
@@ -6701,11 +6723,11 @@
         <v>32</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F194" s="1"/>
       <c r="G194" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="I194" s="6">
         <v>45292</v>
@@ -6715,29 +6737,29 @@
       <c r="B196" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C196" s="27" t="s">
-        <v>575</v>
-      </c>
-      <c r="D196" s="27"/>
+      <c r="C196" s="22" t="s">
+        <v>569</v>
+      </c>
+      <c r="D196" s="22"/>
       <c r="E196" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F196" s="26"/>
-      <c r="G196" s="26"/>
+      <c r="F196" s="23"/>
+      <c r="G196" s="23"/>
     </row>
     <row r="197" spans="2:9">
       <c r="B197" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C197" s="26" t="s">
-        <v>574</v>
-      </c>
-      <c r="D197" s="26"/>
+      <c r="C197" s="23" t="s">
+        <v>568</v>
+      </c>
+      <c r="D197" s="23"/>
       <c r="E197" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F197" s="26"/>
-      <c r="G197" s="26"/>
+      <c r="F197" s="23"/>
+      <c r="G197" s="23"/>
     </row>
     <row r="198" spans="2:9">
       <c r="B198" s="2" t="s">
@@ -6764,17 +6786,17 @@
         <v>1</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F199" s="1"/>
       <c r="G199" s="1" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
     </row>
     <row r="200" spans="2:9">
@@ -6782,19 +6804,19 @@
         <v>2</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F200" s="1">
         <v>100</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="201" spans="2:9">
@@ -6802,19 +6824,19 @@
         <v>3</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F201" s="1">
         <v>200</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="202" spans="2:9">
@@ -6822,19 +6844,19 @@
         <v>4</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F202" s="1">
         <v>50</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="203" spans="2:9">
@@ -6842,19 +6864,19 @@
         <v>5</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F203" s="1">
         <v>50</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="204" spans="2:9">
@@ -6862,13 +6884,13 @@
         <v>6</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F204" s="1">
         <v>500</v>
@@ -6886,11 +6908,11 @@
         <v>29</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F205" s="1"/>
       <c r="G205" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="I205" s="6">
         <v>45292</v>
@@ -6907,11 +6929,11 @@
         <v>32</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F206" s="1"/>
       <c r="G206" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="I206" s="6">
         <v>45292</v>
@@ -6921,32 +6943,32 @@
       <c r="B208" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C208" s="27" t="s">
-        <v>251</v>
-      </c>
-      <c r="D208" s="27"/>
+      <c r="C208" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="D208" s="22"/>
       <c r="E208" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F208" s="26"/>
-      <c r="G208" s="26"/>
+      <c r="F208" s="23"/>
+      <c r="G208" s="23"/>
     </row>
     <row r="209" spans="2:9">
       <c r="B209" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C209" s="26" t="s">
-        <v>511</v>
-      </c>
-      <c r="D209" s="26"/>
+      <c r="C209" s="23" t="s">
+        <v>505</v>
+      </c>
+      <c r="D209" s="23"/>
       <c r="E209" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F209" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="G209" s="26" t="s">
-        <v>253</v>
+      <c r="F209" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="G209" s="23" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="210" spans="2:9">
@@ -6974,17 +6996,17 @@
         <v>1</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F211" s="1"/>
       <c r="G211" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="212" spans="2:9">
@@ -6992,17 +7014,17 @@
         <v>2</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F212" s="1"/>
       <c r="G212" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="213" spans="2:9">
@@ -7010,17 +7032,17 @@
         <v>3</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F213" s="1"/>
       <c r="G213" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="214" spans="2:9">
@@ -7028,17 +7050,17 @@
         <v>4</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F214" s="1"/>
       <c r="G214" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="215" spans="2:9">
@@ -7052,11 +7074,11 @@
         <v>29</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F215" s="1"/>
       <c r="G215" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="I215" s="6">
         <v>45292.000694444447</v>
@@ -7066,32 +7088,32 @@
       <c r="B217" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C217" s="27" t="s">
-        <v>512</v>
-      </c>
-      <c r="D217" s="27"/>
+      <c r="C217" s="22" t="s">
+        <v>506</v>
+      </c>
+      <c r="D217" s="22"/>
       <c r="E217" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F217" s="26"/>
-      <c r="G217" s="26"/>
+      <c r="F217" s="23"/>
+      <c r="G217" s="23"/>
     </row>
     <row r="218" spans="2:9">
       <c r="B218" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C218" s="26" t="s">
-        <v>535</v>
-      </c>
-      <c r="D218" s="26"/>
+      <c r="C218" s="23" t="s">
+        <v>529</v>
+      </c>
+      <c r="D218" s="23"/>
       <c r="E218" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F218" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="G218" s="26" t="s">
-        <v>265</v>
+      <c r="F218" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="G218" s="23" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="219" spans="2:9">
@@ -7119,10 +7141,10 @@
         <v>1</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>13</v>
@@ -7155,17 +7177,17 @@
         <v>3</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F222" s="1"/>
       <c r="G222" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="223" spans="2:9">
@@ -7179,45 +7201,45 @@
         <v>29</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F223" s="1"/>
       <c r="G223" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="I223" s="6" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
     </row>
     <row r="225" spans="2:9" s="19" customFormat="1" ht="16.5" customHeight="1">
       <c r="B225" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C225" s="30" t="s">
-        <v>623</v>
-      </c>
-      <c r="D225" s="30"/>
+      <c r="C225" s="26" t="s">
+        <v>617</v>
+      </c>
+      <c r="D225" s="26"/>
       <c r="E225" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="F225" s="31"/>
-      <c r="G225" s="31"/>
+      <c r="F225" s="27"/>
+      <c r="G225" s="27"/>
     </row>
     <row r="226" spans="2:9">
       <c r="B226" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C226" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="D226" s="26"/>
+      <c r="C226" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="D226" s="23"/>
       <c r="E226" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F226" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="G226" s="26"/>
+      <c r="F226" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="G226" s="23"/>
     </row>
     <row r="227" spans="2:9">
       <c r="B227" s="2" t="s">
@@ -7244,10 +7266,10 @@
         <v>1</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>13</v>
@@ -7262,10 +7284,10 @@
         <v>2</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>13</v>
@@ -7280,13 +7302,13 @@
         <v>3</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F230" s="1"/>
       <c r="G230" s="1"/>
@@ -7297,13 +7319,13 @@
         <v>4</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F231" s="1"/>
       <c r="G231" s="1"/>
@@ -7314,10 +7336,10 @@
         <v>5</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="E232" s="1" t="s">
         <v>20</v>
@@ -7330,10 +7352,10 @@
         <v>6</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E233" s="1" t="s">
         <v>20</v>
@@ -7346,10 +7368,10 @@
         <v>7</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>20</v>
@@ -7362,13 +7384,13 @@
         <v>8</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F235" s="1"/>
       <c r="G235" s="1"/>
@@ -7382,10 +7404,10 @@
         <v>64</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F236" s="1"/>
       <c r="G236" s="1"/>
@@ -7401,7 +7423,7 @@
         <v>29</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F237" s="1"/>
       <c r="G237" s="1"/>
@@ -7411,32 +7433,32 @@
       <c r="B239" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C239" s="30" t="s">
-        <v>630</v>
-      </c>
-      <c r="D239" s="30"/>
+      <c r="C239" s="26" t="s">
+        <v>624</v>
+      </c>
+      <c r="D239" s="26"/>
       <c r="E239" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="F239" s="31"/>
-      <c r="G239" s="31"/>
+      <c r="F239" s="27"/>
+      <c r="G239" s="27"/>
     </row>
     <row r="240" spans="2:9">
       <c r="B240" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C240" s="26" t="s">
-        <v>629</v>
-      </c>
-      <c r="D240" s="26"/>
+      <c r="C240" s="23" t="s">
+        <v>623</v>
+      </c>
+      <c r="D240" s="23"/>
       <c r="E240" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F240" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="G240" s="26" t="s">
-        <v>139</v>
+      <c r="F240" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="G240" s="23" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="241" spans="2:7">
@@ -7464,10 +7486,10 @@
         <v>1</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>13</v>
@@ -7482,17 +7504,17 @@
         <v>2</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F243" s="1"/>
       <c r="G243" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="244" spans="2:7">
@@ -7510,7 +7532,7 @@
       </c>
       <c r="F244" s="1"/>
       <c r="G244" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="245" spans="2:7">
@@ -7518,13 +7540,13 @@
         <v>4</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F245" s="1"/>
       <c r="G245" s="1"/>
@@ -7534,10 +7556,10 @@
         <v>5</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>20</v>
@@ -7550,10 +7572,10 @@
         <v>6</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="E247" s="1" t="s">
         <v>20</v>
@@ -7566,10 +7588,10 @@
         <v>7</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E248" s="1" t="s">
         <v>20</v>
@@ -7582,10 +7604,10 @@
         <v>8</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="E249" s="1" t="s">
         <v>20</v>
@@ -7597,29 +7619,29 @@
       <c r="B251" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C251" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="D251" s="27"/>
+      <c r="C251" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="D251" s="22"/>
       <c r="E251" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F251" s="26"/>
-      <c r="G251" s="26"/>
+      <c r="F251" s="23"/>
+      <c r="G251" s="23"/>
     </row>
     <row r="252" spans="2:7">
       <c r="B252" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C252" s="26" t="s">
-        <v>285</v>
-      </c>
-      <c r="D252" s="26"/>
+      <c r="C252" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="D252" s="23"/>
       <c r="E252" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F252" s="26"/>
-      <c r="G252" s="26"/>
+      <c r="F252" s="23"/>
+      <c r="G252" s="23"/>
     </row>
     <row r="253" spans="2:7">
       <c r="B253" s="2" t="s">
@@ -7646,17 +7668,17 @@
         <v>1</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F254" s="1"/>
       <c r="G254" s="1" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
     </row>
     <row r="255" spans="2:7">
@@ -7664,17 +7686,17 @@
         <v>2</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F255" s="1"/>
       <c r="G255" s="1" t="s">
-        <v>289</v>
+        <v>659</v>
       </c>
     </row>
     <row r="256" spans="2:7">
@@ -7682,17 +7704,17 @@
         <v>3</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F256" s="1"/>
       <c r="G256" s="1" t="s">
-        <v>154</v>
+        <v>660</v>
       </c>
     </row>
     <row r="257" spans="2:9">
@@ -7700,64 +7722,72 @@
         <v>4</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F257" s="1"/>
-      <c r="G257" s="1"/>
+      <c r="G257" s="1" t="s">
+        <v>661</v>
+      </c>
     </row>
     <row r="258" spans="2:9">
       <c r="B258" s="1">
         <v>5</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F258" s="1"/>
-      <c r="G258" s="1"/>
+      <c r="G258" s="1" t="s">
+        <v>661</v>
+      </c>
     </row>
     <row r="259" spans="2:9">
       <c r="B259" s="1">
         <v>6</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F259" s="1"/>
-      <c r="G259" s="1"/>
+      <c r="G259" s="1" t="s">
+        <v>661</v>
+      </c>
     </row>
     <row r="260" spans="2:9">
       <c r="B260" s="1">
         <v>7</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F260" s="1"/>
-      <c r="G260" s="1"/>
+      <c r="G260" s="1" t="s">
+        <v>661</v>
+      </c>
     </row>
     <row r="261" spans="2:9">
       <c r="B261" s="1">
@@ -7770,10 +7800,12 @@
         <v>29</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F261" s="1"/>
-      <c r="G261" s="1"/>
+      <c r="G261" s="1" t="s">
+        <v>661</v>
+      </c>
       <c r="I261" s="14">
         <v>45292</v>
       </c>
@@ -7782,32 +7814,32 @@
       <c r="B263" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C263" s="27" t="s">
-        <v>637</v>
-      </c>
-      <c r="D263" s="27"/>
+      <c r="C263" s="22" t="s">
+        <v>631</v>
+      </c>
+      <c r="D263" s="22"/>
       <c r="E263" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F263" s="26"/>
-      <c r="G263" s="26"/>
+      <c r="F263" s="23"/>
+      <c r="G263" s="23"/>
     </row>
     <row r="264" spans="2:9">
       <c r="B264" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C264" s="26" t="s">
-        <v>636</v>
-      </c>
-      <c r="D264" s="26"/>
+      <c r="C264" s="23" t="s">
+        <v>630</v>
+      </c>
+      <c r="D264" s="23"/>
       <c r="E264" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F264" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="G264" s="26" t="s">
-        <v>301</v>
+      <c r="F264" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="G264" s="23" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="265" spans="2:9">
@@ -7835,10 +7867,10 @@
         <v>1</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>13</v>
@@ -7853,10 +7885,10 @@
         <v>2</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>13</v>
@@ -7871,17 +7903,17 @@
         <v>3</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F268" s="1"/>
       <c r="G268" s="1" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="269" spans="2:9">
@@ -7889,18 +7921,18 @@
         <v>4</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F269" s="1"/>
       <c r="G269" s="1"/>
       <c r="I269" s="15" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
     </row>
     <row r="270" spans="2:9">
@@ -7908,18 +7940,18 @@
         <v>5</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F270" s="1"/>
       <c r="G270" s="1"/>
       <c r="I270" s="15" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
     </row>
     <row r="271" spans="2:9">
@@ -7927,17 +7959,17 @@
         <v>6</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F271" s="1"/>
       <c r="G271" s="1" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
     </row>
     <row r="272" spans="2:9">
@@ -7948,14 +7980,14 @@
         <v>64</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F272" s="1"/>
       <c r="G272" s="1" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="273" spans="2:9">
@@ -7969,43 +8001,43 @@
         <v>29</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F273" s="1"/>
       <c r="G273" s="1"/>
       <c r="I273" s="15" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
     </row>
     <row r="275" spans="2:9" s="19" customFormat="1" ht="16.5" customHeight="1">
       <c r="B275" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C275" s="30" t="s">
-        <v>628</v>
-      </c>
-      <c r="D275" s="30"/>
+      <c r="C275" s="26" t="s">
+        <v>622</v>
+      </c>
+      <c r="D275" s="26"/>
       <c r="E275" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="F275" s="31"/>
-      <c r="G275" s="31"/>
+      <c r="F275" s="27"/>
+      <c r="G275" s="27"/>
     </row>
     <row r="276" spans="2:9">
       <c r="B276" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C276" s="26" t="s">
-        <v>627</v>
-      </c>
-      <c r="D276" s="26"/>
+      <c r="C276" s="23" t="s">
+        <v>621</v>
+      </c>
+      <c r="D276" s="23"/>
       <c r="E276" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F276" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="G276" s="26"/>
+      <c r="F276" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="G276" s="23"/>
     </row>
     <row r="277" spans="2:9">
       <c r="B277" s="2" t="s">
@@ -8032,10 +8064,10 @@
         <v>1</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>13</v>
@@ -8050,17 +8082,17 @@
         <v>2</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F279" s="1"/>
       <c r="G279" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="280" spans="2:9" s="10" customFormat="1">
@@ -8068,18 +8100,18 @@
         <v>3</v>
       </c>
       <c r="C280" s="20" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="D280" s="20" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="E280" s="20" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F280" s="20"/>
       <c r="G280" s="20"/>
       <c r="I280" s="21" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
     </row>
     <row r="281" spans="2:9" s="10" customFormat="1">
@@ -8087,18 +8119,18 @@
         <v>4</v>
       </c>
       <c r="C281" s="20" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="D281" s="20" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="E281" s="20" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F281" s="20"/>
       <c r="G281" s="20"/>
       <c r="I281" s="21" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
     </row>
     <row r="282" spans="2:9">
@@ -8106,10 +8138,10 @@
         <v>5</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>20</v>
@@ -8122,17 +8154,17 @@
         <v>6</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F283" s="1"/>
       <c r="G283" s="1" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
     </row>
     <row r="284" spans="2:9">
@@ -8140,13 +8172,13 @@
         <v>7</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F284" s="1"/>
       <c r="G284" s="1"/>
@@ -8163,7 +8195,7 @@
         <v>29</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F285" s="1"/>
       <c r="G285" s="1"/>
@@ -8174,13 +8206,13 @@
         <v>9</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D286" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F286" s="1"/>
       <c r="G286" s="1"/>
@@ -8189,29 +8221,29 @@
       <c r="B288" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C288" s="27" t="s">
-        <v>595</v>
-      </c>
-      <c r="D288" s="27"/>
+      <c r="C288" s="22" t="s">
+        <v>589</v>
+      </c>
+      <c r="D288" s="22"/>
       <c r="E288" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F288" s="26"/>
-      <c r="G288" s="26"/>
+      <c r="F288" s="23"/>
+      <c r="G288" s="23"/>
     </row>
     <row r="289" spans="2:9">
       <c r="B289" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C289" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="D289" s="26"/>
+      <c r="C289" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="D289" s="23"/>
       <c r="E289" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F289" s="26"/>
-      <c r="G289" s="26"/>
+      <c r="F289" s="23"/>
+      <c r="G289" s="23"/>
     </row>
     <row r="290" spans="2:9">
       <c r="B290" s="2" t="s">
@@ -8238,17 +8270,17 @@
         <v>1</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F291" s="1"/>
       <c r="G291" s="1" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
     </row>
     <row r="292" spans="2:9">
@@ -8256,17 +8288,17 @@
         <v>2</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F292" s="1"/>
       <c r="G292" s="1" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="293" spans="2:9">
@@ -8274,10 +8306,10 @@
         <v>3</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>13</v>
@@ -8290,17 +8322,17 @@
         <v>4</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F294" s="1"/>
       <c r="G294" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="295" spans="2:9">
@@ -8308,17 +8340,17 @@
         <v>5</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F295" s="1"/>
       <c r="G295" s="1" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="296" spans="2:9">
@@ -8326,18 +8358,18 @@
         <v>6</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F296" s="1"/>
       <c r="G296" s="1"/>
       <c r="I296" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="297" spans="2:9">
@@ -8345,18 +8377,18 @@
         <v>7</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F297" s="1"/>
       <c r="G297" s="1"/>
       <c r="I297" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="298" spans="2:9">
@@ -8364,13 +8396,13 @@
         <v>8</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F298" s="1"/>
       <c r="G298" s="1"/>
@@ -8386,7 +8418,7 @@
         <v>29</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F299" s="1"/>
       <c r="G299" s="1"/>
@@ -8398,32 +8430,32 @@
       <c r="B301" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C301" s="27" t="s">
-        <v>596</v>
-      </c>
-      <c r="D301" s="27"/>
+      <c r="C301" s="22" t="s">
+        <v>590</v>
+      </c>
+      <c r="D301" s="22"/>
       <c r="E301" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F301" s="26"/>
-      <c r="G301" s="26"/>
+      <c r="F301" s="23"/>
+      <c r="G301" s="23"/>
     </row>
     <row r="302" spans="2:9">
       <c r="B302" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C302" s="26" t="s">
-        <v>338</v>
-      </c>
-      <c r="D302" s="26"/>
+      <c r="C302" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="D302" s="23"/>
       <c r="E302" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F302" s="26" t="s">
-        <v>339</v>
-      </c>
-      <c r="G302" s="26" t="s">
-        <v>139</v>
+      <c r="F302" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="G302" s="23" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="303" spans="2:9">
@@ -8451,10 +8483,10 @@
         <v>1</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>13</v>
@@ -8479,7 +8511,7 @@
       </c>
       <c r="F305" s="1"/>
       <c r="G305" s="1" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
     </row>
     <row r="306" spans="2:9">
@@ -8497,7 +8529,7 @@
       </c>
       <c r="F306" s="1"/>
       <c r="G306" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="307" spans="2:9">
@@ -8505,13 +8537,13 @@
         <v>4</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F307" s="1"/>
       <c r="G307" s="1"/>
@@ -8521,17 +8553,17 @@
         <v>5</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F308" s="1"/>
       <c r="G308" s="1" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="309" spans="2:9">
@@ -8539,10 +8571,10 @@
         <v>6</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E309" s="1" t="s">
         <v>13</v>
@@ -8555,18 +8587,18 @@
         <v>7</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F310" s="1"/>
       <c r="G310" s="1"/>
       <c r="I310" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
     </row>
     <row r="311" spans="2:9">
@@ -8574,18 +8606,18 @@
         <v>8</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F311" s="1"/>
       <c r="G311" s="1"/>
       <c r="I311" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
     </row>
     <row r="312" spans="2:9">
@@ -8593,13 +8625,13 @@
         <v>9</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D312" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F312" s="1"/>
       <c r="G312" s="1"/>
@@ -8608,31 +8640,31 @@
       <c r="B314" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C314" s="27" t="s">
-        <v>348</v>
-      </c>
-      <c r="D314" s="27"/>
+      <c r="C314" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="D314" s="22"/>
       <c r="E314" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F314" s="26"/>
-      <c r="G314" s="26"/>
+      <c r="F314" s="23"/>
+      <c r="G314" s="23"/>
     </row>
     <row r="315" spans="2:9">
       <c r="B315" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C315" s="26" t="s">
-        <v>349</v>
-      </c>
-      <c r="D315" s="26"/>
+      <c r="C315" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="D315" s="23"/>
       <c r="E315" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F315" s="26" t="s">
-        <v>350</v>
-      </c>
-      <c r="G315" s="26"/>
+      <c r="F315" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="G315" s="23"/>
     </row>
     <row r="316" spans="2:9">
       <c r="B316" s="2" t="s">
@@ -8659,13 +8691,13 @@
         <v>1</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F317" s="1"/>
       <c r="G317" s="1" t="s">
@@ -8677,17 +8709,17 @@
         <v>2</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F318" s="1"/>
       <c r="G318" s="1" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="319" spans="2:9">
@@ -8695,17 +8727,17 @@
         <v>3</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F319" s="1"/>
       <c r="G319" s="1" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="320" spans="2:9">
@@ -8716,10 +8748,10 @@
         <v>72</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F320" s="1"/>
       <c r="G320" s="1"/>
@@ -8729,13 +8761,13 @@
         <v>5</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F321" s="1"/>
       <c r="G321" s="1"/>
@@ -8745,10 +8777,10 @@
         <v>6</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>13</v>
@@ -8761,13 +8793,13 @@
         <v>7</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F323" s="1"/>
       <c r="G323" s="1"/>
@@ -8783,7 +8815,7 @@
         <v>29</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F324" s="1"/>
       <c r="G324" s="1"/>
@@ -8802,7 +8834,7 @@
         <v>33</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F325" s="1"/>
       <c r="G325" s="1"/>
@@ -8814,32 +8846,32 @@
       <c r="B327" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C327" s="27" t="s">
-        <v>597</v>
-      </c>
-      <c r="D327" s="27"/>
+      <c r="C327" s="22" t="s">
+        <v>591</v>
+      </c>
+      <c r="D327" s="22"/>
       <c r="E327" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F327" s="26"/>
-      <c r="G327" s="26"/>
+      <c r="F327" s="23"/>
+      <c r="G327" s="23"/>
     </row>
     <row r="328" spans="2:9">
       <c r="B328" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C328" s="26" t="s">
-        <v>362</v>
-      </c>
-      <c r="D328" s="26"/>
+      <c r="C328" s="23" t="s">
+        <v>356</v>
+      </c>
+      <c r="D328" s="23"/>
       <c r="E328" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F328" s="26" t="s">
-        <v>363</v>
-      </c>
-      <c r="G328" s="26" t="s">
-        <v>364</v>
+      <c r="F328" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="G328" s="23" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="329" spans="2:9">
@@ -8867,13 +8899,13 @@
         <v>1</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F330" s="1"/>
       <c r="G330" s="1" t="s">
@@ -8885,17 +8917,17 @@
         <v>2</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F331" s="1"/>
       <c r="G331" s="1" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="332" spans="2:9">
@@ -8903,17 +8935,17 @@
         <v>3</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F332" s="1"/>
       <c r="G332" s="1" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="333" spans="2:9">
@@ -8921,13 +8953,13 @@
         <v>4</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F333" s="1"/>
       <c r="G333" s="1" t="s">
@@ -8939,13 +8971,13 @@
         <v>5</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F334" s="1"/>
       <c r="G334" s="1"/>
@@ -8955,13 +8987,13 @@
         <v>6</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F335" s="1"/>
       <c r="G335" s="1"/>
@@ -8971,13 +9003,13 @@
         <v>7</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F336" s="1"/>
       <c r="G336" s="1"/>
@@ -8987,13 +9019,13 @@
         <v>8</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F337" s="1"/>
       <c r="G337" s="1"/>
@@ -9003,18 +9035,18 @@
         <v>9</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F338" s="1"/>
       <c r="G338" s="1"/>
       <c r="I338" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
     </row>
     <row r="339" spans="2:9">
@@ -9022,10 +9054,10 @@
         <v>10</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="E339" s="1" t="s">
         <v>13</v>
@@ -9038,10 +9070,10 @@
         <v>11</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="E340" s="1" t="s">
         <v>13</v>
@@ -9054,10 +9086,10 @@
         <v>12</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>13</v>
@@ -9073,14 +9105,14 @@
         <v>64</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F342" s="1"/>
       <c r="G342" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="343" spans="2:9">
@@ -9094,12 +9126,12 @@
         <v>29</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F343" s="1"/>
       <c r="G343" s="1"/>
       <c r="I343" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
     </row>
     <row r="344" spans="2:9">
@@ -9113,43 +9145,43 @@
         <v>33</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F344" s="1"/>
       <c r="G344" s="1"/>
       <c r="I344" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
     </row>
     <row r="346" spans="2:9" ht="16.5" customHeight="1">
       <c r="B346" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C346" s="27" t="s">
-        <v>386</v>
-      </c>
-      <c r="D346" s="27"/>
+      <c r="C346" s="22" t="s">
+        <v>380</v>
+      </c>
+      <c r="D346" s="22"/>
       <c r="E346" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F346" s="26"/>
-      <c r="G346" s="26"/>
+      <c r="F346" s="23"/>
+      <c r="G346" s="23"/>
     </row>
     <row r="347" spans="2:9">
       <c r="B347" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C347" s="26" t="s">
-        <v>616</v>
-      </c>
-      <c r="D347" s="26"/>
+      <c r="C347" s="23" t="s">
+        <v>610</v>
+      </c>
+      <c r="D347" s="23"/>
       <c r="E347" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F347" s="26" t="s">
-        <v>388</v>
-      </c>
-      <c r="G347" s="26"/>
+      <c r="F347" s="23" t="s">
+        <v>382</v>
+      </c>
+      <c r="G347" s="23"/>
     </row>
     <row r="348" spans="2:9">
       <c r="B348" s="2" t="s">
@@ -9176,13 +9208,13 @@
         <v>1</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F349" s="1"/>
       <c r="G349" s="1" t="s">
@@ -9194,17 +9226,17 @@
         <v>2</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F350" s="1"/>
       <c r="G350" s="1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="351" spans="2:9">
@@ -9218,7 +9250,7 @@
         <v>68</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F351" s="1"/>
       <c r="G351" s="1"/>
@@ -9228,17 +9260,17 @@
         <v>4</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F352" s="1"/>
       <c r="G352" s="1" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="353" spans="2:7">
@@ -9246,13 +9278,13 @@
         <v>5</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F353" s="1"/>
       <c r="G353" s="1"/>
@@ -9262,13 +9294,13 @@
         <v>6</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F354" s="1"/>
       <c r="G354" s="1"/>
@@ -9278,13 +9310,13 @@
         <v>7</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F355" s="1"/>
       <c r="G355" s="1"/>
@@ -9300,7 +9332,7 @@
         <v>29</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F356" s="1"/>
       <c r="G356" s="1"/>
@@ -9309,32 +9341,32 @@
       <c r="B358" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C358" s="27" t="s">
-        <v>402</v>
-      </c>
-      <c r="D358" s="27"/>
+      <c r="C358" s="22" t="s">
+        <v>396</v>
+      </c>
+      <c r="D358" s="22"/>
       <c r="E358" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F358" s="26"/>
-      <c r="G358" s="26"/>
+      <c r="F358" s="23"/>
+      <c r="G358" s="23"/>
     </row>
     <row r="359" spans="2:7">
       <c r="B359" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C359" s="26" t="s">
-        <v>403</v>
-      </c>
-      <c r="D359" s="26"/>
+      <c r="C359" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="D359" s="23"/>
       <c r="E359" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F359" s="26" t="s">
-        <v>404</v>
-      </c>
-      <c r="G359" s="26" t="s">
-        <v>405</v>
+      <c r="F359" s="23" t="s">
+        <v>398</v>
+      </c>
+      <c r="G359" s="23" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="360" spans="2:7">
@@ -9362,13 +9394,13 @@
         <v>1</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F361" s="1"/>
       <c r="G361" s="1" t="s">
@@ -9380,17 +9412,17 @@
         <v>2</v>
       </c>
       <c r="C362" s="16" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="D362" s="16" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="E362" s="16" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F362" s="16"/>
       <c r="G362" s="16" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="363" spans="2:7">
@@ -9398,13 +9430,13 @@
         <v>3</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F363" s="1"/>
       <c r="G363" s="1"/>
@@ -9414,13 +9446,13 @@
         <v>4</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F364" s="1"/>
       <c r="G364" s="1" t="s">
@@ -9432,13 +9464,13 @@
         <v>5</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F365" s="1"/>
       <c r="G365" s="1"/>
@@ -9448,13 +9480,13 @@
         <v>6</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F366" s="1"/>
       <c r="G366" s="1"/>
@@ -9464,13 +9496,13 @@
         <v>7</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F367" s="1"/>
       <c r="G367" s="1"/>
@@ -9480,17 +9512,17 @@
         <v>8</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F368" s="1"/>
       <c r="G368" s="1" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="369" spans="2:9">
@@ -9498,17 +9530,17 @@
         <v>9</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F369" s="1"/>
       <c r="G369" s="1" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="370" spans="2:9">
@@ -9519,14 +9551,14 @@
         <v>64</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F370" s="1"/>
       <c r="G370" s="1" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
     </row>
     <row r="371" spans="2:9">
@@ -9540,12 +9572,12 @@
         <v>29</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F371" s="1"/>
       <c r="G371" s="1"/>
       <c r="I371" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
     </row>
     <row r="372" spans="2:9">
@@ -9559,41 +9591,41 @@
         <v>32</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F372" s="1"/>
       <c r="G372" s="1"/>
       <c r="I372" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
     </row>
     <row r="374" spans="2:9" ht="16.5" customHeight="1">
       <c r="B374" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C374" s="27" t="s">
-        <v>419</v>
-      </c>
-      <c r="D374" s="27"/>
+      <c r="C374" s="22" t="s">
+        <v>413</v>
+      </c>
+      <c r="D374" s="22"/>
       <c r="E374" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F374" s="26"/>
-      <c r="G374" s="26"/>
+      <c r="F374" s="23"/>
+      <c r="G374" s="23"/>
     </row>
     <row r="375" spans="2:9">
       <c r="B375" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C375" s="26" t="s">
-        <v>420</v>
-      </c>
-      <c r="D375" s="26"/>
+      <c r="C375" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="D375" s="23"/>
       <c r="E375" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F375" s="26"/>
-      <c r="G375" s="26"/>
+      <c r="F375" s="23"/>
+      <c r="G375" s="23"/>
     </row>
     <row r="376" spans="2:9">
       <c r="B376" s="2" t="s">
@@ -9620,17 +9652,17 @@
         <v>1</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F377" s="1"/>
       <c r="G377" s="1" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
     </row>
     <row r="378" spans="2:9">
@@ -9641,16 +9673,16 @@
         <v>72</v>
       </c>
       <c r="D378" s="1" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F378" s="1">
         <v>50</v>
       </c>
       <c r="G378" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="379" spans="2:9">
@@ -9658,17 +9690,17 @@
         <v>3</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F379" s="1"/>
       <c r="G379" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="380" spans="2:9">
@@ -9676,7 +9708,7 @@
         <v>11</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D380" s="1"/>
       <c r="E380" s="1"/>
@@ -9687,30 +9719,30 @@
       <c r="B382" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C382" s="28" t="s">
-        <v>522</v>
-      </c>
-      <c r="D382" s="28"/>
+      <c r="C382" s="24" t="s">
+        <v>516</v>
+      </c>
+      <c r="D382" s="24"/>
       <c r="E382" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F382" s="29"/>
-      <c r="G382" s="29"/>
+      <c r="F382" s="25"/>
+      <c r="G382" s="25"/>
       <c r="I382"/>
     </row>
     <row r="383" spans="2:9" s="5" customFormat="1">
       <c r="B383" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C383" s="29" t="s">
-        <v>420</v>
-      </c>
-      <c r="D383" s="29"/>
+      <c r="C383" s="25" t="s">
+        <v>414</v>
+      </c>
+      <c r="D383" s="25"/>
       <c r="E383" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F383" s="29"/>
-      <c r="G383" s="29"/>
+      <c r="F383" s="25"/>
+      <c r="G383" s="25"/>
       <c r="I383"/>
     </row>
     <row r="384" spans="2:9" s="5" customFormat="1">
@@ -9739,17 +9771,17 @@
         <v>1</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="E385" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F385" s="4"/>
       <c r="G385" s="4" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="I385"/>
     </row>
@@ -9758,17 +9790,17 @@
         <v>2</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D386" s="4" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="E386" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F386" s="4"/>
       <c r="G386" s="4" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="I386"/>
     </row>
@@ -9777,17 +9809,17 @@
         <v>3</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="E387" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F387" s="4"/>
       <c r="G387" s="4" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="I387"/>
     </row>
@@ -9796,7 +9828,7 @@
         <v>11</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="D388" s="4"/>
       <c r="E388" s="4"/>
@@ -9808,32 +9840,32 @@
       <c r="B390" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C390" s="27" t="s">
-        <v>425</v>
-      </c>
-      <c r="D390" s="27"/>
+      <c r="C390" s="22" t="s">
+        <v>419</v>
+      </c>
+      <c r="D390" s="22"/>
       <c r="E390" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F390" s="26"/>
-      <c r="G390" s="26"/>
+      <c r="F390" s="23"/>
+      <c r="G390" s="23"/>
     </row>
     <row r="391" spans="2:9">
       <c r="B391" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C391" s="26" t="s">
-        <v>426</v>
-      </c>
-      <c r="D391" s="26"/>
+      <c r="C391" s="23" t="s">
+        <v>420</v>
+      </c>
+      <c r="D391" s="23"/>
       <c r="E391" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F391" s="27" t="s">
-        <v>561</v>
-      </c>
-      <c r="G391" s="26" t="s">
-        <v>427</v>
+      <c r="F391" s="22" t="s">
+        <v>555</v>
+      </c>
+      <c r="G391" s="23" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="392" spans="2:9">
@@ -9861,17 +9893,17 @@
         <v>1</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="F393" s="1"/>
       <c r="G393" s="1" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="394" spans="2:9">
@@ -9885,7 +9917,7 @@
         <v>68</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F394" s="1"/>
       <c r="G394" s="1" t="s">
@@ -9897,7 +9929,7 @@
         <v>3</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D395" s="1" t="s">
         <v>16</v>
@@ -9915,19 +9947,19 @@
         <v>4</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F396" s="1">
         <v>120</v>
       </c>
       <c r="G396" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="397" spans="2:9">
@@ -9935,19 +9967,19 @@
         <v>5</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F397" s="1">
         <v>100</v>
       </c>
       <c r="G397" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="398" spans="2:9">
@@ -9955,17 +9987,17 @@
         <v>6</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F398" s="1"/>
       <c r="G398" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="399" spans="2:9">
@@ -9973,19 +10005,19 @@
         <v>7</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F399" s="1">
         <v>255</v>
       </c>
       <c r="G399" s="1" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="400" spans="2:9">
@@ -9993,13 +10025,13 @@
         <v>8</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="D400" s="1" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F400" s="1">
         <v>30</v>
@@ -10011,13 +10043,13 @@
         <v>9</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D401" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F401" s="1">
         <v>255</v>
@@ -10029,13 +10061,13 @@
         <v>10</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F402" s="1">
         <v>255</v>
@@ -10047,18 +10079,18 @@
         <v>11</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F403" s="1"/>
       <c r="G403" s="1"/>
       <c r="I403" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
     </row>
     <row r="404" spans="2:9">
@@ -10066,18 +10098,18 @@
         <v>12</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F404" s="1"/>
       <c r="G404" s="1"/>
       <c r="I404" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
     </row>
     <row r="405" spans="2:9">
@@ -10085,17 +10117,17 @@
         <v>13</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F405" s="1"/>
       <c r="G405" s="1" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="406" spans="2:9">
@@ -10106,14 +10138,14 @@
         <v>64</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F406" s="1"/>
       <c r="G406" s="1" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="407" spans="2:9">
@@ -10127,14 +10159,14 @@
         <v>29</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F407" s="1"/>
       <c r="G407" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I407" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
     </row>
     <row r="408" spans="2:9">
@@ -10148,14 +10180,14 @@
         <v>32</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F408" s="1"/>
       <c r="G408" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I408" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
     </row>
     <row r="409" spans="2:9">
@@ -10163,18 +10195,18 @@
         <v>17</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D409" s="1" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F409" s="1"/>
       <c r="G409" s="1"/>
       <c r="I409" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
     </row>
     <row r="410" spans="2:9">
@@ -10182,13 +10214,13 @@
         <v>18</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="E410" s="1" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="F410" s="1"/>
       <c r="G410" s="1"/>
@@ -10198,7 +10230,7 @@
         <v>11</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="D411" s="1"/>
       <c r="E411" s="1"/>
@@ -10209,31 +10241,31 @@
       <c r="B413" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C413" s="27" t="s">
-        <v>448</v>
-      </c>
-      <c r="D413" s="27"/>
+      <c r="C413" s="22" t="s">
+        <v>442</v>
+      </c>
+      <c r="D413" s="22"/>
       <c r="E413" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F413" s="26"/>
-      <c r="G413" s="26"/>
+      <c r="F413" s="23"/>
+      <c r="G413" s="23"/>
     </row>
     <row r="414" spans="2:9">
       <c r="B414" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C414" s="26" t="s">
-        <v>449</v>
-      </c>
-      <c r="D414" s="26"/>
+      <c r="C414" s="23" t="s">
+        <v>443</v>
+      </c>
+      <c r="D414" s="23"/>
       <c r="E414" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F414" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="G414" s="26"/>
+      <c r="F414" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="G414" s="23"/>
     </row>
     <row r="415" spans="2:9">
       <c r="B415" s="2" t="s">
@@ -10260,17 +10292,17 @@
         <v>1</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F416" s="1"/>
       <c r="G416" s="1" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
     </row>
     <row r="417" spans="2:9">
@@ -10296,19 +10328,19 @@
         <v>3</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="F418" s="1">
         <v>50</v>
       </c>
       <c r="G418" s="1" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
     </row>
     <row r="419" spans="2:9">
@@ -10316,17 +10348,17 @@
         <v>4</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F419" s="1"/>
       <c r="G419" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
     </row>
     <row r="420" spans="2:9">
@@ -10340,43 +10372,43 @@
         <v>29</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F420" s="1"/>
       <c r="G420" s="1" t="s">
         <v>30</v>
       </c>
       <c r="I420" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
     </row>
     <row r="422" spans="2:9" ht="16.5" customHeight="1">
       <c r="B422" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C422" s="27" t="s">
-        <v>456</v>
-      </c>
-      <c r="D422" s="27"/>
+      <c r="C422" s="22" t="s">
+        <v>450</v>
+      </c>
+      <c r="D422" s="22"/>
       <c r="E422" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F422" s="26"/>
-      <c r="G422" s="26"/>
+      <c r="F422" s="23"/>
+      <c r="G422" s="23"/>
     </row>
     <row r="423" spans="2:9">
       <c r="B423" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C423" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="D423" s="26"/>
+      <c r="C423" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="D423" s="23"/>
       <c r="E423" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F423" s="26"/>
-      <c r="G423" s="26"/>
+      <c r="F423" s="23"/>
+      <c r="G423" s="23"/>
     </row>
     <row r="424" spans="2:9">
       <c r="B424" s="2" t="s">
@@ -10403,10 +10435,10 @@
         <v>1</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>13</v>
@@ -10421,19 +10453,19 @@
         <v>2</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="E426" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F426" s="1">
         <v>100</v>
       </c>
       <c r="G426" s="1" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
     </row>
     <row r="427" spans="2:9">
@@ -10441,19 +10473,19 @@
         <v>3</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F427" s="1">
         <v>50</v>
       </c>
       <c r="G427" s="1" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="428" spans="2:9">
@@ -10461,17 +10493,17 @@
         <v>4</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F428" s="1"/>
       <c r="G428" s="1" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="429" spans="2:9">
@@ -10479,19 +10511,19 @@
         <v>5</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
     </row>
     <row r="430" spans="2:9">
@@ -10499,17 +10531,17 @@
         <v>6</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F430" s="1"/>
       <c r="G430" s="1" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
     </row>
     <row r="431" spans="2:9">
@@ -10523,43 +10555,43 @@
         <v>29</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F431" s="1"/>
       <c r="G431" s="1"/>
       <c r="I431" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
     </row>
     <row r="433" spans="2:9" ht="16.5" customHeight="1">
       <c r="B433" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C433" s="27" t="s">
-        <v>468</v>
-      </c>
-      <c r="D433" s="27"/>
+      <c r="C433" s="22" t="s">
+        <v>462</v>
+      </c>
+      <c r="D433" s="22"/>
       <c r="E433" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F433" s="26"/>
-      <c r="G433" s="26"/>
+      <c r="F433" s="23"/>
+      <c r="G433" s="23"/>
     </row>
     <row r="434" spans="2:9">
       <c r="B434" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C434" s="26" t="s">
-        <v>469</v>
-      </c>
-      <c r="D434" s="26"/>
+      <c r="C434" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="D434" s="23"/>
       <c r="E434" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F434" s="26" t="s">
-        <v>470</v>
-      </c>
-      <c r="G434" s="26"/>
+      <c r="F434" s="23" t="s">
+        <v>464</v>
+      </c>
+      <c r="G434" s="23"/>
     </row>
     <row r="435" spans="2:9">
       <c r="B435" s="2" t="s">
@@ -10586,10 +10618,10 @@
         <v>1</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>13</v>
@@ -10604,17 +10636,17 @@
         <v>2</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F437" s="1"/>
       <c r="G437" s="1" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
     <row r="438" spans="2:9">
@@ -10622,17 +10654,17 @@
         <v>3</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F438" s="1"/>
       <c r="G438" s="1" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
     </row>
     <row r="439" spans="2:9">
@@ -10640,19 +10672,19 @@
         <v>4</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="G439" s="1" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="440" spans="2:9">
@@ -10660,19 +10692,19 @@
         <v>5</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="G440" s="1" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
     </row>
     <row r="441" spans="2:9">
@@ -10683,46 +10715,46 @@
         <v>28</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F441" s="1"/>
       <c r="G441" s="1"/>
       <c r="I441" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
     </row>
     <row r="443" spans="2:9" ht="16.5" customHeight="1">
       <c r="B443" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C443" s="27" t="s">
-        <v>484</v>
-      </c>
-      <c r="D443" s="27"/>
+      <c r="C443" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="D443" s="22"/>
       <c r="E443" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F443" s="26"/>
-      <c r="G443" s="26"/>
+      <c r="F443" s="23"/>
+      <c r="G443" s="23"/>
     </row>
     <row r="444" spans="2:9">
       <c r="B444" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C444" s="26" t="s">
-        <v>485</v>
-      </c>
-      <c r="D444" s="26"/>
+      <c r="C444" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="D444" s="23"/>
       <c r="E444" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F444" s="26" t="s">
-        <v>486</v>
-      </c>
-      <c r="G444" s="26"/>
+      <c r="F444" s="23" t="s">
+        <v>480</v>
+      </c>
+      <c r="G444" s="23"/>
     </row>
     <row r="445" spans="2:9">
       <c r="B445" s="2" t="s">
@@ -10749,19 +10781,19 @@
         <v>1</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F446" s="1">
         <v>24</v>
       </c>
       <c r="G446" s="1" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
     </row>
     <row r="447" spans="2:9">
@@ -10769,10 +10801,10 @@
         <v>2</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>13</v>
@@ -10787,16 +10819,16 @@
         <v>3</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="G448" s="1"/>
     </row>
@@ -10805,13 +10837,13 @@
         <v>4</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F449" s="1">
         <v>500</v>
@@ -10820,140 +10852,6 @@
     </row>
   </sheetData>
   <mergeCells count="152">
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="F114:G114"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="F115:G115"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="F127:G127"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="F99:G99"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="F107:G107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="F108:G108"/>
-    <mergeCell ref="C152:D152"/>
-    <mergeCell ref="F152:G152"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="F128:G128"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="F140:G140"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="F141:G141"/>
-    <mergeCell ref="C178:D178"/>
-    <mergeCell ref="F178:G178"/>
-    <mergeCell ref="C179:D179"/>
-    <mergeCell ref="F179:G179"/>
-    <mergeCell ref="C186:D186"/>
-    <mergeCell ref="F186:G186"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="F153:G153"/>
-    <mergeCell ref="C164:D164"/>
-    <mergeCell ref="F164:G164"/>
-    <mergeCell ref="C165:D165"/>
-    <mergeCell ref="F165:G165"/>
-    <mergeCell ref="C208:D208"/>
-    <mergeCell ref="F208:G208"/>
-    <mergeCell ref="C209:D209"/>
-    <mergeCell ref="F209:G209"/>
-    <mergeCell ref="C217:D217"/>
-    <mergeCell ref="F217:G217"/>
-    <mergeCell ref="C187:D187"/>
-    <mergeCell ref="F187:G187"/>
-    <mergeCell ref="C196:D196"/>
-    <mergeCell ref="F196:G196"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="F197:G197"/>
-    <mergeCell ref="C239:D239"/>
-    <mergeCell ref="F239:G239"/>
-    <mergeCell ref="C240:D240"/>
-    <mergeCell ref="F240:G240"/>
-    <mergeCell ref="C251:D251"/>
-    <mergeCell ref="F251:G251"/>
-    <mergeCell ref="C218:D218"/>
-    <mergeCell ref="F218:G218"/>
-    <mergeCell ref="C225:D225"/>
-    <mergeCell ref="F225:G225"/>
-    <mergeCell ref="C226:D226"/>
-    <mergeCell ref="F226:G226"/>
-    <mergeCell ref="C275:D275"/>
-    <mergeCell ref="F275:G275"/>
-    <mergeCell ref="C276:D276"/>
-    <mergeCell ref="F276:G276"/>
-    <mergeCell ref="C288:D288"/>
-    <mergeCell ref="F288:G288"/>
-    <mergeCell ref="C252:D252"/>
-    <mergeCell ref="F252:G252"/>
-    <mergeCell ref="C263:D263"/>
-    <mergeCell ref="F263:G263"/>
-    <mergeCell ref="C264:D264"/>
-    <mergeCell ref="F264:G264"/>
-    <mergeCell ref="C314:D314"/>
-    <mergeCell ref="F314:G314"/>
-    <mergeCell ref="C315:D315"/>
-    <mergeCell ref="F315:G315"/>
-    <mergeCell ref="C327:D327"/>
-    <mergeCell ref="F327:G327"/>
-    <mergeCell ref="C289:D289"/>
-    <mergeCell ref="F289:G289"/>
-    <mergeCell ref="C301:D301"/>
-    <mergeCell ref="F301:G301"/>
-    <mergeCell ref="C302:D302"/>
-    <mergeCell ref="F302:G302"/>
-    <mergeCell ref="C358:D358"/>
-    <mergeCell ref="F358:G358"/>
-    <mergeCell ref="C328:D328"/>
-    <mergeCell ref="F328:G328"/>
-    <mergeCell ref="C346:D346"/>
-    <mergeCell ref="F346:G346"/>
-    <mergeCell ref="C347:D347"/>
-    <mergeCell ref="F347:G347"/>
-    <mergeCell ref="C374:D374"/>
-    <mergeCell ref="F374:G374"/>
-    <mergeCell ref="C375:D375"/>
-    <mergeCell ref="F375:G375"/>
-    <mergeCell ref="C390:D390"/>
-    <mergeCell ref="F390:G390"/>
-    <mergeCell ref="C359:D359"/>
-    <mergeCell ref="F359:G359"/>
-    <mergeCell ref="C382:D382"/>
-    <mergeCell ref="F382:G382"/>
-    <mergeCell ref="C383:D383"/>
-    <mergeCell ref="F383:G383"/>
     <mergeCell ref="C391:D391"/>
     <mergeCell ref="F391:G391"/>
     <mergeCell ref="C413:D413"/>
@@ -10972,61 +10870,215 @@
     <mergeCell ref="F433:G433"/>
     <mergeCell ref="C434:D434"/>
     <mergeCell ref="F434:G434"/>
+    <mergeCell ref="C375:D375"/>
+    <mergeCell ref="F375:G375"/>
+    <mergeCell ref="C390:D390"/>
+    <mergeCell ref="F390:G390"/>
+    <mergeCell ref="C359:D359"/>
+    <mergeCell ref="F359:G359"/>
+    <mergeCell ref="C382:D382"/>
+    <mergeCell ref="F382:G382"/>
+    <mergeCell ref="C383:D383"/>
+    <mergeCell ref="F383:G383"/>
+    <mergeCell ref="C358:D358"/>
+    <mergeCell ref="F358:G358"/>
+    <mergeCell ref="C328:D328"/>
+    <mergeCell ref="F328:G328"/>
+    <mergeCell ref="C346:D346"/>
+    <mergeCell ref="F346:G346"/>
+    <mergeCell ref="C347:D347"/>
+    <mergeCell ref="F347:G347"/>
+    <mergeCell ref="C374:D374"/>
+    <mergeCell ref="F374:G374"/>
+    <mergeCell ref="C314:D314"/>
+    <mergeCell ref="F314:G314"/>
+    <mergeCell ref="C315:D315"/>
+    <mergeCell ref="F315:G315"/>
+    <mergeCell ref="C327:D327"/>
+    <mergeCell ref="F327:G327"/>
+    <mergeCell ref="C289:D289"/>
+    <mergeCell ref="F289:G289"/>
+    <mergeCell ref="C301:D301"/>
+    <mergeCell ref="F301:G301"/>
+    <mergeCell ref="C302:D302"/>
+    <mergeCell ref="F302:G302"/>
+    <mergeCell ref="C275:D275"/>
+    <mergeCell ref="F275:G275"/>
+    <mergeCell ref="C276:D276"/>
+    <mergeCell ref="F276:G276"/>
+    <mergeCell ref="C288:D288"/>
+    <mergeCell ref="F288:G288"/>
+    <mergeCell ref="C252:D252"/>
+    <mergeCell ref="F252:G252"/>
+    <mergeCell ref="C263:D263"/>
+    <mergeCell ref="F263:G263"/>
+    <mergeCell ref="C264:D264"/>
+    <mergeCell ref="F264:G264"/>
+    <mergeCell ref="C239:D239"/>
+    <mergeCell ref="F239:G239"/>
+    <mergeCell ref="C240:D240"/>
+    <mergeCell ref="F240:G240"/>
+    <mergeCell ref="C251:D251"/>
+    <mergeCell ref="F251:G251"/>
+    <mergeCell ref="C218:D218"/>
+    <mergeCell ref="F218:G218"/>
+    <mergeCell ref="C225:D225"/>
+    <mergeCell ref="F225:G225"/>
+    <mergeCell ref="C226:D226"/>
+    <mergeCell ref="F226:G226"/>
+    <mergeCell ref="C208:D208"/>
+    <mergeCell ref="F208:G208"/>
+    <mergeCell ref="C209:D209"/>
+    <mergeCell ref="F209:G209"/>
+    <mergeCell ref="C217:D217"/>
+    <mergeCell ref="F217:G217"/>
+    <mergeCell ref="C187:D187"/>
+    <mergeCell ref="F187:G187"/>
+    <mergeCell ref="C196:D196"/>
+    <mergeCell ref="F196:G196"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="F197:G197"/>
+    <mergeCell ref="C178:D178"/>
+    <mergeCell ref="F178:G178"/>
+    <mergeCell ref="C186:D186"/>
+    <mergeCell ref="F186:G186"/>
+    <mergeCell ref="C151:D151"/>
+    <mergeCell ref="F151:G151"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="F162:G162"/>
+    <mergeCell ref="C163:D163"/>
+    <mergeCell ref="F163:G163"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="F150:G150"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="F126:G126"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="F138:G138"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="F139:G139"/>
+    <mergeCell ref="C177:D177"/>
+    <mergeCell ref="F177:G177"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="F112:G112"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="F113:G113"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="F125:G125"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="F49:G49"/>
   </mergeCells>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="E1:E47 E58:E1048576">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+  <conditionalFormatting sqref="E1:E46 E57:E173 E175:E182 E184:E1048576">
+    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
       <formula>"DATETIME2"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I40 I10:I11 B1:G47 B58:G1010">
-    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="USER.user_id">
+  <conditionalFormatting sqref="I39 I10:I11 B1:G46 B57:G173 B175:G182 B184:G1010">
+    <cfRule type="containsText" dxfId="13" priority="15" operator="containsText" text="USER.user_id">
       <formula>NOT(ISERROR(SEARCH("USER.user_id",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I82:I83">
-    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="USER.user_id">
-      <formula>NOT(ISERROR(SEARCH("USER.user_id",I82)))</formula>
+  <conditionalFormatting sqref="I81:I82">
+    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="USER.user_id">
+      <formula>NOT(ISERROR(SEARCH("USER.user_id",I81)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E48:E54">
+  <conditionalFormatting sqref="E47:E53">
+    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
+      <formula>"DATETIME2"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B47:G50 C53:G53 B53:B56 B51:F51 B52:G52">
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="USER.user_id">
+      <formula>NOT(ISERROR(SEARCH("USER.user_id",B47)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C54:D56 F54:G56">
+    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="USER.user_id">
+      <formula>NOT(ISERROR(SEARCH("USER.user_id",C54)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E56">
     <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>"DATETIME2"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48:G51 C54:G54 B54:B57 B52:F52 B53:G53">
+  <conditionalFormatting sqref="E56">
     <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="USER.user_id">
-      <formula>NOT(ISERROR(SEARCH("USER.user_id",B48)))</formula>
+      <formula>NOT(ISERROR(SEARCH("USER.user_id",E56)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C55:D57 F55:G57">
-    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="USER.user_id">
-      <formula>NOT(ISERROR(SEARCH("USER.user_id",C55)))</formula>
+  <conditionalFormatting sqref="G51">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="USER.user_id">
+      <formula>NOT(ISERROR(SEARCH("USER.user_id",G51)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E57">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+  <conditionalFormatting sqref="E54:E55">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"DATETIME2"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E57">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="USER.user_id">
-      <formula>NOT(ISERROR(SEARCH("USER.user_id",E57)))</formula>
+  <conditionalFormatting sqref="E54:E55">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="USER.user_id">
+      <formula>NOT(ISERROR(SEARCH("USER.user_id",E54)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G52">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="USER.user_id">
-      <formula>NOT(ISERROR(SEARCH("USER.user_id",G52)))</formula>
+  <conditionalFormatting sqref="E174">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"DATETIME2"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E55:E56">
+  <conditionalFormatting sqref="B174:G174">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="USER.user_id">
+      <formula>NOT(ISERROR(SEARCH("USER.user_id",B174)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E183">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"DATETIME2"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E55:E56">
+  <conditionalFormatting sqref="B183:G183">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="USER.user_id">
-      <formula>NOT(ISERROR(SEARCH("USER.user_id",E55)))</formula>
+      <formula>NOT(ISERROR(SEARCH("USER.user_id",B183)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
